--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="1" r:id="Rab364f4f1a804830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" r:id="R5a9757e97e7a4d82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="3" r:id="R47e1afee12a44f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="1" r:id="R7d12193cfa934755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="2" r:id="Re655cfdc693741a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" r:id="Ra7c4c30a87544473"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="4" r:id="R73e53caaedc84b00"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +22,7 @@
     <x:numFmt numFmtId="202" formatCode="0.00&quot;x&quot;"/>
     <x:numFmt numFmtId="203" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="17">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -103,6 +104,10 @@
     </x:font>
     <x:font>
       <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="14"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -287,7 +292,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="94">
+  <x:cellXfs count="123">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -354,6 +359,14 @@
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -516,6 +529,81 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -523,6 +611,205 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>What added to or used cash? January–June 2026</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>USD millions</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="737985"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Repayment review'!$F$28:$F$33</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Repayment review'!$G$28:$G$33</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="750">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:r>
+                  <a:t>USD millions (negative = cash used)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0,," sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="750">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R81c17877e17e4414"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -727,7 +1014,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="43" t="str">
+      <x:c r="A2" s="47" t="str">
         <x:v>Eli Lilly and Company</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
@@ -735,7 +1022,7 @@
       <x:c r="D2" s="31"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="44" t="str">
+      <x:c r="A3" s="48" t="str">
         <x:v>Balance sheet June 30, 2026. TTM July 2025–June 2026. USD millions unless ratio or %.</x:v>
       </x:c>
       <x:c r="B3" s="31"/>
@@ -749,141 +1036,141 @@
       <x:c r="D4" s="31"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="74" t="str">
+      <x:c r="A5" s="78" t="str">
         <x:v>Measure</x:v>
       </x:c>
-      <x:c r="B5" s="75" t="str">
+      <x:c r="B5" s="79" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C5" s="75" t="str">
+      <x:c r="C5" s="79" t="str">
         <x:v>Period end</x:v>
       </x:c>
-      <x:c r="D5" s="76" t="str">
+      <x:c r="D5" s="80" t="str">
         <x:v>Basis / limitation</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="46" customHeight="1">
-      <x:c r="A6" s="48" t="str">
+      <x:c r="A6" s="52" t="str">
         <x:v>Cash and cash equivalents</x:v>
       </x:c>
-      <x:c r="B6" s="49" t="n">
+      <x:c r="B6" s="53" t="n">
         <x:f>IF(ISNUMBER('Data'!B2),'Data'!B2,NA())</x:f>
         <x:v>8950000000</x:v>
       </x:c>
-      <x:c r="C6" s="50" t="d">
+      <x:c r="C6" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D6" s="87" t="str"/>
+      <x:c r="D6" s="91" t="str"/>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
-      <x:c r="A7" s="81" t="str">
+      <x:c r="A7" s="85" t="str">
         <x:v>Baseline gross debt</x:v>
       </x:c>
-      <x:c r="B7" s="82" t="n">
+      <x:c r="B7" s="86" t="n">
         <x:f>IF(ISNUMBER('Data'!B3),'Data'!B3,NA())+IF(ISNUMBER('Data'!B4),'Data'!B4,NA())</x:f>
         <x:v>54908000000</x:v>
       </x:c>
-      <x:c r="C7" s="83" t="d">
+      <x:c r="C7" s="87" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D7" s="88" t="str">
+      <x:c r="D7" s="92" t="str">
         <x:v>In this 10-Q, the Note 8 fair-value table's carrying amounts (commercial paper 5,284M plus long-term debt including current portion 49,624M) present the same 54,908M; they are not added. Excluded: fair-value-table carrying amounts of the same borrowings (commercial paper, long-term debt)</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
-      <x:c r="A8" s="81" t="str">
+      <x:c r="A8" s="85" t="str">
         <x:v>Net debt</x:v>
       </x:c>
-      <x:c r="B8" s="86" t="n">
+      <x:c r="B8" s="90" t="n">
         <x:f>B7-B6</x:f>
         <x:v>45958000000</x:v>
       </x:c>
-      <x:c r="C8" s="83" t="d">
+      <x:c r="C8" s="87" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D8" s="88" t="str"/>
+      <x:c r="D8" s="92" t="str"/>
     </x:row>
     <x:row r="9" ht="46" customHeight="1">
-      <x:c r="A9" s="48" t="str">
+      <x:c r="A9" s="52" t="str">
         <x:v>Current ratio</x:v>
       </x:c>
-      <x:c r="B9" s="53" t="n">
+      <x:c r="B9" s="57" t="n">
         <x:f>IF(IF(ISNUMBER('Data'!B5),'Data'!B5,NA())&gt;0,IF(ISNUMBER('Data'!B6),'Data'!B6,NA())/IF(ISNUMBER('Data'!B5),'Data'!B5,NA()),NA())</x:f>
         <x:v>1.3546427598919168</x:v>
       </x:c>
-      <x:c r="C9" s="50" t="d">
+      <x:c r="C9" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D9" s="87" t="str"/>
+      <x:c r="D9" s="91" t="str"/>
     </x:row>
     <x:row r="10" ht="46" customHeight="1">
-      <x:c r="A10" s="48" t="str">
+      <x:c r="A10" s="52" t="str">
         <x:v>Operating cash flow</x:v>
       </x:c>
-      <x:c r="B10" s="49" t="n">
+      <x:c r="B10" s="53" t="n">
         <x:f>(1*IF(ISNUMBER('Data'!B7),'Data'!B7,NA())) + (1*IF(ISNUMBER('Data'!B8),'Data'!B8,NA())) + (-1*IF(ISNUMBER('Data'!B9),'Data'!B9,NA()))</x:f>
         <x:v>28083000000</x:v>
       </x:c>
-      <x:c r="C10" s="50" t="d">
+      <x:c r="C10" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D10" s="87" t="str"/>
+      <x:c r="D10" s="91" t="str"/>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
-      <x:c r="A11" s="48" t="str">
+      <x:c r="A11" s="52" t="str">
         <x:v>Purchases of property and equipment</x:v>
       </x:c>
-      <x:c r="B11" s="49" t="n">
+      <x:c r="B11" s="53" t="n">
         <x:f>(1*IF(ISNUMBER('Data'!B10),'Data'!B10,NA())) + (1*IF(ISNUMBER('Data'!B11),'Data'!B11,NA())) + (-1*IF(ISNUMBER('Data'!B12),'Data'!B12,NA()))</x:f>
         <x:v>9893000000</x:v>
       </x:c>
-      <x:c r="C11" s="50" t="d">
+      <x:c r="C11" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D11" s="87" t="str"/>
+      <x:c r="D11" s="91" t="str"/>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
-      <x:c r="A12" s="81" t="str">
+      <x:c r="A12" s="85" t="str">
         <x:v>Free cash flow</x:v>
       </x:c>
-      <x:c r="B12" s="86" t="n">
+      <x:c r="B12" s="90" t="n">
         <x:f>B10-B11</x:f>
         <x:v>18190000000</x:v>
       </x:c>
-      <x:c r="C12" s="83" t="d">
+      <x:c r="C12" s="87" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D12" s="88" t="str">
+      <x:c r="D12" s="92" t="str">
         <x:v>Reported purchases of property and equipment; excludes acquisitions and other investing cash flows.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
-      <x:c r="A13" s="48" t="str">
+      <x:c r="A13" s="52" t="str">
         <x:v>Operating cash flow / debt</x:v>
       </x:c>
-      <x:c r="B13" s="54" t="n">
+      <x:c r="B13" s="58" t="n">
         <x:f>IF(B7&gt;0,B10/B7,NA())</x:f>
         <x:v>0.511455525606469</x:v>
       </x:c>
-      <x:c r="C13" s="50" t="d">
+      <x:c r="C13" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D13" s="87" t="str">
+      <x:c r="D13" s="91" t="str">
         <x:v>Historical TTM flow / period-end debt. Not repayment coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
-      <x:c r="A14" s="55" t="str">
+      <x:c r="A14" s="59" t="str">
         <x:v>Free cash flow / debt</x:v>
       </x:c>
-      <x:c r="B14" s="56" t="n">
+      <x:c r="B14" s="60" t="n">
         <x:f>IF(B7&gt;0,B12/B7,NA())</x:f>
         <x:v>0.33128141618707657</x:v>
       </x:c>
-      <x:c r="C14" s="57" t="d">
+      <x:c r="C14" s="61" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D14" s="89" t="str">
+      <x:c r="D14" s="93" t="str">
         <x:v>Historical TTM flow / period-end debt. Not repayment coverage.</x:v>
       </x:c>
     </x:row>
@@ -908,42 +1195,42 @@
       <x:c r="D17" s="31"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="74" t="str">
+      <x:c r="A18" s="78" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B18" s="75" t="str">
+      <x:c r="B18" s="79" t="str">
         <x:v>Disclosed amount / timing</x:v>
       </x:c>
-      <x:c r="C18" s="76" t="str">
+      <x:c r="C18" s="80" t="str">
         <x:v>Basis</x:v>
       </x:c>
       <x:c r="D18" s="31"/>
     </x:row>
     <x:row r="19" ht="62" customHeight="1">
-      <x:c r="A19" s="59" t="str">
+      <x:c r="A19" s="63" t="str">
         <x:f>'Data'!A16</x:f>
         <x:v>Pending AtaiBeckley acquisition</x:v>
       </x:c>
-      <x:c r="B19" s="60" t="str">
+      <x:c r="B19" s="64" t="str">
         <x:f>'Data'!B16</x:f>
         <x:v>Approximately $2.8B</x:v>
       </x:c>
-      <x:c r="C19" s="61" t="str">
+      <x:c r="C19" s="65" t="str">
         <x:f>'Data'!I16</x:f>
         <x:v>Potential payment at closing, subject to closing conditions. Not recognized as borrowing.</x:v>
       </x:c>
       <x:c r="D19" s="31"/>
     </x:row>
     <x:row r="20" ht="62" customHeight="1">
-      <x:c r="A20" s="62" t="str">
+      <x:c r="A20" s="66" t="str">
         <x:f>'Data'!A17</x:f>
         <x:v>Venture fund commitments</x:v>
       </x:c>
-      <x:c r="B20" s="63" t="str">
+      <x:c r="B20" s="67" t="str">
         <x:f>'Data'!B17</x:f>
         <x:v>Approximately $806M</x:v>
       </x:c>
-      <x:c r="C20" s="64" t="str">
+      <x:c r="C20" s="68" t="str">
         <x:f>'Data'!I17</x:f>
         <x:v>Expected to be paid over up to ten years. Not recognized as borrowing.</x:v>
       </x:c>
@@ -970,24 +1257,24 @@
       <x:c r="D23" s="31"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="44" t="str">
-        <x:v>June lease liabilities, full maturity review and interest coverage are Unavailable.</x:v>
+      <x:c r="A24" s="48" t="str">
+        <x:v>June lease liabilities, updated principal maturities and interest coverage are Unavailable.</x:v>
       </x:c>
       <x:c r="B24" s="31"/>
       <x:c r="C24" s="31"/>
       <x:c r="D24" s="31"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="44" t="str">
-        <x:v>Contingencies, tax, collaboration and investment notes require further review.</x:v>
+      <x:c r="A25" s="48" t="str">
+        <x:v>See Repayment review for dated cash flows, facilities, acquisitions and manufacturing commitments.</x:v>
       </x:c>
       <x:c r="B25" s="31"/>
       <x:c r="C25" s="31"/>
       <x:c r="D25" s="31"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="44" t="str">
-        <x:v>Sources and selection rules are in Data. No later financing findings are loaded in this review.</x:v>
+      <x:c r="A26" s="48" t="str">
+        <x:v>Sources and selection rules are in Data. Saved August 5 earnings exhibit reviewed; no complete filing inventory claimed.</x:v>
       </x:c>
       <x:c r="B26" s="31"/>
       <x:c r="C26" s="31"/>
@@ -999,6 +1286,1209 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="99" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="3" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="11" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="11" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="11" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="47" t="str">
+        <x:v>Lilly — dated liquidity and repayment review</x:v>
+      </x:c>
+      <x:c r="B2" s="31"/>
+      <x:c r="C2" s="31"/>
+      <x:c r="D2" s="31"/>
+      <x:c r="E2" s="31"/>
+      <x:c r="F2" s="31"/>
+      <x:c r="G2" s="31"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="48" t="str">
+        <x:v>Saved filings reviewed October 15, 2026. Cash flows: January–June 2026. USD millions.</x:v>
+      </x:c>
+      <x:c r="B3" s="31"/>
+      <x:c r="C3" s="31"/>
+      <x:c r="D3" s="31"/>
+      <x:c r="E3" s="31"/>
+      <x:c r="F3" s="31"/>
+      <x:c r="G3" s="31"/>
+    </x:row>
+    <x:row r="4" ht="43" customHeight="1">
+      <x:c r="A4" s="31" t="str">
+        <x:v>H1 cash generation after PP&amp;E was positive; acquisitions and payouts competed for it. Net borrowing contributed to cash growth. Future funding coverage: Unavailable.</x:v>
+      </x:c>
+      <x:c r="B4" s="31"/>
+      <x:c r="C4" s="31"/>
+      <x:c r="D4" s="31"/>
+      <x:c r="E4" s="31"/>
+      <x:c r="F4" s="31"/>
+      <x:c r="G4" s="31"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="31"/>
+      <x:c r="B5" s="31"/>
+      <x:c r="C5" s="31"/>
+      <x:c r="D5" s="31"/>
+      <x:c r="E5" s="31"/>
+      <x:c r="F5" s="31"/>
+      <x:c r="G5" s="31"/>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="78" t="str">
+        <x:v>Half-year cash build</x:v>
+      </x:c>
+      <x:c r="B6" s="79" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C6" s="79" t="str">
+        <x:v>Period / basis</x:v>
+      </x:c>
+      <x:c r="D6" s="80" t="str">
+        <x:v>Interpretation</x:v>
+      </x:c>
+      <x:c r="E6" s="31"/>
+      <x:c r="F6" s="31"/>
+      <x:c r="G6" s="31"/>
+    </x:row>
+    <x:row r="7" ht="43" customHeight="1">
+      <x:c r="A7" s="52" t="str">
+        <x:v>Opening cash</x:v>
+      </x:c>
+      <x:c r="B7" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B37),'Data'!B37,NA())</x:f>
+        <x:v>7268000000</x:v>
+      </x:c>
+      <x:c r="C7" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D7" s="55" t="str">
+        <x:v>Excludes restricted cash. Not an additional half-year flow.</x:v>
+      </x:c>
+      <x:c r="E7" s="31"/>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="31"/>
+    </x:row>
+    <x:row r="8" ht="43" customHeight="1">
+      <x:c r="A8" s="52" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="B8" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B21),'Data'!B21,NA())</x:f>
+        <x:v>16023000000</x:v>
+      </x:c>
+      <x:c r="C8" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D8" s="55" t="str">
+        <x:v>Historical; includes working capital. Future recurrence not established.</x:v>
+      </x:c>
+      <x:c r="E8" s="31"/>
+      <x:c r="F8" s="31"/>
+      <x:c r="G8" s="31"/>
+    </x:row>
+    <x:row r="9" ht="43" customHeight="1">
+      <x:c r="A9" s="52" t="str">
+        <x:v>Cash PP&amp;E spending</x:v>
+      </x:c>
+      <x:c r="B9" s="53" t="n">
+        <x:f>-IF(ISNUMBER('Data'!B22),'Data'!B22,NA())</x:f>
+        <x:v>-5259000000</x:v>
+      </x:c>
+      <x:c r="C9" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D9" s="55" t="str">
+        <x:v>Cash use, not a forecast of manufacturing investment.</x:v>
+      </x:c>
+      <x:c r="E9" s="31"/>
+      <x:c r="F9" s="31"/>
+      <x:c r="G9" s="31"/>
+    </x:row>
+    <x:row r="10" ht="43" customHeight="1">
+      <x:c r="A10" s="52" t="str">
+        <x:v>Cash acquisitions, net of cash acquired</x:v>
+      </x:c>
+      <x:c r="B10" s="53" t="n">
+        <x:f>-IF(ISNUMBER('Data'!B25),'Data'!B25,NA())</x:f>
+        <x:v>-9805000000</x:v>
+      </x:c>
+      <x:c r="C10" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D10" s="55" t="str">
+        <x:v>Not added again to the approximately $13.3B business-development disclosure.</x:v>
+      </x:c>
+      <x:c r="E10" s="31"/>
+      <x:c r="F10" s="31"/>
+      <x:c r="G10" s="31"/>
+    </x:row>
+    <x:row r="11" ht="43" customHeight="1">
+      <x:c r="A11" s="52" t="str">
+        <x:v>Purchased in-process R&amp;D</x:v>
+      </x:c>
+      <x:c r="B11" s="53" t="n">
+        <x:f>-IF(ISNUMBER('Data'!B24),'Data'!B24,NA())</x:f>
+        <x:v>-3486000000</x:v>
+      </x:c>
+      <x:c r="C11" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D11" s="55" t="str">
+        <x:v>Separate cash use; not all acquisition-related expense is cash.</x:v>
+      </x:c>
+      <x:c r="E11" s="31"/>
+      <x:c r="F11" s="31"/>
+      <x:c r="G11" s="31"/>
+    </x:row>
+    <x:row r="12" ht="43" customHeight="1">
+      <x:c r="A12" s="52" t="str">
+        <x:v>Cash dividends</x:v>
+      </x:c>
+      <x:c r="B12" s="53" t="n">
+        <x:f>-IF(ISNUMBER('Data'!B28),'Data'!B28,NA())</x:f>
+        <x:v>-3094000000</x:v>
+      </x:c>
+      <x:c r="C12" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D12" s="55" t="str">
+        <x:v>Competes with repayments for cash.</x:v>
+      </x:c>
+      <x:c r="E12" s="31"/>
+      <x:c r="F12" s="31"/>
+      <x:c r="G12" s="31"/>
+    </x:row>
+    <x:row r="13" ht="43" customHeight="1">
+      <x:c r="A13" s="52" t="str">
+        <x:v>Share repurchases</x:v>
+      </x:c>
+      <x:c r="B13" s="53" t="n">
+        <x:f>-IF(ISNUMBER('Data'!B32),'Data'!B32,NA())</x:f>
+        <x:v>-3957000000</x:v>
+      </x:c>
+      <x:c r="C13" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D13" s="55" t="str">
+        <x:v>Historical spending; no future pace assumed.</x:v>
+      </x:c>
+      <x:c r="E13" s="31"/>
+      <x:c r="F13" s="31"/>
+      <x:c r="G13" s="31"/>
+    </x:row>
+    <x:row r="14" ht="43" customHeight="1">
+      <x:c r="A14" s="52" t="str">
+        <x:v>Short-term borrowing, net</x:v>
+      </x:c>
+      <x:c r="B14" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B29),'Data'!B29,NA())</x:f>
+        <x:v>5284000000</x:v>
+      </x:c>
+      <x:c r="C14" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D14" s="55" t="str">
+        <x:v>Financing inflow, not recurring operating generation.</x:v>
+      </x:c>
+      <x:c r="E14" s="31"/>
+      <x:c r="F14" s="31"/>
+      <x:c r="G14" s="31"/>
+    </x:row>
+    <x:row r="15" ht="43" customHeight="1">
+      <x:c r="A15" s="52" t="str">
+        <x:v>Long-term debt proceeds, net</x:v>
+      </x:c>
+      <x:c r="B15" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B30),'Data'!B30,NA())</x:f>
+        <x:v>8941000000</x:v>
+      </x:c>
+      <x:c r="C15" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D15" s="55" t="str">
+        <x:v>May $9B issue is already included here; net cash differs from face amount.</x:v>
+      </x:c>
+      <x:c r="E15" s="31"/>
+      <x:c r="F15" s="31"/>
+      <x:c r="G15" s="31"/>
+    </x:row>
+    <x:row r="16" ht="43" customHeight="1">
+      <x:c r="A16" s="52" t="str">
+        <x:v>Long-term debt repaid</x:v>
+      </x:c>
+      <x:c r="B16" s="53" t="n">
+        <x:f>-IF(ISNUMBER('Data'!B31),'Data'!B31,NA())</x:f>
+        <x:v>-1623000000</x:v>
+      </x:c>
+      <x:c r="C16" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D16" s="55" t="str">
+        <x:v>Already paid; not a future maturity schedule.</x:v>
+      </x:c>
+      <x:c r="E16" s="31"/>
+      <x:c r="F16" s="31"/>
+      <x:c r="G16" s="31"/>
+    </x:row>
+    <x:row r="17" ht="43" customHeight="1">
+      <x:c r="A17" s="52" t="str">
+        <x:v>Other investing and financing</x:v>
+      </x:c>
+      <x:c r="B17" s="53" t="n">
+        <x:f>-IF(ISNUMBER('Data'!B23),'Data'!B23,NA())-IF(ISNUMBER('Data'!B26),'Data'!B26,NA())+IF(ISNUMBER('Data'!B33),'Data'!B33,NA())</x:f>
+        <x:v>-1357000000</x:v>
+      </x:c>
+      <x:c r="C17" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D17" s="55" t="str">
+        <x:v>Investment purchases, other investing and other financing.</x:v>
+      </x:c>
+      <x:c r="E17" s="31"/>
+      <x:c r="F17" s="31"/>
+      <x:c r="G17" s="31"/>
+    </x:row>
+    <x:row r="18" ht="43" customHeight="1">
+      <x:c r="A18" s="52" t="str">
+        <x:v>Exchange-rate effect</x:v>
+      </x:c>
+      <x:c r="B18" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B35),'Data'!B35,NA())</x:f>
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="C18" s="95" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D18" s="55" t="str">
+        <x:v>Reconciles the cash balance.</x:v>
+      </x:c>
+      <x:c r="E18" s="31"/>
+      <x:c r="F18" s="31"/>
+      <x:c r="G18" s="31"/>
+    </x:row>
+    <x:row r="19" ht="43" customHeight="1">
+      <x:c r="A19" s="85" t="str">
+        <x:v>Calculated cash change</x:v>
+      </x:c>
+      <x:c r="B19" s="90" t="n">
+        <x:f>SUM(B8:B18)</x:f>
+        <x:v>1682000000</x:v>
+      </x:c>
+      <x:c r="C19" s="105" t="str">
+        <x:v>January–June 2026</x:v>
+      </x:c>
+      <x:c r="D19" s="88" t="str">
+        <x:v>All signed flows counted once.</x:v>
+      </x:c>
+      <x:c r="E19" s="31"/>
+      <x:c r="F19" s="31"/>
+      <x:c r="G19" s="31"/>
+    </x:row>
+    <x:row r="20" ht="43" customHeight="1">
+      <x:c r="A20" s="85" t="str">
+        <x:v>Calculated closing cash</x:v>
+      </x:c>
+      <x:c r="B20" s="90" t="n">
+        <x:f>B7+B19</x:f>
+        <x:v>8950000000</x:v>
+      </x:c>
+      <x:c r="C20" s="105" t="str">
+        <x:v>June 30, 2026</x:v>
+      </x:c>
+      <x:c r="D20" s="88" t="str">
+        <x:v>Opening cash plus change.</x:v>
+      </x:c>
+      <x:c r="E20" s="31"/>
+      <x:c r="F20" s="31"/>
+      <x:c r="G20" s="31"/>
+    </x:row>
+    <x:row r="21" ht="43" customHeight="1">
+      <x:c r="A21" s="52" t="str">
+        <x:v>Reported closing cash</x:v>
+      </x:c>
+      <x:c r="B21" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B38),'Data'!B38,NA())</x:f>
+        <x:v>8950000000</x:v>
+      </x:c>
+      <x:c r="C21" s="95" t="str">
+        <x:v>June 30, 2026</x:v>
+      </x:c>
+      <x:c r="D21" s="55" t="str">
+        <x:v>Not a current cash balance after subsequent payments.</x:v>
+      </x:c>
+      <x:c r="E21" s="31"/>
+      <x:c r="F21" s="31"/>
+      <x:c r="G21" s="31"/>
+    </x:row>
+    <x:row r="22" ht="43" customHeight="1">
+      <x:c r="A22" s="85" t="str">
+        <x:v>Cash reconciliation difference</x:v>
+      </x:c>
+      <x:c r="B22" s="90" t="n">
+        <x:f>B20-B21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="105" t="str">
+        <x:v>Zero = reconciled</x:v>
+      </x:c>
+      <x:c r="D22" s="88" t="str">
+        <x:v>No cash forecast or unrestricted-funding total.</x:v>
+      </x:c>
+      <x:c r="E22" s="31"/>
+      <x:c r="F22" s="31"/>
+      <x:c r="G22" s="31"/>
+    </x:row>
+    <x:row r="23" ht="43" customHeight="1">
+      <x:c r="A23" s="85" t="str">
+        <x:v>OCF less cash PP&amp;E spending</x:v>
+      </x:c>
+      <x:c r="B23" s="90" t="n">
+        <x:f>B8+B9</x:f>
+        <x:v>10764000000</x:v>
+      </x:c>
+      <x:c r="C23" s="105" t="str">
+        <x:v>Historical H1 only</x:v>
+      </x:c>
+      <x:c r="D23" s="88" t="str">
+        <x:v>Excludes acquisitions, payouts and other cash uses.</x:v>
+      </x:c>
+      <x:c r="E23" s="31"/>
+      <x:c r="F23" s="31"/>
+      <x:c r="G23" s="31"/>
+    </x:row>
+    <x:row r="24" ht="43" customHeight="1">
+      <x:c r="A24" s="85" t="str">
+        <x:v>Net borrowing cash flow</x:v>
+      </x:c>
+      <x:c r="B24" s="90" t="n">
+        <x:f>SUM(B14:B16)</x:f>
+        <x:v>12602000000</x:v>
+      </x:c>
+      <x:c r="C24" s="105" t="str">
+        <x:v>Historical H1 only</x:v>
+      </x:c>
+      <x:c r="D24" s="88" t="str">
+        <x:v>Borrowing contributed to closing cash.</x:v>
+      </x:c>
+      <x:c r="E24" s="31"/>
+      <x:c r="F24" s="31"/>
+      <x:c r="G24" s="31"/>
+    </x:row>
+    <x:row r="25" ht="43" customHeight="1">
+      <x:c r="A25" s="85" t="str">
+        <x:v>Acquisitions + purchased IPR&amp;D</x:v>
+      </x:c>
+      <x:c r="B25" s="90" t="n">
+        <x:f>-SUM(B10:B11)</x:f>
+        <x:v>13291000000</x:v>
+      </x:c>
+      <x:c r="C25" s="105" t="str">
+        <x:v>Historical H1 only</x:v>
+      </x:c>
+      <x:c r="D25" s="88" t="str">
+        <x:v>Approximately $13.3B, already spent.</x:v>
+      </x:c>
+      <x:c r="E25" s="31"/>
+      <x:c r="F25" s="31"/>
+      <x:c r="G25" s="31"/>
+    </x:row>
+    <x:row r="26" ht="43" customHeight="1">
+      <x:c r="A26" s="110" t="str">
+        <x:v>Dividends + buybacks</x:v>
+      </x:c>
+      <x:c r="B26" s="114" t="n">
+        <x:f>-SUM(B12:B13)</x:f>
+        <x:v>7051000000</x:v>
+      </x:c>
+      <x:c r="C26" s="112" t="str">
+        <x:v>Historical H1 only</x:v>
+      </x:c>
+      <x:c r="D26" s="113" t="str">
+        <x:v>Not automatically recurring future obligations.</x:v>
+      </x:c>
+      <x:c r="E26" s="31"/>
+      <x:c r="F26" s="31"/>
+      <x:c r="G26" s="31"/>
+    </x:row>
+    <x:row r="27" ht="30" customHeight="1">
+      <x:c r="A27" s="31"/>
+      <x:c r="B27" s="115"/>
+      <x:c r="C27" s="31"/>
+      <x:c r="D27" s="31"/>
+      <x:c r="E27" s="31"/>
+      <x:c r="F27" s="31" t="str">
+        <x:v>H1 cash contribution</x:v>
+      </x:c>
+      <x:c r="G27" s="31" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="30" customHeight="1">
+      <x:c r="A28" s="31"/>
+      <x:c r="B28" s="115"/>
+      <x:c r="C28" s="31"/>
+      <x:c r="D28" s="31"/>
+      <x:c r="E28" s="31"/>
+      <x:c r="F28" s="31" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="G28" s="115" t="n">
+        <x:f>B8</x:f>
+        <x:v>16023000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="30" customHeight="1">
+      <x:c r="A29" s="78" t="str">
+        <x:v>Credit capacity, dates kept separate</x:v>
+      </x:c>
+      <x:c r="B29" s="116" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C29" s="79" t="str">
+        <x:v>Date / expiry</x:v>
+      </x:c>
+      <x:c r="D29" s="80" t="str">
+        <x:v>Availability limitation</x:v>
+      </x:c>
+      <x:c r="E29" s="31"/>
+      <x:c r="F29" s="31" t="str">
+        <x:v>Cash PP&amp;E spending</x:v>
+      </x:c>
+      <x:c r="G29" s="115" t="n">
+        <x:f>B9</x:f>
+        <x:v>-5259000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="70" customHeight="1">
+      <x:c r="A30" s="52" t="str">
+        <x:v>Unused committed facilities</x:v>
+      </x:c>
+      <x:c r="B30" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B58),'Data'!B58,NA())</x:f>
+        <x:v>10100000000</x:v>
+      </x:c>
+      <x:c r="C30" s="95" t="str">
+        <x:v>June 30, 2026</x:v>
+      </x:c>
+      <x:c r="D30" s="55" t="str">
+        <x:v>Reported unused, not cash or verified drawable. $10B supports CP and is not added again.</x:v>
+      </x:c>
+      <x:c r="E30" s="31"/>
+      <x:c r="F30" s="31" t="str">
+        <x:v>Acquisitions + purchased IPR&amp;D</x:v>
+      </x:c>
+      <x:c r="G30" s="115" t="n">
+        <x:f>-B25</x:f>
+        <x:v>-13291000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="70" customHeight="1">
+      <x:c r="A31" s="52" t="str">
+        <x:v>364-day facility expires August 2026</x:v>
+      </x:c>
+      <x:c r="B31" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B56),'Data'!B56,NA())</x:f>
+        <x:v>6000000000</x:v>
+      </x:c>
+      <x:c r="C31" s="95" t="str">
+        <x:v>August 2026 expiry</x:v>
+      </x:c>
+      <x:c r="D31" s="55" t="str">
+        <x:v>Annual terms: 364-day facility. Exact expiry day and renewal Unavailable; do not carry June capacity past expiry.</x:v>
+      </x:c>
+      <x:c r="E31" s="31"/>
+      <x:c r="F31" s="31" t="str">
+        <x:v>Dividends + buybacks</x:v>
+      </x:c>
+      <x:c r="G31" s="115" t="n">
+        <x:f>-B26</x:f>
+        <x:v>-7051000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="70" customHeight="1">
+      <x:c r="A32" s="52" t="str">
+        <x:v>Facility expires December 2029</x:v>
+      </x:c>
+      <x:c r="B32" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B57),'Data'!B57,NA())</x:f>
+        <x:v>4000000000</x:v>
+      </x:c>
+      <x:c r="C32" s="95" t="str">
+        <x:v>December 2029 expiry</x:v>
+      </x:c>
+      <x:c r="D32" s="55" t="str">
+        <x:v>Annual terms only. Exact day, June facility composition, contract conditions and current draws Unavailable.</x:v>
+      </x:c>
+      <x:c r="E32" s="31"/>
+      <x:c r="F32" s="31" t="str">
+        <x:v>Net borrowing</x:v>
+      </x:c>
+      <x:c r="G32" s="115" t="n">
+        <x:f>B24</x:f>
+        <x:v>12602000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="70" customHeight="1">
+      <x:c r="A33" s="52"/>
+      <x:c r="B33" s="117"/>
+      <x:c r="C33" s="95"/>
+      <x:c r="D33" s="55"/>
+      <x:c r="E33" s="31"/>
+      <x:c r="F33" s="31" t="str">
+        <x:v>Other cash flows including FX</x:v>
+      </x:c>
+      <x:c r="G33" s="115" t="n">
+        <x:f>B17+B18</x:f>
+        <x:v>-1342000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="70" customHeight="1">
+      <x:c r="A34" s="52" t="str">
+        <x:v>Drawable credit</x:v>
+      </x:c>
+      <x:c r="B34" s="117" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C34" s="95" t="str">
+        <x:v>No saved credit agreement</x:v>
+      </x:c>
+      <x:c r="D34" s="55" t="str">
+        <x:v>Draw conditions, covenants, permitted uses and post-August renewal not established. Cash + commitments is not a verified funding total.</x:v>
+      </x:c>
+      <x:c r="E34" s="31"/>
+      <x:c r="F34" s="31"/>
+      <x:c r="G34" s="31"/>
+    </x:row>
+    <x:row r="35" ht="70" customHeight="1">
+      <x:c r="A35" s="59" t="str">
+        <x:v>December unused capacity</x:v>
+      </x:c>
+      <x:c r="B35" s="118" t="n">
+        <x:f>IF(ISNUMBER('Data'!B55),'Data'!B55,NA())</x:f>
+        <x:v>10100000000</x:v>
+      </x:c>
+      <x:c r="C35" s="97" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D35" s="62" t="str">
+        <x:v>Annual unused total is $10.1B, primarily the $6B and $4B facilities. The residual $0.1B is not separately described.</x:v>
+      </x:c>
+      <x:c r="E35" s="31"/>
+      <x:c r="F35" s="31"/>
+      <x:c r="G35" s="31"/>
+    </x:row>
+    <x:row r="36" ht="30" customHeight="1">
+      <x:c r="A36" s="31"/>
+      <x:c r="B36" s="115"/>
+      <x:c r="C36" s="31"/>
+      <x:c r="D36" s="31"/>
+      <x:c r="E36" s="31"/>
+      <x:c r="F36" s="31"/>
+      <x:c r="G36" s="31"/>
+    </x:row>
+    <x:row r="37" ht="30" customHeight="1">
+      <x:c r="A37" s="31"/>
+      <x:c r="B37" s="115"/>
+      <x:c r="C37" s="31"/>
+      <x:c r="D37" s="31"/>
+      <x:c r="E37" s="31"/>
+      <x:c r="F37" s="31"/>
+      <x:c r="G37" s="31"/>
+    </x:row>
+    <x:row r="38" ht="30" customHeight="1">
+      <x:c r="A38" s="78" t="str">
+        <x:v>Acquisitions / manufacturing</x:v>
+      </x:c>
+      <x:c r="B38" s="116" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C38" s="79" t="str">
+        <x:v>Date and classification</x:v>
+      </x:c>
+      <x:c r="D38" s="80" t="str">
+        <x:v>Timing, overlap and funding limitation</x:v>
+      </x:c>
+      <x:c r="E38" s="31"/>
+      <x:c r="F38" s="31"/>
+      <x:c r="G38" s="31"/>
+    </x:row>
+    <x:row r="39" ht="96" customHeight="1">
+      <x:c r="A39" s="52" t="str">
+        <x:v>Pending AtaiBeckley acquisition</x:v>
+      </x:c>
+      <x:c r="B39" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B60),'Data'!B60,NA())</x:f>
+        <x:v>2800000000</x:v>
+      </x:c>
+      <x:c r="C39" s="95" t="str">
+        <x:v>Disclosed August 5, 2026 · Approximate conditional closing payment</x:v>
+      </x:c>
+      <x:c r="D39" s="55" t="str">
+        <x:v>Payable at closing, subject to conditions. Disclosed after quarter end; closing date, completion and funding allocation are not established here.</x:v>
+      </x:c>
+      <x:c r="E39" s="31"/>
+      <x:c r="F39" s="31"/>
+      <x:c r="G39" s="31"/>
+    </x:row>
+    <x:row r="40" ht="96" customHeight="1">
+      <x:c r="A40" s="52" t="str">
+        <x:v>Unpaid Kelonia cash consideration</x:v>
+      </x:c>
+      <x:c r="B40" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B61),'Data'!B61,NA())</x:f>
+        <x:v>208000000</x:v>
+      </x:c>
+      <x:c r="C40" s="95" t="str">
+        <x:v>2026-06-30 · Unpaid acquisition consideration</x:v>
+      </x:c>
+      <x:c r="D40" s="55" t="str">
+        <x:v>Payment date Unavailable. Separate from cash already paid and from contingent-consideration fair value.</x:v>
+      </x:c>
+      <x:c r="E40" s="31"/>
+      <x:c r="F40" s="31"/>
+      <x:c r="G40" s="31"/>
+    </x:row>
+    <x:row r="41" ht="96" customHeight="1">
+      <x:c r="A41" s="52" t="str">
+        <x:v>Unpaid Centessa cash consideration</x:v>
+      </x:c>
+      <x:c r="B41" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B62),'Data'!B62,NA())</x:f>
+        <x:v>88000000</x:v>
+      </x:c>
+      <x:c r="C41" s="95" t="str">
+        <x:v>2026-06-30 · Unpaid acquisition consideration</x:v>
+      </x:c>
+      <x:c r="D41" s="55" t="str">
+        <x:v>Payment date Unavailable. Do not add to paid acquisition cash or contingent-consideration fair value.</x:v>
+      </x:c>
+      <x:c r="E41" s="31"/>
+      <x:c r="F41" s="31"/>
+      <x:c r="G41" s="31"/>
+    </x:row>
+    <x:row r="42" ht="96" customHeight="1">
+      <x:c r="A42" s="52" t="str">
+        <x:v>July infectious-disease acquisitions: cash paid</x:v>
+      </x:c>
+      <x:c r="B42" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B63),'Data'!B63,NA())</x:f>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="C42" s="95" t="str">
+        <x:v>July 2026 · Approximate subsequent cash use</x:v>
+      </x:c>
+      <x:c r="D42" s="55" t="str">
+        <x:v>Already paid after June. Other July cash flows are unknown; June cash less this payment is not a current cash balance.</x:v>
+      </x:c>
+      <x:c r="E42" s="31"/>
+      <x:c r="F42" s="31"/>
+      <x:c r="G42" s="31"/>
+    </x:row>
+    <x:row r="43" ht="96" customHeight="1">
+      <x:c r="A43" s="52" t="str">
+        <x:v>July acquisitions: aggregate consideration up to</x:v>
+      </x:c>
+      <x:c r="B43" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B64),'Data'!B64,NA())</x:f>
+        <x:v>3900000000</x:v>
+      </x:c>
+      <x:c r="C43" s="95" t="str">
+        <x:v>July 2026 · Conditional aggregate ceiling</x:v>
+      </x:c>
+      <x:c r="D43" s="55" t="str">
+        <x:v>Includes upfront cash and potential clinical, regulatory and commercial milestones. Includes the approximately $2B paid; do not add the two amounts or infer a precise remaining cash bill.</x:v>
+      </x:c>
+      <x:c r="E43" s="31"/>
+      <x:c r="F43" s="31"/>
+      <x:c r="G43" s="31"/>
+    </x:row>
+    <x:row r="44" ht="96" customHeight="1">
+      <x:c r="A44" s="52" t="str">
+        <x:v>Unfunded venture fund commitments</x:v>
+      </x:c>
+      <x:c r="B44" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B65),'Data'!B65,NA())</x:f>
+        <x:v>806000000</x:v>
+      </x:c>
+      <x:c r="C44" s="95" t="str">
+        <x:v>2026-06-30 · Approximate investment commitment</x:v>
+      </x:c>
+      <x:c r="D44" s="55" t="str">
+        <x:v>Expected to be paid over up to ten years. Individual capital-call dates are Unavailable.</x:v>
+      </x:c>
+      <x:c r="E44" s="31"/>
+      <x:c r="F44" s="31"/>
+      <x:c r="G44" s="31"/>
+    </x:row>
+    <x:row r="45" ht="96" customHeight="1">
+      <x:c r="A45" s="52" t="str">
+        <x:v>Development-medicine supply arrangements: up to</x:v>
+      </x:c>
+      <x:c r="B45" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B66),'Data'!B66,NA())</x:f>
+        <x:v>10000000000</x:v>
+      </x:c>
+      <x:c r="C45" s="95" t="str">
+        <x:v>2025-12-31 · Approximate conditional purchase shortfall ceiling</x:v>
+      </x:c>
+      <x:c r="D45" s="55" t="str">
+        <x:v>Payments if specified purchases are not met under executed manufacturing and supply agreements; durations generally up to eight years. Not an unconditional $10B bill. Updated June ceiling, annual payments and overlap with other spending are Unavailable.</x:v>
+      </x:c>
+      <x:c r="E45" s="31"/>
+      <x:c r="F45" s="31"/>
+      <x:c r="G45" s="31"/>
+    </x:row>
+    <x:row r="46" ht="96" customHeight="1">
+      <x:c r="A46" s="59" t="str">
+        <x:v>Additional Indiana manufacturing investment</x:v>
+      </x:c>
+      <x:c r="B46" s="118" t="n">
+        <x:f>IF(ISNUMBER('Data'!B67),'Data'!B67,NA())</x:f>
+        <x:v>4500000000</x:v>
+      </x:c>
+      <x:c r="C46" s="97" t="str">
+        <x:v>Announced August 5, 2026 · Announced investment commitment</x:v>
+      </x:c>
+      <x:c r="D46" s="62" t="str">
+        <x:v>Release says committed an additional $4.5B. Contractual payment schedule, spending to date and overlap with capex or supply commitments are not established by this release. Not added to debt or the $10B ceiling.</x:v>
+      </x:c>
+      <x:c r="E46" s="31"/>
+      <x:c r="F46" s="31"/>
+      <x:c r="G46" s="31"/>
+    </x:row>
+    <x:row r="47" ht="30" customHeight="1">
+      <x:c r="A47" s="31"/>
+      <x:c r="B47" s="115"/>
+      <x:c r="C47" s="31"/>
+      <x:c r="D47" s="31"/>
+      <x:c r="E47" s="31"/>
+      <x:c r="F47" s="31"/>
+      <x:c r="G47" s="31"/>
+    </x:row>
+    <x:row r="48" ht="68" customHeight="1">
+      <x:c r="A48" s="49" t="str">
+        <x:v>Contingent consideration fair value</x:v>
+      </x:c>
+      <x:c r="B48" s="119" t="n">
+        <x:f>IF(ISNUMBER('Data'!B41),'Data'!B41,NA())+IF(ISNUMBER('Data'!B42),'Data'!B42,NA())</x:f>
+        <x:v>2518000000</x:v>
+      </x:c>
+      <x:c r="C48" s="50" t="str">
+        <x:v>June 30, 2026</x:v>
+      </x:c>
+      <x:c r="D48" s="51" t="str">
+        <x:v>Current $814M + noncurrent $1,704M. Valuation, not dated payment or contractual maximum. Not added to acquisition amounts above.</x:v>
+      </x:c>
+      <x:c r="E48" s="31"/>
+      <x:c r="F48" s="31"/>
+      <x:c r="G48" s="31"/>
+    </x:row>
+    <x:row r="49" ht="68" customHeight="1">
+      <x:c r="A49" s="52" t="str">
+        <x:v>Future funding coverage</x:v>
+      </x:c>
+      <x:c r="B49" s="117" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C49" s="95" t="str">
+        <x:v>Each future obligation</x:v>
+      </x:c>
+      <x:c r="D49" s="55" t="str">
+        <x:v>Future principal dates, future cash generation, payment dates and drawable credit not all established. No coverage ratio calculated.</x:v>
+      </x:c>
+      <x:c r="E49" s="31"/>
+      <x:c r="F49" s="31"/>
+      <x:c r="G49" s="31"/>
+    </x:row>
+    <x:row r="50" ht="68" customHeight="1">
+      <x:c r="A50" s="59" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="B50" s="120" t="str">
+        <x:v>Saved filings only</x:v>
+      </x:c>
+      <x:c r="C50" s="97" t="str">
+        <x:v>10-K; 10-Q; Aug 5 Ex. 99.1</x:v>
+      </x:c>
+      <x:c r="D50" s="62" t="str">
+        <x:v>Not a complete SEC filing inventory. No combined total of commitments, milestones, capex plans or debt.</x:v>
+      </x:c>
+      <x:c r="E50" s="31"/>
+      <x:c r="F50" s="31"/>
+      <x:c r="G50" s="31"/>
+    </x:row>
+    <x:row r="51" ht="30" customHeight="1">
+      <x:c r="A51" s="31"/>
+      <x:c r="B51" s="115"/>
+      <x:c r="C51" s="31"/>
+      <x:c r="D51" s="31"/>
+      <x:c r="E51" s="31"/>
+      <x:c r="F51" s="31"/>
+      <x:c r="G51" s="31"/>
+    </x:row>
+    <x:row r="52" ht="30" customHeight="1">
+      <x:c r="A52" s="31"/>
+      <x:c r="B52" s="115"/>
+      <x:c r="C52" s="31"/>
+      <x:c r="D52" s="31"/>
+      <x:c r="E52" s="31"/>
+      <x:c r="F52" s="31"/>
+      <x:c r="G52" s="31"/>
+    </x:row>
+    <x:row r="53" ht="30" customHeight="1">
+      <x:c r="A53" s="78" t="str">
+        <x:v>Notes grouped by due year</x:v>
+      </x:c>
+      <x:c r="B53" s="116" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C53" s="79" t="str">
+        <x:v>Basis date</x:v>
+      </x:c>
+      <x:c r="D53" s="80" t="str">
+        <x:v>Interpretation</x:v>
+      </x:c>
+      <x:c r="E53" s="31"/>
+      <x:c r="F53" s="31"/>
+      <x:c r="G53" s="31"/>
+    </x:row>
+    <x:row r="54" ht="43" customHeight="1">
+      <x:c r="A54" s="52" t="str">
+        <x:v>Notes due 2026</x:v>
+      </x:c>
+      <x:c r="B54" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B43),'Data'!B43,NA())</x:f>
+        <x:v>1632000000</x:v>
+      </x:c>
+      <x:c r="C54" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D54" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E54" s="31"/>
+      <x:c r="F54" s="31"/>
+      <x:c r="G54" s="31"/>
+    </x:row>
+    <x:row r="55" ht="43" customHeight="1">
+      <x:c r="A55" s="52" t="str">
+        <x:v>Notes due 2027</x:v>
+      </x:c>
+      <x:c r="B55" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B44),'Data'!B44,NA())</x:f>
+        <x:v>2516000000</x:v>
+      </x:c>
+      <x:c r="C55" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D55" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E55" s="31"/>
+      <x:c r="F55" s="31"/>
+      <x:c r="G55" s="31"/>
+    </x:row>
+    <x:row r="56" ht="43" customHeight="1">
+      <x:c r="A56" s="52" t="str">
+        <x:v>Notes due 2028</x:v>
+      </x:c>
+      <x:c r="B56" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B45),'Data'!B45,NA())</x:f>
+        <x:v>3256000000</x:v>
+      </x:c>
+      <x:c r="C56" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D56" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E56" s="31"/>
+      <x:c r="F56" s="31"/>
+      <x:c r="G56" s="31"/>
+    </x:row>
+    <x:row r="57" ht="43" customHeight="1">
+      <x:c r="A57" s="52" t="str">
+        <x:v>Notes due 2029</x:v>
+      </x:c>
+      <x:c r="B57" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B46),'Data'!B46,NA())</x:f>
+        <x:v>3077000000</x:v>
+      </x:c>
+      <x:c r="C57" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D57" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E57" s="31"/>
+      <x:c r="F57" s="31"/>
+      <x:c r="G57" s="31"/>
+    </x:row>
+    <x:row r="58" ht="43" customHeight="1">
+      <x:c r="A58" s="52" t="str">
+        <x:v>Notes due 2030</x:v>
+      </x:c>
+      <x:c r="B58" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B47),'Data'!B47,NA())</x:f>
+        <x:v>2132000000</x:v>
+      </x:c>
+      <x:c r="C58" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D58" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E58" s="31"/>
+      <x:c r="F58" s="31"/>
+      <x:c r="G58" s="31"/>
+    </x:row>
+    <x:row r="59" ht="43" customHeight="1">
+      <x:c r="A59" s="52" t="str">
+        <x:v>Notes due 2031–2040</x:v>
+      </x:c>
+      <x:c r="B59" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B48),'Data'!B48,NA())</x:f>
+        <x:v>11582000000</x:v>
+      </x:c>
+      <x:c r="C59" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D59" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E59" s="31"/>
+      <x:c r="F59" s="31"/>
+      <x:c r="G59" s="31"/>
+    </x:row>
+    <x:row r="60" ht="43" customHeight="1">
+      <x:c r="A60" s="52" t="str">
+        <x:v>Notes due 2041–2050</x:v>
+      </x:c>
+      <x:c r="B60" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B49),'Data'!B49,NA())</x:f>
+        <x:v>4543000000</x:v>
+      </x:c>
+      <x:c r="C60" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D60" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E60" s="31"/>
+      <x:c r="F60" s="31"/>
+      <x:c r="G60" s="31"/>
+    </x:row>
+    <x:row r="61" ht="43" customHeight="1">
+      <x:c r="A61" s="52" t="str">
+        <x:v>Notes due 2051–2060</x:v>
+      </x:c>
+      <x:c r="B61" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B50),'Data'!B50,NA())</x:f>
+        <x:v>8280000000</x:v>
+      </x:c>
+      <x:c r="C61" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D61" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E61" s="31"/>
+      <x:c r="F61" s="31"/>
+      <x:c r="G61" s="31"/>
+    </x:row>
+    <x:row r="62" ht="43" customHeight="1">
+      <x:c r="A62" s="52" t="str">
+        <x:v>Notes due 2061–2070</x:v>
+      </x:c>
+      <x:c r="B62" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B51),'Data'!B51,NA())</x:f>
+        <x:v>5824000000</x:v>
+      </x:c>
+      <x:c r="C62" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D62" s="55" t="str">
+        <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
+      </x:c>
+      <x:c r="E62" s="31"/>
+      <x:c r="F62" s="31"/>
+      <x:c r="G62" s="31"/>
+    </x:row>
+    <x:row r="63" ht="43" customHeight="1">
+      <x:c r="A63" s="85" t="str">
+        <x:v>Total notes</x:v>
+      </x:c>
+      <x:c r="B63" s="90" t="n">
+        <x:f>SUM(B54:B62)</x:f>
+        <x:v>42842000000</x:v>
+      </x:c>
+      <x:c r="C63" s="105" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D63" s="88" t="str">
+        <x:v>Carrying amount; not payment total.</x:v>
+      </x:c>
+      <x:c r="E63" s="31"/>
+      <x:c r="F63" s="31"/>
+      <x:c r="G63" s="31"/>
+    </x:row>
+    <x:row r="64" ht="43" customHeight="1">
+      <x:c r="A64" s="52" t="str">
+        <x:v>Other debt and adjustments</x:v>
+      </x:c>
+      <x:c r="B64" s="53" t="n">
+        <x:f>-IF(ISNUMBER('Data'!B52),'Data'!B52,NA())</x:f>
+        <x:v>-339000000</x:v>
+      </x:c>
+      <x:c r="C64" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D64" s="55" t="str">
+        <x:v>Printed as (339). Tagged +339 source magnitude; presentation coefficient −1.</x:v>
+      </x:c>
+      <x:c r="E64" s="31"/>
+      <x:c r="F64" s="31"/>
+      <x:c r="G64" s="31"/>
+    </x:row>
+    <x:row r="65" ht="43" customHeight="1">
+      <x:c r="A65" s="52" t="str">
+        <x:v>Commercial paper</x:v>
+      </x:c>
+      <x:c r="B65" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B53),'Data'!B53,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C65" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D65" s="55" t="str">
+        <x:v>Reported zero at December 31, 2025.</x:v>
+      </x:c>
+      <x:c r="E65" s="31"/>
+      <x:c r="F65" s="31"/>
+      <x:c r="G65" s="31"/>
+    </x:row>
+    <x:row r="66" ht="43" customHeight="1">
+      <x:c r="A66" s="85" t="str">
+        <x:v>Calculated total debt</x:v>
+      </x:c>
+      <x:c r="B66" s="90" t="n">
+        <x:f>SUM(B63:B65)</x:f>
+        <x:v>42503000000</x:v>
+      </x:c>
+      <x:c r="C66" s="105" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D66" s="88" t="str">
+        <x:v>Same annual filing; no roll-forward to June.</x:v>
+      </x:c>
+      <x:c r="E66" s="31"/>
+      <x:c r="F66" s="31"/>
+      <x:c r="G66" s="31"/>
+    </x:row>
+    <x:row r="67" ht="43" customHeight="1">
+      <x:c r="A67" s="52" t="str">
+        <x:v>Reported total debt</x:v>
+      </x:c>
+      <x:c r="B67" s="53" t="n">
+        <x:f>IF(ISNUMBER('Data'!B54),'Data'!B54,NA())</x:f>
+        <x:v>42503000000</x:v>
+      </x:c>
+      <x:c r="C67" s="95" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D67" s="55" t="str">
+        <x:v>Reconciles to annual balance sheet.</x:v>
+      </x:c>
+      <x:c r="E67" s="31"/>
+      <x:c r="F67" s="31"/>
+      <x:c r="G67" s="31"/>
+    </x:row>
+    <x:row r="68" ht="43" customHeight="1">
+      <x:c r="A68" s="110" t="str">
+        <x:v>Debt reconciliation difference</x:v>
+      </x:c>
+      <x:c r="B68" s="114" t="n">
+        <x:f>B66-B67</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C68" s="112" t="str">
+        <x:v>December 31, 2025</x:v>
+      </x:c>
+      <x:c r="D68" s="113" t="str">
+        <x:v>Zero = reconciled.</x:v>
+      </x:c>
+      <x:c r="E68" s="31"/>
+      <x:c r="F68" s="31"/>
+      <x:c r="G68" s="31"/>
+    </x:row>
+    <x:row r="69" ht="30" customHeight="1">
+      <x:c r="A69" s="31"/>
+      <x:c r="B69" s="31"/>
+      <x:c r="C69" s="31"/>
+      <x:c r="D69" s="31"/>
+      <x:c r="E69" s="31"/>
+      <x:c r="F69" s="31"/>
+      <x:c r="G69" s="31"/>
+    </x:row>
+    <x:row r="70" ht="80" customHeight="1">
+      <x:c r="A70" s="49" t="str">
+        <x:v>June 30 principal schedule</x:v>
+      </x:c>
+      <x:c r="B70" s="50" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C70" s="50" t="str">
+        <x:v>Updated payment dates missing</x:v>
+      </x:c>
+      <x:c r="D70" s="51" t="str">
+        <x:v>Do not allocate May issuance or H1 repayments to annual buckets. Current borrowing $7.050B is not an instrument-level schedule.</x:v>
+      </x:c>
+      <x:c r="E70" s="31"/>
+      <x:c r="F70" s="31"/>
+      <x:c r="G70" s="31"/>
+    </x:row>
+    <x:row r="71" ht="80" customHeight="1">
+      <x:c r="A71" s="59" t="str">
+        <x:v>Repayment conclusion</x:v>
+      </x:c>
+      <x:c r="B71" s="97"/>
+      <x:c r="C71" s="97" t="str">
+        <x:v>Coverage Unavailable</x:v>
+      </x:c>
+      <x:c r="D71" s="62" t="str">
+        <x:v>H1 cash generation after PP&amp;E was positive; acquisitions and payouts competed for cash. Net borrowing contributed materially. Updated debt dates, draw terms/renewal and payment calendars are needed.</x:v>
+      </x:c>
+      <x:c r="E71" s="31"/>
+      <x:c r="F71" s="31"/>
+      <x:c r="G71" s="31"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A4:D4"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb73ab5a2ae284972"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1010,494 +2500,533 @@
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="33" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="68" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="68" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="75" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="75" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="60" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="90" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="85" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="100" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="72" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="74" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>Input</x:v>
       </x:c>
-      <x:c r="B1" s="75" t="str">
+      <x:c r="B1" s="79" t="str">
         <x:v>USD millions</x:v>
       </x:c>
-      <x:c r="C1" s="75" t="str">
+      <x:c r="C1" s="79" t="str">
         <x:v>Period start</x:v>
       </x:c>
-      <x:c r="D1" s="75" t="str">
+      <x:c r="D1" s="79" t="str">
         <x:v>Period end</x:v>
       </x:c>
-      <x:c r="E1" s="75" t="str">
+      <x:c r="E1" s="79" t="str">
         <x:v>Form</x:v>
       </x:c>
-      <x:c r="F1" s="75" t="str">
+      <x:c r="F1" s="79" t="str">
         <x:v>Filed</x:v>
       </x:c>
-      <x:c r="G1" s="75" t="str">
+      <x:c r="G1" s="79" t="str">
         <x:v>Accession</x:v>
       </x:c>
-      <x:c r="H1" s="75" t="str">
+      <x:c r="H1" s="79" t="str">
         <x:v>Tag</x:v>
       </x:c>
-      <x:c r="I1" s="75" t="str">
+      <x:c r="I1" s="79" t="str">
         <x:v>Context</x:v>
       </x:c>
-      <x:c r="J1" s="75" t="str">
+      <x:c r="J1" s="79" t="str">
         <x:v>Scale</x:v>
       </x:c>
-      <x:c r="K1" s="75" t="str">
+      <x:c r="K1" s="79" t="str">
         <x:v>Decimals</x:v>
       </x:c>
-      <x:c r="L1" s="75" t="str">
+      <x:c r="L1" s="79" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="M1" s="75" t="str">
+      <x:c r="M1" s="79" t="str">
         <x:v>Selection rule</x:v>
       </x:c>
-      <x:c r="N1" s="75" t="str">
+      <x:c r="N1" s="79" t="str">
         <x:v>Unavailable reason</x:v>
       </x:c>
-      <x:c r="O1" s="76" t="str">
+      <x:c r="O1" s="80" t="str">
         <x:v>Notes</x:v>
       </x:c>
+      <x:c r="P1" s="31"/>
+      <x:c r="Q1" s="31"/>
+      <x:c r="R1" s="31"/>
     </x:row>
     <x:row r="2" ht="65" customHeight="1">
-      <x:c r="A2" s="48" t="str">
+      <x:c r="A2" s="52" t="str">
         <x:v>Cash and cash equivalents</x:v>
       </x:c>
-      <x:c r="B2" s="90" t="n">
+      <x:c r="B2" s="94" t="n">
         <x:v>8950000000</x:v>
       </x:c>
-      <x:c r="C2" s="50"/>
-      <x:c r="D2" s="50" t="d">
+      <x:c r="C2" s="54"/>
+      <x:c r="D2" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E2" s="91" t="str">
+      <x:c r="E2" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F2" s="50" t="d">
+      <x:c r="F2" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G2" s="91" t="str">
+      <x:c r="G2" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H2" s="91" t="str">
+      <x:c r="H2" s="95" t="str">
         <x:v>us-gaap:CashAndCashEquivalentsAtCarryingValue</x:v>
       </x:c>
-      <x:c r="I2" s="91"/>
-      <x:c r="J2" s="91"/>
-      <x:c r="K2" s="91"/>
-      <x:c r="L2" s="91" t="str">
+      <x:c r="I2" s="95"/>
+      <x:c r="J2" s="95"/>
+      <x:c r="K2" s="95"/>
+      <x:c r="L2" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M2" s="91" t="str">
+      <x:c r="M2" s="95" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N2" s="91" t="str"/>
-      <x:c r="O2" s="51" t="str"/>
+      <x:c r="N2" s="95" t="str"/>
+      <x:c r="O2" s="55" t="str"/>
+      <x:c r="P2" s="31"/>
+      <x:c r="Q2" s="31"/>
+      <x:c r="R2" s="31"/>
     </x:row>
     <x:row r="3" ht="65" customHeight="1">
-      <x:c r="A3" s="48" t="str">
+      <x:c r="A3" s="52" t="str">
         <x:v>Short-term borrowings and current maturities of long-term debt</x:v>
       </x:c>
-      <x:c r="B3" s="90" t="n">
+      <x:c r="B3" s="94" t="n">
         <x:v>7050000000</x:v>
       </x:c>
-      <x:c r="C3" s="50"/>
-      <x:c r="D3" s="50" t="d">
+      <x:c r="C3" s="54"/>
+      <x:c r="D3" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E3" s="91" t="str">
+      <x:c r="E3" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F3" s="50" t="d">
+      <x:c r="F3" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G3" s="91" t="str">
+      <x:c r="G3" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H3" s="91" t="str">
+      <x:c r="H3" s="95" t="str">
         <x:v>us-gaap:DebtCurrent</x:v>
       </x:c>
-      <x:c r="I3" s="91"/>
-      <x:c r="J3" s="91"/>
-      <x:c r="K3" s="91"/>
-      <x:c r="L3" s="91" t="str">
+      <x:c r="I3" s="95"/>
+      <x:c r="J3" s="95"/>
+      <x:c r="K3" s="95"/>
+      <x:c r="L3" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M3" s="91" t="str">
+      <x:c r="M3" s="95" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N3" s="91" t="str"/>
-      <x:c r="O3" s="51" t="str"/>
+      <x:c r="N3" s="95" t="str"/>
+      <x:c r="O3" s="55" t="str"/>
+      <x:c r="P3" s="31"/>
+      <x:c r="Q3" s="31"/>
+      <x:c r="R3" s="31"/>
     </x:row>
     <x:row r="4" ht="65" customHeight="1">
-      <x:c r="A4" s="48" t="str">
+      <x:c r="A4" s="52" t="str">
         <x:v>Long-term debt</x:v>
       </x:c>
-      <x:c r="B4" s="90" t="n">
+      <x:c r="B4" s="94" t="n">
         <x:v>47858000000</x:v>
       </x:c>
-      <x:c r="C4" s="50"/>
-      <x:c r="D4" s="50" t="d">
+      <x:c r="C4" s="54"/>
+      <x:c r="D4" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E4" s="91" t="str">
+      <x:c r="E4" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F4" s="50" t="d">
+      <x:c r="F4" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G4" s="91" t="str">
+      <x:c r="G4" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H4" s="91" t="str">
+      <x:c r="H4" s="95" t="str">
         <x:v>us-gaap:LongTermDebtNoncurrent</x:v>
       </x:c>
-      <x:c r="I4" s="91"/>
-      <x:c r="J4" s="91"/>
-      <x:c r="K4" s="91"/>
-      <x:c r="L4" s="91" t="str">
+      <x:c r="I4" s="95"/>
+      <x:c r="J4" s="95"/>
+      <x:c r="K4" s="95"/>
+      <x:c r="L4" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M4" s="91" t="str">
+      <x:c r="M4" s="95" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N4" s="91" t="str"/>
-      <x:c r="O4" s="51" t="str"/>
+      <x:c r="N4" s="95" t="str"/>
+      <x:c r="O4" s="55" t="str"/>
+      <x:c r="P4" s="31"/>
+      <x:c r="Q4" s="31"/>
+      <x:c r="R4" s="31"/>
     </x:row>
     <x:row r="5" ht="65" customHeight="1">
-      <x:c r="A5" s="48" t="str">
+      <x:c r="A5" s="52" t="str">
         <x:v>Current liabilities</x:v>
       </x:c>
-      <x:c r="B5" s="90" t="n">
+      <x:c r="B5" s="94" t="n">
         <x:v>47741000000</x:v>
       </x:c>
-      <x:c r="C5" s="50"/>
-      <x:c r="D5" s="50" t="d">
+      <x:c r="C5" s="54"/>
+      <x:c r="D5" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E5" s="91" t="str">
+      <x:c r="E5" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F5" s="50" t="d">
+      <x:c r="F5" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G5" s="91" t="str">
+      <x:c r="G5" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H5" s="91" t="str">
+      <x:c r="H5" s="95" t="str">
         <x:v>us-gaap:LiabilitiesCurrent</x:v>
       </x:c>
-      <x:c r="I5" s="91"/>
-      <x:c r="J5" s="91"/>
-      <x:c r="K5" s="91"/>
-      <x:c r="L5" s="91" t="str">
+      <x:c r="I5" s="95"/>
+      <x:c r="J5" s="95"/>
+      <x:c r="K5" s="95"/>
+      <x:c r="L5" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M5" s="91" t="str">
+      <x:c r="M5" s="95" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N5" s="91" t="str"/>
-      <x:c r="O5" s="51" t="str"/>
+      <x:c r="N5" s="95" t="str"/>
+      <x:c r="O5" s="55" t="str"/>
+      <x:c r="P5" s="31"/>
+      <x:c r="Q5" s="31"/>
+      <x:c r="R5" s="31"/>
     </x:row>
     <x:row r="6" ht="65" customHeight="1">
-      <x:c r="A6" s="48" t="str">
+      <x:c r="A6" s="52" t="str">
         <x:v>Current assets</x:v>
       </x:c>
-      <x:c r="B6" s="90" t="n">
+      <x:c r="B6" s="94" t="n">
         <x:v>64672000000</x:v>
       </x:c>
-      <x:c r="C6" s="50"/>
-      <x:c r="D6" s="50" t="d">
+      <x:c r="C6" s="54"/>
+      <x:c r="D6" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E6" s="91" t="str">
+      <x:c r="E6" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F6" s="50" t="d">
+      <x:c r="F6" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G6" s="91" t="str">
+      <x:c r="G6" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H6" s="91" t="str">
+      <x:c r="H6" s="95" t="str">
         <x:v>us-gaap:AssetsCurrent</x:v>
       </x:c>
-      <x:c r="I6" s="91"/>
-      <x:c r="J6" s="91"/>
-      <x:c r="K6" s="91"/>
-      <x:c r="L6" s="91" t="str">
+      <x:c r="I6" s="95"/>
+      <x:c r="J6" s="95"/>
+      <x:c r="K6" s="95"/>
+      <x:c r="L6" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M6" s="91" t="str">
+      <x:c r="M6" s="95" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N6" s="91" t="str"/>
-      <x:c r="O6" s="51" t="str"/>
+      <x:c r="N6" s="95" t="str"/>
+      <x:c r="O6" s="55" t="str"/>
+      <x:c r="P6" s="31"/>
+      <x:c r="Q6" s="31"/>
+      <x:c r="R6" s="31"/>
     </x:row>
     <x:row r="7" ht="65" customHeight="1">
-      <x:c r="A7" s="48" t="str">
+      <x:c r="A7" s="52" t="str">
         <x:v>Operating cash flow · fiscal year</x:v>
       </x:c>
-      <x:c r="B7" s="90" t="n">
+      <x:c r="B7" s="94" t="n">
         <x:v>16813000000</x:v>
       </x:c>
-      <x:c r="C7" s="50" t="d">
+      <x:c r="C7" s="54" t="d">
         <x:v>2025-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D7" s="50" t="d">
+      <x:c r="D7" s="54" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E7" s="91" t="str">
+      <x:c r="E7" s="95" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="F7" s="50" t="d">
+      <x:c r="F7" s="54" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G7" s="91" t="str">
+      <x:c r="G7" s="95" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="H7" s="91" t="str">
+      <x:c r="H7" s="95" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
       </x:c>
-      <x:c r="I7" s="91" t="str">
+      <x:c r="I7" s="95" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="J7" s="91" t="n">
+      <x:c r="J7" s="95" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K7" s="91" t="str">
+      <x:c r="K7" s="95" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L7" s="91" t="str">
+      <x:c r="L7" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="M7" s="91" t="str">
+      <x:c r="M7" s="95" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N7" s="91" t="str"/>
-      <x:c r="O7" s="51" t="str"/>
+      <x:c r="N7" s="95" t="str"/>
+      <x:c r="O7" s="55" t="str"/>
+      <x:c r="P7" s="31"/>
+      <x:c r="Q7" s="31"/>
+      <x:c r="R7" s="31"/>
     </x:row>
     <x:row r="8" ht="65" customHeight="1">
-      <x:c r="A8" s="48" t="str">
+      <x:c r="A8" s="52" t="str">
         <x:v>Operating cash flow · current year to date</x:v>
       </x:c>
-      <x:c r="B8" s="90" t="n">
+      <x:c r="B8" s="94" t="n">
         <x:v>16023000000</x:v>
       </x:c>
-      <x:c r="C8" s="50" t="d">
+      <x:c r="C8" s="54" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D8" s="50" t="d">
+      <x:c r="D8" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E8" s="91" t="str">
+      <x:c r="E8" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F8" s="50" t="d">
+      <x:c r="F8" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G8" s="91" t="str">
+      <x:c r="G8" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H8" s="91" t="str">
+      <x:c r="H8" s="95" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
       </x:c>
-      <x:c r="I8" s="91" t="str">
+      <x:c r="I8" s="95" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="J8" s="91" t="n">
+      <x:c r="J8" s="95" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K8" s="91" t="str">
+      <x:c r="K8" s="95" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L8" s="91" t="str">
+      <x:c r="L8" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M8" s="91" t="str">
+      <x:c r="M8" s="95" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N8" s="91" t="str"/>
-      <x:c r="O8" s="51" t="str"/>
+      <x:c r="N8" s="95" t="str"/>
+      <x:c r="O8" s="55" t="str"/>
+      <x:c r="P8" s="31"/>
+      <x:c r="Q8" s="31"/>
+      <x:c r="R8" s="31"/>
     </x:row>
     <x:row r="9" ht="65" customHeight="1">
-      <x:c r="A9" s="48" t="str">
+      <x:c r="A9" s="52" t="str">
         <x:v>Operating cash flow · prior year to date</x:v>
       </x:c>
-      <x:c r="B9" s="90" t="n">
+      <x:c r="B9" s="94" t="n">
         <x:v>4753000000</x:v>
       </x:c>
-      <x:c r="C9" s="50" t="d">
+      <x:c r="C9" s="54" t="d">
         <x:v>2025-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D9" s="50" t="d">
+      <x:c r="D9" s="54" t="d">
         <x:v>2025-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E9" s="91" t="str">
+      <x:c r="E9" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F9" s="50" t="d">
+      <x:c r="F9" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G9" s="91" t="str">
+      <x:c r="G9" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H9" s="91" t="str">
+      <x:c r="H9" s="95" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
       </x:c>
-      <x:c r="I9" s="91" t="str">
+      <x:c r="I9" s="95" t="str">
         <x:v>c-14</x:v>
       </x:c>
-      <x:c r="J9" s="91" t="n">
+      <x:c r="J9" s="95" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K9" s="91" t="str">
+      <x:c r="K9" s="95" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L9" s="91" t="str">
+      <x:c r="L9" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M9" s="91" t="str">
+      <x:c r="M9" s="95" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N9" s="91" t="str"/>
-      <x:c r="O9" s="51" t="str"/>
+      <x:c r="N9" s="95" t="str"/>
+      <x:c r="O9" s="55" t="str"/>
+      <x:c r="P9" s="31"/>
+      <x:c r="Q9" s="31"/>
+      <x:c r="R9" s="31"/>
     </x:row>
     <x:row r="10" ht="65" customHeight="1">
-      <x:c r="A10" s="48" t="str">
+      <x:c r="A10" s="52" t="str">
         <x:v>Purchases of property and equipment · fiscal year</x:v>
       </x:c>
-      <x:c r="B10" s="90" t="n">
+      <x:c r="B10" s="94" t="n">
         <x:v>7841000000</x:v>
       </x:c>
-      <x:c r="C10" s="50" t="d">
+      <x:c r="C10" s="54" t="d">
         <x:v>2025-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D10" s="50" t="d">
+      <x:c r="D10" s="54" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E10" s="91" t="str">
+      <x:c r="E10" s="95" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="F10" s="50" t="d">
+      <x:c r="F10" s="54" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G10" s="91" t="str">
+      <x:c r="G10" s="95" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="H10" s="91" t="str">
+      <x:c r="H10" s="95" t="str">
         <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
       </x:c>
-      <x:c r="I10" s="91" t="str">
+      <x:c r="I10" s="95" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="J10" s="91" t="n">
+      <x:c r="J10" s="95" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K10" s="91" t="str">
+      <x:c r="K10" s="95" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L10" s="91" t="str">
+      <x:c r="L10" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="M10" s="91" t="str">
+      <x:c r="M10" s="95" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N10" s="91" t="str"/>
-      <x:c r="O10" s="51" t="str"/>
+      <x:c r="N10" s="95" t="str"/>
+      <x:c r="O10" s="55" t="str"/>
+      <x:c r="P10" s="31"/>
+      <x:c r="Q10" s="31"/>
+      <x:c r="R10" s="31"/>
     </x:row>
     <x:row r="11" ht="65" customHeight="1">
-      <x:c r="A11" s="48" t="str">
+      <x:c r="A11" s="52" t="str">
         <x:v>Purchases of property and equipment · current year to date</x:v>
       </x:c>
-      <x:c r="B11" s="90" t="n">
+      <x:c r="B11" s="94" t="n">
         <x:v>5259000000</x:v>
       </x:c>
-      <x:c r="C11" s="50" t="d">
+      <x:c r="C11" s="54" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D11" s="50" t="d">
+      <x:c r="D11" s="54" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E11" s="91" t="str">
+      <x:c r="E11" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F11" s="50" t="d">
+      <x:c r="F11" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G11" s="91" t="str">
+      <x:c r="G11" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H11" s="91" t="str">
+      <x:c r="H11" s="95" t="str">
         <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
       </x:c>
-      <x:c r="I11" s="91" t="str">
+      <x:c r="I11" s="95" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="J11" s="91" t="n">
+      <x:c r="J11" s="95" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K11" s="91" t="str">
+      <x:c r="K11" s="95" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L11" s="91" t="str">
+      <x:c r="L11" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M11" s="91" t="str">
+      <x:c r="M11" s="95" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N11" s="91" t="str"/>
-      <x:c r="O11" s="51" t="str"/>
+      <x:c r="N11" s="95" t="str"/>
+      <x:c r="O11" s="55" t="str"/>
+      <x:c r="P11" s="31"/>
+      <x:c r="Q11" s="31"/>
+      <x:c r="R11" s="31"/>
     </x:row>
     <x:row r="12" ht="65" customHeight="1">
-      <x:c r="A12" s="55" t="str">
+      <x:c r="A12" s="59" t="str">
         <x:v>Purchases of property and equipment · prior year to date</x:v>
       </x:c>
-      <x:c r="B12" s="92" t="n">
+      <x:c r="B12" s="96" t="n">
         <x:v>3207000000</x:v>
       </x:c>
-      <x:c r="C12" s="57" t="d">
+      <x:c r="C12" s="61" t="d">
         <x:v>2025-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D12" s="57" t="d">
+      <x:c r="D12" s="61" t="d">
         <x:v>2025-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E12" s="93" t="str">
+      <x:c r="E12" s="97" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F12" s="57" t="d">
+      <x:c r="F12" s="61" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G12" s="93" t="str">
+      <x:c r="G12" s="97" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H12" s="93" t="str">
+      <x:c r="H12" s="97" t="str">
         <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
       </x:c>
-      <x:c r="I12" s="93" t="str">
+      <x:c r="I12" s="97" t="str">
         <x:v>c-14</x:v>
       </x:c>
-      <x:c r="J12" s="93" t="n">
+      <x:c r="J12" s="97" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K12" s="93" t="str">
+      <x:c r="K12" s="97" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L12" s="93" t="str">
+      <x:c r="L12" s="97" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M12" s="93" t="str">
+      <x:c r="M12" s="97" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N12" s="93" t="str"/>
-      <x:c r="O12" s="58" t="str"/>
+      <x:c r="N12" s="97" t="str"/>
+      <x:c r="O12" s="62" t="str"/>
+      <x:c r="P12" s="31"/>
+      <x:c r="Q12" s="31"/>
+      <x:c r="R12" s="31"/>
     </x:row>
     <x:row r="13" ht="65" customHeight="1">
       <x:c r="A13" s="31"/>
@@ -1515,6 +3044,9 @@
       <x:c r="M13" s="31"/>
       <x:c r="N13" s="31"/>
       <x:c r="O13" s="31"/>
+      <x:c r="P13" s="31"/>
+      <x:c r="Q13" s="31"/>
+      <x:c r="R13" s="31"/>
     </x:row>
     <x:row r="14" ht="65" customHeight="1">
       <x:c r="A14" s="31"/>
@@ -1532,33 +3064,36 @@
       <x:c r="M14" s="31"/>
       <x:c r="N14" s="31"/>
       <x:c r="O14" s="31"/>
+      <x:c r="P14" s="31"/>
+      <x:c r="Q14" s="31"/>
+      <x:c r="R14" s="31"/>
     </x:row>
     <x:row r="15" ht="80" customHeight="1">
-      <x:c r="A15" s="74" t="str">
+      <x:c r="A15" s="78" t="str">
         <x:v>Disclosure</x:v>
       </x:c>
-      <x:c r="B15" s="75" t="str">
+      <x:c r="B15" s="79" t="str">
         <x:v>Amount as disclosed</x:v>
       </x:c>
-      <x:c r="C15" s="75" t="str">
+      <x:c r="C15" s="79" t="str">
         <x:v>As of</x:v>
       </x:c>
-      <x:c r="D15" s="75" t="str">
+      <x:c r="D15" s="79" t="str">
         <x:v>Form</x:v>
       </x:c>
-      <x:c r="E15" s="75" t="str">
+      <x:c r="E15" s="79" t="str">
         <x:v>Filed</x:v>
       </x:c>
-      <x:c r="F15" s="75" t="str">
+      <x:c r="F15" s="79" t="str">
         <x:v>Accession</x:v>
       </x:c>
-      <x:c r="G15" s="75" t="str">
+      <x:c r="G15" s="79" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="H15" s="75" t="str">
+      <x:c r="H15" s="79" t="str">
         <x:v>Filing location</x:v>
       </x:c>
-      <x:c r="I15" s="76" t="str">
+      <x:c r="I15" s="80" t="str">
         <x:v>Conditions</x:v>
       </x:c>
       <x:c r="J15" s="31"/>
@@ -1567,33 +3102,36 @@
       <x:c r="M15" s="31"/>
       <x:c r="N15" s="31"/>
       <x:c r="O15" s="31"/>
+      <x:c r="P15" s="31"/>
+      <x:c r="Q15" s="31"/>
+      <x:c r="R15" s="31"/>
     </x:row>
     <x:row r="16" ht="80" customHeight="1">
-      <x:c r="A16" s="48" t="str">
+      <x:c r="A16" s="52" t="str">
         <x:v>Pending AtaiBeckley acquisition</x:v>
       </x:c>
-      <x:c r="B16" s="91" t="str">
+      <x:c r="B16" s="95" t="str">
         <x:v>Approximately $2.8B</x:v>
       </x:c>
-      <x:c r="C16" s="50" t="d">
-        <x:v>2026-06-30T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="D16" s="91" t="str">
+      <x:c r="C16" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D16" s="95" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="E16" s="50" t="d">
+      <x:c r="E16" s="54" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F16" s="91" t="str">
+      <x:c r="F16" s="95" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="G16" s="91" t="str">
+      <x:c r="G16" s="95" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="H16" s="91" t="str">
+      <x:c r="H16" s="95" t="str">
         <x:v>10-Q MD&amp;A, p. 31</x:v>
       </x:c>
-      <x:c r="I16" s="51" t="str">
+      <x:c r="I16" s="55" t="str">
         <x:v>Potential payment at closing, subject to closing conditions. Not recognized as borrowing.</x:v>
       </x:c>
       <x:c r="J16" s="31"/>
@@ -1602,33 +3140,36 @@
       <x:c r="M16" s="31"/>
       <x:c r="N16" s="31"/>
       <x:c r="O16" s="31"/>
+      <x:c r="P16" s="31"/>
+      <x:c r="Q16" s="31"/>
+      <x:c r="R16" s="31"/>
     </x:row>
     <x:row r="17" ht="80" customHeight="1">
-      <x:c r="A17" s="55" t="str">
+      <x:c r="A17" s="59" t="str">
         <x:v>Venture fund commitments</x:v>
       </x:c>
-      <x:c r="B17" s="93" t="str">
+      <x:c r="B17" s="97" t="str">
         <x:v>Approximately $806M</x:v>
       </x:c>
-      <x:c r="C17" s="57" t="d">
+      <x:c r="C17" s="61" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D17" s="93" t="str">
+      <x:c r="D17" s="97" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="E17" s="57" t="d">
+      <x:c r="E17" s="61" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F17" s="93" t="str">
+      <x:c r="F17" s="97" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="G17" s="93" t="str">
+      <x:c r="G17" s="97" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="H17" s="93" t="str">
+      <x:c r="H17" s="97" t="str">
         <x:v>10-Q MD&amp;A, p. 31; Note 8</x:v>
       </x:c>
-      <x:c r="I17" s="58" t="str">
+      <x:c r="I17" s="62" t="str">
         <x:v>Expected to be paid over up to ten years. Not recognized as borrowing.</x:v>
       </x:c>
       <x:c r="J17" s="31"/>
@@ -1637,13 +3178,2528 @@
       <x:c r="M17" s="31"/>
       <x:c r="N17" s="31"/>
       <x:c r="O17" s="31"/>
+      <x:c r="P17" s="31"/>
+      <x:c r="Q17" s="31"/>
+      <x:c r="R17" s="31"/>
+    </x:row>
+    <x:row r="18" ht="65" customHeight="1">
+      <x:c r="A18" s="31"/>
+      <x:c r="B18" s="31"/>
+      <x:c r="C18" s="31"/>
+      <x:c r="D18" s="31"/>
+      <x:c r="E18" s="31"/>
+      <x:c r="F18" s="31"/>
+      <x:c r="G18" s="31"/>
+      <x:c r="H18" s="31"/>
+      <x:c r="I18" s="31"/>
+      <x:c r="J18" s="31"/>
+      <x:c r="K18" s="31"/>
+      <x:c r="L18" s="31"/>
+      <x:c r="M18" s="31"/>
+      <x:c r="N18" s="31"/>
+      <x:c r="O18" s="31"/>
+      <x:c r="P18" s="31"/>
+      <x:c r="Q18" s="31"/>
+      <x:c r="R18" s="31"/>
+    </x:row>
+    <x:row r="19" ht="65" customHeight="1">
+      <x:c r="A19" s="31"/>
+      <x:c r="B19" s="31"/>
+      <x:c r="C19" s="31"/>
+      <x:c r="D19" s="31"/>
+      <x:c r="E19" s="31"/>
+      <x:c r="F19" s="31"/>
+      <x:c r="G19" s="31"/>
+      <x:c r="H19" s="31"/>
+      <x:c r="I19" s="31"/>
+      <x:c r="J19" s="31"/>
+      <x:c r="K19" s="31"/>
+      <x:c r="L19" s="31"/>
+      <x:c r="M19" s="31"/>
+      <x:c r="N19" s="31"/>
+      <x:c r="O19" s="31"/>
+      <x:c r="P19" s="31"/>
+      <x:c r="Q19" s="31"/>
+      <x:c r="R19" s="31"/>
+    </x:row>
+    <x:row r="20" ht="85" customHeight="1">
+      <x:c r="A20" s="78" t="str">
+        <x:v>Review input key</x:v>
+      </x:c>
+      <x:c r="B20" s="79" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C20" s="79" t="str">
+        <x:v>Label</x:v>
+      </x:c>
+      <x:c r="D20" s="79" t="str">
+        <x:v>Period start</x:v>
+      </x:c>
+      <x:c r="E20" s="79" t="str">
+        <x:v>Date / disclosure basis</x:v>
+      </x:c>
+      <x:c r="F20" s="79" t="str">
+        <x:v>Form</x:v>
+      </x:c>
+      <x:c r="G20" s="79" t="str">
+        <x:v>Filed</x:v>
+      </x:c>
+      <x:c r="H20" s="79" t="str">
+        <x:v>Accession</x:v>
+      </x:c>
+      <x:c r="I20" s="79" t="str">
+        <x:v>Tag</x:v>
+      </x:c>
+      <x:c r="J20" s="79" t="str">
+        <x:v>Context</x:v>
+      </x:c>
+      <x:c r="K20" s="79" t="str">
+        <x:v>Scale</x:v>
+      </x:c>
+      <x:c r="L20" s="79" t="str">
+        <x:v>Decimals</x:v>
+      </x:c>
+      <x:c r="M20" s="79" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="N20" s="79" t="str">
+        <x:v>Filing location</x:v>
+      </x:c>
+      <x:c r="O20" s="79" t="str">
+        <x:v>Source kind</x:v>
+      </x:c>
+      <x:c r="P20" s="79" t="str">
+        <x:v>Dimensions</x:v>
+      </x:c>
+      <x:c r="Q20" s="79" t="str">
+        <x:v>Limitations</x:v>
+      </x:c>
+      <x:c r="R20" s="80" t="str">
+        <x:v>Reviewed source SHA256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="85" customHeight="1">
+      <x:c r="A21" s="52" t="str">
+        <x:v>ocf</x:v>
+      </x:c>
+      <x:c r="B21" s="94" t="n">
+        <x:v>16023000000</x:v>
+      </x:c>
+      <x:c r="C21" s="95" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="D21" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E21" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F21" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G21" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H21" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I21" s="95" t="str">
+        <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
+      </x:c>
+      <x:c r="J21" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K21" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L21" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M21" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N21" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O21" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P21" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q21" s="95" t="str"/>
+      <x:c r="R21" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="85" customHeight="1">
+      <x:c r="A22" s="52" t="str">
+        <x:v>capex</x:v>
+      </x:c>
+      <x:c r="B22" s="94" t="n">
+        <x:v>5259000000</x:v>
+      </x:c>
+      <x:c r="C22" s="95" t="str">
+        <x:v>Cash purchases of other PP&amp;E</x:v>
+      </x:c>
+      <x:c r="D22" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E22" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F22" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G22" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H22" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I22" s="95" t="str">
+        <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
+      </x:c>
+      <x:c r="J22" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K22" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L22" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M22" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N22" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O22" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P22" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q22" s="95" t="str"/>
+      <x:c r="R22" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="85" customHeight="1">
+      <x:c r="A23" s="52" t="str">
+        <x:v>investments</x:v>
+      </x:c>
+      <x:c r="B23" s="94" t="n">
+        <x:v>604000000</x:v>
+      </x:c>
+      <x:c r="C23" s="95" t="str">
+        <x:v>Investment purchases</x:v>
+      </x:c>
+      <x:c r="D23" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E23" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F23" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G23" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H23" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I23" s="95" t="str">
+        <x:v>us-gaap:PaymentsToAcquireOtherInvestments</x:v>
+      </x:c>
+      <x:c r="J23" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K23" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L23" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M23" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N23" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O23" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P23" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q23" s="95" t="str"/>
+      <x:c r="R23" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="85" customHeight="1">
+      <x:c r="A24" s="52" t="str">
+        <x:v>iprd</x:v>
+      </x:c>
+      <x:c r="B24" s="94" t="n">
+        <x:v>3486000000</x:v>
+      </x:c>
+      <x:c r="C24" s="95" t="str">
+        <x:v>Purchased in-process R&amp;D</x:v>
+      </x:c>
+      <x:c r="D24" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E24" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F24" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G24" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H24" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I24" s="95" t="str">
+        <x:v>us-gaap:PaymentsToAcquireInProcessResearchAndDevelopment</x:v>
+      </x:c>
+      <x:c r="J24" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K24" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L24" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M24" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N24" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O24" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P24" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q24" s="95" t="str"/>
+      <x:c r="R24" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="85" customHeight="1">
+      <x:c r="A25" s="52" t="str">
+        <x:v>acquisitions</x:v>
+      </x:c>
+      <x:c r="B25" s="94" t="n">
+        <x:v>9805000000</x:v>
+      </x:c>
+      <x:c r="C25" s="95" t="str">
+        <x:v>Acquisitions, net of cash acquired</x:v>
+      </x:c>
+      <x:c r="D25" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E25" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F25" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G25" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H25" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I25" s="95" t="str">
+        <x:v>us-gaap:OtherPaymentsToAcquireBusinesses</x:v>
+      </x:c>
+      <x:c r="J25" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K25" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L25" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M25" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N25" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O25" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P25" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q25" s="95" t="str"/>
+      <x:c r="R25" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="85" customHeight="1">
+      <x:c r="A26" s="52" t="str">
+        <x:v>other_investing</x:v>
+      </x:c>
+      <x:c r="B26" s="94" t="n">
+        <x:v>158000000</x:v>
+      </x:c>
+      <x:c r="C26" s="95" t="str">
+        <x:v>Other investing cash used</x:v>
+      </x:c>
+      <x:c r="D26" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E26" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F26" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G26" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H26" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I26" s="95" t="str">
+        <x:v>us-gaap:PaymentsForProceedsFromOtherInvestingActivities</x:v>
+      </x:c>
+      <x:c r="J26" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K26" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L26" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M26" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N26" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O26" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P26" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q26" s="95" t="str"/>
+      <x:c r="R26" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="85" customHeight="1">
+      <x:c r="A27" s="52" t="str">
+        <x:v>investing_total</x:v>
+      </x:c>
+      <x:c r="B27" s="94" t="n">
+        <x:v>-19312000000</x:v>
+      </x:c>
+      <x:c r="C27" s="95" t="str">
+        <x:v>Reported net investing cash flow</x:v>
+      </x:c>
+      <x:c r="D27" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E27" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F27" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G27" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H27" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I27" s="95" t="str">
+        <x:v>us-gaap:NetCashProvidedByUsedInInvestingActivities</x:v>
+      </x:c>
+      <x:c r="J27" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K27" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L27" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M27" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N27" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O27" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P27" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q27" s="95" t="str"/>
+      <x:c r="R27" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="85" customHeight="1">
+      <x:c r="A28" s="52" t="str">
+        <x:v>dividends</x:v>
+      </x:c>
+      <x:c r="B28" s="94" t="n">
+        <x:v>3094000000</x:v>
+      </x:c>
+      <x:c r="C28" s="95" t="str">
+        <x:v>Cash dividends</x:v>
+      </x:c>
+      <x:c r="D28" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E28" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F28" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G28" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H28" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I28" s="95" t="str">
+        <x:v>us-gaap:PaymentsOfDividends</x:v>
+      </x:c>
+      <x:c r="J28" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K28" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L28" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M28" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N28" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O28" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P28" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q28" s="95" t="str"/>
+      <x:c r="R28" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="85" customHeight="1">
+      <x:c r="A29" s="52" t="str">
+        <x:v>short_debt</x:v>
+      </x:c>
+      <x:c r="B29" s="94" t="n">
+        <x:v>5284000000</x:v>
+      </x:c>
+      <x:c r="C29" s="95" t="str">
+        <x:v>Short-term borrowings, net</x:v>
+      </x:c>
+      <x:c r="D29" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E29" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F29" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G29" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H29" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I29" s="95" t="str">
+        <x:v>us-gaap:ProceedsFromRepaymentsOfShortTermDebt</x:v>
+      </x:c>
+      <x:c r="J29" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K29" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L29" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M29" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N29" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O29" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P29" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q29" s="95" t="str"/>
+      <x:c r="R29" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="85" customHeight="1">
+      <x:c r="A30" s="52" t="str">
+        <x:v>long_proceeds</x:v>
+      </x:c>
+      <x:c r="B30" s="94" t="n">
+        <x:v>8941000000</x:v>
+      </x:c>
+      <x:c r="C30" s="95" t="str">
+        <x:v>Long-term borrowing proceeds, net</x:v>
+      </x:c>
+      <x:c r="D30" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E30" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F30" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G30" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H30" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I30" s="95" t="str">
+        <x:v>us-gaap:ProceedsFromIssuanceOfLongTermDebt</x:v>
+      </x:c>
+      <x:c r="J30" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K30" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L30" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M30" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N30" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O30" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P30" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q30" s="95" t="str"/>
+      <x:c r="R30" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="85" customHeight="1">
+      <x:c r="A31" s="52" t="str">
+        <x:v>long_repayments</x:v>
+      </x:c>
+      <x:c r="B31" s="94" t="n">
+        <x:v>1623000000</x:v>
+      </x:c>
+      <x:c r="C31" s="95" t="str">
+        <x:v>Long-term debt repaid</x:v>
+      </x:c>
+      <x:c r="D31" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E31" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F31" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G31" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H31" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I31" s="95" t="str">
+        <x:v>us-gaap:RepaymentsOfLongTermDebt</x:v>
+      </x:c>
+      <x:c r="J31" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K31" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L31" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M31" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N31" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O31" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P31" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q31" s="95" t="str"/>
+      <x:c r="R31" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="85" customHeight="1">
+      <x:c r="A32" s="52" t="str">
+        <x:v>buybacks</x:v>
+      </x:c>
+      <x:c r="B32" s="94" t="n">
+        <x:v>3957000000</x:v>
+      </x:c>
+      <x:c r="C32" s="95" t="str">
+        <x:v>Share repurchases</x:v>
+      </x:c>
+      <x:c r="D32" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E32" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F32" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G32" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H32" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I32" s="95" t="str">
+        <x:v>us-gaap:PaymentsForRepurchaseOfCommonStock</x:v>
+      </x:c>
+      <x:c r="J32" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K32" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L32" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M32" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N32" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O32" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P32" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q32" s="95" t="str"/>
+      <x:c r="R32" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="85" customHeight="1">
+      <x:c r="A33" s="52" t="str">
+        <x:v>other_financing</x:v>
+      </x:c>
+      <x:c r="B33" s="94" t="n">
+        <x:v>-595000000</x:v>
+      </x:c>
+      <x:c r="C33" s="95" t="str">
+        <x:v>Other financing cash flow</x:v>
+      </x:c>
+      <x:c r="D33" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E33" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F33" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G33" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H33" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I33" s="95" t="str">
+        <x:v>us-gaap:ProceedsFromPaymentsForOtherFinancingActivities</x:v>
+      </x:c>
+      <x:c r="J33" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K33" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L33" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M33" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N33" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O33" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P33" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q33" s="95" t="str"/>
+      <x:c r="R33" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="85" customHeight="1">
+      <x:c r="A34" s="52" t="str">
+        <x:v>financing_total</x:v>
+      </x:c>
+      <x:c r="B34" s="94" t="n">
+        <x:v>4956000000</x:v>
+      </x:c>
+      <x:c r="C34" s="95" t="str">
+        <x:v>Reported net financing cash flow</x:v>
+      </x:c>
+      <x:c r="D34" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E34" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F34" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G34" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H34" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I34" s="95" t="str">
+        <x:v>us-gaap:NetCashProvidedByUsedInFinancingActivities</x:v>
+      </x:c>
+      <x:c r="J34" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K34" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L34" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M34" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N34" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O34" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P34" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q34" s="95" t="str"/>
+      <x:c r="R34" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="85" customHeight="1">
+      <x:c r="A35" s="52" t="str">
+        <x:v>fx</x:v>
+      </x:c>
+      <x:c r="B35" s="94" t="n">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="C35" s="95" t="str">
+        <x:v>Exchange-rate effect on cash</x:v>
+      </x:c>
+      <x:c r="D35" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E35" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F35" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G35" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H35" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I35" s="95" t="str">
+        <x:v>us-gaap:EffectOfExchangeRateOnCashCashEquivalentsRestrictedCashAndRestrictedCashEquivalents</x:v>
+      </x:c>
+      <x:c r="J35" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K35" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L35" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M35" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N35" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O35" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P35" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q35" s="95" t="str"/>
+      <x:c r="R35" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="85" customHeight="1">
+      <x:c r="A36" s="52" t="str">
+        <x:v>change</x:v>
+      </x:c>
+      <x:c r="B36" s="94" t="n">
+        <x:v>1682000000</x:v>
+      </x:c>
+      <x:c r="C36" s="95" t="str">
+        <x:v>Reported cash increase</x:v>
+      </x:c>
+      <x:c r="D36" s="54" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E36" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F36" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G36" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H36" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I36" s="95" t="str">
+        <x:v>us-gaap:CashCashEquivalentsRestrictedCashAndRestrictedCashEquivalentsPeriodIncreaseDecreaseIncludingExchangeRateEffect</x:v>
+      </x:c>
+      <x:c r="J36" s="95" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="K36" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L36" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M36" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N36" s="95" t="str">
+        <x:v>Cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O36" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P36" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q36" s="95" t="str"/>
+      <x:c r="R36" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="85" customHeight="1">
+      <x:c r="A37" s="52" t="str">
+        <x:v>opening</x:v>
+      </x:c>
+      <x:c r="B37" s="94" t="n">
+        <x:v>7268000000</x:v>
+      </x:c>
+      <x:c r="C37" s="95" t="str">
+        <x:v>Opening cash and equivalents</x:v>
+      </x:c>
+      <x:c r="D37" s="54"/>
+      <x:c r="E37" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F37" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G37" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H37" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I37" s="95" t="str">
+        <x:v>us-gaap:CashAndCashEquivalentsAtCarryingValue</x:v>
+      </x:c>
+      <x:c r="J37" s="95" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="K37" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L37" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M37" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N37" s="95" t="str">
+        <x:v>Balance sheet p. 7; cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O37" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P37" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q37" s="95" t="str"/>
+      <x:c r="R37" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="85" customHeight="1">
+      <x:c r="A38" s="52" t="str">
+        <x:v>closing</x:v>
+      </x:c>
+      <x:c r="B38" s="94" t="n">
+        <x:v>8950000000</x:v>
+      </x:c>
+      <x:c r="C38" s="95" t="str">
+        <x:v>Closing cash and equivalents</x:v>
+      </x:c>
+      <x:c r="D38" s="54"/>
+      <x:c r="E38" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F38" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G38" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H38" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I38" s="95" t="str">
+        <x:v>us-gaap:CashAndCashEquivalentsAtCarryingValue</x:v>
+      </x:c>
+      <x:c r="J38" s="95" t="str">
+        <x:v>c-15</x:v>
+      </x:c>
+      <x:c r="K38" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L38" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M38" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N38" s="95" t="str">
+        <x:v>Balance sheet p. 7; cash flows p. 8</x:v>
+      </x:c>
+      <x:c r="O38" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P38" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q38" s="95" t="str"/>
+      <x:c r="R38" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="85" customHeight="1">
+      <x:c r="A39" s="52" t="str">
+        <x:v>current_debt</x:v>
+      </x:c>
+      <x:c r="B39" s="94" t="n">
+        <x:v>7050000000</x:v>
+      </x:c>
+      <x:c r="C39" s="95" t="str">
+        <x:v>Current borrowing</x:v>
+      </x:c>
+      <x:c r="D39" s="54"/>
+      <x:c r="E39" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F39" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G39" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H39" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I39" s="95" t="str">
+        <x:v>us-gaap:DebtCurrent</x:v>
+      </x:c>
+      <x:c r="J39" s="95" t="str">
+        <x:v>c-15</x:v>
+      </x:c>
+      <x:c r="K39" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L39" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M39" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N39" s="95" t="str">
+        <x:v>Balance sheet p. 7</x:v>
+      </x:c>
+      <x:c r="O39" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P39" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q39" s="95" t="str"/>
+      <x:c r="R39" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="85" customHeight="1">
+      <x:c r="A40" s="52" t="str">
+        <x:v>noncurrent_debt</x:v>
+      </x:c>
+      <x:c r="B40" s="94" t="n">
+        <x:v>47858000000</x:v>
+      </x:c>
+      <x:c r="C40" s="95" t="str">
+        <x:v>Noncurrent borrowing</x:v>
+      </x:c>
+      <x:c r="D40" s="54"/>
+      <x:c r="E40" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F40" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G40" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H40" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I40" s="95" t="str">
+        <x:v>us-gaap:LongTermDebtNoncurrent</x:v>
+      </x:c>
+      <x:c r="J40" s="95" t="str">
+        <x:v>c-15</x:v>
+      </x:c>
+      <x:c r="K40" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L40" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M40" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N40" s="95" t="str">
+        <x:v>Balance sheet p. 7</x:v>
+      </x:c>
+      <x:c r="O40" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P40" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q40" s="95" t="str"/>
+      <x:c r="R40" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="85" customHeight="1">
+      <x:c r="A41" s="52" t="str">
+        <x:v>contingent_current</x:v>
+      </x:c>
+      <x:c r="B41" s="94" t="n">
+        <x:v>814000000</x:v>
+      </x:c>
+      <x:c r="C41" s="95" t="str">
+        <x:v>Contingent consideration fair value: current</x:v>
+      </x:c>
+      <x:c r="D41" s="54"/>
+      <x:c r="E41" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F41" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G41" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H41" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I41" s="95" t="str">
+        <x:v>us-gaap:BusinessCombinationContingentConsiderationLiabilityCurrent</x:v>
+      </x:c>
+      <x:c r="J41" s="95" t="str">
+        <x:v>c-301</x:v>
+      </x:c>
+      <x:c r="K41" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L41" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M41" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N41" s="95" t="str">
+        <x:v>Note 8 p. 17</x:v>
+      </x:c>
+      <x:c r="O41" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P41" s="95" t="str">
+        <x:v>[["us-gaap:FairValueByFairValueHierarchyLevelAxis","us-gaap:FairValueInputsLevel3Member"]]</x:v>
+      </x:c>
+      <x:c r="Q41" s="95" t="str"/>
+      <x:c r="R41" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="85" customHeight="1">
+      <x:c r="A42" s="52" t="str">
+        <x:v>contingent_noncurrent</x:v>
+      </x:c>
+      <x:c r="B42" s="94" t="n">
+        <x:v>1704000000</x:v>
+      </x:c>
+      <x:c r="C42" s="95" t="str">
+        <x:v>Contingent consideration fair value: noncurrent</x:v>
+      </x:c>
+      <x:c r="D42" s="54"/>
+      <x:c r="E42" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F42" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G42" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H42" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I42" s="95" t="str">
+        <x:v>us-gaap:BusinessCombinationContingentConsiderationLiabilityNoncurrent</x:v>
+      </x:c>
+      <x:c r="J42" s="95" t="str">
+        <x:v>c-301</x:v>
+      </x:c>
+      <x:c r="K42" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L42" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M42" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N42" s="95" t="str">
+        <x:v>Note 8 p. 17</x:v>
+      </x:c>
+      <x:c r="O42" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P42" s="95" t="str">
+        <x:v>[["us-gaap:FairValueByFairValueHierarchyLevelAxis","us-gaap:FairValueInputsLevel3Member"]]</x:v>
+      </x:c>
+      <x:c r="Q42" s="95" t="str"/>
+      <x:c r="R42" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="85" customHeight="1">
+      <x:c r="A43" s="52" t="str">
+        <x:v>notes_2026</x:v>
+      </x:c>
+      <x:c r="B43" s="94" t="n">
+        <x:v>1632000000</x:v>
+      </x:c>
+      <x:c r="C43" s="95" t="str">
+        <x:v>Notes due 2026</x:v>
+      </x:c>
+      <x:c r="D43" s="54"/>
+      <x:c r="E43" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F43" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G43" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H43" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I43" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J43" s="95" t="str">
+        <x:v>c-297</x:v>
+      </x:c>
+      <x:c r="K43" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L43" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M43" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N43" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O43" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P43" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2026Member"]]</x:v>
+      </x:c>
+      <x:c r="Q43" s="95" t="str"/>
+      <x:c r="R43" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="85" customHeight="1">
+      <x:c r="A44" s="52" t="str">
+        <x:v>notes_2027</x:v>
+      </x:c>
+      <x:c r="B44" s="94" t="n">
+        <x:v>2516000000</x:v>
+      </x:c>
+      <x:c r="C44" s="95" t="str">
+        <x:v>Notes due 2027</x:v>
+      </x:c>
+      <x:c r="D44" s="54"/>
+      <x:c r="E44" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F44" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G44" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H44" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I44" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J44" s="95" t="str">
+        <x:v>c-301</x:v>
+      </x:c>
+      <x:c r="K44" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L44" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M44" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N44" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O44" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P44" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2027Member"]]</x:v>
+      </x:c>
+      <x:c r="Q44" s="95" t="str"/>
+      <x:c r="R44" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="85" customHeight="1">
+      <x:c r="A45" s="52" t="str">
+        <x:v>notes_2028</x:v>
+      </x:c>
+      <x:c r="B45" s="94" t="n">
+        <x:v>3256000000</x:v>
+      </x:c>
+      <x:c r="C45" s="95" t="str">
+        <x:v>Notes due 2028</x:v>
+      </x:c>
+      <x:c r="D45" s="54"/>
+      <x:c r="E45" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F45" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G45" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H45" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I45" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J45" s="95" t="str">
+        <x:v>c-305</x:v>
+      </x:c>
+      <x:c r="K45" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L45" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M45" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N45" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O45" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P45" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2028Member"]]</x:v>
+      </x:c>
+      <x:c r="Q45" s="95" t="str"/>
+      <x:c r="R45" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="85" customHeight="1">
+      <x:c r="A46" s="52" t="str">
+        <x:v>notes_2029</x:v>
+      </x:c>
+      <x:c r="B46" s="94" t="n">
+        <x:v>3077000000</x:v>
+      </x:c>
+      <x:c r="C46" s="95" t="str">
+        <x:v>Notes due 2029</x:v>
+      </x:c>
+      <x:c r="D46" s="54"/>
+      <x:c r="E46" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F46" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G46" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H46" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I46" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J46" s="95" t="str">
+        <x:v>c-309</x:v>
+      </x:c>
+      <x:c r="K46" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L46" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M46" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N46" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O46" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P46" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2029Member"]]</x:v>
+      </x:c>
+      <x:c r="Q46" s="95" t="str"/>
+      <x:c r="R46" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="85" customHeight="1">
+      <x:c r="A47" s="52" t="str">
+        <x:v>notes_2030</x:v>
+      </x:c>
+      <x:c r="B47" s="94" t="n">
+        <x:v>2132000000</x:v>
+      </x:c>
+      <x:c r="C47" s="95" t="str">
+        <x:v>Notes due 2030</x:v>
+      </x:c>
+      <x:c r="D47" s="54"/>
+      <x:c r="E47" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F47" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G47" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H47" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I47" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J47" s="95" t="str">
+        <x:v>c-313</x:v>
+      </x:c>
+      <x:c r="K47" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L47" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M47" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N47" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O47" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P47" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2030Member"]]</x:v>
+      </x:c>
+      <x:c r="Q47" s="95" t="str"/>
+      <x:c r="R47" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="85" customHeight="1">
+      <x:c r="A48" s="52" t="str">
+        <x:v>notes_20312040</x:v>
+      </x:c>
+      <x:c r="B48" s="94" t="n">
+        <x:v>11582000000</x:v>
+      </x:c>
+      <x:c r="C48" s="95" t="str">
+        <x:v>Notes due 2031–2040</x:v>
+      </x:c>
+      <x:c r="D48" s="54"/>
+      <x:c r="E48" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F48" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G48" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H48" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I48" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J48" s="95" t="str">
+        <x:v>c-317</x:v>
+      </x:c>
+      <x:c r="K48" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L48" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M48" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N48" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O48" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P48" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue20312040Member"]]</x:v>
+      </x:c>
+      <x:c r="Q48" s="95" t="str"/>
+      <x:c r="R48" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="85" customHeight="1">
+      <x:c r="A49" s="52" t="str">
+        <x:v>notes_20412050</x:v>
+      </x:c>
+      <x:c r="B49" s="94" t="n">
+        <x:v>4543000000</x:v>
+      </x:c>
+      <x:c r="C49" s="95" t="str">
+        <x:v>Notes due 2041–2050</x:v>
+      </x:c>
+      <x:c r="D49" s="54"/>
+      <x:c r="E49" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F49" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G49" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H49" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I49" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J49" s="95" t="str">
+        <x:v>c-321</x:v>
+      </x:c>
+      <x:c r="K49" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L49" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M49" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N49" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O49" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P49" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue20412050Member"]]</x:v>
+      </x:c>
+      <x:c r="Q49" s="95" t="str"/>
+      <x:c r="R49" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="85" customHeight="1">
+      <x:c r="A50" s="52" t="str">
+        <x:v>notes_20512060</x:v>
+      </x:c>
+      <x:c r="B50" s="94" t="n">
+        <x:v>8280000000</x:v>
+      </x:c>
+      <x:c r="C50" s="95" t="str">
+        <x:v>Notes due 2051–2060</x:v>
+      </x:c>
+      <x:c r="D50" s="54"/>
+      <x:c r="E50" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F50" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G50" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H50" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I50" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J50" s="95" t="str">
+        <x:v>c-325</x:v>
+      </x:c>
+      <x:c r="K50" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L50" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M50" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N50" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O50" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P50" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue20512060Member"]]</x:v>
+      </x:c>
+      <x:c r="Q50" s="95" t="str"/>
+      <x:c r="R50" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="85" customHeight="1">
+      <x:c r="A51" s="52" t="str">
+        <x:v>notes_20612070</x:v>
+      </x:c>
+      <x:c r="B51" s="94" t="n">
+        <x:v>5824000000</x:v>
+      </x:c>
+      <x:c r="C51" s="95" t="str">
+        <x:v>Notes due 2061–2070</x:v>
+      </x:c>
+      <x:c r="D51" s="54"/>
+      <x:c r="E51" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F51" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G51" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H51" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I51" s="95" t="str">
+        <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
+      </x:c>
+      <x:c r="J51" s="95" t="str">
+        <x:v>c-329</x:v>
+      </x:c>
+      <x:c r="K51" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L51" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M51" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N51" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O51" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P51" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue20612070Member"]]</x:v>
+      </x:c>
+      <x:c r="Q51" s="95" t="str"/>
+      <x:c r="R51" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="85" customHeight="1">
+      <x:c r="A52" s="52" t="str">
+        <x:v>adjustment</x:v>
+      </x:c>
+      <x:c r="B52" s="94" t="n">
+        <x:v>339000000</x:v>
+      </x:c>
+      <x:c r="C52" s="95" t="str">
+        <x:v>Other long-term debt and adjustments (source magnitude)</x:v>
+      </x:c>
+      <x:c r="D52" s="54"/>
+      <x:c r="E52" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F52" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G52" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H52" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I52" s="95" t="str">
+        <x:v>us-gaap:OtherLongTermDebt</x:v>
+      </x:c>
+      <x:c r="J52" s="95" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="K52" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L52" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M52" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N52" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O52" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P52" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q52" s="95" t="str"/>
+      <x:c r="R52" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="85" customHeight="1">
+      <x:c r="A53" s="52" t="str">
+        <x:v>annual_cp</x:v>
+      </x:c>
+      <x:c r="B53" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C53" s="95" t="str">
+        <x:v>Commercial paper</x:v>
+      </x:c>
+      <x:c r="D53" s="54"/>
+      <x:c r="E53" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F53" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G53" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H53" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I53" s="95" t="str">
+        <x:v>us-gaap:CommercialPaper</x:v>
+      </x:c>
+      <x:c r="J53" s="95" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="K53" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L53" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M53" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N53" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O53" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P53" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q53" s="95" t="str"/>
+      <x:c r="R53" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="85" customHeight="1">
+      <x:c r="A54" s="52" t="str">
+        <x:v>annual_total</x:v>
+      </x:c>
+      <x:c r="B54" s="94" t="n">
+        <x:v>42503000000</x:v>
+      </x:c>
+      <x:c r="C54" s="95" t="str">
+        <x:v>Reported total debt</x:v>
+      </x:c>
+      <x:c r="D54" s="54"/>
+      <x:c r="E54" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F54" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G54" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H54" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I54" s="95" t="str">
+        <x:v>us-gaap:DebtLongtermAndShorttermCombinedAmount</x:v>
+      </x:c>
+      <x:c r="J54" s="95" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="K54" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L54" s="95" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="M54" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N54" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O54" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P54" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q54" s="95" t="str"/>
+      <x:c r="R54" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="85" customHeight="1">
+      <x:c r="A55" s="52" t="str">
+        <x:v>annual_unused</x:v>
+      </x:c>
+      <x:c r="B55" s="94" t="n">
+        <x:v>10100000000</x:v>
+      </x:c>
+      <x:c r="C55" s="95" t="str">
+        <x:v>Unused facilities at December 31</x:v>
+      </x:c>
+      <x:c r="D55" s="54"/>
+      <x:c r="E55" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F55" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G55" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H55" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I55" s="95" t="str">
+        <x:v>us-gaap:LineOfCreditFacilityRemainingBorrowingCapacity</x:v>
+      </x:c>
+      <x:c r="J55" s="95" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="K55" s="95" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L55" s="95" t="str">
+        <x:v>-8</x:v>
+      </x:c>
+      <x:c r="M55" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N55" s="95" t="str">
+        <x:v>Note 11 p. 76</x:v>
+      </x:c>
+      <x:c r="O55" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P55" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q55" s="95" t="str"/>
+      <x:c r="R55" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="85" customHeight="1">
+      <x:c r="A56" s="52" t="str">
+        <x:v>facility_2026</x:v>
+      </x:c>
+      <x:c r="B56" s="94" t="n">
+        <x:v>6000000000</x:v>
+      </x:c>
+      <x:c r="C56" s="95" t="str">
+        <x:v>364-day facility expires August 2026</x:v>
+      </x:c>
+      <x:c r="D56" s="54"/>
+      <x:c r="E56" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F56" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G56" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H56" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I56" s="95" t="str">
+        <x:v>us-gaap:LineOfCreditFacilityMaximumBorrowingCapacity</x:v>
+      </x:c>
+      <x:c r="J56" s="95" t="str">
+        <x:v>c-334</x:v>
+      </x:c>
+      <x:c r="K56" s="95" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L56" s="95" t="str">
+        <x:v>INF</x:v>
+      </x:c>
+      <x:c r="M56" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N56" s="95" t="str">
+        <x:v>Note 11 p. 76; MD&amp;A p. 51</x:v>
+      </x:c>
+      <x:c r="O56" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P56" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentRedemptionPeriodAxis","lly:MaturityDate2026Member"]]</x:v>
+      </x:c>
+      <x:c r="Q56" s="95" t="str"/>
+      <x:c r="R56" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="85" customHeight="1">
+      <x:c r="A57" s="52" t="str">
+        <x:v>facility_2029</x:v>
+      </x:c>
+      <x:c r="B57" s="94" t="n">
+        <x:v>4000000000</x:v>
+      </x:c>
+      <x:c r="C57" s="95" t="str">
+        <x:v>Facility expires December 2029</x:v>
+      </x:c>
+      <x:c r="D57" s="54"/>
+      <x:c r="E57" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F57" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G57" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H57" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I57" s="95" t="str">
+        <x:v>us-gaap:LineOfCreditFacilityMaximumBorrowingCapacity</x:v>
+      </x:c>
+      <x:c r="J57" s="95" t="str">
+        <x:v>c-333</x:v>
+      </x:c>
+      <x:c r="K57" s="95" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L57" s="95" t="str">
+        <x:v>INF</x:v>
+      </x:c>
+      <x:c r="M57" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N57" s="95" t="str">
+        <x:v>Note 11 p. 76; MD&amp;A p. 51</x:v>
+      </x:c>
+      <x:c r="O57" s="95" t="str">
+        <x:v>Inline XBRL</x:v>
+      </x:c>
+      <x:c r="P57" s="95" t="str">
+        <x:v>[["us-gaap:DebtInstrumentRedemptionPeriodAxis","lly:MaturityDateDecember2029Member"]]</x:v>
+      </x:c>
+      <x:c r="Q57" s="95" t="str"/>
+      <x:c r="R57" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="85" customHeight="1">
+      <x:c r="A58" s="52" t="str">
+        <x:v>unused_june</x:v>
+      </x:c>
+      <x:c r="B58" s="94" t="n">
+        <x:v>10100000000</x:v>
+      </x:c>
+      <x:c r="C58" s="95" t="str">
+        <x:v>Unused committed facilities</x:v>
+      </x:c>
+      <x:c r="D58" s="54"/>
+      <x:c r="E58" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F58" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G58" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H58" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I58" s="95"/>
+      <x:c r="J58" s="95"/>
+      <x:c r="K58" s="95"/>
+      <x:c r="L58" s="95"/>
+      <x:c r="M58" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N58" s="95" t="str">
+        <x:v>MD&amp;A p. 31</x:v>
+      </x:c>
+      <x:c r="O58" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P58" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q58" s="95" t="str">
+        <x:v>Of this, $10B supports commercial paper. Not cash or verified drawable credit; do not add CP capacity again. Agreement conditions and facility-by-facility June composition are Unavailable.</x:v>
+      </x:c>
+      <x:c r="R58" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="85" customHeight="1">
+      <x:c r="A59" s="52" t="str">
+        <x:v>cp_support</x:v>
+      </x:c>
+      <x:c r="B59" s="94" t="n">
+        <x:v>10000000000</x:v>
+      </x:c>
+      <x:c r="C59" s="95" t="str">
+        <x:v>Facilities supporting commercial paper</x:v>
+      </x:c>
+      <x:c r="D59" s="54"/>
+      <x:c r="E59" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F59" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G59" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H59" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I59" s="95"/>
+      <x:c r="J59" s="95"/>
+      <x:c r="K59" s="95"/>
+      <x:c r="L59" s="95"/>
+      <x:c r="M59" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N59" s="95" t="str">
+        <x:v>MD&amp;A p. 31</x:v>
+      </x:c>
+      <x:c r="O59" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P59" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q59" s="95" t="str">
+        <x:v>Included in the $10.1B; not another source of funds.</x:v>
+      </x:c>
+      <x:c r="R59" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="85" customHeight="1">
+      <x:c r="A60" s="52" t="str">
+        <x:v>atai</x:v>
+      </x:c>
+      <x:c r="B60" s="94" t="n">
+        <x:v>2800000000</x:v>
+      </x:c>
+      <x:c r="C60" s="95" t="str">
+        <x:v>Pending AtaiBeckley acquisition</x:v>
+      </x:c>
+      <x:c r="D60" s="54"/>
+      <x:c r="E60" s="54" t="str">
+        <x:v>Disclosed August 5, 2026</x:v>
+      </x:c>
+      <x:c r="F60" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G60" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H60" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I60" s="95"/>
+      <x:c r="J60" s="95"/>
+      <x:c r="K60" s="95"/>
+      <x:c r="L60" s="95"/>
+      <x:c r="M60" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N60" s="95" t="str">
+        <x:v>MD&amp;A p. 31</x:v>
+      </x:c>
+      <x:c r="O60" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P60" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q60" s="95" t="str">
+        <x:v>Payable at closing, subject to conditions. Disclosed after quarter end; closing date, completion and funding allocation are not established here.</x:v>
+      </x:c>
+      <x:c r="R60" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="85" customHeight="1">
+      <x:c r="A61" s="52" t="str">
+        <x:v>unpaid_kelonia</x:v>
+      </x:c>
+      <x:c r="B61" s="94" t="n">
+        <x:v>208000000</x:v>
+      </x:c>
+      <x:c r="C61" s="95" t="str">
+        <x:v>Unpaid Kelonia cash consideration</x:v>
+      </x:c>
+      <x:c r="D61" s="54"/>
+      <x:c r="E61" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F61" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G61" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H61" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I61" s="95"/>
+      <x:c r="J61" s="95"/>
+      <x:c r="K61" s="95"/>
+      <x:c r="L61" s="95"/>
+      <x:c r="M61" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N61" s="95" t="str">
+        <x:v>Note 4 p. 13</x:v>
+      </x:c>
+      <x:c r="O61" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P61" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q61" s="95" t="str">
+        <x:v>Payment date Unavailable. Separate from cash already paid and from contingent-consideration fair value.</x:v>
+      </x:c>
+      <x:c r="R61" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="85" customHeight="1">
+      <x:c r="A62" s="52" t="str">
+        <x:v>unpaid_centessa</x:v>
+      </x:c>
+      <x:c r="B62" s="94" t="n">
+        <x:v>88000000</x:v>
+      </x:c>
+      <x:c r="C62" s="95" t="str">
+        <x:v>Unpaid Centessa cash consideration</x:v>
+      </x:c>
+      <x:c r="D62" s="54"/>
+      <x:c r="E62" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F62" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G62" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H62" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I62" s="95"/>
+      <x:c r="J62" s="95"/>
+      <x:c r="K62" s="95"/>
+      <x:c r="L62" s="95"/>
+      <x:c r="M62" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N62" s="95" t="str">
+        <x:v>Note 4 p. 13</x:v>
+      </x:c>
+      <x:c r="O62" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P62" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q62" s="95" t="str">
+        <x:v>Payment date Unavailable. Do not add to paid acquisition cash or contingent-consideration fair value.</x:v>
+      </x:c>
+      <x:c r="R62" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="85" customHeight="1">
+      <x:c r="A63" s="52" t="str">
+        <x:v>july_paid</x:v>
+      </x:c>
+      <x:c r="B63" s="94" t="n">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="C63" s="95" t="str">
+        <x:v>July infectious-disease acquisitions: cash paid</x:v>
+      </x:c>
+      <x:c r="D63" s="54"/>
+      <x:c r="E63" s="54" t="str">
+        <x:v>July 2026</x:v>
+      </x:c>
+      <x:c r="F63" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G63" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H63" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I63" s="95"/>
+      <x:c r="J63" s="95"/>
+      <x:c r="K63" s="95"/>
+      <x:c r="L63" s="95"/>
+      <x:c r="M63" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N63" s="95" t="str">
+        <x:v>MD&amp;A p. 31; Note 4 pp. 13–14</x:v>
+      </x:c>
+      <x:c r="O63" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P63" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q63" s="95" t="str">
+        <x:v>Already paid after June. Other July cash flows are unknown; June cash less this payment is not a current cash balance.</x:v>
+      </x:c>
+      <x:c r="R63" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="85" customHeight="1">
+      <x:c r="A64" s="52" t="str">
+        <x:v>july_ceiling</x:v>
+      </x:c>
+      <x:c r="B64" s="94" t="n">
+        <x:v>3900000000</x:v>
+      </x:c>
+      <x:c r="C64" s="95" t="str">
+        <x:v>July acquisitions: aggregate consideration up to</x:v>
+      </x:c>
+      <x:c r="D64" s="54"/>
+      <x:c r="E64" s="54" t="str">
+        <x:v>July 2026</x:v>
+      </x:c>
+      <x:c r="F64" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G64" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H64" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I64" s="95"/>
+      <x:c r="J64" s="95"/>
+      <x:c r="K64" s="95"/>
+      <x:c r="L64" s="95"/>
+      <x:c r="M64" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N64" s="95" t="str">
+        <x:v>Note 4 pp. 13–14</x:v>
+      </x:c>
+      <x:c r="O64" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P64" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q64" s="95" t="str">
+        <x:v>Includes upfront cash and potential clinical, regulatory and commercial milestones. Includes the approximately $2B paid; do not add the two amounts or infer a precise remaining cash bill.</x:v>
+      </x:c>
+      <x:c r="R64" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="85" customHeight="1">
+      <x:c r="A65" s="52" t="str">
+        <x:v>vc</x:v>
+      </x:c>
+      <x:c r="B65" s="94" t="n">
+        <x:v>806000000</x:v>
+      </x:c>
+      <x:c r="C65" s="95" t="str">
+        <x:v>Unfunded venture fund commitments</x:v>
+      </x:c>
+      <x:c r="D65" s="54"/>
+      <x:c r="E65" s="54" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F65" s="95" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="G65" s="54" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H65" s="95" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="I65" s="95"/>
+      <x:c r="J65" s="95"/>
+      <x:c r="K65" s="95"/>
+      <x:c r="L65" s="95"/>
+      <x:c r="M65" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="N65" s="95" t="str">
+        <x:v>MD&amp;A p. 31</x:v>
+      </x:c>
+      <x:c r="O65" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P65" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q65" s="95" t="str">
+        <x:v>Expected to be paid over up to ten years. Individual capital-call dates are Unavailable.</x:v>
+      </x:c>
+      <x:c r="R65" s="55" t="str">
+        <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="85" customHeight="1">
+      <x:c r="A66" s="52" t="str">
+        <x:v>manufacturing</x:v>
+      </x:c>
+      <x:c r="B66" s="94" t="n">
+        <x:v>10000000000</x:v>
+      </x:c>
+      <x:c r="C66" s="95" t="str">
+        <x:v>Development-medicine supply arrangements: up to</x:v>
+      </x:c>
+      <x:c r="D66" s="54"/>
+      <x:c r="E66" s="54" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F66" s="95" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="G66" s="54" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H66" s="95" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="I66" s="95"/>
+      <x:c r="J66" s="95"/>
+      <x:c r="K66" s="95"/>
+      <x:c r="L66" s="95"/>
+      <x:c r="M66" s="95" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="N66" s="95" t="str">
+        <x:v>MD&amp;A p. 51</x:v>
+      </x:c>
+      <x:c r="O66" s="95" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P66" s="95" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q66" s="95" t="str">
+        <x:v>Payments if specified purchases are not met under executed manufacturing and supply agreements; durations generally up to eight years. Not an unconditional $10B bill. Updated June ceiling, annual payments and overlap with other spending are Unavailable.</x:v>
+      </x:c>
+      <x:c r="R66" s="55" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="85" customHeight="1">
+      <x:c r="A67" s="59" t="str">
+        <x:v>indiana</x:v>
+      </x:c>
+      <x:c r="B67" s="96" t="n">
+        <x:v>4500000000</x:v>
+      </x:c>
+      <x:c r="C67" s="97" t="str">
+        <x:v>Additional Indiana manufacturing investment</x:v>
+      </x:c>
+      <x:c r="D67" s="61"/>
+      <x:c r="E67" s="61" t="str">
+        <x:v>Announced August 5, 2026</x:v>
+      </x:c>
+      <x:c r="F67" s="97" t="str">
+        <x:v>8-K Ex. 99.1</x:v>
+      </x:c>
+      <x:c r="G67" s="61" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H67" s="97" t="str">
+        <x:v>0000059478-26-000077</x:v>
+      </x:c>
+      <x:c r="I67" s="97"/>
+      <x:c r="J67" s="97"/>
+      <x:c r="K67" s="97"/>
+      <x:c r="L67" s="97"/>
+      <x:c r="M67" s="97" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000077/q226lillysalesandearningsp.htm</x:v>
+      </x:c>
+      <x:c r="N67" s="97" t="str">
+        <x:v>Highlights; Other announcements</x:v>
+      </x:c>
+      <x:c r="O67" s="97" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P67" s="97" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q67" s="97" t="str">
+        <x:v>Release says committed an additional $4.5B. Contractual payment schedule, spending to date and overlap with capex or supply commitments are not established by this release. Not added to debt or the $10B ceiling.</x:v>
+      </x:c>
+      <x:c r="R67" s="62" t="str">
+        <x:v>5397056cb6aebc1496e22de6f9c8b062b11ff0c7f5ee30428e3f68fc8aea748a</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1653,67 +5709,89 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="74" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>Topic</x:v>
       </x:c>
-      <x:c r="B1" s="75" t="str">
+      <x:c r="B1" s="79" t="str">
         <x:v>Explanation</x:v>
       </x:c>
-      <x:c r="C1" s="76" t="str">
+      <x:c r="C1" s="80" t="str">
         <x:v>Source</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="70" customHeight="1">
-      <x:c r="A2" s="48" t="str">
+      <x:c r="A2" s="52" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="B2" s="91" t="str">
+      <x:c r="B2" s="95" t="str">
         <x:v>Lilly only. Checked snapshot October 14, 2026. Financial statements dated June 30, 2026. Not investment advice.</x:v>
       </x:c>
-      <x:c r="C2" s="51" t="str">
+      <x:c r="C2" s="55" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="70" customHeight="1">
-      <x:c r="A3" s="48" t="str">
+      <x:c r="A3" s="52" t="str">
         <x:v>Colors</x:v>
       </x:c>
-      <x:c r="B3" s="91" t="str">
+      <x:c r="B3" s="95" t="str">
         <x:v>Arial 10. Full USD displayed in millions. Blue reported inputs, green cross-sheet links, black same-sheet calculations. Zero is a dash. Missing inputs are not zero.</x:v>
       </x:c>
-      <x:c r="C3" s="51"/>
+      <x:c r="C3" s="55"/>
     </x:row>
     <x:row r="4" ht="70" customHeight="1">
-      <x:c r="A4" s="48" t="str">
+      <x:c r="A4" s="52" t="str">
         <x:v>Cash generation</x:v>
       </x:c>
-      <x:c r="B4" s="91" t="str">
+      <x:c r="B4" s="95" t="str">
         <x:v>Fiscal year + current YTD − prior YTD. Capital spending uses Lilly’s checked other-PP&amp;E tag. FCF excludes acquisitions, dividends and other cash uses.</x:v>
       </x:c>
-      <x:c r="C4" s="51" t="str">
+      <x:c r="C4" s="55" t="str">
         <x:v>docs/pilot_cashflow_reconciliation.md</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="70" customHeight="1">
-      <x:c r="A5" s="48" t="str">
+      <x:c r="A5" s="52" t="str">
         <x:v>Borrowing</x:v>
       </x:c>
-      <x:c r="B5" s="91" t="str">
+      <x:c r="B5" s="95" t="str">
         <x:v>Balance-sheet current and noncurrent borrowing are added once. Fair-value table carrying amounts are not added again.</x:v>
       </x:c>
-      <x:c r="C5" s="51" t="str">
+      <x:c r="C5" s="55" t="str">
         <x:v>docs/pilot_evidence_lly.md</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
-      <x:c r="A6" s="55" t="str">
+      <x:c r="A6" s="59" t="str">
         <x:v>Selected commitments</x:v>
       </x:c>
-      <x:c r="B6" s="93" t="str">
-        <x:v>Descriptions and amount wording retain the June 30 filing basis. They are not added to debt or to each other.</x:v>
-      </x:c>
-      <x:c r="C6" s="58" t="str">
+      <x:c r="B6" s="97" t="str">
+        <x:v>Descriptions retain their disclosure dates; AtaiBeckley was disclosed after quarter end. They are not added to debt or to each other.</x:v>
+      </x:c>
+      <x:c r="C6" s="62" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="95" customHeight="1">
+      <x:c r="A7" s="52" t="str">
+        <x:v>Dated review</x:v>
+      </x:c>
+      <x:c r="B7" s="95" t="str">
+        <x:v>Repayment review uses exact H1 cash flows and historical annual carrying-debt buckets. Future coverage remains Unavailable. Text disclosures are identified separately; source hashes and dimensions are in Data.</x:v>
+      </x:c>
+      <x:c r="C7" s="55" t="str">
+        <x:v>docs/lly_liquidity_review.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="95" customHeight="1">
+      <x:c r="A8" s="59" t="str">
+        <x:v>Post-quarter events</x:v>
+      </x:c>
+      <x:c r="B8" s="97" t="str">
+        <x:v>July acquisition cash is separate from June cash. The July $3.9B ceiling includes upfront cash. August $4.5B manufacturing announcement has no dated cash schedule. No overlap total inferred.</x:v>
+      </x:c>
+      <x:c r="C8" s="62" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000077/q226lillysalesandearningsp.htm</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="1" r:id="R7d12193cfa934755"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="2" r:id="Re655cfdc693741a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" r:id="Ra7c4c30a87544473"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="4" r:id="R73e53caaedc84b00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="1" r:id="Rce2a7deb26ac4846"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="2" r:id="R50dc3fefa7fa4d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" r:id="R308d0b3a9b494e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="4" r:id="R4633d2c746794947"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,11 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="#,##0,,;(#,##0,,);&quot;-&quot;"/>
     <x:numFmt numFmtId="201" formatCode="mmm d, yyyy"/>
     <x:numFmt numFmtId="202" formatCode="0.00&quot;x&quot;"/>
     <x:numFmt numFmtId="203" formatCode="0.0%"/>
+    <x:numFmt numFmtId="204" formatCode="0.000%"/>
   </x:numFmts>
   <x:fonts count="18">
     <x:font>
@@ -292,7 +293,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="123">
+  <x:cellXfs count="138">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -303,6 +304,7 @@
     <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="203" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -360,11 +362,19 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -604,6 +614,36 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -803,7 +843,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R81c17877e17e4414"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rac956dbf6bae4ffc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1014,271 +1054,271 @@
   </x:cols>
   <x:sheetData>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="47" t="str">
+      <x:c r="A2" s="52" t="str">
         <x:v>Eli Lilly and Company</x:v>
       </x:c>
-      <x:c r="B2" s="31"/>
-      <x:c r="C2" s="31"/>
-      <x:c r="D2" s="31"/>
+      <x:c r="B2" s="32"/>
+      <x:c r="C2" s="32"/>
+      <x:c r="D2" s="32"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="48" t="str">
+      <x:c r="A3" s="53" t="str">
         <x:v>Balance sheet June 30, 2026. TTM July 2025–June 2026. USD millions unless ratio or %.</x:v>
       </x:c>
-      <x:c r="B3" s="31"/>
-      <x:c r="C3" s="31"/>
-      <x:c r="D3" s="31"/>
+      <x:c r="B3" s="32"/>
+      <x:c r="C3" s="32"/>
+      <x:c r="D3" s="32"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="31"/>
-      <x:c r="B4" s="31"/>
-      <x:c r="C4" s="31"/>
-      <x:c r="D4" s="31"/>
+      <x:c r="A4" s="32"/>
+      <x:c r="B4" s="32"/>
+      <x:c r="C4" s="32"/>
+      <x:c r="D4" s="32"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="78" t="str">
+      <x:c r="A5" s="83" t="str">
         <x:v>Measure</x:v>
       </x:c>
-      <x:c r="B5" s="79" t="str">
+      <x:c r="B5" s="84" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C5" s="79" t="str">
+      <x:c r="C5" s="84" t="str">
         <x:v>Period end</x:v>
       </x:c>
-      <x:c r="D5" s="80" t="str">
+      <x:c r="D5" s="85" t="str">
         <x:v>Basis / limitation</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="46" customHeight="1">
-      <x:c r="A6" s="52" t="str">
+      <x:c r="A6" s="57" t="str">
         <x:v>Cash and cash equivalents</x:v>
       </x:c>
-      <x:c r="B6" s="53" t="n">
+      <x:c r="B6" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B2),'Data'!B2,NA())</x:f>
         <x:v>8950000000</x:v>
       </x:c>
-      <x:c r="C6" s="54" t="d">
+      <x:c r="C6" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D6" s="91" t="str"/>
+      <x:c r="D6" s="96" t="str"/>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
-      <x:c r="A7" s="85" t="str">
+      <x:c r="A7" s="90" t="str">
         <x:v>Baseline gross debt</x:v>
       </x:c>
-      <x:c r="B7" s="86" t="n">
+      <x:c r="B7" s="91" t="n">
         <x:f>IF(ISNUMBER('Data'!B3),'Data'!B3,NA())+IF(ISNUMBER('Data'!B4),'Data'!B4,NA())</x:f>
         <x:v>54908000000</x:v>
       </x:c>
-      <x:c r="C7" s="87" t="d">
+      <x:c r="C7" s="92" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D7" s="92" t="str">
+      <x:c r="D7" s="97" t="str">
         <x:v>In this 10-Q, the Note 8 fair-value table's carrying amounts (commercial paper 5,284M plus long-term debt including current portion 49,624M) present the same 54,908M; they are not added. Excluded: fair-value-table carrying amounts of the same borrowings (commercial paper, long-term debt)</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
-      <x:c r="A8" s="85" t="str">
+      <x:c r="A8" s="90" t="str">
         <x:v>Net debt</x:v>
       </x:c>
-      <x:c r="B8" s="90" t="n">
+      <x:c r="B8" s="95" t="n">
         <x:f>B7-B6</x:f>
         <x:v>45958000000</x:v>
       </x:c>
-      <x:c r="C8" s="87" t="d">
+      <x:c r="C8" s="92" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D8" s="92" t="str"/>
+      <x:c r="D8" s="97" t="str"/>
     </x:row>
     <x:row r="9" ht="46" customHeight="1">
-      <x:c r="A9" s="52" t="str">
+      <x:c r="A9" s="57" t="str">
         <x:v>Current ratio</x:v>
       </x:c>
-      <x:c r="B9" s="57" t="n">
+      <x:c r="B9" s="62" t="n">
         <x:f>IF(IF(ISNUMBER('Data'!B5),'Data'!B5,NA())&gt;0,IF(ISNUMBER('Data'!B6),'Data'!B6,NA())/IF(ISNUMBER('Data'!B5),'Data'!B5,NA()),NA())</x:f>
         <x:v>1.3546427598919168</x:v>
       </x:c>
-      <x:c r="C9" s="54" t="d">
+      <x:c r="C9" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D9" s="91" t="str"/>
+      <x:c r="D9" s="96" t="str"/>
     </x:row>
     <x:row r="10" ht="46" customHeight="1">
-      <x:c r="A10" s="52" t="str">
+      <x:c r="A10" s="57" t="str">
         <x:v>Operating cash flow</x:v>
       </x:c>
-      <x:c r="B10" s="53" t="n">
+      <x:c r="B10" s="58" t="n">
         <x:f>(1*IF(ISNUMBER('Data'!B7),'Data'!B7,NA())) + (1*IF(ISNUMBER('Data'!B8),'Data'!B8,NA())) + (-1*IF(ISNUMBER('Data'!B9),'Data'!B9,NA()))</x:f>
         <x:v>28083000000</x:v>
       </x:c>
-      <x:c r="C10" s="54" t="d">
+      <x:c r="C10" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D10" s="91" t="str"/>
+      <x:c r="D10" s="96" t="str"/>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
-      <x:c r="A11" s="52" t="str">
+      <x:c r="A11" s="57" t="str">
         <x:v>Purchases of property and equipment</x:v>
       </x:c>
-      <x:c r="B11" s="53" t="n">
+      <x:c r="B11" s="58" t="n">
         <x:f>(1*IF(ISNUMBER('Data'!B10),'Data'!B10,NA())) + (1*IF(ISNUMBER('Data'!B11),'Data'!B11,NA())) + (-1*IF(ISNUMBER('Data'!B12),'Data'!B12,NA()))</x:f>
         <x:v>9893000000</x:v>
       </x:c>
-      <x:c r="C11" s="54" t="d">
+      <x:c r="C11" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D11" s="91" t="str"/>
+      <x:c r="D11" s="96" t="str"/>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
-      <x:c r="A12" s="85" t="str">
+      <x:c r="A12" s="90" t="str">
         <x:v>Free cash flow</x:v>
       </x:c>
-      <x:c r="B12" s="90" t="n">
+      <x:c r="B12" s="95" t="n">
         <x:f>B10-B11</x:f>
         <x:v>18190000000</x:v>
       </x:c>
-      <x:c r="C12" s="87" t="d">
+      <x:c r="C12" s="92" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D12" s="92" t="str">
+      <x:c r="D12" s="97" t="str">
         <x:v>Reported purchases of property and equipment; excludes acquisitions and other investing cash flows.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
-      <x:c r="A13" s="52" t="str">
+      <x:c r="A13" s="57" t="str">
         <x:v>Operating cash flow / debt</x:v>
       </x:c>
-      <x:c r="B13" s="58" t="n">
+      <x:c r="B13" s="63" t="n">
         <x:f>IF(B7&gt;0,B10/B7,NA())</x:f>
         <x:v>0.511455525606469</x:v>
       </x:c>
-      <x:c r="C13" s="54" t="d">
+      <x:c r="C13" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D13" s="91" t="str">
+      <x:c r="D13" s="96" t="str">
         <x:v>Historical TTM flow / period-end debt. Not repayment coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
-      <x:c r="A14" s="59" t="str">
+      <x:c r="A14" s="64" t="str">
         <x:v>Free cash flow / debt</x:v>
       </x:c>
-      <x:c r="B14" s="60" t="n">
+      <x:c r="B14" s="65" t="n">
         <x:f>IF(B7&gt;0,B12/B7,NA())</x:f>
         <x:v>0.33128141618707657</x:v>
       </x:c>
-      <x:c r="C14" s="61" t="d">
+      <x:c r="C14" s="66" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D14" s="93" t="str">
+      <x:c r="D14" s="98" t="str">
         <x:v>Historical TTM flow / period-end debt. Not repayment coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="31"/>
-      <x:c r="B15" s="31"/>
-      <x:c r="C15" s="31"/>
-      <x:c r="D15" s="31"/>
+      <x:c r="A15" s="32"/>
+      <x:c r="B15" s="32"/>
+      <x:c r="C15" s="32"/>
+      <x:c r="D15" s="32"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="31"/>
-      <x:c r="B16" s="31"/>
-      <x:c r="C16" s="31"/>
-      <x:c r="D16" s="31"/>
+      <x:c r="A16" s="32"/>
+      <x:c r="B16" s="32"/>
+      <x:c r="C16" s="32"/>
+      <x:c r="D16" s="32"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="31" t="str">
+      <x:c r="A17" s="32" t="str">
         <x:v>Selected obligations, separate from borrowing</x:v>
       </x:c>
-      <x:c r="B17" s="31"/>
-      <x:c r="C17" s="31"/>
-      <x:c r="D17" s="31"/>
+      <x:c r="B17" s="32"/>
+      <x:c r="C17" s="32"/>
+      <x:c r="D17" s="32"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="78" t="str">
+      <x:c r="A18" s="83" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B18" s="79" t="str">
+      <x:c r="B18" s="84" t="str">
         <x:v>Disclosed amount / timing</x:v>
       </x:c>
-      <x:c r="C18" s="80" t="str">
+      <x:c r="C18" s="85" t="str">
         <x:v>Basis</x:v>
       </x:c>
-      <x:c r="D18" s="31"/>
+      <x:c r="D18" s="32"/>
     </x:row>
     <x:row r="19" ht="62" customHeight="1">
-      <x:c r="A19" s="63" t="str">
+      <x:c r="A19" s="68" t="str">
         <x:f>'Data'!A16</x:f>
         <x:v>Pending AtaiBeckley acquisition</x:v>
       </x:c>
-      <x:c r="B19" s="64" t="str">
+      <x:c r="B19" s="69" t="str">
         <x:f>'Data'!B16</x:f>
         <x:v>Approximately $2.8B</x:v>
       </x:c>
-      <x:c r="C19" s="65" t="str">
+      <x:c r="C19" s="70" t="str">
         <x:f>'Data'!I16</x:f>
         <x:v>Potential payment at closing, subject to closing conditions. Not recognized as borrowing.</x:v>
       </x:c>
-      <x:c r="D19" s="31"/>
+      <x:c r="D19" s="32"/>
     </x:row>
     <x:row r="20" ht="62" customHeight="1">
-      <x:c r="A20" s="66" t="str">
+      <x:c r="A20" s="71" t="str">
         <x:f>'Data'!A17</x:f>
         <x:v>Venture fund commitments</x:v>
       </x:c>
-      <x:c r="B20" s="67" t="str">
+      <x:c r="B20" s="72" t="str">
         <x:f>'Data'!B17</x:f>
         <x:v>Approximately $806M</x:v>
       </x:c>
-      <x:c r="C20" s="68" t="str">
+      <x:c r="C20" s="73" t="str">
         <x:f>'Data'!I17</x:f>
         <x:v>Expected to be paid over up to ten years. Not recognized as borrowing.</x:v>
       </x:c>
-      <x:c r="D20" s="31"/>
+      <x:c r="D20" s="32"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="31"/>
-      <x:c r="B21" s="31"/>
-      <x:c r="C21" s="31"/>
-      <x:c r="D21" s="31"/>
+      <x:c r="A21" s="32"/>
+      <x:c r="B21" s="32"/>
+      <x:c r="C21" s="32"/>
+      <x:c r="D21" s="32"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="31"/>
-      <x:c r="B22" s="31"/>
-      <x:c r="C22" s="31"/>
-      <x:c r="D22" s="31"/>
+      <x:c r="A22" s="32"/>
+      <x:c r="B22" s="32"/>
+      <x:c r="C22" s="32"/>
+      <x:c r="D22" s="32"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="31" t="str">
+      <x:c r="A23" s="32" t="str">
         <x:v>Remaining gaps</x:v>
       </x:c>
-      <x:c r="B23" s="31"/>
-      <x:c r="C23" s="31"/>
-      <x:c r="D23" s="31"/>
+      <x:c r="B23" s="32"/>
+      <x:c r="C23" s="32"/>
+      <x:c r="D23" s="32"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="48" t="str">
+      <x:c r="A24" s="53" t="str">
         <x:v>June lease liabilities, updated principal maturities and interest coverage are Unavailable.</x:v>
       </x:c>
-      <x:c r="B24" s="31"/>
-      <x:c r="C24" s="31"/>
-      <x:c r="D24" s="31"/>
+      <x:c r="B24" s="32"/>
+      <x:c r="C24" s="32"/>
+      <x:c r="D24" s="32"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="48" t="str">
+      <x:c r="A25" s="53" t="str">
         <x:v>See Repayment review for dated cash flows, facilities, acquisitions and manufacturing commitments.</x:v>
       </x:c>
-      <x:c r="B25" s="31"/>
-      <x:c r="C25" s="31"/>
-      <x:c r="D25" s="31"/>
+      <x:c r="B25" s="32"/>
+      <x:c r="C25" s="32"/>
+      <x:c r="D25" s="32"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="48" t="str">
-        <x:v>Sources and selection rules are in Data. Saved August 5 earnings exhibit reviewed; no complete filing inventory claimed.</x:v>
-      </x:c>
-      <x:c r="B26" s="31"/>
-      <x:c r="C26" s="31"/>
-      <x:c r="D26" s="31"/>
+      <x:c r="A26" s="53" t="str">
+        <x:v>Financing index checked through October 15, 2026. See Repayment review for May terms; all sources and limits are in Data.</x:v>
+      </x:c>
+      <x:c r="B26" s="32"/>
+      <x:c r="C26" s="32"/>
+      <x:c r="D26" s="32"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1308,1183 +1348,1570 @@
   </x:cols>
   <x:sheetData>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="47" t="str">
+      <x:c r="A2" s="52" t="str">
         <x:v>Lilly — dated liquidity and repayment review</x:v>
       </x:c>
-      <x:c r="B2" s="31"/>
-      <x:c r="C2" s="31"/>
-      <x:c r="D2" s="31"/>
-      <x:c r="E2" s="31"/>
-      <x:c r="F2" s="31"/>
-      <x:c r="G2" s="31"/>
+      <x:c r="B2" s="32"/>
+      <x:c r="C2" s="32"/>
+      <x:c r="D2" s="32"/>
+      <x:c r="E2" s="32"/>
+      <x:c r="F2" s="32"/>
+      <x:c r="G2" s="32"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="48" t="str">
+      <x:c r="A3" s="53" t="str">
         <x:v>Saved filings reviewed October 15, 2026. Cash flows: January–June 2026. USD millions.</x:v>
       </x:c>
-      <x:c r="B3" s="31"/>
-      <x:c r="C3" s="31"/>
-      <x:c r="D3" s="31"/>
-      <x:c r="E3" s="31"/>
-      <x:c r="F3" s="31"/>
-      <x:c r="G3" s="31"/>
+      <x:c r="B3" s="32"/>
+      <x:c r="C3" s="32"/>
+      <x:c r="D3" s="32"/>
+      <x:c r="E3" s="32"/>
+      <x:c r="F3" s="32"/>
+      <x:c r="G3" s="32"/>
     </x:row>
     <x:row r="4" ht="43" customHeight="1">
-      <x:c r="A4" s="31" t="str">
+      <x:c r="A4" s="32" t="str">
         <x:v>H1 cash generation after PP&amp;E was positive; acquisitions and payouts competed for it. Net borrowing contributed to cash growth. Future funding coverage: Unavailable.</x:v>
       </x:c>
-      <x:c r="B4" s="31"/>
-      <x:c r="C4" s="31"/>
-      <x:c r="D4" s="31"/>
-      <x:c r="E4" s="31"/>
-      <x:c r="F4" s="31"/>
-      <x:c r="G4" s="31"/>
+      <x:c r="B4" s="32"/>
+      <x:c r="C4" s="32"/>
+      <x:c r="D4" s="32"/>
+      <x:c r="E4" s="32"/>
+      <x:c r="F4" s="32"/>
+      <x:c r="G4" s="32"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="31"/>
-      <x:c r="B5" s="31"/>
-      <x:c r="C5" s="31"/>
-      <x:c r="D5" s="31"/>
-      <x:c r="E5" s="31"/>
-      <x:c r="F5" s="31"/>
-      <x:c r="G5" s="31"/>
+      <x:c r="A5" s="32"/>
+      <x:c r="B5" s="32"/>
+      <x:c r="C5" s="32"/>
+      <x:c r="D5" s="32"/>
+      <x:c r="E5" s="32"/>
+      <x:c r="F5" s="32"/>
+      <x:c r="G5" s="32"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="78" t="str">
+      <x:c r="A6" s="83" t="str">
         <x:v>Half-year cash build</x:v>
       </x:c>
-      <x:c r="B6" s="79" t="str">
+      <x:c r="B6" s="84" t="str">
         <x:v>USD millions</x:v>
       </x:c>
-      <x:c r="C6" s="79" t="str">
+      <x:c r="C6" s="84" t="str">
         <x:v>Period / basis</x:v>
       </x:c>
-      <x:c r="D6" s="80" t="str">
+      <x:c r="D6" s="85" t="str">
         <x:v>Interpretation</x:v>
       </x:c>
-      <x:c r="E6" s="31"/>
-      <x:c r="F6" s="31"/>
-      <x:c r="G6" s="31"/>
+      <x:c r="E6" s="32"/>
+      <x:c r="F6" s="32"/>
+      <x:c r="G6" s="32"/>
     </x:row>
     <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="52" t="str">
+      <x:c r="A7" s="57" t="str">
         <x:v>Opening cash</x:v>
       </x:c>
-      <x:c r="B7" s="53" t="n">
+      <x:c r="B7" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B37),'Data'!B37,NA())</x:f>
         <x:v>7268000000</x:v>
       </x:c>
-      <x:c r="C7" s="95" t="str">
+      <x:c r="C7" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D7" s="55" t="str">
+      <x:c r="D7" s="60" t="str">
         <x:v>Excludes restricted cash. Not an additional half-year flow.</x:v>
       </x:c>
-      <x:c r="E7" s="31"/>
-      <x:c r="F7" s="31"/>
-      <x:c r="G7" s="31"/>
+      <x:c r="E7" s="32"/>
+      <x:c r="F7" s="32"/>
+      <x:c r="G7" s="32"/>
     </x:row>
     <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="52" t="str">
+      <x:c r="A8" s="57" t="str">
         <x:v>Operating cash flow</x:v>
       </x:c>
-      <x:c r="B8" s="53" t="n">
+      <x:c r="B8" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B21),'Data'!B21,NA())</x:f>
         <x:v>16023000000</x:v>
       </x:c>
-      <x:c r="C8" s="95" t="str">
+      <x:c r="C8" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D8" s="55" t="str">
+      <x:c r="D8" s="60" t="str">
         <x:v>Historical; includes working capital. Future recurrence not established.</x:v>
       </x:c>
-      <x:c r="E8" s="31"/>
-      <x:c r="F8" s="31"/>
-      <x:c r="G8" s="31"/>
+      <x:c r="E8" s="32"/>
+      <x:c r="F8" s="32"/>
+      <x:c r="G8" s="32"/>
     </x:row>
     <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="52" t="str">
+      <x:c r="A9" s="57" t="str">
         <x:v>Cash PP&amp;E spending</x:v>
       </x:c>
-      <x:c r="B9" s="53" t="n">
+      <x:c r="B9" s="58" t="n">
         <x:f>-IF(ISNUMBER('Data'!B22),'Data'!B22,NA())</x:f>
         <x:v>-5259000000</x:v>
       </x:c>
-      <x:c r="C9" s="95" t="str">
+      <x:c r="C9" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D9" s="55" t="str">
+      <x:c r="D9" s="60" t="str">
         <x:v>Cash use, not a forecast of manufacturing investment.</x:v>
       </x:c>
-      <x:c r="E9" s="31"/>
-      <x:c r="F9" s="31"/>
-      <x:c r="G9" s="31"/>
+      <x:c r="E9" s="32"/>
+      <x:c r="F9" s="32"/>
+      <x:c r="G9" s="32"/>
     </x:row>
     <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="52" t="str">
+      <x:c r="A10" s="57" t="str">
         <x:v>Cash acquisitions, net of cash acquired</x:v>
       </x:c>
-      <x:c r="B10" s="53" t="n">
+      <x:c r="B10" s="58" t="n">
         <x:f>-IF(ISNUMBER('Data'!B25),'Data'!B25,NA())</x:f>
         <x:v>-9805000000</x:v>
       </x:c>
-      <x:c r="C10" s="95" t="str">
+      <x:c r="C10" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D10" s="55" t="str">
+      <x:c r="D10" s="60" t="str">
         <x:v>Not added again to the approximately $13.3B business-development disclosure.</x:v>
       </x:c>
-      <x:c r="E10" s="31"/>
-      <x:c r="F10" s="31"/>
-      <x:c r="G10" s="31"/>
+      <x:c r="E10" s="32"/>
+      <x:c r="F10" s="32"/>
+      <x:c r="G10" s="32"/>
     </x:row>
     <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="52" t="str">
+      <x:c r="A11" s="57" t="str">
         <x:v>Purchased in-process R&amp;D</x:v>
       </x:c>
-      <x:c r="B11" s="53" t="n">
+      <x:c r="B11" s="58" t="n">
         <x:f>-IF(ISNUMBER('Data'!B24),'Data'!B24,NA())</x:f>
         <x:v>-3486000000</x:v>
       </x:c>
-      <x:c r="C11" s="95" t="str">
+      <x:c r="C11" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D11" s="55" t="str">
+      <x:c r="D11" s="60" t="str">
         <x:v>Separate cash use; not all acquisition-related expense is cash.</x:v>
       </x:c>
-      <x:c r="E11" s="31"/>
-      <x:c r="F11" s="31"/>
-      <x:c r="G11" s="31"/>
+      <x:c r="E11" s="32"/>
+      <x:c r="F11" s="32"/>
+      <x:c r="G11" s="32"/>
     </x:row>
     <x:row r="12" ht="43" customHeight="1">
-      <x:c r="A12" s="52" t="str">
+      <x:c r="A12" s="57" t="str">
         <x:v>Cash dividends</x:v>
       </x:c>
-      <x:c r="B12" s="53" t="n">
+      <x:c r="B12" s="58" t="n">
         <x:f>-IF(ISNUMBER('Data'!B28),'Data'!B28,NA())</x:f>
         <x:v>-3094000000</x:v>
       </x:c>
-      <x:c r="C12" s="95" t="str">
+      <x:c r="C12" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D12" s="55" t="str">
+      <x:c r="D12" s="60" t="str">
         <x:v>Competes with repayments for cash.</x:v>
       </x:c>
-      <x:c r="E12" s="31"/>
-      <x:c r="F12" s="31"/>
-      <x:c r="G12" s="31"/>
+      <x:c r="E12" s="32"/>
+      <x:c r="F12" s="32"/>
+      <x:c r="G12" s="32"/>
     </x:row>
     <x:row r="13" ht="43" customHeight="1">
-      <x:c r="A13" s="52" t="str">
+      <x:c r="A13" s="57" t="str">
         <x:v>Share repurchases</x:v>
       </x:c>
-      <x:c r="B13" s="53" t="n">
+      <x:c r="B13" s="58" t="n">
         <x:f>-IF(ISNUMBER('Data'!B32),'Data'!B32,NA())</x:f>
         <x:v>-3957000000</x:v>
       </x:c>
-      <x:c r="C13" s="95" t="str">
+      <x:c r="C13" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D13" s="55" t="str">
+      <x:c r="D13" s="60" t="str">
         <x:v>Historical spending; no future pace assumed.</x:v>
       </x:c>
-      <x:c r="E13" s="31"/>
-      <x:c r="F13" s="31"/>
-      <x:c r="G13" s="31"/>
+      <x:c r="E13" s="32"/>
+      <x:c r="F13" s="32"/>
+      <x:c r="G13" s="32"/>
     </x:row>
     <x:row r="14" ht="43" customHeight="1">
-      <x:c r="A14" s="52" t="str">
+      <x:c r="A14" s="57" t="str">
         <x:v>Short-term borrowing, net</x:v>
       </x:c>
-      <x:c r="B14" s="53" t="n">
+      <x:c r="B14" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B29),'Data'!B29,NA())</x:f>
         <x:v>5284000000</x:v>
       </x:c>
-      <x:c r="C14" s="95" t="str">
+      <x:c r="C14" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D14" s="55" t="str">
+      <x:c r="D14" s="60" t="str">
         <x:v>Financing inflow, not recurring operating generation.</x:v>
       </x:c>
-      <x:c r="E14" s="31"/>
-      <x:c r="F14" s="31"/>
-      <x:c r="G14" s="31"/>
+      <x:c r="E14" s="32"/>
+      <x:c r="F14" s="32"/>
+      <x:c r="G14" s="32"/>
     </x:row>
     <x:row r="15" ht="43" customHeight="1">
-      <x:c r="A15" s="52" t="str">
+      <x:c r="A15" s="57" t="str">
         <x:v>Long-term debt proceeds, net</x:v>
       </x:c>
-      <x:c r="B15" s="53" t="n">
+      <x:c r="B15" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B30),'Data'!B30,NA())</x:f>
         <x:v>8941000000</x:v>
       </x:c>
-      <x:c r="C15" s="95" t="str">
+      <x:c r="C15" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D15" s="55" t="str">
+      <x:c r="D15" s="60" t="str">
         <x:v>May $9B issue is already included here; net cash differs from face amount.</x:v>
       </x:c>
-      <x:c r="E15" s="31"/>
-      <x:c r="F15" s="31"/>
-      <x:c r="G15" s="31"/>
+      <x:c r="E15" s="32"/>
+      <x:c r="F15" s="32"/>
+      <x:c r="G15" s="32"/>
     </x:row>
     <x:row r="16" ht="43" customHeight="1">
-      <x:c r="A16" s="52" t="str">
+      <x:c r="A16" s="57" t="str">
         <x:v>Long-term debt repaid</x:v>
       </x:c>
-      <x:c r="B16" s="53" t="n">
+      <x:c r="B16" s="58" t="n">
         <x:f>-IF(ISNUMBER('Data'!B31),'Data'!B31,NA())</x:f>
         <x:v>-1623000000</x:v>
       </x:c>
-      <x:c r="C16" s="95" t="str">
+      <x:c r="C16" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D16" s="55" t="str">
+      <x:c r="D16" s="60" t="str">
         <x:v>Already paid; not a future maturity schedule.</x:v>
       </x:c>
-      <x:c r="E16" s="31"/>
-      <x:c r="F16" s="31"/>
-      <x:c r="G16" s="31"/>
+      <x:c r="E16" s="32"/>
+      <x:c r="F16" s="32"/>
+      <x:c r="G16" s="32"/>
     </x:row>
     <x:row r="17" ht="43" customHeight="1">
-      <x:c r="A17" s="52" t="str">
+      <x:c r="A17" s="57" t="str">
         <x:v>Other investing and financing</x:v>
       </x:c>
-      <x:c r="B17" s="53" t="n">
+      <x:c r="B17" s="58" t="n">
         <x:f>-IF(ISNUMBER('Data'!B23),'Data'!B23,NA())-IF(ISNUMBER('Data'!B26),'Data'!B26,NA())+IF(ISNUMBER('Data'!B33),'Data'!B33,NA())</x:f>
         <x:v>-1357000000</x:v>
       </x:c>
-      <x:c r="C17" s="95" t="str">
+      <x:c r="C17" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D17" s="55" t="str">
+      <x:c r="D17" s="60" t="str">
         <x:v>Investment purchases, other investing and other financing.</x:v>
       </x:c>
-      <x:c r="E17" s="31"/>
-      <x:c r="F17" s="31"/>
-      <x:c r="G17" s="31"/>
+      <x:c r="E17" s="32"/>
+      <x:c r="F17" s="32"/>
+      <x:c r="G17" s="32"/>
     </x:row>
     <x:row r="18" ht="43" customHeight="1">
-      <x:c r="A18" s="52" t="str">
+      <x:c r="A18" s="57" t="str">
         <x:v>Exchange-rate effect</x:v>
       </x:c>
-      <x:c r="B18" s="53" t="n">
+      <x:c r="B18" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B35),'Data'!B35,NA())</x:f>
         <x:v>15000000</x:v>
       </x:c>
-      <x:c r="C18" s="95" t="str">
+      <x:c r="C18" s="100" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D18" s="55" t="str">
+      <x:c r="D18" s="60" t="str">
         <x:v>Reconciles the cash balance.</x:v>
       </x:c>
-      <x:c r="E18" s="31"/>
-      <x:c r="F18" s="31"/>
-      <x:c r="G18" s="31"/>
+      <x:c r="E18" s="32"/>
+      <x:c r="F18" s="32"/>
+      <x:c r="G18" s="32"/>
     </x:row>
     <x:row r="19" ht="43" customHeight="1">
-      <x:c r="A19" s="85" t="str">
+      <x:c r="A19" s="90" t="str">
         <x:v>Calculated cash change</x:v>
       </x:c>
-      <x:c r="B19" s="90" t="n">
+      <x:c r="B19" s="95" t="n">
         <x:f>SUM(B8:B18)</x:f>
         <x:v>1682000000</x:v>
       </x:c>
-      <x:c r="C19" s="105" t="str">
+      <x:c r="C19" s="110" t="str">
         <x:v>January–June 2026</x:v>
       </x:c>
-      <x:c r="D19" s="88" t="str">
+      <x:c r="D19" s="93" t="str">
         <x:v>All signed flows counted once.</x:v>
       </x:c>
-      <x:c r="E19" s="31"/>
-      <x:c r="F19" s="31"/>
-      <x:c r="G19" s="31"/>
+      <x:c r="E19" s="32"/>
+      <x:c r="F19" s="32"/>
+      <x:c r="G19" s="32"/>
     </x:row>
     <x:row r="20" ht="43" customHeight="1">
-      <x:c r="A20" s="85" t="str">
+      <x:c r="A20" s="90" t="str">
         <x:v>Calculated closing cash</x:v>
       </x:c>
-      <x:c r="B20" s="90" t="n">
+      <x:c r="B20" s="95" t="n">
         <x:f>B7+B19</x:f>
         <x:v>8950000000</x:v>
       </x:c>
-      <x:c r="C20" s="105" t="str">
+      <x:c r="C20" s="110" t="str">
         <x:v>June 30, 2026</x:v>
       </x:c>
-      <x:c r="D20" s="88" t="str">
+      <x:c r="D20" s="93" t="str">
         <x:v>Opening cash plus change.</x:v>
       </x:c>
-      <x:c r="E20" s="31"/>
-      <x:c r="F20" s="31"/>
-      <x:c r="G20" s="31"/>
+      <x:c r="E20" s="32"/>
+      <x:c r="F20" s="32"/>
+      <x:c r="G20" s="32"/>
     </x:row>
     <x:row r="21" ht="43" customHeight="1">
-      <x:c r="A21" s="52" t="str">
+      <x:c r="A21" s="57" t="str">
         <x:v>Reported closing cash</x:v>
       </x:c>
-      <x:c r="B21" s="53" t="n">
+      <x:c r="B21" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B38),'Data'!B38,NA())</x:f>
         <x:v>8950000000</x:v>
       </x:c>
-      <x:c r="C21" s="95" t="str">
+      <x:c r="C21" s="100" t="str">
         <x:v>June 30, 2026</x:v>
       </x:c>
-      <x:c r="D21" s="55" t="str">
+      <x:c r="D21" s="60" t="str">
         <x:v>Not a current cash balance after subsequent payments.</x:v>
       </x:c>
-      <x:c r="E21" s="31"/>
-      <x:c r="F21" s="31"/>
-      <x:c r="G21" s="31"/>
+      <x:c r="E21" s="32"/>
+      <x:c r="F21" s="32"/>
+      <x:c r="G21" s="32"/>
     </x:row>
     <x:row r="22" ht="43" customHeight="1">
-      <x:c r="A22" s="85" t="str">
+      <x:c r="A22" s="90" t="str">
         <x:v>Cash reconciliation difference</x:v>
       </x:c>
-      <x:c r="B22" s="90" t="n">
+      <x:c r="B22" s="95" t="n">
         <x:f>B20-B21</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C22" s="105" t="str">
+      <x:c r="C22" s="110" t="str">
         <x:v>Zero = reconciled</x:v>
       </x:c>
-      <x:c r="D22" s="88" t="str">
+      <x:c r="D22" s="93" t="str">
         <x:v>No cash forecast or unrestricted-funding total.</x:v>
       </x:c>
-      <x:c r="E22" s="31"/>
-      <x:c r="F22" s="31"/>
-      <x:c r="G22" s="31"/>
+      <x:c r="E22" s="32"/>
+      <x:c r="F22" s="32"/>
+      <x:c r="G22" s="32"/>
     </x:row>
     <x:row r="23" ht="43" customHeight="1">
-      <x:c r="A23" s="85" t="str">
+      <x:c r="A23" s="90" t="str">
         <x:v>OCF less cash PP&amp;E spending</x:v>
       </x:c>
-      <x:c r="B23" s="90" t="n">
+      <x:c r="B23" s="95" t="n">
         <x:f>B8+B9</x:f>
         <x:v>10764000000</x:v>
       </x:c>
-      <x:c r="C23" s="105" t="str">
+      <x:c r="C23" s="110" t="str">
         <x:v>Historical H1 only</x:v>
       </x:c>
-      <x:c r="D23" s="88" t="str">
+      <x:c r="D23" s="93" t="str">
         <x:v>Excludes acquisitions, payouts and other cash uses.</x:v>
       </x:c>
-      <x:c r="E23" s="31"/>
-      <x:c r="F23" s="31"/>
-      <x:c r="G23" s="31"/>
+      <x:c r="E23" s="32"/>
+      <x:c r="F23" s="32"/>
+      <x:c r="G23" s="32"/>
     </x:row>
     <x:row r="24" ht="43" customHeight="1">
-      <x:c r="A24" s="85" t="str">
+      <x:c r="A24" s="90" t="str">
         <x:v>Net borrowing cash flow</x:v>
       </x:c>
-      <x:c r="B24" s="90" t="n">
+      <x:c r="B24" s="95" t="n">
         <x:f>SUM(B14:B16)</x:f>
         <x:v>12602000000</x:v>
       </x:c>
-      <x:c r="C24" s="105" t="str">
+      <x:c r="C24" s="110" t="str">
         <x:v>Historical H1 only</x:v>
       </x:c>
-      <x:c r="D24" s="88" t="str">
+      <x:c r="D24" s="93" t="str">
         <x:v>Borrowing contributed to closing cash.</x:v>
       </x:c>
-      <x:c r="E24" s="31"/>
-      <x:c r="F24" s="31"/>
-      <x:c r="G24" s="31"/>
+      <x:c r="E24" s="32"/>
+      <x:c r="F24" s="32"/>
+      <x:c r="G24" s="32"/>
     </x:row>
     <x:row r="25" ht="43" customHeight="1">
-      <x:c r="A25" s="85" t="str">
+      <x:c r="A25" s="90" t="str">
         <x:v>Acquisitions + purchased IPR&amp;D</x:v>
       </x:c>
-      <x:c r="B25" s="90" t="n">
+      <x:c r="B25" s="95" t="n">
         <x:f>-SUM(B10:B11)</x:f>
         <x:v>13291000000</x:v>
       </x:c>
-      <x:c r="C25" s="105" t="str">
+      <x:c r="C25" s="110" t="str">
         <x:v>Historical H1 only</x:v>
       </x:c>
-      <x:c r="D25" s="88" t="str">
+      <x:c r="D25" s="93" t="str">
         <x:v>Approximately $13.3B, already spent.</x:v>
       </x:c>
-      <x:c r="E25" s="31"/>
-      <x:c r="F25" s="31"/>
-      <x:c r="G25" s="31"/>
+      <x:c r="E25" s="32"/>
+      <x:c r="F25" s="32"/>
+      <x:c r="G25" s="32"/>
     </x:row>
     <x:row r="26" ht="43" customHeight="1">
-      <x:c r="A26" s="110" t="str">
+      <x:c r="A26" s="115" t="str">
         <x:v>Dividends + buybacks</x:v>
       </x:c>
-      <x:c r="B26" s="114" t="n">
+      <x:c r="B26" s="119" t="n">
         <x:f>-SUM(B12:B13)</x:f>
         <x:v>7051000000</x:v>
       </x:c>
-      <x:c r="C26" s="112" t="str">
+      <x:c r="C26" s="117" t="str">
         <x:v>Historical H1 only</x:v>
       </x:c>
-      <x:c r="D26" s="113" t="str">
+      <x:c r="D26" s="118" t="str">
         <x:v>Not automatically recurring future obligations.</x:v>
       </x:c>
-      <x:c r="E26" s="31"/>
-      <x:c r="F26" s="31"/>
-      <x:c r="G26" s="31"/>
+      <x:c r="E26" s="32"/>
+      <x:c r="F26" s="32"/>
+      <x:c r="G26" s="32"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
-      <x:c r="A27" s="31"/>
-      <x:c r="B27" s="115"/>
-      <x:c r="C27" s="31"/>
-      <x:c r="D27" s="31"/>
-      <x:c r="E27" s="31"/>
-      <x:c r="F27" s="31" t="str">
+      <x:c r="A27" s="32"/>
+      <x:c r="B27" s="120"/>
+      <x:c r="C27" s="32"/>
+      <x:c r="D27" s="32"/>
+      <x:c r="E27" s="32"/>
+      <x:c r="F27" s="32" t="str">
         <x:v>H1 cash contribution</x:v>
       </x:c>
-      <x:c r="G27" s="31" t="str">
+      <x:c r="G27" s="32" t="str">
         <x:v>USD millions</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
-      <x:c r="A28" s="31"/>
-      <x:c r="B28" s="115"/>
-      <x:c r="C28" s="31"/>
-      <x:c r="D28" s="31"/>
-      <x:c r="E28" s="31"/>
-      <x:c r="F28" s="31" t="str">
+      <x:c r="A28" s="32"/>
+      <x:c r="B28" s="120"/>
+      <x:c r="C28" s="32"/>
+      <x:c r="D28" s="32"/>
+      <x:c r="E28" s="32"/>
+      <x:c r="F28" s="32" t="str">
         <x:v>Operating cash flow</x:v>
       </x:c>
-      <x:c r="G28" s="115" t="n">
+      <x:c r="G28" s="120" t="n">
         <x:f>B8</x:f>
         <x:v>16023000000</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
-      <x:c r="A29" s="78" t="str">
+      <x:c r="A29" s="83" t="str">
         <x:v>Credit capacity, dates kept separate</x:v>
       </x:c>
-      <x:c r="B29" s="116" t="str">
+      <x:c r="B29" s="121" t="str">
         <x:v>USD millions</x:v>
       </x:c>
-      <x:c r="C29" s="79" t="str">
+      <x:c r="C29" s="84" t="str">
         <x:v>Date / expiry</x:v>
       </x:c>
-      <x:c r="D29" s="80" t="str">
+      <x:c r="D29" s="85" t="str">
         <x:v>Availability limitation</x:v>
       </x:c>
-      <x:c r="E29" s="31"/>
-      <x:c r="F29" s="31" t="str">
+      <x:c r="E29" s="32"/>
+      <x:c r="F29" s="32" t="str">
         <x:v>Cash PP&amp;E spending</x:v>
       </x:c>
-      <x:c r="G29" s="115" t="n">
+      <x:c r="G29" s="120" t="n">
         <x:f>B9</x:f>
         <x:v>-5259000000</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="70" customHeight="1">
-      <x:c r="A30" s="52" t="str">
+      <x:c r="A30" s="57" t="str">
         <x:v>Unused committed facilities</x:v>
       </x:c>
-      <x:c r="B30" s="53" t="n">
+      <x:c r="B30" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B58),'Data'!B58,NA())</x:f>
         <x:v>10100000000</x:v>
       </x:c>
-      <x:c r="C30" s="95" t="str">
+      <x:c r="C30" s="100" t="str">
         <x:v>June 30, 2026</x:v>
       </x:c>
-      <x:c r="D30" s="55" t="str">
+      <x:c r="D30" s="60" t="str">
         <x:v>Reported unused, not cash or verified drawable. $10B supports CP and is not added again.</x:v>
       </x:c>
-      <x:c r="E30" s="31"/>
-      <x:c r="F30" s="31" t="str">
+      <x:c r="E30" s="32"/>
+      <x:c r="F30" s="32" t="str">
         <x:v>Acquisitions + purchased IPR&amp;D</x:v>
       </x:c>
-      <x:c r="G30" s="115" t="n">
+      <x:c r="G30" s="120" t="n">
         <x:f>-B25</x:f>
         <x:v>-13291000000</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="70" customHeight="1">
-      <x:c r="A31" s="52" t="str">
+      <x:c r="A31" s="57" t="str">
         <x:v>364-day facility expires August 2026</x:v>
       </x:c>
-      <x:c r="B31" s="53" t="n">
+      <x:c r="B31" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B56),'Data'!B56,NA())</x:f>
         <x:v>6000000000</x:v>
       </x:c>
-      <x:c r="C31" s="95" t="str">
+      <x:c r="C31" s="100" t="str">
         <x:v>August 2026 expiry</x:v>
       </x:c>
-      <x:c r="D31" s="55" t="str">
+      <x:c r="D31" s="60" t="str">
         <x:v>Annual terms: 364-day facility. Exact expiry day and renewal Unavailable; do not carry June capacity past expiry.</x:v>
       </x:c>
-      <x:c r="E31" s="31"/>
-      <x:c r="F31" s="31" t="str">
+      <x:c r="E31" s="32"/>
+      <x:c r="F31" s="32" t="str">
         <x:v>Dividends + buybacks</x:v>
       </x:c>
-      <x:c r="G31" s="115" t="n">
+      <x:c r="G31" s="120" t="n">
         <x:f>-B26</x:f>
         <x:v>-7051000000</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="70" customHeight="1">
-      <x:c r="A32" s="52" t="str">
+      <x:c r="A32" s="57" t="str">
         <x:v>Facility expires December 2029</x:v>
       </x:c>
-      <x:c r="B32" s="53" t="n">
+      <x:c r="B32" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B57),'Data'!B57,NA())</x:f>
         <x:v>4000000000</x:v>
       </x:c>
-      <x:c r="C32" s="95" t="str">
+      <x:c r="C32" s="100" t="str">
         <x:v>December 2029 expiry</x:v>
       </x:c>
-      <x:c r="D32" s="55" t="str">
+      <x:c r="D32" s="60" t="str">
         <x:v>Annual terms only. Exact day, June facility composition, contract conditions and current draws Unavailable.</x:v>
       </x:c>
-      <x:c r="E32" s="31"/>
-      <x:c r="F32" s="31" t="str">
+      <x:c r="E32" s="32"/>
+      <x:c r="F32" s="32" t="str">
         <x:v>Net borrowing</x:v>
       </x:c>
-      <x:c r="G32" s="115" t="n">
+      <x:c r="G32" s="120" t="n">
         <x:f>B24</x:f>
         <x:v>12602000000</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="70" customHeight="1">
-      <x:c r="A33" s="52"/>
-      <x:c r="B33" s="117"/>
-      <x:c r="C33" s="95"/>
-      <x:c r="D33" s="55"/>
-      <x:c r="E33" s="31"/>
-      <x:c r="F33" s="31" t="str">
+      <x:c r="A33" s="57"/>
+      <x:c r="B33" s="122"/>
+      <x:c r="C33" s="100"/>
+      <x:c r="D33" s="60"/>
+      <x:c r="E33" s="32"/>
+      <x:c r="F33" s="32" t="str">
         <x:v>Other cash flows including FX</x:v>
       </x:c>
-      <x:c r="G33" s="115" t="n">
+      <x:c r="G33" s="120" t="n">
         <x:f>B17+B18</x:f>
         <x:v>-1342000000</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="70" customHeight="1">
-      <x:c r="A34" s="52" t="str">
+      <x:c r="A34" s="57" t="str">
         <x:v>Drawable credit</x:v>
       </x:c>
-      <x:c r="B34" s="117" t="str">
+      <x:c r="B34" s="122" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
-      <x:c r="C34" s="95" t="str">
+      <x:c r="C34" s="100" t="str">
         <x:v>No saved credit agreement</x:v>
       </x:c>
-      <x:c r="D34" s="55" t="str">
+      <x:c r="D34" s="60" t="str">
         <x:v>Draw conditions, covenants, permitted uses and post-August renewal not established. Cash + commitments is not a verified funding total.</x:v>
       </x:c>
-      <x:c r="E34" s="31"/>
-      <x:c r="F34" s="31"/>
-      <x:c r="G34" s="31"/>
+      <x:c r="E34" s="32"/>
+      <x:c r="F34" s="32"/>
+      <x:c r="G34" s="32"/>
     </x:row>
     <x:row r="35" ht="70" customHeight="1">
-      <x:c r="A35" s="59" t="str">
+      <x:c r="A35" s="64" t="str">
         <x:v>December unused capacity</x:v>
       </x:c>
-      <x:c r="B35" s="118" t="n">
+      <x:c r="B35" s="123" t="n">
         <x:f>IF(ISNUMBER('Data'!B55),'Data'!B55,NA())</x:f>
         <x:v>10100000000</x:v>
       </x:c>
-      <x:c r="C35" s="97" t="str">
+      <x:c r="C35" s="102" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D35" s="62" t="str">
+      <x:c r="D35" s="67" t="str">
         <x:v>Annual unused total is $10.1B, primarily the $6B and $4B facilities. The residual $0.1B is not separately described.</x:v>
       </x:c>
-      <x:c r="E35" s="31"/>
-      <x:c r="F35" s="31"/>
-      <x:c r="G35" s="31"/>
+      <x:c r="E35" s="32"/>
+      <x:c r="F35" s="32"/>
+      <x:c r="G35" s="32"/>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
-      <x:c r="A36" s="31"/>
-      <x:c r="B36" s="115"/>
-      <x:c r="C36" s="31"/>
-      <x:c r="D36" s="31"/>
-      <x:c r="E36" s="31"/>
-      <x:c r="F36" s="31"/>
-      <x:c r="G36" s="31"/>
+      <x:c r="A36" s="32"/>
+      <x:c r="B36" s="120"/>
+      <x:c r="C36" s="32"/>
+      <x:c r="D36" s="32"/>
+      <x:c r="E36" s="32"/>
+      <x:c r="F36" s="32"/>
+      <x:c r="G36" s="32"/>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
-      <x:c r="A37" s="31"/>
-      <x:c r="B37" s="115"/>
-      <x:c r="C37" s="31"/>
-      <x:c r="D37" s="31"/>
-      <x:c r="E37" s="31"/>
-      <x:c r="F37" s="31"/>
-      <x:c r="G37" s="31"/>
+      <x:c r="A37" s="32"/>
+      <x:c r="B37" s="120"/>
+      <x:c r="C37" s="32"/>
+      <x:c r="D37" s="32"/>
+      <x:c r="E37" s="32"/>
+      <x:c r="F37" s="32"/>
+      <x:c r="G37" s="32"/>
     </x:row>
     <x:row r="38" ht="30" customHeight="1">
-      <x:c r="A38" s="78" t="str">
+      <x:c r="A38" s="83" t="str">
         <x:v>Acquisitions / manufacturing</x:v>
       </x:c>
-      <x:c r="B38" s="116" t="str">
+      <x:c r="B38" s="121" t="str">
         <x:v>USD millions</x:v>
       </x:c>
-      <x:c r="C38" s="79" t="str">
+      <x:c r="C38" s="84" t="str">
         <x:v>Date and classification</x:v>
       </x:c>
-      <x:c r="D38" s="80" t="str">
+      <x:c r="D38" s="85" t="str">
         <x:v>Timing, overlap and funding limitation</x:v>
       </x:c>
-      <x:c r="E38" s="31"/>
-      <x:c r="F38" s="31"/>
-      <x:c r="G38" s="31"/>
+      <x:c r="E38" s="32"/>
+      <x:c r="F38" s="32"/>
+      <x:c r="G38" s="32"/>
     </x:row>
     <x:row r="39" ht="96" customHeight="1">
-      <x:c r="A39" s="52" t="str">
+      <x:c r="A39" s="57" t="str">
         <x:v>Pending AtaiBeckley acquisition</x:v>
       </x:c>
-      <x:c r="B39" s="53" t="n">
+      <x:c r="B39" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B60),'Data'!B60,NA())</x:f>
         <x:v>2800000000</x:v>
       </x:c>
-      <x:c r="C39" s="95" t="str">
+      <x:c r="C39" s="100" t="str">
         <x:v>Disclosed August 5, 2026 · Approximate conditional closing payment</x:v>
       </x:c>
-      <x:c r="D39" s="55" t="str">
+      <x:c r="D39" s="60" t="str">
         <x:v>Payable at closing, subject to conditions. Disclosed after quarter end; closing date, completion and funding allocation are not established here.</x:v>
       </x:c>
-      <x:c r="E39" s="31"/>
-      <x:c r="F39" s="31"/>
-      <x:c r="G39" s="31"/>
+      <x:c r="E39" s="32"/>
+      <x:c r="F39" s="32"/>
+      <x:c r="G39" s="32"/>
     </x:row>
     <x:row r="40" ht="96" customHeight="1">
-      <x:c r="A40" s="52" t="str">
+      <x:c r="A40" s="57" t="str">
         <x:v>Unpaid Kelonia cash consideration</x:v>
       </x:c>
-      <x:c r="B40" s="53" t="n">
+      <x:c r="B40" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B61),'Data'!B61,NA())</x:f>
         <x:v>208000000</x:v>
       </x:c>
-      <x:c r="C40" s="95" t="str">
+      <x:c r="C40" s="100" t="str">
         <x:v>2026-06-30 · Unpaid acquisition consideration</x:v>
       </x:c>
-      <x:c r="D40" s="55" t="str">
+      <x:c r="D40" s="60" t="str">
         <x:v>Payment date Unavailable. Separate from cash already paid and from contingent-consideration fair value.</x:v>
       </x:c>
-      <x:c r="E40" s="31"/>
-      <x:c r="F40" s="31"/>
-      <x:c r="G40" s="31"/>
+      <x:c r="E40" s="32"/>
+      <x:c r="F40" s="32"/>
+      <x:c r="G40" s="32"/>
     </x:row>
     <x:row r="41" ht="96" customHeight="1">
-      <x:c r="A41" s="52" t="str">
+      <x:c r="A41" s="57" t="str">
         <x:v>Unpaid Centessa cash consideration</x:v>
       </x:c>
-      <x:c r="B41" s="53" t="n">
+      <x:c r="B41" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B62),'Data'!B62,NA())</x:f>
         <x:v>88000000</x:v>
       </x:c>
-      <x:c r="C41" s="95" t="str">
+      <x:c r="C41" s="100" t="str">
         <x:v>2026-06-30 · Unpaid acquisition consideration</x:v>
       </x:c>
-      <x:c r="D41" s="55" t="str">
+      <x:c r="D41" s="60" t="str">
         <x:v>Payment date Unavailable. Do not add to paid acquisition cash or contingent-consideration fair value.</x:v>
       </x:c>
-      <x:c r="E41" s="31"/>
-      <x:c r="F41" s="31"/>
-      <x:c r="G41" s="31"/>
+      <x:c r="E41" s="32"/>
+      <x:c r="F41" s="32"/>
+      <x:c r="G41" s="32"/>
     </x:row>
     <x:row r="42" ht="96" customHeight="1">
-      <x:c r="A42" s="52" t="str">
+      <x:c r="A42" s="57" t="str">
         <x:v>July infectious-disease acquisitions: cash paid</x:v>
       </x:c>
-      <x:c r="B42" s="53" t="n">
+      <x:c r="B42" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B63),'Data'!B63,NA())</x:f>
         <x:v>2000000000</x:v>
       </x:c>
-      <x:c r="C42" s="95" t="str">
+      <x:c r="C42" s="100" t="str">
         <x:v>July 2026 · Approximate subsequent cash use</x:v>
       </x:c>
-      <x:c r="D42" s="55" t="str">
+      <x:c r="D42" s="60" t="str">
         <x:v>Already paid after June. Other July cash flows are unknown; June cash less this payment is not a current cash balance.</x:v>
       </x:c>
-      <x:c r="E42" s="31"/>
-      <x:c r="F42" s="31"/>
-      <x:c r="G42" s="31"/>
+      <x:c r="E42" s="32"/>
+      <x:c r="F42" s="32"/>
+      <x:c r="G42" s="32"/>
     </x:row>
     <x:row r="43" ht="96" customHeight="1">
-      <x:c r="A43" s="52" t="str">
+      <x:c r="A43" s="57" t="str">
         <x:v>July acquisitions: aggregate consideration up to</x:v>
       </x:c>
-      <x:c r="B43" s="53" t="n">
+      <x:c r="B43" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B64),'Data'!B64,NA())</x:f>
         <x:v>3900000000</x:v>
       </x:c>
-      <x:c r="C43" s="95" t="str">
+      <x:c r="C43" s="100" t="str">
         <x:v>July 2026 · Conditional aggregate ceiling</x:v>
       </x:c>
-      <x:c r="D43" s="55" t="str">
+      <x:c r="D43" s="60" t="str">
         <x:v>Includes upfront cash and potential clinical, regulatory and commercial milestones. Includes the approximately $2B paid; do not add the two amounts or infer a precise remaining cash bill.</x:v>
       </x:c>
-      <x:c r="E43" s="31"/>
-      <x:c r="F43" s="31"/>
-      <x:c r="G43" s="31"/>
+      <x:c r="E43" s="32"/>
+      <x:c r="F43" s="32"/>
+      <x:c r="G43" s="32"/>
     </x:row>
     <x:row r="44" ht="96" customHeight="1">
-      <x:c r="A44" s="52" t="str">
+      <x:c r="A44" s="57" t="str">
         <x:v>Unfunded venture fund commitments</x:v>
       </x:c>
-      <x:c r="B44" s="53" t="n">
+      <x:c r="B44" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B65),'Data'!B65,NA())</x:f>
         <x:v>806000000</x:v>
       </x:c>
-      <x:c r="C44" s="95" t="str">
+      <x:c r="C44" s="100" t="str">
         <x:v>2026-06-30 · Approximate investment commitment</x:v>
       </x:c>
-      <x:c r="D44" s="55" t="str">
+      <x:c r="D44" s="60" t="str">
         <x:v>Expected to be paid over up to ten years. Individual capital-call dates are Unavailable.</x:v>
       </x:c>
-      <x:c r="E44" s="31"/>
-      <x:c r="F44" s="31"/>
-      <x:c r="G44" s="31"/>
+      <x:c r="E44" s="32"/>
+      <x:c r="F44" s="32"/>
+      <x:c r="G44" s="32"/>
     </x:row>
     <x:row r="45" ht="96" customHeight="1">
-      <x:c r="A45" s="52" t="str">
+      <x:c r="A45" s="57" t="str">
         <x:v>Development-medicine supply arrangements: up to</x:v>
       </x:c>
-      <x:c r="B45" s="53" t="n">
+      <x:c r="B45" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B66),'Data'!B66,NA())</x:f>
         <x:v>10000000000</x:v>
       </x:c>
-      <x:c r="C45" s="95" t="str">
+      <x:c r="C45" s="100" t="str">
         <x:v>2025-12-31 · Approximate conditional purchase shortfall ceiling</x:v>
       </x:c>
-      <x:c r="D45" s="55" t="str">
+      <x:c r="D45" s="60" t="str">
         <x:v>Payments if specified purchases are not met under executed manufacturing and supply agreements; durations generally up to eight years. Not an unconditional $10B bill. Updated June ceiling, annual payments and overlap with other spending are Unavailable.</x:v>
       </x:c>
-      <x:c r="E45" s="31"/>
-      <x:c r="F45" s="31"/>
-      <x:c r="G45" s="31"/>
+      <x:c r="E45" s="32"/>
+      <x:c r="F45" s="32"/>
+      <x:c r="G45" s="32"/>
     </x:row>
     <x:row r="46" ht="96" customHeight="1">
-      <x:c r="A46" s="59" t="str">
+      <x:c r="A46" s="64" t="str">
         <x:v>Additional Indiana manufacturing investment</x:v>
       </x:c>
-      <x:c r="B46" s="118" t="n">
+      <x:c r="B46" s="123" t="n">
         <x:f>IF(ISNUMBER('Data'!B67),'Data'!B67,NA())</x:f>
         <x:v>4500000000</x:v>
       </x:c>
-      <x:c r="C46" s="97" t="str">
+      <x:c r="C46" s="102" t="str">
         <x:v>Announced August 5, 2026 · Announced investment commitment</x:v>
       </x:c>
-      <x:c r="D46" s="62" t="str">
+      <x:c r="D46" s="67" t="str">
         <x:v>Release says committed an additional $4.5B. Contractual payment schedule, spending to date and overlap with capex or supply commitments are not established by this release. Not added to debt or the $10B ceiling.</x:v>
       </x:c>
-      <x:c r="E46" s="31"/>
-      <x:c r="F46" s="31"/>
-      <x:c r="G46" s="31"/>
+      <x:c r="E46" s="32"/>
+      <x:c r="F46" s="32"/>
+      <x:c r="G46" s="32"/>
     </x:row>
     <x:row r="47" ht="30" customHeight="1">
-      <x:c r="A47" s="31"/>
-      <x:c r="B47" s="115"/>
-      <x:c r="C47" s="31"/>
-      <x:c r="D47" s="31"/>
-      <x:c r="E47" s="31"/>
-      <x:c r="F47" s="31"/>
-      <x:c r="G47" s="31"/>
+      <x:c r="A47" s="32"/>
+      <x:c r="B47" s="120"/>
+      <x:c r="C47" s="32"/>
+      <x:c r="D47" s="32"/>
+      <x:c r="E47" s="32"/>
+      <x:c r="F47" s="32"/>
+      <x:c r="G47" s="32"/>
     </x:row>
     <x:row r="48" ht="68" customHeight="1">
-      <x:c r="A48" s="49" t="str">
+      <x:c r="A48" s="54" t="str">
         <x:v>Contingent consideration fair value</x:v>
       </x:c>
-      <x:c r="B48" s="119" t="n">
+      <x:c r="B48" s="124" t="n">
         <x:f>IF(ISNUMBER('Data'!B41),'Data'!B41,NA())+IF(ISNUMBER('Data'!B42),'Data'!B42,NA())</x:f>
         <x:v>2518000000</x:v>
       </x:c>
-      <x:c r="C48" s="50" t="str">
+      <x:c r="C48" s="55" t="str">
         <x:v>June 30, 2026</x:v>
       </x:c>
-      <x:c r="D48" s="51" t="str">
+      <x:c r="D48" s="56" t="str">
         <x:v>Current $814M + noncurrent $1,704M. Valuation, not dated payment or contractual maximum. Not added to acquisition amounts above.</x:v>
       </x:c>
-      <x:c r="E48" s="31"/>
-      <x:c r="F48" s="31"/>
-      <x:c r="G48" s="31"/>
+      <x:c r="E48" s="32"/>
+      <x:c r="F48" s="32"/>
+      <x:c r="G48" s="32"/>
     </x:row>
     <x:row r="49" ht="68" customHeight="1">
-      <x:c r="A49" s="52" t="str">
+      <x:c r="A49" s="57" t="str">
         <x:v>Future funding coverage</x:v>
       </x:c>
-      <x:c r="B49" s="117" t="str">
+      <x:c r="B49" s="122" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
-      <x:c r="C49" s="95" t="str">
+      <x:c r="C49" s="100" t="str">
         <x:v>Each future obligation</x:v>
       </x:c>
-      <x:c r="D49" s="55" t="str">
+      <x:c r="D49" s="60" t="str">
         <x:v>Future principal dates, future cash generation, payment dates and drawable credit not all established. No coverage ratio calculated.</x:v>
       </x:c>
-      <x:c r="E49" s="31"/>
-      <x:c r="F49" s="31"/>
-      <x:c r="G49" s="31"/>
+      <x:c r="E49" s="32"/>
+      <x:c r="F49" s="32"/>
+      <x:c r="G49" s="32"/>
     </x:row>
     <x:row r="50" ht="68" customHeight="1">
-      <x:c r="A50" s="59" t="str">
+      <x:c r="A50" s="64" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="B50" s="120" t="str">
+      <x:c r="B50" s="125" t="str">
         <x:v>Saved filings only</x:v>
       </x:c>
-      <x:c r="C50" s="97" t="str">
+      <x:c r="C50" s="102" t="str">
         <x:v>10-K; 10-Q; Aug 5 Ex. 99.1</x:v>
       </x:c>
-      <x:c r="D50" s="62" t="str">
+      <x:c r="D50" s="67" t="str">
         <x:v>Not a complete SEC filing inventory. No combined total of commitments, milestones, capex plans or debt.</x:v>
       </x:c>
-      <x:c r="E50" s="31"/>
-      <x:c r="F50" s="31"/>
-      <x:c r="G50" s="31"/>
+      <x:c r="E50" s="32"/>
+      <x:c r="F50" s="32"/>
+      <x:c r="G50" s="32"/>
     </x:row>
     <x:row r="51" ht="30" customHeight="1">
-      <x:c r="A51" s="31"/>
-      <x:c r="B51" s="115"/>
-      <x:c r="C51" s="31"/>
-      <x:c r="D51" s="31"/>
-      <x:c r="E51" s="31"/>
-      <x:c r="F51" s="31"/>
-      <x:c r="G51" s="31"/>
+      <x:c r="A51" s="32"/>
+      <x:c r="B51" s="120"/>
+      <x:c r="C51" s="32"/>
+      <x:c r="D51" s="32"/>
+      <x:c r="E51" s="32"/>
+      <x:c r="F51" s="32"/>
+      <x:c r="G51" s="32"/>
     </x:row>
     <x:row r="52" ht="30" customHeight="1">
-      <x:c r="A52" s="31"/>
-      <x:c r="B52" s="115"/>
-      <x:c r="C52" s="31"/>
-      <x:c r="D52" s="31"/>
-      <x:c r="E52" s="31"/>
-      <x:c r="F52" s="31"/>
-      <x:c r="G52" s="31"/>
+      <x:c r="A52" s="32"/>
+      <x:c r="B52" s="120"/>
+      <x:c r="C52" s="32"/>
+      <x:c r="D52" s="32"/>
+      <x:c r="E52" s="32"/>
+      <x:c r="F52" s="32"/>
+      <x:c r="G52" s="32"/>
     </x:row>
     <x:row r="53" ht="30" customHeight="1">
-      <x:c r="A53" s="78" t="str">
+      <x:c r="A53" s="83" t="str">
         <x:v>Notes grouped by due year</x:v>
       </x:c>
-      <x:c r="B53" s="116" t="str">
+      <x:c r="B53" s="121" t="str">
         <x:v>USD millions</x:v>
       </x:c>
-      <x:c r="C53" s="79" t="str">
+      <x:c r="C53" s="84" t="str">
         <x:v>Basis date</x:v>
       </x:c>
-      <x:c r="D53" s="80" t="str">
+      <x:c r="D53" s="85" t="str">
         <x:v>Interpretation</x:v>
       </x:c>
-      <x:c r="E53" s="31"/>
-      <x:c r="F53" s="31"/>
-      <x:c r="G53" s="31"/>
+      <x:c r="E53" s="32"/>
+      <x:c r="F53" s="32"/>
+      <x:c r="G53" s="32"/>
     </x:row>
     <x:row r="54" ht="43" customHeight="1">
-      <x:c r="A54" s="52" t="str">
+      <x:c r="A54" s="57" t="str">
         <x:v>Notes due 2026</x:v>
       </x:c>
-      <x:c r="B54" s="53" t="n">
+      <x:c r="B54" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B43),'Data'!B43,NA())</x:f>
         <x:v>1632000000</x:v>
       </x:c>
-      <x:c r="C54" s="95" t="str">
+      <x:c r="C54" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D54" s="55" t="str">
+      <x:c r="D54" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E54" s="31"/>
-      <x:c r="F54" s="31"/>
-      <x:c r="G54" s="31"/>
+      <x:c r="E54" s="32"/>
+      <x:c r="F54" s="32"/>
+      <x:c r="G54" s="32"/>
     </x:row>
     <x:row r="55" ht="43" customHeight="1">
-      <x:c r="A55" s="52" t="str">
+      <x:c r="A55" s="57" t="str">
         <x:v>Notes due 2027</x:v>
       </x:c>
-      <x:c r="B55" s="53" t="n">
+      <x:c r="B55" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B44),'Data'!B44,NA())</x:f>
         <x:v>2516000000</x:v>
       </x:c>
-      <x:c r="C55" s="95" t="str">
+      <x:c r="C55" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D55" s="55" t="str">
+      <x:c r="D55" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E55" s="31"/>
-      <x:c r="F55" s="31"/>
-      <x:c r="G55" s="31"/>
+      <x:c r="E55" s="32"/>
+      <x:c r="F55" s="32"/>
+      <x:c r="G55" s="32"/>
     </x:row>
     <x:row r="56" ht="43" customHeight="1">
-      <x:c r="A56" s="52" t="str">
+      <x:c r="A56" s="57" t="str">
         <x:v>Notes due 2028</x:v>
       </x:c>
-      <x:c r="B56" s="53" t="n">
+      <x:c r="B56" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B45),'Data'!B45,NA())</x:f>
         <x:v>3256000000</x:v>
       </x:c>
-      <x:c r="C56" s="95" t="str">
+      <x:c r="C56" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D56" s="55" t="str">
+      <x:c r="D56" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E56" s="31"/>
-      <x:c r="F56" s="31"/>
-      <x:c r="G56" s="31"/>
+      <x:c r="E56" s="32"/>
+      <x:c r="F56" s="32"/>
+      <x:c r="G56" s="32"/>
     </x:row>
     <x:row r="57" ht="43" customHeight="1">
-      <x:c r="A57" s="52" t="str">
+      <x:c r="A57" s="57" t="str">
         <x:v>Notes due 2029</x:v>
       </x:c>
-      <x:c r="B57" s="53" t="n">
+      <x:c r="B57" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B46),'Data'!B46,NA())</x:f>
         <x:v>3077000000</x:v>
       </x:c>
-      <x:c r="C57" s="95" t="str">
+      <x:c r="C57" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D57" s="55" t="str">
+      <x:c r="D57" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E57" s="31"/>
-      <x:c r="F57" s="31"/>
-      <x:c r="G57" s="31"/>
+      <x:c r="E57" s="32"/>
+      <x:c r="F57" s="32"/>
+      <x:c r="G57" s="32"/>
     </x:row>
     <x:row r="58" ht="43" customHeight="1">
-      <x:c r="A58" s="52" t="str">
+      <x:c r="A58" s="57" t="str">
         <x:v>Notes due 2030</x:v>
       </x:c>
-      <x:c r="B58" s="53" t="n">
+      <x:c r="B58" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B47),'Data'!B47,NA())</x:f>
         <x:v>2132000000</x:v>
       </x:c>
-      <x:c r="C58" s="95" t="str">
+      <x:c r="C58" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D58" s="55" t="str">
+      <x:c r="D58" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E58" s="31"/>
-      <x:c r="F58" s="31"/>
-      <x:c r="G58" s="31"/>
+      <x:c r="E58" s="32"/>
+      <x:c r="F58" s="32"/>
+      <x:c r="G58" s="32"/>
     </x:row>
     <x:row r="59" ht="43" customHeight="1">
-      <x:c r="A59" s="52" t="str">
+      <x:c r="A59" s="57" t="str">
         <x:v>Notes due 2031–2040</x:v>
       </x:c>
-      <x:c r="B59" s="53" t="n">
+      <x:c r="B59" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B48),'Data'!B48,NA())</x:f>
         <x:v>11582000000</x:v>
       </x:c>
-      <x:c r="C59" s="95" t="str">
+      <x:c r="C59" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D59" s="55" t="str">
+      <x:c r="D59" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E59" s="31"/>
-      <x:c r="F59" s="31"/>
-      <x:c r="G59" s="31"/>
+      <x:c r="E59" s="32"/>
+      <x:c r="F59" s="32"/>
+      <x:c r="G59" s="32"/>
     </x:row>
     <x:row r="60" ht="43" customHeight="1">
-      <x:c r="A60" s="52" t="str">
+      <x:c r="A60" s="57" t="str">
         <x:v>Notes due 2041–2050</x:v>
       </x:c>
-      <x:c r="B60" s="53" t="n">
+      <x:c r="B60" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B49),'Data'!B49,NA())</x:f>
         <x:v>4543000000</x:v>
       </x:c>
-      <x:c r="C60" s="95" t="str">
+      <x:c r="C60" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D60" s="55" t="str">
+      <x:c r="D60" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E60" s="31"/>
-      <x:c r="F60" s="31"/>
-      <x:c r="G60" s="31"/>
+      <x:c r="E60" s="32"/>
+      <x:c r="F60" s="32"/>
+      <x:c r="G60" s="32"/>
     </x:row>
     <x:row r="61" ht="43" customHeight="1">
-      <x:c r="A61" s="52" t="str">
+      <x:c r="A61" s="57" t="str">
         <x:v>Notes due 2051–2060</x:v>
       </x:c>
-      <x:c r="B61" s="53" t="n">
+      <x:c r="B61" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B50),'Data'!B50,NA())</x:f>
         <x:v>8280000000</x:v>
       </x:c>
-      <x:c r="C61" s="95" t="str">
+      <x:c r="C61" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D61" s="55" t="str">
+      <x:c r="D61" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E61" s="31"/>
-      <x:c r="F61" s="31"/>
-      <x:c r="G61" s="31"/>
+      <x:c r="E61" s="32"/>
+      <x:c r="F61" s="32"/>
+      <x:c r="G61" s="32"/>
     </x:row>
     <x:row r="62" ht="43" customHeight="1">
-      <x:c r="A62" s="52" t="str">
+      <x:c r="A62" s="57" t="str">
         <x:v>Notes due 2061–2070</x:v>
       </x:c>
-      <x:c r="B62" s="53" t="n">
+      <x:c r="B62" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B51),'Data'!B51,NA())</x:f>
         <x:v>5824000000</x:v>
       </x:c>
-      <x:c r="C62" s="95" t="str">
+      <x:c r="C62" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D62" s="55" t="str">
+      <x:c r="D62" s="60" t="str">
         <x:v>Historical carrying amount; not principal cash payments. Multi-year groups are combined.</x:v>
       </x:c>
-      <x:c r="E62" s="31"/>
-      <x:c r="F62" s="31"/>
-      <x:c r="G62" s="31"/>
+      <x:c r="E62" s="32"/>
+      <x:c r="F62" s="32"/>
+      <x:c r="G62" s="32"/>
     </x:row>
     <x:row r="63" ht="43" customHeight="1">
-      <x:c r="A63" s="85" t="str">
+      <x:c r="A63" s="90" t="str">
         <x:v>Total notes</x:v>
       </x:c>
-      <x:c r="B63" s="90" t="n">
+      <x:c r="B63" s="95" t="n">
         <x:f>SUM(B54:B62)</x:f>
         <x:v>42842000000</x:v>
       </x:c>
-      <x:c r="C63" s="105" t="str">
+      <x:c r="C63" s="110" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D63" s="88" t="str">
+      <x:c r="D63" s="93" t="str">
         <x:v>Carrying amount; not payment total.</x:v>
       </x:c>
-      <x:c r="E63" s="31"/>
-      <x:c r="F63" s="31"/>
-      <x:c r="G63" s="31"/>
+      <x:c r="E63" s="32"/>
+      <x:c r="F63" s="32"/>
+      <x:c r="G63" s="32"/>
     </x:row>
     <x:row r="64" ht="43" customHeight="1">
-      <x:c r="A64" s="52" t="str">
+      <x:c r="A64" s="57" t="str">
         <x:v>Other debt and adjustments</x:v>
       </x:c>
-      <x:c r="B64" s="53" t="n">
+      <x:c r="B64" s="58" t="n">
         <x:f>-IF(ISNUMBER('Data'!B52),'Data'!B52,NA())</x:f>
         <x:v>-339000000</x:v>
       </x:c>
-      <x:c r="C64" s="95" t="str">
+      <x:c r="C64" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D64" s="55" t="str">
+      <x:c r="D64" s="60" t="str">
         <x:v>Printed as (339). Tagged +339 source magnitude; presentation coefficient −1.</x:v>
       </x:c>
-      <x:c r="E64" s="31"/>
-      <x:c r="F64" s="31"/>
-      <x:c r="G64" s="31"/>
+      <x:c r="E64" s="32"/>
+      <x:c r="F64" s="32"/>
+      <x:c r="G64" s="32"/>
     </x:row>
     <x:row r="65" ht="43" customHeight="1">
-      <x:c r="A65" s="52" t="str">
+      <x:c r="A65" s="57" t="str">
         <x:v>Commercial paper</x:v>
       </x:c>
-      <x:c r="B65" s="53" t="n">
+      <x:c r="B65" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B53),'Data'!B53,NA())</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C65" s="95" t="str">
+      <x:c r="C65" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D65" s="55" t="str">
+      <x:c r="D65" s="60" t="str">
         <x:v>Reported zero at December 31, 2025.</x:v>
       </x:c>
-      <x:c r="E65" s="31"/>
-      <x:c r="F65" s="31"/>
-      <x:c r="G65" s="31"/>
+      <x:c r="E65" s="32"/>
+      <x:c r="F65" s="32"/>
+      <x:c r="G65" s="32"/>
     </x:row>
     <x:row r="66" ht="43" customHeight="1">
-      <x:c r="A66" s="85" t="str">
+      <x:c r="A66" s="90" t="str">
         <x:v>Calculated total debt</x:v>
       </x:c>
-      <x:c r="B66" s="90" t="n">
+      <x:c r="B66" s="95" t="n">
         <x:f>SUM(B63:B65)</x:f>
         <x:v>42503000000</x:v>
       </x:c>
-      <x:c r="C66" s="105" t="str">
+      <x:c r="C66" s="110" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D66" s="88" t="str">
+      <x:c r="D66" s="93" t="str">
         <x:v>Same annual filing; no roll-forward to June.</x:v>
       </x:c>
-      <x:c r="E66" s="31"/>
-      <x:c r="F66" s="31"/>
-      <x:c r="G66" s="31"/>
+      <x:c r="E66" s="32"/>
+      <x:c r="F66" s="32"/>
+      <x:c r="G66" s="32"/>
     </x:row>
     <x:row r="67" ht="43" customHeight="1">
-      <x:c r="A67" s="52" t="str">
+      <x:c r="A67" s="57" t="str">
         <x:v>Reported total debt</x:v>
       </x:c>
-      <x:c r="B67" s="53" t="n">
+      <x:c r="B67" s="58" t="n">
         <x:f>IF(ISNUMBER('Data'!B54),'Data'!B54,NA())</x:f>
         <x:v>42503000000</x:v>
       </x:c>
-      <x:c r="C67" s="95" t="str">
+      <x:c r="C67" s="100" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D67" s="55" t="str">
+      <x:c r="D67" s="60" t="str">
         <x:v>Reconciles to annual balance sheet.</x:v>
       </x:c>
-      <x:c r="E67" s="31"/>
-      <x:c r="F67" s="31"/>
-      <x:c r="G67" s="31"/>
+      <x:c r="E67" s="32"/>
+      <x:c r="F67" s="32"/>
+      <x:c r="G67" s="32"/>
     </x:row>
     <x:row r="68" ht="43" customHeight="1">
-      <x:c r="A68" s="110" t="str">
+      <x:c r="A68" s="115" t="str">
         <x:v>Debt reconciliation difference</x:v>
       </x:c>
-      <x:c r="B68" s="114" t="n">
+      <x:c r="B68" s="119" t="n">
         <x:f>B66-B67</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C68" s="112" t="str">
+      <x:c r="C68" s="117" t="str">
         <x:v>December 31, 2025</x:v>
       </x:c>
-      <x:c r="D68" s="113" t="str">
+      <x:c r="D68" s="118" t="str">
         <x:v>Zero = reconciled.</x:v>
       </x:c>
-      <x:c r="E68" s="31"/>
-      <x:c r="F68" s="31"/>
-      <x:c r="G68" s="31"/>
+      <x:c r="E68" s="32"/>
+      <x:c r="F68" s="32"/>
+      <x:c r="G68" s="32"/>
     </x:row>
     <x:row r="69" ht="30" customHeight="1">
-      <x:c r="A69" s="31"/>
-      <x:c r="B69" s="31"/>
-      <x:c r="C69" s="31"/>
-      <x:c r="D69" s="31"/>
-      <x:c r="E69" s="31"/>
-      <x:c r="F69" s="31"/>
-      <x:c r="G69" s="31"/>
+      <x:c r="A69" s="32"/>
+      <x:c r="B69" s="32"/>
+      <x:c r="C69" s="32"/>
+      <x:c r="D69" s="32"/>
+      <x:c r="E69" s="32"/>
+      <x:c r="F69" s="32"/>
+      <x:c r="G69" s="32"/>
     </x:row>
     <x:row r="70" ht="80" customHeight="1">
-      <x:c r="A70" s="49" t="str">
+      <x:c r="A70" s="54" t="str">
         <x:v>June 30 principal schedule</x:v>
       </x:c>
-      <x:c r="B70" s="50" t="str">
+      <x:c r="B70" s="55" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
-      <x:c r="C70" s="50" t="str">
+      <x:c r="C70" s="55" t="str">
         <x:v>Updated payment dates missing</x:v>
       </x:c>
-      <x:c r="D70" s="51" t="str">
+      <x:c r="D70" s="56" t="str">
         <x:v>Do not allocate May issuance or H1 repayments to annual buckets. Current borrowing $7.050B is not an instrument-level schedule.</x:v>
       </x:c>
-      <x:c r="E70" s="31"/>
-      <x:c r="F70" s="31"/>
-      <x:c r="G70" s="31"/>
+      <x:c r="E70" s="32"/>
+      <x:c r="F70" s="32"/>
+      <x:c r="G70" s="32"/>
     </x:row>
     <x:row r="71" ht="80" customHeight="1">
-      <x:c r="A71" s="59" t="str">
+      <x:c r="A71" s="64" t="str">
         <x:v>Repayment conclusion</x:v>
       </x:c>
-      <x:c r="B71" s="97"/>
-      <x:c r="C71" s="97" t="str">
+      <x:c r="B71" s="102"/>
+      <x:c r="C71" s="102" t="str">
         <x:v>Coverage Unavailable</x:v>
       </x:c>
-      <x:c r="D71" s="62" t="str">
+      <x:c r="D71" s="67" t="str">
         <x:v>H1 cash generation after PP&amp;E was positive; acquisitions and payouts competed for cash. Net borrowing contributed materially. Updated debt dates, draw terms/renewal and payment calendars are needed.</x:v>
       </x:c>
-      <x:c r="E71" s="31"/>
-      <x:c r="F71" s="31"/>
-      <x:c r="G71" s="31"/>
+      <x:c r="E71" s="32"/>
+      <x:c r="F71" s="32"/>
+      <x:c r="G71" s="32"/>
+    </x:row>
+    <x:row r="72" ht="30" customHeight="1">
+      <x:c r="A72" s="32"/>
+      <x:c r="B72" s="32"/>
+      <x:c r="C72" s="32"/>
+      <x:c r="D72" s="32"/>
+      <x:c r="E72" s="32"/>
+      <x:c r="F72" s="32"/>
+      <x:c r="G72" s="32"/>
+    </x:row>
+    <x:row r="73" ht="30" customHeight="1">
+      <x:c r="A73" s="32"/>
+      <x:c r="B73" s="32"/>
+      <x:c r="C73" s="32"/>
+      <x:c r="D73" s="32"/>
+      <x:c r="E73" s="32"/>
+      <x:c r="F73" s="32"/>
+      <x:c r="G73" s="32"/>
+    </x:row>
+    <x:row r="74" ht="30" customHeight="1">
+      <x:c r="A74" s="51" t="str">
+        <x:v>May 2026 issue — documented stated maturities</x:v>
+      </x:c>
+      <x:c r="B74" s="32"/>
+      <x:c r="C74" s="32"/>
+      <x:c r="D74" s="32"/>
+      <x:c r="E74" s="32"/>
+      <x:c r="F74" s="32"/>
+      <x:c r="G74" s="32"/>
+    </x:row>
+    <x:row r="75" ht="43" customHeight="1">
+      <x:c r="A75" s="32" t="str">
+        <x:v>Initial issue principal, not a complete June/October outstanding-debt schedule. Already in June borrowing and H1 proceeds; do not add to either.</x:v>
+      </x:c>
+      <x:c r="B75" s="32"/>
+      <x:c r="C75" s="32"/>
+      <x:c r="D75" s="32"/>
+      <x:c r="E75" s="32"/>
+      <x:c r="F75" s="32"/>
+      <x:c r="G75" s="32"/>
+    </x:row>
+    <x:row r="76" ht="43" customHeight="1">
+      <x:c r="A76" s="83" t="str">
+        <x:v>Series</x:v>
+      </x:c>
+      <x:c r="B76" s="84" t="str">
+        <x:v>Initial principal, USD millions</x:v>
+      </x:c>
+      <x:c r="C76" s="84" t="str">
+        <x:v>Stated maturity</x:v>
+      </x:c>
+      <x:c r="D76" s="85" t="str">
+        <x:v>Contract rate</x:v>
+      </x:c>
+      <x:c r="E76" s="32"/>
+      <x:c r="F76" s="32"/>
+      <x:c r="G76" s="32"/>
+    </x:row>
+    <x:row r="77" ht="43" customHeight="1">
+      <x:c r="A77" s="57" t="str">
+        <x:v>Floating 2028</x:v>
+      </x:c>
+      <x:c r="B77" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B68),'Data'!B68,NA())</x:f>
+        <x:v>750000000</x:v>
+      </x:c>
+      <x:c r="C77" s="129" t="n">
+        <x:f>'Data'!E68</x:f>
+        <x:v>46893</x:v>
+      </x:c>
+      <x:c r="D77" s="70" t="str">
+        <x:f>"Compounded SOFR + "&amp;TEXT('Data'!T68,"0.000%")</x:f>
+        <x:v>Compounded SOFR + 0.350%</x:v>
+      </x:c>
+      <x:c r="E77" s="32"/>
+      <x:c r="F77" s="32"/>
+      <x:c r="G77" s="32"/>
+    </x:row>
+    <x:row r="78" ht="43" customHeight="1">
+      <x:c r="A78" s="57" t="str">
+        <x:v>Floating 2029</x:v>
+      </x:c>
+      <x:c r="B78" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B69),'Data'!B69,NA())</x:f>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="C78" s="129" t="n">
+        <x:f>'Data'!E69</x:f>
+        <x:v>47258</x:v>
+      </x:c>
+      <x:c r="D78" s="70" t="str">
+        <x:f>"Compounded SOFR + "&amp;TEXT('Data'!T69,"0.000%")</x:f>
+        <x:v>Compounded SOFR + 0.460%</x:v>
+      </x:c>
+      <x:c r="E78" s="32"/>
+      <x:c r="F78" s="32"/>
+      <x:c r="G78" s="32"/>
+    </x:row>
+    <x:row r="79" ht="43" customHeight="1">
+      <x:c r="A79" s="57" t="str">
+        <x:v>Fixed 2029</x:v>
+      </x:c>
+      <x:c r="B79" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B70),'Data'!B70,NA())</x:f>
+        <x:v>750000000</x:v>
+      </x:c>
+      <x:c r="C79" s="129" t="n">
+        <x:f>'Data'!E70</x:f>
+        <x:v>47258</x:v>
+      </x:c>
+      <x:c r="D79" s="128" t="n">
+        <x:f>'Data'!S70</x:f>
+        <x:v>0.0415</x:v>
+      </x:c>
+      <x:c r="E79" s="32"/>
+      <x:c r="F79" s="32"/>
+      <x:c r="G79" s="32"/>
+    </x:row>
+    <x:row r="80" ht="43" customHeight="1">
+      <x:c r="A80" s="57" t="str">
+        <x:v>Fixed 2031</x:v>
+      </x:c>
+      <x:c r="B80" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B71),'Data'!B71,NA())</x:f>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="C80" s="129" t="n">
+        <x:f>'Data'!E71</x:f>
+        <x:v>47988</x:v>
+      </x:c>
+      <x:c r="D80" s="128" t="n">
+        <x:f>'Data'!S71</x:f>
+        <x:v>0.04375</x:v>
+      </x:c>
+      <x:c r="E80" s="32"/>
+      <x:c r="F80" s="32"/>
+      <x:c r="G80" s="32"/>
+    </x:row>
+    <x:row r="81" ht="43" customHeight="1">
+      <x:c r="A81" s="57" t="str">
+        <x:v>Fixed 2033</x:v>
+      </x:c>
+      <x:c r="B81" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B72),'Data'!B72,NA())</x:f>
+        <x:v>1250000000</x:v>
+      </x:c>
+      <x:c r="C81" s="129" t="n">
+        <x:f>'Data'!E72</x:f>
+        <x:v>48719</x:v>
+      </x:c>
+      <x:c r="D81" s="128" t="n">
+        <x:f>'Data'!S72</x:f>
+        <x:v>0.0465</x:v>
+      </x:c>
+      <x:c r="E81" s="32"/>
+      <x:c r="F81" s="32"/>
+      <x:c r="G81" s="32"/>
+    </x:row>
+    <x:row r="82" ht="43" customHeight="1">
+      <x:c r="A82" s="57" t="str">
+        <x:v>Fixed 2036</x:v>
+      </x:c>
+      <x:c r="B82" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B73),'Data'!B73,NA())</x:f>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="C82" s="129" t="n">
+        <x:f>'Data'!E73</x:f>
+        <x:v>49815</x:v>
+      </x:c>
+      <x:c r="D82" s="128" t="n">
+        <x:f>'Data'!S73</x:f>
+        <x:v>0.0485</x:v>
+      </x:c>
+      <x:c r="E82" s="32"/>
+      <x:c r="F82" s="32"/>
+      <x:c r="G82" s="32"/>
+    </x:row>
+    <x:row r="83" ht="43" customHeight="1">
+      <x:c r="A83" s="57" t="str">
+        <x:v>Fixed 2056</x:v>
+      </x:c>
+      <x:c r="B83" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B74),'Data'!B74,NA())</x:f>
+        <x:v>1750000000</x:v>
+      </x:c>
+      <x:c r="C83" s="129" t="n">
+        <x:f>'Data'!E74</x:f>
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="D83" s="128" t="n">
+        <x:f>'Data'!S74</x:f>
+        <x:v>0.056</x:v>
+      </x:c>
+      <x:c r="E83" s="32"/>
+      <x:c r="F83" s="32"/>
+      <x:c r="G83" s="32"/>
+    </x:row>
+    <x:row r="84" ht="43" customHeight="1">
+      <x:c r="A84" s="57" t="str">
+        <x:v>Fixed 2066</x:v>
+      </x:c>
+      <x:c r="B84" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B75),'Data'!B75,NA())</x:f>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="C84" s="129" t="n">
+        <x:f>'Data'!E75</x:f>
+        <x:v>60772</x:v>
+      </x:c>
+      <x:c r="D84" s="128" t="n">
+        <x:f>'Data'!S75</x:f>
+        <x:v>0.057</x:v>
+      </x:c>
+      <x:c r="E84" s="32"/>
+      <x:c r="F84" s="32"/>
+      <x:c r="G84" s="32"/>
+    </x:row>
+    <x:row r="85" ht="43" customHeight="1">
+      <x:c r="A85" s="90" t="str">
+        <x:v>Calculated initial issue total</x:v>
+      </x:c>
+      <x:c r="B85" s="131" t="n">
+        <x:f>SUM(B77:B84)</x:f>
+        <x:v>9000000000</x:v>
+      </x:c>
+      <x:c r="C85" s="110" t="str">
+        <x:v>May 20, 2026</x:v>
+      </x:c>
+      <x:c r="D85" s="93" t="str">
+        <x:v>Eight series; not additional June debt.</x:v>
+      </x:c>
+      <x:c r="E85" s="32"/>
+      <x:c r="F85" s="32"/>
+      <x:c r="G85" s="32"/>
+    </x:row>
+    <x:row r="86" ht="43" customHeight="1">
+      <x:c r="A86" s="57" t="str">
+        <x:v>Reported completed issue total</x:v>
+      </x:c>
+      <x:c r="B86" s="58" t="n">
+        <x:f>IF(ISNUMBER('Data'!B76),'Data'!B76,NA())</x:f>
+        <x:v>9000000000</x:v>
+      </x:c>
+      <x:c r="C86" s="100" t="str">
+        <x:v>May 20, 2026</x:v>
+      </x:c>
+      <x:c r="D86" s="60" t="str">
+        <x:v>8-K Item 8.01; face principal differs from net cash proceeds.</x:v>
+      </x:c>
+      <x:c r="E86" s="32"/>
+      <x:c r="F86" s="32"/>
+      <x:c r="G86" s="32"/>
+    </x:row>
+    <x:row r="87" ht="43" customHeight="1">
+      <x:c r="A87" s="90" t="str">
+        <x:v>Issue reconciliation difference</x:v>
+      </x:c>
+      <x:c r="B87" s="131" t="n">
+        <x:f>B85-B86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C87" s="110" t="str">
+        <x:v>Zero = reconciled</x:v>
+      </x:c>
+      <x:c r="D87" s="93" t="str">
+        <x:v>No roll-forward to June outstanding principal.</x:v>
+      </x:c>
+      <x:c r="E87" s="32"/>
+      <x:c r="F87" s="32"/>
+      <x:c r="G87" s="32"/>
+    </x:row>
+    <x:row r="88" ht="43" customHeight="1">
+      <x:c r="A88" s="57" t="str">
+        <x:v>Current outstanding by series</x:v>
+      </x:c>
+      <x:c r="B88" s="100" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C88" s="100" t="str">
+        <x:v>June / October 2026</x:v>
+      </x:c>
+      <x:c r="D88" s="60" t="str">
+        <x:v>Initial issue amounts do not establish current balances.</x:v>
+      </x:c>
+      <x:c r="E88" s="32"/>
+      <x:c r="F88" s="32"/>
+      <x:c r="G88" s="32"/>
+    </x:row>
+    <x:row r="89" ht="43" customHeight="1">
+      <x:c r="A89" s="64" t="str">
+        <x:v>Drawable capacity / future coverage</x:v>
+      </x:c>
+      <x:c r="B89" s="102" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C89" s="102" t="str">
+        <x:v>October 15 review</x:v>
+      </x:c>
+      <x:c r="D89" s="67" t="str">
+        <x:v>No new verified facility renewal, drawable credit or complete future funding coverage.</x:v>
+      </x:c>
+      <x:c r="E89" s="32"/>
+      <x:c r="F89" s="32"/>
+      <x:c r="G89" s="32"/>
+    </x:row>
+    <x:row r="90" ht="30" customHeight="1">
+      <x:c r="A90" s="32"/>
+      <x:c r="B90" s="32"/>
+      <x:c r="C90" s="32"/>
+      <x:c r="D90" s="32"/>
+      <x:c r="E90" s="32"/>
+      <x:c r="F90" s="32"/>
+      <x:c r="G90" s="32"/>
+    </x:row>
+    <x:row r="91" ht="70" customHeight="1">
+      <x:c r="A91" s="32" t="str">
+        <x:v>The May 20 8-K's interest paragraph says 4.650% for the fixed 2029 notes, while its series title, final prospectus and Exhibit 4.3 clauses (i)/(v) agree on 4.150%. This review uses the corroborated contract rate, 4.150%, and retains the conflicting statement here.</x:v>
+      </x:c>
+      <x:c r="B91" s="32"/>
+      <x:c r="C91" s="32"/>
+      <x:c r="D91" s="32"/>
+      <x:c r="E91" s="32"/>
+      <x:c r="F91" s="32"/>
+      <x:c r="G91" s="32"/>
+    </x:row>
+    <x:row r="92" ht="70" customHeight="1">
+      <x:c r="A92" s="32" t="str">
+        <x:v>The May terms require 101% special redemption of specified series if the Centessa acquisition fails under the stated conditions. The terms cease to apply upon consummation; the June 10-Q Note 4 records acquisition on June 24, 2026. This resolved acquisition-failure condition is not presented as a future 101% cash bill. Optional redemptions and default acceleration remain possible; none is assumed.</x:v>
+      </x:c>
+      <x:c r="B92" s="32"/>
+      <x:c r="C92" s="32"/>
+      <x:c r="D92" s="32"/>
+      <x:c r="E92" s="32"/>
+      <x:c r="F92" s="32"/>
+      <x:c r="G92" s="32"/>
+    </x:row>
+    <x:row r="93" ht="70" customHeight="1">
+      <x:c r="A93" s="32" t="str">
+        <x:v>SEC submissions contain 1,001 filings, October 15, 2026 back to December 16, 2021; older pages end before the review period. All 2026 form rows were screened, prioritizing periodic reports, amendments, 8-Ks, shelf/prospectus/pricing filings and debt delisting. After June 30, the only 8-K is the saved August 5 earnings report; no later periodic report or amendment, 424B2 or FWP is listed. Ownership filings are not corporate financing capacity.</x:v>
+      </x:c>
+      <x:c r="B93" s="32"/>
+      <x:c r="C93" s="32"/>
+      <x:c r="D93" s="32"/>
+      <x:c r="E93" s="32"/>
+      <x:c r="F93" s="32"/>
+      <x:c r="G93" s="32"/>
+    </x:row>
+    <x:row r="94" ht="70" customHeight="1">
+      <x:c r="A94" s="32" t="str">
+        <x:v>The retrieved September 2025 10-Q describes the August 2025 renewal to $6B and extension of the $4B facility to December 2029. This is historical, not an August 2026 renewal. The annual and March/June reports and reviewed exhibit lists establish no current credit agreement or post-August 2026 renewal. No relevant bank agreement was identified in the reviewed SEC filing and exhibit references. Draw conditions, current usage, covenant headroom and actual drawable capacity remain Unavailable.</x:v>
+      </x:c>
+      <x:c r="B94" s="32"/>
+      <x:c r="C94" s="32"/>
+      <x:c r="D94" s="32"/>
+      <x:c r="E94" s="32"/>
+      <x:c r="F94" s="32"/>
+      <x:c r="G94" s="32"/>
+    </x:row>
+    <x:row r="95" ht="70" customHeight="1">
+      <x:c r="A95" s="32" t="str">
+        <x:v>Dates are stated contractual maturities, not calendar-adjusted payment forecasts. Indenture §1.11 and note-specific business-day provisions apply. Future interest amounts, floating-rate resets, actual early redemptions and cash available at maturity are not modeled.</x:v>
+      </x:c>
+      <x:c r="B95" s="32"/>
+      <x:c r="C95" s="32"/>
+      <x:c r="D95" s="32"/>
+      <x:c r="E95" s="32"/>
+      <x:c r="F95" s="32"/>
+      <x:c r="G95" s="32"/>
+    </x:row>
+    <x:row r="96" ht="70" customHeight="1">
+      <x:c r="A96" s="32" t="str">
+        <x:v>The June 2 Form 25 removes the 1.625% notes due 2026 from listing. It does not establish an instrument-level cash repayment amount and is not used to allocate H1 repayments.</x:v>
+      </x:c>
+      <x:c r="B96" s="32"/>
+      <x:c r="C96" s="32"/>
+      <x:c r="D96" s="32"/>
+      <x:c r="E96" s="32"/>
+      <x:c r="F96" s="32"/>
+      <x:c r="G96" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A4:D4"/>
+    <x:mergeCell ref="A75:D75"/>
+    <x:mergeCell ref="A91:D91"/>
+    <x:mergeCell ref="A92:D92"/>
+    <x:mergeCell ref="A93:D93"/>
+    <x:mergeCell ref="A94:D94"/>
+    <x:mergeCell ref="A95:D95"/>
+    <x:mergeCell ref="A96:D96"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb73ab5a2ae284972"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48a7ec2ea8b64192"/>
 </x:worksheet>
 </file>
 
@@ -2510,3189 +2937,3777 @@
     <x:col min="16" max="16" width="85" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="100" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="72" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="23" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="23" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="78" t="str">
+      <x:c r="A1" s="83" t="str">
         <x:v>Input</x:v>
       </x:c>
-      <x:c r="B1" s="79" t="str">
+      <x:c r="B1" s="84" t="str">
         <x:v>USD millions</x:v>
       </x:c>
-      <x:c r="C1" s="79" t="str">
+      <x:c r="C1" s="84" t="str">
         <x:v>Period start</x:v>
       </x:c>
-      <x:c r="D1" s="79" t="str">
+      <x:c r="D1" s="84" t="str">
         <x:v>Period end</x:v>
       </x:c>
-      <x:c r="E1" s="79" t="str">
+      <x:c r="E1" s="84" t="str">
         <x:v>Form</x:v>
       </x:c>
-      <x:c r="F1" s="79" t="str">
+      <x:c r="F1" s="84" t="str">
         <x:v>Filed</x:v>
       </x:c>
-      <x:c r="G1" s="79" t="str">
+      <x:c r="G1" s="84" t="str">
         <x:v>Accession</x:v>
       </x:c>
-      <x:c r="H1" s="79" t="str">
+      <x:c r="H1" s="84" t="str">
         <x:v>Tag</x:v>
       </x:c>
-      <x:c r="I1" s="79" t="str">
+      <x:c r="I1" s="84" t="str">
         <x:v>Context</x:v>
       </x:c>
-      <x:c r="J1" s="79" t="str">
+      <x:c r="J1" s="84" t="str">
         <x:v>Scale</x:v>
       </x:c>
-      <x:c r="K1" s="79" t="str">
+      <x:c r="K1" s="84" t="str">
         <x:v>Decimals</x:v>
       </x:c>
-      <x:c r="L1" s="79" t="str">
+      <x:c r="L1" s="84" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="M1" s="79" t="str">
+      <x:c r="M1" s="84" t="str">
         <x:v>Selection rule</x:v>
       </x:c>
-      <x:c r="N1" s="79" t="str">
+      <x:c r="N1" s="84" t="str">
         <x:v>Unavailable reason</x:v>
       </x:c>
-      <x:c r="O1" s="80" t="str">
+      <x:c r="O1" s="85" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="P1" s="31"/>
-      <x:c r="Q1" s="31"/>
-      <x:c r="R1" s="31"/>
+      <x:c r="P1" s="32"/>
+      <x:c r="Q1" s="32"/>
+      <x:c r="R1" s="32"/>
+      <x:c r="S1" s="32"/>
+      <x:c r="T1" s="32"/>
     </x:row>
     <x:row r="2" ht="65" customHeight="1">
-      <x:c r="A2" s="52" t="str">
+      <x:c r="A2" s="57" t="str">
         <x:v>Cash and cash equivalents</x:v>
       </x:c>
-      <x:c r="B2" s="94" t="n">
+      <x:c r="B2" s="99" t="n">
         <x:v>8950000000</x:v>
       </x:c>
-      <x:c r="C2" s="54"/>
-      <x:c r="D2" s="54" t="d">
+      <x:c r="C2" s="59"/>
+      <x:c r="D2" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E2" s="95" t="str">
+      <x:c r="E2" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F2" s="54" t="d">
+      <x:c r="F2" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G2" s="95" t="str">
+      <x:c r="G2" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H2" s="95" t="str">
+      <x:c r="H2" s="100" t="str">
         <x:v>us-gaap:CashAndCashEquivalentsAtCarryingValue</x:v>
       </x:c>
-      <x:c r="I2" s="95"/>
-      <x:c r="J2" s="95"/>
-      <x:c r="K2" s="95"/>
-      <x:c r="L2" s="95" t="str">
+      <x:c r="I2" s="100"/>
+      <x:c r="J2" s="100"/>
+      <x:c r="K2" s="100"/>
+      <x:c r="L2" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M2" s="95" t="str">
+      <x:c r="M2" s="100" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N2" s="95" t="str"/>
-      <x:c r="O2" s="55" t="str"/>
-      <x:c r="P2" s="31"/>
-      <x:c r="Q2" s="31"/>
-      <x:c r="R2" s="31"/>
+      <x:c r="N2" s="100" t="str"/>
+      <x:c r="O2" s="60" t="str"/>
+      <x:c r="P2" s="32"/>
+      <x:c r="Q2" s="32"/>
+      <x:c r="R2" s="32"/>
+      <x:c r="S2" s="32"/>
+      <x:c r="T2" s="32"/>
     </x:row>
     <x:row r="3" ht="65" customHeight="1">
-      <x:c r="A3" s="52" t="str">
+      <x:c r="A3" s="57" t="str">
         <x:v>Short-term borrowings and current maturities of long-term debt</x:v>
       </x:c>
-      <x:c r="B3" s="94" t="n">
+      <x:c r="B3" s="99" t="n">
         <x:v>7050000000</x:v>
       </x:c>
-      <x:c r="C3" s="54"/>
-      <x:c r="D3" s="54" t="d">
+      <x:c r="C3" s="59"/>
+      <x:c r="D3" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E3" s="95" t="str">
+      <x:c r="E3" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F3" s="54" t="d">
+      <x:c r="F3" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G3" s="95" t="str">
+      <x:c r="G3" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H3" s="95" t="str">
+      <x:c r="H3" s="100" t="str">
         <x:v>us-gaap:DebtCurrent</x:v>
       </x:c>
-      <x:c r="I3" s="95"/>
-      <x:c r="J3" s="95"/>
-      <x:c r="K3" s="95"/>
-      <x:c r="L3" s="95" t="str">
+      <x:c r="I3" s="100"/>
+      <x:c r="J3" s="100"/>
+      <x:c r="K3" s="100"/>
+      <x:c r="L3" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M3" s="95" t="str">
+      <x:c r="M3" s="100" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N3" s="95" t="str"/>
-      <x:c r="O3" s="55" t="str"/>
-      <x:c r="P3" s="31"/>
-      <x:c r="Q3" s="31"/>
-      <x:c r="R3" s="31"/>
+      <x:c r="N3" s="100" t="str"/>
+      <x:c r="O3" s="60" t="str"/>
+      <x:c r="P3" s="32"/>
+      <x:c r="Q3" s="32"/>
+      <x:c r="R3" s="32"/>
+      <x:c r="S3" s="32"/>
+      <x:c r="T3" s="32"/>
     </x:row>
     <x:row r="4" ht="65" customHeight="1">
-      <x:c r="A4" s="52" t="str">
+      <x:c r="A4" s="57" t="str">
         <x:v>Long-term debt</x:v>
       </x:c>
-      <x:c r="B4" s="94" t="n">
+      <x:c r="B4" s="99" t="n">
         <x:v>47858000000</x:v>
       </x:c>
-      <x:c r="C4" s="54"/>
-      <x:c r="D4" s="54" t="d">
+      <x:c r="C4" s="59"/>
+      <x:c r="D4" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E4" s="95" t="str">
+      <x:c r="E4" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F4" s="54" t="d">
+      <x:c r="F4" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G4" s="95" t="str">
+      <x:c r="G4" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H4" s="95" t="str">
+      <x:c r="H4" s="100" t="str">
         <x:v>us-gaap:LongTermDebtNoncurrent</x:v>
       </x:c>
-      <x:c r="I4" s="95"/>
-      <x:c r="J4" s="95"/>
-      <x:c r="K4" s="95"/>
-      <x:c r="L4" s="95" t="str">
+      <x:c r="I4" s="100"/>
+      <x:c r="J4" s="100"/>
+      <x:c r="K4" s="100"/>
+      <x:c r="L4" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M4" s="95" t="str">
+      <x:c r="M4" s="100" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N4" s="95" t="str"/>
-      <x:c r="O4" s="55" t="str"/>
-      <x:c r="P4" s="31"/>
-      <x:c r="Q4" s="31"/>
-      <x:c r="R4" s="31"/>
+      <x:c r="N4" s="100" t="str"/>
+      <x:c r="O4" s="60" t="str"/>
+      <x:c r="P4" s="32"/>
+      <x:c r="Q4" s="32"/>
+      <x:c r="R4" s="32"/>
+      <x:c r="S4" s="32"/>
+      <x:c r="T4" s="32"/>
     </x:row>
     <x:row r="5" ht="65" customHeight="1">
-      <x:c r="A5" s="52" t="str">
+      <x:c r="A5" s="57" t="str">
         <x:v>Current liabilities</x:v>
       </x:c>
-      <x:c r="B5" s="94" t="n">
+      <x:c r="B5" s="99" t="n">
         <x:v>47741000000</x:v>
       </x:c>
-      <x:c r="C5" s="54"/>
-      <x:c r="D5" s="54" t="d">
+      <x:c r="C5" s="59"/>
+      <x:c r="D5" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E5" s="95" t="str">
+      <x:c r="E5" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F5" s="54" t="d">
+      <x:c r="F5" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G5" s="95" t="str">
+      <x:c r="G5" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H5" s="95" t="str">
+      <x:c r="H5" s="100" t="str">
         <x:v>us-gaap:LiabilitiesCurrent</x:v>
       </x:c>
-      <x:c r="I5" s="95"/>
-      <x:c r="J5" s="95"/>
-      <x:c r="K5" s="95"/>
-      <x:c r="L5" s="95" t="str">
+      <x:c r="I5" s="100"/>
+      <x:c r="J5" s="100"/>
+      <x:c r="K5" s="100"/>
+      <x:c r="L5" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M5" s="95" t="str">
+      <x:c r="M5" s="100" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N5" s="95" t="str"/>
-      <x:c r="O5" s="55" t="str"/>
-      <x:c r="P5" s="31"/>
-      <x:c r="Q5" s="31"/>
-      <x:c r="R5" s="31"/>
+      <x:c r="N5" s="100" t="str"/>
+      <x:c r="O5" s="60" t="str"/>
+      <x:c r="P5" s="32"/>
+      <x:c r="Q5" s="32"/>
+      <x:c r="R5" s="32"/>
+      <x:c r="S5" s="32"/>
+      <x:c r="T5" s="32"/>
     </x:row>
     <x:row r="6" ht="65" customHeight="1">
-      <x:c r="A6" s="52" t="str">
+      <x:c r="A6" s="57" t="str">
         <x:v>Current assets</x:v>
       </x:c>
-      <x:c r="B6" s="94" t="n">
+      <x:c r="B6" s="99" t="n">
         <x:v>64672000000</x:v>
       </x:c>
-      <x:c r="C6" s="54"/>
-      <x:c r="D6" s="54" t="d">
+      <x:c r="C6" s="59"/>
+      <x:c r="D6" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E6" s="95" t="str">
+      <x:c r="E6" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F6" s="54" t="d">
+      <x:c r="F6" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G6" s="95" t="str">
+      <x:c r="G6" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H6" s="95" t="str">
+      <x:c r="H6" s="100" t="str">
         <x:v>us-gaap:AssetsCurrent</x:v>
       </x:c>
-      <x:c r="I6" s="95"/>
-      <x:c r="J6" s="95"/>
-      <x:c r="K6" s="95"/>
-      <x:c r="L6" s="95" t="str">
+      <x:c r="I6" s="100"/>
+      <x:c r="J6" s="100"/>
+      <x:c r="K6" s="100"/>
+      <x:c r="L6" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M6" s="95" t="str">
+      <x:c r="M6" s="100" t="str">
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
-      <x:c r="N6" s="95" t="str"/>
-      <x:c r="O6" s="55" t="str"/>
-      <x:c r="P6" s="31"/>
-      <x:c r="Q6" s="31"/>
-      <x:c r="R6" s="31"/>
+      <x:c r="N6" s="100" t="str"/>
+      <x:c r="O6" s="60" t="str"/>
+      <x:c r="P6" s="32"/>
+      <x:c r="Q6" s="32"/>
+      <x:c r="R6" s="32"/>
+      <x:c r="S6" s="32"/>
+      <x:c r="T6" s="32"/>
     </x:row>
     <x:row r="7" ht="65" customHeight="1">
-      <x:c r="A7" s="52" t="str">
+      <x:c r="A7" s="57" t="str">
         <x:v>Operating cash flow · fiscal year</x:v>
       </x:c>
-      <x:c r="B7" s="94" t="n">
+      <x:c r="B7" s="99" t="n">
         <x:v>16813000000</x:v>
       </x:c>
-      <x:c r="C7" s="54" t="d">
+      <x:c r="C7" s="59" t="d">
         <x:v>2025-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D7" s="54" t="d">
+      <x:c r="D7" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E7" s="95" t="str">
+      <x:c r="E7" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="F7" s="54" t="d">
+      <x:c r="F7" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G7" s="95" t="str">
+      <x:c r="G7" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="H7" s="95" t="str">
+      <x:c r="H7" s="100" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
       </x:c>
-      <x:c r="I7" s="95" t="str">
+      <x:c r="I7" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="J7" s="95" t="n">
+      <x:c r="J7" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K7" s="95" t="str">
+      <x:c r="K7" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L7" s="95" t="str">
+      <x:c r="L7" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="M7" s="95" t="str">
+      <x:c r="M7" s="100" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N7" s="95" t="str"/>
-      <x:c r="O7" s="55" t="str"/>
-      <x:c r="P7" s="31"/>
-      <x:c r="Q7" s="31"/>
-      <x:c r="R7" s="31"/>
+      <x:c r="N7" s="100" t="str"/>
+      <x:c r="O7" s="60" t="str"/>
+      <x:c r="P7" s="32"/>
+      <x:c r="Q7" s="32"/>
+      <x:c r="R7" s="32"/>
+      <x:c r="S7" s="32"/>
+      <x:c r="T7" s="32"/>
     </x:row>
     <x:row r="8" ht="65" customHeight="1">
-      <x:c r="A8" s="52" t="str">
+      <x:c r="A8" s="57" t="str">
         <x:v>Operating cash flow · current year to date</x:v>
       </x:c>
-      <x:c r="B8" s="94" t="n">
+      <x:c r="B8" s="99" t="n">
         <x:v>16023000000</x:v>
       </x:c>
-      <x:c r="C8" s="54" t="d">
+      <x:c r="C8" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D8" s="54" t="d">
+      <x:c r="D8" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E8" s="95" t="str">
+      <x:c r="E8" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F8" s="54" t="d">
+      <x:c r="F8" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G8" s="95" t="str">
+      <x:c r="G8" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H8" s="95" t="str">
+      <x:c r="H8" s="100" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
       </x:c>
-      <x:c r="I8" s="95" t="str">
+      <x:c r="I8" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="J8" s="95" t="n">
+      <x:c r="J8" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K8" s="95" t="str">
+      <x:c r="K8" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L8" s="95" t="str">
+      <x:c r="L8" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M8" s="95" t="str">
+      <x:c r="M8" s="100" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N8" s="95" t="str"/>
-      <x:c r="O8" s="55" t="str"/>
-      <x:c r="P8" s="31"/>
-      <x:c r="Q8" s="31"/>
-      <x:c r="R8" s="31"/>
+      <x:c r="N8" s="100" t="str"/>
+      <x:c r="O8" s="60" t="str"/>
+      <x:c r="P8" s="32"/>
+      <x:c r="Q8" s="32"/>
+      <x:c r="R8" s="32"/>
+      <x:c r="S8" s="32"/>
+      <x:c r="T8" s="32"/>
     </x:row>
     <x:row r="9" ht="65" customHeight="1">
-      <x:c r="A9" s="52" t="str">
+      <x:c r="A9" s="57" t="str">
         <x:v>Operating cash flow · prior year to date</x:v>
       </x:c>
-      <x:c r="B9" s="94" t="n">
+      <x:c r="B9" s="99" t="n">
         <x:v>4753000000</x:v>
       </x:c>
-      <x:c r="C9" s="54" t="d">
+      <x:c r="C9" s="59" t="d">
         <x:v>2025-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D9" s="54" t="d">
+      <x:c r="D9" s="59" t="d">
         <x:v>2025-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E9" s="95" t="str">
+      <x:c r="E9" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F9" s="54" t="d">
+      <x:c r="F9" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G9" s="95" t="str">
+      <x:c r="G9" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H9" s="95" t="str">
+      <x:c r="H9" s="100" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
       </x:c>
-      <x:c r="I9" s="95" t="str">
+      <x:c r="I9" s="100" t="str">
         <x:v>c-14</x:v>
       </x:c>
-      <x:c r="J9" s="95" t="n">
+      <x:c r="J9" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K9" s="95" t="str">
+      <x:c r="K9" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L9" s="95" t="str">
+      <x:c r="L9" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M9" s="95" t="str">
+      <x:c r="M9" s="100" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N9" s="95" t="str"/>
-      <x:c r="O9" s="55" t="str"/>
-      <x:c r="P9" s="31"/>
-      <x:c r="Q9" s="31"/>
-      <x:c r="R9" s="31"/>
+      <x:c r="N9" s="100" t="str"/>
+      <x:c r="O9" s="60" t="str"/>
+      <x:c r="P9" s="32"/>
+      <x:c r="Q9" s="32"/>
+      <x:c r="R9" s="32"/>
+      <x:c r="S9" s="32"/>
+      <x:c r="T9" s="32"/>
     </x:row>
     <x:row r="10" ht="65" customHeight="1">
-      <x:c r="A10" s="52" t="str">
+      <x:c r="A10" s="57" t="str">
         <x:v>Purchases of property and equipment · fiscal year</x:v>
       </x:c>
-      <x:c r="B10" s="94" t="n">
+      <x:c r="B10" s="99" t="n">
         <x:v>7841000000</x:v>
       </x:c>
-      <x:c r="C10" s="54" t="d">
+      <x:c r="C10" s="59" t="d">
         <x:v>2025-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D10" s="54" t="d">
+      <x:c r="D10" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E10" s="95" t="str">
+      <x:c r="E10" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="F10" s="54" t="d">
+      <x:c r="F10" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G10" s="95" t="str">
+      <x:c r="G10" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="H10" s="95" t="str">
+      <x:c r="H10" s="100" t="str">
         <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
       </x:c>
-      <x:c r="I10" s="95" t="str">
+      <x:c r="I10" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="J10" s="95" t="n">
+      <x:c r="J10" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K10" s="95" t="str">
+      <x:c r="K10" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L10" s="95" t="str">
+      <x:c r="L10" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="M10" s="95" t="str">
+      <x:c r="M10" s="100" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N10" s="95" t="str"/>
-      <x:c r="O10" s="55" t="str"/>
-      <x:c r="P10" s="31"/>
-      <x:c r="Q10" s="31"/>
-      <x:c r="R10" s="31"/>
+      <x:c r="N10" s="100" t="str"/>
+      <x:c r="O10" s="60" t="str"/>
+      <x:c r="P10" s="32"/>
+      <x:c r="Q10" s="32"/>
+      <x:c r="R10" s="32"/>
+      <x:c r="S10" s="32"/>
+      <x:c r="T10" s="32"/>
     </x:row>
     <x:row r="11" ht="65" customHeight="1">
-      <x:c r="A11" s="52" t="str">
+      <x:c r="A11" s="57" t="str">
         <x:v>Purchases of property and equipment · current year to date</x:v>
       </x:c>
-      <x:c r="B11" s="94" t="n">
+      <x:c r="B11" s="99" t="n">
         <x:v>5259000000</x:v>
       </x:c>
-      <x:c r="C11" s="54" t="d">
+      <x:c r="C11" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D11" s="54" t="d">
+      <x:c r="D11" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E11" s="95" t="str">
+      <x:c r="E11" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F11" s="54" t="d">
+      <x:c r="F11" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G11" s="95" t="str">
+      <x:c r="G11" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H11" s="95" t="str">
+      <x:c r="H11" s="100" t="str">
         <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
       </x:c>
-      <x:c r="I11" s="95" t="str">
+      <x:c r="I11" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="J11" s="95" t="n">
+      <x:c r="J11" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K11" s="95" t="str">
+      <x:c r="K11" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L11" s="95" t="str">
+      <x:c r="L11" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M11" s="95" t="str">
+      <x:c r="M11" s="100" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N11" s="95" t="str"/>
-      <x:c r="O11" s="55" t="str"/>
-      <x:c r="P11" s="31"/>
-      <x:c r="Q11" s="31"/>
-      <x:c r="R11" s="31"/>
+      <x:c r="N11" s="100" t="str"/>
+      <x:c r="O11" s="60" t="str"/>
+      <x:c r="P11" s="32"/>
+      <x:c r="Q11" s="32"/>
+      <x:c r="R11" s="32"/>
+      <x:c r="S11" s="32"/>
+      <x:c r="T11" s="32"/>
     </x:row>
     <x:row r="12" ht="65" customHeight="1">
-      <x:c r="A12" s="59" t="str">
+      <x:c r="A12" s="64" t="str">
         <x:v>Purchases of property and equipment · prior year to date</x:v>
       </x:c>
-      <x:c r="B12" s="96" t="n">
+      <x:c r="B12" s="101" t="n">
         <x:v>3207000000</x:v>
       </x:c>
-      <x:c r="C12" s="61" t="d">
+      <x:c r="C12" s="66" t="d">
         <x:v>2025-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D12" s="61" t="d">
+      <x:c r="D12" s="66" t="d">
         <x:v>2025-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E12" s="97" t="str">
+      <x:c r="E12" s="102" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="F12" s="61" t="d">
+      <x:c r="F12" s="66" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G12" s="97" t="str">
+      <x:c r="G12" s="102" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="H12" s="97" t="str">
+      <x:c r="H12" s="102" t="str">
         <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
       </x:c>
-      <x:c r="I12" s="97" t="str">
+      <x:c r="I12" s="102" t="str">
         <x:v>c-14</x:v>
       </x:c>
-      <x:c r="J12" s="97" t="n">
+      <x:c r="J12" s="102" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K12" s="97" t="str">
+      <x:c r="K12" s="102" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="L12" s="97" t="str">
+      <x:c r="L12" s="102" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="M12" s="97" t="str">
+      <x:c r="M12" s="102" t="str">
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
-      <x:c r="N12" s="97" t="str"/>
-      <x:c r="O12" s="62" t="str"/>
-      <x:c r="P12" s="31"/>
-      <x:c r="Q12" s="31"/>
-      <x:c r="R12" s="31"/>
+      <x:c r="N12" s="102" t="str"/>
+      <x:c r="O12" s="67" t="str"/>
+      <x:c r="P12" s="32"/>
+      <x:c r="Q12" s="32"/>
+      <x:c r="R12" s="32"/>
+      <x:c r="S12" s="32"/>
+      <x:c r="T12" s="32"/>
     </x:row>
     <x:row r="13" ht="65" customHeight="1">
-      <x:c r="A13" s="31"/>
-      <x:c r="B13" s="31"/>
-      <x:c r="C13" s="31"/>
-      <x:c r="D13" s="31"/>
-      <x:c r="E13" s="31"/>
-      <x:c r="F13" s="31"/>
-      <x:c r="G13" s="31"/>
-      <x:c r="H13" s="31"/>
-      <x:c r="I13" s="31"/>
-      <x:c r="J13" s="31"/>
-      <x:c r="K13" s="31"/>
-      <x:c r="L13" s="31"/>
-      <x:c r="M13" s="31"/>
-      <x:c r="N13" s="31"/>
-      <x:c r="O13" s="31"/>
-      <x:c r="P13" s="31"/>
-      <x:c r="Q13" s="31"/>
-      <x:c r="R13" s="31"/>
+      <x:c r="A13" s="32"/>
+      <x:c r="B13" s="32"/>
+      <x:c r="C13" s="32"/>
+      <x:c r="D13" s="32"/>
+      <x:c r="E13" s="32"/>
+      <x:c r="F13" s="32"/>
+      <x:c r="G13" s="32"/>
+      <x:c r="H13" s="32"/>
+      <x:c r="I13" s="32"/>
+      <x:c r="J13" s="32"/>
+      <x:c r="K13" s="32"/>
+      <x:c r="L13" s="32"/>
+      <x:c r="M13" s="32"/>
+      <x:c r="N13" s="32"/>
+      <x:c r="O13" s="32"/>
+      <x:c r="P13" s="32"/>
+      <x:c r="Q13" s="32"/>
+      <x:c r="R13" s="32"/>
+      <x:c r="S13" s="32"/>
+      <x:c r="T13" s="32"/>
     </x:row>
     <x:row r="14" ht="65" customHeight="1">
-      <x:c r="A14" s="31"/>
-      <x:c r="B14" s="31"/>
-      <x:c r="C14" s="31"/>
-      <x:c r="D14" s="31"/>
-      <x:c r="E14" s="31"/>
-      <x:c r="F14" s="31"/>
-      <x:c r="G14" s="31"/>
-      <x:c r="H14" s="31"/>
-      <x:c r="I14" s="31"/>
-      <x:c r="J14" s="31"/>
-      <x:c r="K14" s="31"/>
-      <x:c r="L14" s="31"/>
-      <x:c r="M14" s="31"/>
-      <x:c r="N14" s="31"/>
-      <x:c r="O14" s="31"/>
-      <x:c r="P14" s="31"/>
-      <x:c r="Q14" s="31"/>
-      <x:c r="R14" s="31"/>
+      <x:c r="A14" s="32"/>
+      <x:c r="B14" s="32"/>
+      <x:c r="C14" s="32"/>
+      <x:c r="D14" s="32"/>
+      <x:c r="E14" s="32"/>
+      <x:c r="F14" s="32"/>
+      <x:c r="G14" s="32"/>
+      <x:c r="H14" s="32"/>
+      <x:c r="I14" s="32"/>
+      <x:c r="J14" s="32"/>
+      <x:c r="K14" s="32"/>
+      <x:c r="L14" s="32"/>
+      <x:c r="M14" s="32"/>
+      <x:c r="N14" s="32"/>
+      <x:c r="O14" s="32"/>
+      <x:c r="P14" s="32"/>
+      <x:c r="Q14" s="32"/>
+      <x:c r="R14" s="32"/>
+      <x:c r="S14" s="32"/>
+      <x:c r="T14" s="32"/>
     </x:row>
     <x:row r="15" ht="80" customHeight="1">
-      <x:c r="A15" s="78" t="str">
+      <x:c r="A15" s="83" t="str">
         <x:v>Disclosure</x:v>
       </x:c>
-      <x:c r="B15" s="79" t="str">
+      <x:c r="B15" s="84" t="str">
         <x:v>Amount as disclosed</x:v>
       </x:c>
-      <x:c r="C15" s="79" t="str">
+      <x:c r="C15" s="84" t="str">
         <x:v>As of</x:v>
       </x:c>
-      <x:c r="D15" s="79" t="str">
+      <x:c r="D15" s="84" t="str">
         <x:v>Form</x:v>
       </x:c>
-      <x:c r="E15" s="79" t="str">
+      <x:c r="E15" s="84" t="str">
         <x:v>Filed</x:v>
       </x:c>
-      <x:c r="F15" s="79" t="str">
+      <x:c r="F15" s="84" t="str">
         <x:v>Accession</x:v>
       </x:c>
-      <x:c r="G15" s="79" t="str">
+      <x:c r="G15" s="84" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="H15" s="79" t="str">
+      <x:c r="H15" s="84" t="str">
         <x:v>Filing location</x:v>
       </x:c>
-      <x:c r="I15" s="80" t="str">
+      <x:c r="I15" s="85" t="str">
         <x:v>Conditions</x:v>
       </x:c>
-      <x:c r="J15" s="31"/>
-      <x:c r="K15" s="31"/>
-      <x:c r="L15" s="31"/>
-      <x:c r="M15" s="31"/>
-      <x:c r="N15" s="31"/>
-      <x:c r="O15" s="31"/>
-      <x:c r="P15" s="31"/>
-      <x:c r="Q15" s="31"/>
-      <x:c r="R15" s="31"/>
+      <x:c r="J15" s="32"/>
+      <x:c r="K15" s="32"/>
+      <x:c r="L15" s="32"/>
+      <x:c r="M15" s="32"/>
+      <x:c r="N15" s="32"/>
+      <x:c r="O15" s="32"/>
+      <x:c r="P15" s="32"/>
+      <x:c r="Q15" s="32"/>
+      <x:c r="R15" s="32"/>
+      <x:c r="S15" s="32"/>
+      <x:c r="T15" s="32"/>
     </x:row>
     <x:row r="16" ht="80" customHeight="1">
-      <x:c r="A16" s="52" t="str">
+      <x:c r="A16" s="57" t="str">
         <x:v>Pending AtaiBeckley acquisition</x:v>
       </x:c>
-      <x:c r="B16" s="95" t="str">
+      <x:c r="B16" s="100" t="str">
         <x:v>Approximately $2.8B</x:v>
       </x:c>
-      <x:c r="C16" s="54" t="d">
+      <x:c r="C16" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D16" s="95" t="str">
+      <x:c r="D16" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="E16" s="54" t="d">
+      <x:c r="E16" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F16" s="95" t="str">
+      <x:c r="F16" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="G16" s="95" t="str">
+      <x:c r="G16" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="H16" s="95" t="str">
+      <x:c r="H16" s="100" t="str">
         <x:v>10-Q MD&amp;A, p. 31</x:v>
       </x:c>
-      <x:c r="I16" s="55" t="str">
+      <x:c r="I16" s="60" t="str">
         <x:v>Potential payment at closing, subject to closing conditions. Not recognized as borrowing.</x:v>
       </x:c>
-      <x:c r="J16" s="31"/>
-      <x:c r="K16" s="31"/>
-      <x:c r="L16" s="31"/>
-      <x:c r="M16" s="31"/>
-      <x:c r="N16" s="31"/>
-      <x:c r="O16" s="31"/>
-      <x:c r="P16" s="31"/>
-      <x:c r="Q16" s="31"/>
-      <x:c r="R16" s="31"/>
+      <x:c r="J16" s="32"/>
+      <x:c r="K16" s="32"/>
+      <x:c r="L16" s="32"/>
+      <x:c r="M16" s="32"/>
+      <x:c r="N16" s="32"/>
+      <x:c r="O16" s="32"/>
+      <x:c r="P16" s="32"/>
+      <x:c r="Q16" s="32"/>
+      <x:c r="R16" s="32"/>
+      <x:c r="S16" s="32"/>
+      <x:c r="T16" s="32"/>
     </x:row>
     <x:row r="17" ht="80" customHeight="1">
-      <x:c r="A17" s="59" t="str">
+      <x:c r="A17" s="64" t="str">
         <x:v>Venture fund commitments</x:v>
       </x:c>
-      <x:c r="B17" s="97" t="str">
+      <x:c r="B17" s="102" t="str">
         <x:v>Approximately $806M</x:v>
       </x:c>
-      <x:c r="C17" s="61" t="d">
+      <x:c r="C17" s="66" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D17" s="97" t="str">
+      <x:c r="D17" s="102" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="E17" s="61" t="d">
+      <x:c r="E17" s="66" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F17" s="97" t="str">
+      <x:c r="F17" s="102" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="G17" s="97" t="str">
+      <x:c r="G17" s="102" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="H17" s="97" t="str">
+      <x:c r="H17" s="102" t="str">
         <x:v>10-Q MD&amp;A, p. 31; Note 8</x:v>
       </x:c>
-      <x:c r="I17" s="62" t="str">
+      <x:c r="I17" s="67" t="str">
         <x:v>Expected to be paid over up to ten years. Not recognized as borrowing.</x:v>
       </x:c>
-      <x:c r="J17" s="31"/>
-      <x:c r="K17" s="31"/>
-      <x:c r="L17" s="31"/>
-      <x:c r="M17" s="31"/>
-      <x:c r="N17" s="31"/>
-      <x:c r="O17" s="31"/>
-      <x:c r="P17" s="31"/>
-      <x:c r="Q17" s="31"/>
-      <x:c r="R17" s="31"/>
+      <x:c r="J17" s="32"/>
+      <x:c r="K17" s="32"/>
+      <x:c r="L17" s="32"/>
+      <x:c r="M17" s="32"/>
+      <x:c r="N17" s="32"/>
+      <x:c r="O17" s="32"/>
+      <x:c r="P17" s="32"/>
+      <x:c r="Q17" s="32"/>
+      <x:c r="R17" s="32"/>
+      <x:c r="S17" s="32"/>
+      <x:c r="T17" s="32"/>
     </x:row>
     <x:row r="18" ht="65" customHeight="1">
-      <x:c r="A18" s="31"/>
-      <x:c r="B18" s="31"/>
-      <x:c r="C18" s="31"/>
-      <x:c r="D18" s="31"/>
-      <x:c r="E18" s="31"/>
-      <x:c r="F18" s="31"/>
-      <x:c r="G18" s="31"/>
-      <x:c r="H18" s="31"/>
-      <x:c r="I18" s="31"/>
-      <x:c r="J18" s="31"/>
-      <x:c r="K18" s="31"/>
-      <x:c r="L18" s="31"/>
-      <x:c r="M18" s="31"/>
-      <x:c r="N18" s="31"/>
-      <x:c r="O18" s="31"/>
-      <x:c r="P18" s="31"/>
-      <x:c r="Q18" s="31"/>
-      <x:c r="R18" s="31"/>
+      <x:c r="A18" s="32"/>
+      <x:c r="B18" s="32"/>
+      <x:c r="C18" s="32"/>
+      <x:c r="D18" s="32"/>
+      <x:c r="E18" s="32"/>
+      <x:c r="F18" s="32"/>
+      <x:c r="G18" s="32"/>
+      <x:c r="H18" s="32"/>
+      <x:c r="I18" s="32"/>
+      <x:c r="J18" s="32"/>
+      <x:c r="K18" s="32"/>
+      <x:c r="L18" s="32"/>
+      <x:c r="M18" s="32"/>
+      <x:c r="N18" s="32"/>
+      <x:c r="O18" s="32"/>
+      <x:c r="P18" s="32"/>
+      <x:c r="Q18" s="32"/>
+      <x:c r="R18" s="32"/>
+      <x:c r="S18" s="32"/>
+      <x:c r="T18" s="32"/>
     </x:row>
     <x:row r="19" ht="65" customHeight="1">
-      <x:c r="A19" s="31"/>
-      <x:c r="B19" s="31"/>
-      <x:c r="C19" s="31"/>
-      <x:c r="D19" s="31"/>
-      <x:c r="E19" s="31"/>
-      <x:c r="F19" s="31"/>
-      <x:c r="G19" s="31"/>
-      <x:c r="H19" s="31"/>
-      <x:c r="I19" s="31"/>
-      <x:c r="J19" s="31"/>
-      <x:c r="K19" s="31"/>
-      <x:c r="L19" s="31"/>
-      <x:c r="M19" s="31"/>
-      <x:c r="N19" s="31"/>
-      <x:c r="O19" s="31"/>
-      <x:c r="P19" s="31"/>
-      <x:c r="Q19" s="31"/>
-      <x:c r="R19" s="31"/>
+      <x:c r="A19" s="32"/>
+      <x:c r="B19" s="32"/>
+      <x:c r="C19" s="32"/>
+      <x:c r="D19" s="32"/>
+      <x:c r="E19" s="32"/>
+      <x:c r="F19" s="32"/>
+      <x:c r="G19" s="32"/>
+      <x:c r="H19" s="32"/>
+      <x:c r="I19" s="32"/>
+      <x:c r="J19" s="32"/>
+      <x:c r="K19" s="32"/>
+      <x:c r="L19" s="32"/>
+      <x:c r="M19" s="32"/>
+      <x:c r="N19" s="32"/>
+      <x:c r="O19" s="32"/>
+      <x:c r="P19" s="32"/>
+      <x:c r="Q19" s="32"/>
+      <x:c r="R19" s="32"/>
+      <x:c r="S19" s="32"/>
+      <x:c r="T19" s="32"/>
     </x:row>
     <x:row r="20" ht="85" customHeight="1">
-      <x:c r="A20" s="78" t="str">
+      <x:c r="A20" s="83" t="str">
         <x:v>Review input key</x:v>
       </x:c>
-      <x:c r="B20" s="79" t="str">
+      <x:c r="B20" s="84" t="str">
         <x:v>USD millions</x:v>
       </x:c>
-      <x:c r="C20" s="79" t="str">
+      <x:c r="C20" s="84" t="str">
         <x:v>Label</x:v>
       </x:c>
-      <x:c r="D20" s="79" t="str">
+      <x:c r="D20" s="84" t="str">
         <x:v>Period start</x:v>
       </x:c>
-      <x:c r="E20" s="79" t="str">
+      <x:c r="E20" s="84" t="str">
         <x:v>Date / disclosure basis</x:v>
       </x:c>
-      <x:c r="F20" s="79" t="str">
+      <x:c r="F20" s="84" t="str">
         <x:v>Form</x:v>
       </x:c>
-      <x:c r="G20" s="79" t="str">
+      <x:c r="G20" s="84" t="str">
         <x:v>Filed</x:v>
       </x:c>
-      <x:c r="H20" s="79" t="str">
+      <x:c r="H20" s="84" t="str">
         <x:v>Accession</x:v>
       </x:c>
-      <x:c r="I20" s="79" t="str">
+      <x:c r="I20" s="84" t="str">
         <x:v>Tag</x:v>
       </x:c>
-      <x:c r="J20" s="79" t="str">
+      <x:c r="J20" s="84" t="str">
         <x:v>Context</x:v>
       </x:c>
-      <x:c r="K20" s="79" t="str">
+      <x:c r="K20" s="84" t="str">
         <x:v>Scale</x:v>
       </x:c>
-      <x:c r="L20" s="79" t="str">
+      <x:c r="L20" s="84" t="str">
         <x:v>Decimals</x:v>
       </x:c>
-      <x:c r="M20" s="79" t="str">
+      <x:c r="M20" s="84" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="N20" s="79" t="str">
+      <x:c r="N20" s="84" t="str">
         <x:v>Filing location</x:v>
       </x:c>
-      <x:c r="O20" s="79" t="str">
+      <x:c r="O20" s="84" t="str">
         <x:v>Source kind</x:v>
       </x:c>
-      <x:c r="P20" s="79" t="str">
+      <x:c r="P20" s="84" t="str">
         <x:v>Dimensions</x:v>
       </x:c>
-      <x:c r="Q20" s="79" t="str">
+      <x:c r="Q20" s="84" t="str">
         <x:v>Limitations</x:v>
       </x:c>
-      <x:c r="R20" s="80" t="str">
+      <x:c r="R20" s="85" t="str">
         <x:v>Reviewed source SHA256</x:v>
       </x:c>
+      <x:c r="S20" s="83" t="str">
+        <x:v>Fixed coupon, fraction</x:v>
+      </x:c>
+      <x:c r="T20" s="85" t="str">
+        <x:v>Compounded SOFR margin, fraction</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="85" customHeight="1">
-      <x:c r="A21" s="52" t="str">
+      <x:c r="A21" s="57" t="str">
         <x:v>ocf</x:v>
       </x:c>
-      <x:c r="B21" s="94" t="n">
+      <x:c r="B21" s="99" t="n">
         <x:v>16023000000</x:v>
       </x:c>
-      <x:c r="C21" s="95" t="str">
+      <x:c r="C21" s="100" t="str">
         <x:v>Operating cash flow</x:v>
       </x:c>
-      <x:c r="D21" s="54" t="d">
+      <x:c r="D21" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E21" s="54" t="d">
+      <x:c r="E21" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F21" s="95" t="str">
+      <x:c r="F21" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G21" s="54" t="d">
+      <x:c r="G21" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H21" s="95" t="str">
+      <x:c r="H21" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I21" s="95" t="str">
+      <x:c r="I21" s="100" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
       </x:c>
-      <x:c r="J21" s="95" t="str">
+      <x:c r="J21" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K21" s="95" t="n">
+      <x:c r="K21" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L21" s="95" t="str">
+      <x:c r="L21" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M21" s="95" t="str">
+      <x:c r="M21" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N21" s="95" t="str">
+      <x:c r="N21" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O21" s="95" t="str">
+      <x:c r="O21" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P21" s="95" t="str">
+      <x:c r="P21" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q21" s="95" t="str"/>
-      <x:c r="R21" s="55" t="str">
+      <x:c r="Q21" s="100" t="str"/>
+      <x:c r="R21" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S21" s="134"/>
+      <x:c r="T21" s="135"/>
     </x:row>
     <x:row r="22" ht="85" customHeight="1">
-      <x:c r="A22" s="52" t="str">
+      <x:c r="A22" s="57" t="str">
         <x:v>capex</x:v>
       </x:c>
-      <x:c r="B22" s="94" t="n">
+      <x:c r="B22" s="99" t="n">
         <x:v>5259000000</x:v>
       </x:c>
-      <x:c r="C22" s="95" t="str">
+      <x:c r="C22" s="100" t="str">
         <x:v>Cash purchases of other PP&amp;E</x:v>
       </x:c>
-      <x:c r="D22" s="54" t="d">
+      <x:c r="D22" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E22" s="54" t="d">
+      <x:c r="E22" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F22" s="95" t="str">
+      <x:c r="F22" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G22" s="54" t="d">
+      <x:c r="G22" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H22" s="95" t="str">
+      <x:c r="H22" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I22" s="95" t="str">
+      <x:c r="I22" s="100" t="str">
         <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
       </x:c>
-      <x:c r="J22" s="95" t="str">
+      <x:c r="J22" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K22" s="95" t="n">
+      <x:c r="K22" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L22" s="95" t="str">
+      <x:c r="L22" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M22" s="95" t="str">
+      <x:c r="M22" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N22" s="95" t="str">
+      <x:c r="N22" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O22" s="95" t="str">
+      <x:c r="O22" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P22" s="95" t="str">
+      <x:c r="P22" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q22" s="95" t="str"/>
-      <x:c r="R22" s="55" t="str">
+      <x:c r="Q22" s="100" t="str"/>
+      <x:c r="R22" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S22" s="134"/>
+      <x:c r="T22" s="135"/>
     </x:row>
     <x:row r="23" ht="85" customHeight="1">
-      <x:c r="A23" s="52" t="str">
+      <x:c r="A23" s="57" t="str">
         <x:v>investments</x:v>
       </x:c>
-      <x:c r="B23" s="94" t="n">
+      <x:c r="B23" s="99" t="n">
         <x:v>604000000</x:v>
       </x:c>
-      <x:c r="C23" s="95" t="str">
+      <x:c r="C23" s="100" t="str">
         <x:v>Investment purchases</x:v>
       </x:c>
-      <x:c r="D23" s="54" t="d">
+      <x:c r="D23" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E23" s="54" t="d">
+      <x:c r="E23" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F23" s="95" t="str">
+      <x:c r="F23" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G23" s="54" t="d">
+      <x:c r="G23" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H23" s="95" t="str">
+      <x:c r="H23" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I23" s="95" t="str">
+      <x:c r="I23" s="100" t="str">
         <x:v>us-gaap:PaymentsToAcquireOtherInvestments</x:v>
       </x:c>
-      <x:c r="J23" s="95" t="str">
+      <x:c r="J23" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K23" s="95" t="n">
+      <x:c r="K23" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L23" s="95" t="str">
+      <x:c r="L23" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M23" s="95" t="str">
+      <x:c r="M23" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N23" s="95" t="str">
+      <x:c r="N23" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O23" s="95" t="str">
+      <x:c r="O23" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P23" s="95" t="str">
+      <x:c r="P23" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q23" s="95" t="str"/>
-      <x:c r="R23" s="55" t="str">
+      <x:c r="Q23" s="100" t="str"/>
+      <x:c r="R23" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S23" s="134"/>
+      <x:c r="T23" s="135"/>
     </x:row>
     <x:row r="24" ht="85" customHeight="1">
-      <x:c r="A24" s="52" t="str">
+      <x:c r="A24" s="57" t="str">
         <x:v>iprd</x:v>
       </x:c>
-      <x:c r="B24" s="94" t="n">
+      <x:c r="B24" s="99" t="n">
         <x:v>3486000000</x:v>
       </x:c>
-      <x:c r="C24" s="95" t="str">
+      <x:c r="C24" s="100" t="str">
         <x:v>Purchased in-process R&amp;D</x:v>
       </x:c>
-      <x:c r="D24" s="54" t="d">
+      <x:c r="D24" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E24" s="54" t="d">
+      <x:c r="E24" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F24" s="95" t="str">
+      <x:c r="F24" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G24" s="54" t="d">
+      <x:c r="G24" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H24" s="95" t="str">
+      <x:c r="H24" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I24" s="95" t="str">
+      <x:c r="I24" s="100" t="str">
         <x:v>us-gaap:PaymentsToAcquireInProcessResearchAndDevelopment</x:v>
       </x:c>
-      <x:c r="J24" s="95" t="str">
+      <x:c r="J24" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K24" s="95" t="n">
+      <x:c r="K24" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L24" s="95" t="str">
+      <x:c r="L24" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M24" s="95" t="str">
+      <x:c r="M24" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N24" s="95" t="str">
+      <x:c r="N24" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O24" s="95" t="str">
+      <x:c r="O24" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P24" s="95" t="str">
+      <x:c r="P24" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q24" s="95" t="str"/>
-      <x:c r="R24" s="55" t="str">
+      <x:c r="Q24" s="100" t="str"/>
+      <x:c r="R24" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S24" s="134"/>
+      <x:c r="T24" s="135"/>
     </x:row>
     <x:row r="25" ht="85" customHeight="1">
-      <x:c r="A25" s="52" t="str">
+      <x:c r="A25" s="57" t="str">
         <x:v>acquisitions</x:v>
       </x:c>
-      <x:c r="B25" s="94" t="n">
+      <x:c r="B25" s="99" t="n">
         <x:v>9805000000</x:v>
       </x:c>
-      <x:c r="C25" s="95" t="str">
+      <x:c r="C25" s="100" t="str">
         <x:v>Acquisitions, net of cash acquired</x:v>
       </x:c>
-      <x:c r="D25" s="54" t="d">
+      <x:c r="D25" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E25" s="54" t="d">
+      <x:c r="E25" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F25" s="95" t="str">
+      <x:c r="F25" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G25" s="54" t="d">
+      <x:c r="G25" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H25" s="95" t="str">
+      <x:c r="H25" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I25" s="95" t="str">
+      <x:c r="I25" s="100" t="str">
         <x:v>us-gaap:OtherPaymentsToAcquireBusinesses</x:v>
       </x:c>
-      <x:c r="J25" s="95" t="str">
+      <x:c r="J25" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K25" s="95" t="n">
+      <x:c r="K25" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L25" s="95" t="str">
+      <x:c r="L25" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M25" s="95" t="str">
+      <x:c r="M25" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N25" s="95" t="str">
+      <x:c r="N25" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O25" s="95" t="str">
+      <x:c r="O25" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P25" s="95" t="str">
+      <x:c r="P25" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q25" s="95" t="str"/>
-      <x:c r="R25" s="55" t="str">
+      <x:c r="Q25" s="100" t="str"/>
+      <x:c r="R25" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S25" s="134"/>
+      <x:c r="T25" s="135"/>
     </x:row>
     <x:row r="26" ht="85" customHeight="1">
-      <x:c r="A26" s="52" t="str">
+      <x:c r="A26" s="57" t="str">
         <x:v>other_investing</x:v>
       </x:c>
-      <x:c r="B26" s="94" t="n">
+      <x:c r="B26" s="99" t="n">
         <x:v>158000000</x:v>
       </x:c>
-      <x:c r="C26" s="95" t="str">
+      <x:c r="C26" s="100" t="str">
         <x:v>Other investing cash used</x:v>
       </x:c>
-      <x:c r="D26" s="54" t="d">
+      <x:c r="D26" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E26" s="54" t="d">
+      <x:c r="E26" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F26" s="95" t="str">
+      <x:c r="F26" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G26" s="54" t="d">
+      <x:c r="G26" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H26" s="95" t="str">
+      <x:c r="H26" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I26" s="95" t="str">
+      <x:c r="I26" s="100" t="str">
         <x:v>us-gaap:PaymentsForProceedsFromOtherInvestingActivities</x:v>
       </x:c>
-      <x:c r="J26" s="95" t="str">
+      <x:c r="J26" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K26" s="95" t="n">
+      <x:c r="K26" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L26" s="95" t="str">
+      <x:c r="L26" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M26" s="95" t="str">
+      <x:c r="M26" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N26" s="95" t="str">
+      <x:c r="N26" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O26" s="95" t="str">
+      <x:c r="O26" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P26" s="95" t="str">
+      <x:c r="P26" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q26" s="95" t="str"/>
-      <x:c r="R26" s="55" t="str">
+      <x:c r="Q26" s="100" t="str"/>
+      <x:c r="R26" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S26" s="134"/>
+      <x:c r="T26" s="135"/>
     </x:row>
     <x:row r="27" ht="85" customHeight="1">
-      <x:c r="A27" s="52" t="str">
+      <x:c r="A27" s="57" t="str">
         <x:v>investing_total</x:v>
       </x:c>
-      <x:c r="B27" s="94" t="n">
+      <x:c r="B27" s="99" t="n">
         <x:v>-19312000000</x:v>
       </x:c>
-      <x:c r="C27" s="95" t="str">
+      <x:c r="C27" s="100" t="str">
         <x:v>Reported net investing cash flow</x:v>
       </x:c>
-      <x:c r="D27" s="54" t="d">
+      <x:c r="D27" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E27" s="54" t="d">
+      <x:c r="E27" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F27" s="95" t="str">
+      <x:c r="F27" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G27" s="54" t="d">
+      <x:c r="G27" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H27" s="95" t="str">
+      <x:c r="H27" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I27" s="95" t="str">
+      <x:c r="I27" s="100" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInInvestingActivities</x:v>
       </x:c>
-      <x:c r="J27" s="95" t="str">
+      <x:c r="J27" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K27" s="95" t="n">
+      <x:c r="K27" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L27" s="95" t="str">
+      <x:c r="L27" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M27" s="95" t="str">
+      <x:c r="M27" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N27" s="95" t="str">
+      <x:c r="N27" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O27" s="95" t="str">
+      <x:c r="O27" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P27" s="95" t="str">
+      <x:c r="P27" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q27" s="95" t="str"/>
-      <x:c r="R27" s="55" t="str">
+      <x:c r="Q27" s="100" t="str"/>
+      <x:c r="R27" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S27" s="134"/>
+      <x:c r="T27" s="135"/>
     </x:row>
     <x:row r="28" ht="85" customHeight="1">
-      <x:c r="A28" s="52" t="str">
+      <x:c r="A28" s="57" t="str">
         <x:v>dividends</x:v>
       </x:c>
-      <x:c r="B28" s="94" t="n">
+      <x:c r="B28" s="99" t="n">
         <x:v>3094000000</x:v>
       </x:c>
-      <x:c r="C28" s="95" t="str">
+      <x:c r="C28" s="100" t="str">
         <x:v>Cash dividends</x:v>
       </x:c>
-      <x:c r="D28" s="54" t="d">
+      <x:c r="D28" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E28" s="54" t="d">
+      <x:c r="E28" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F28" s="95" t="str">
+      <x:c r="F28" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G28" s="54" t="d">
+      <x:c r="G28" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H28" s="95" t="str">
+      <x:c r="H28" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I28" s="95" t="str">
+      <x:c r="I28" s="100" t="str">
         <x:v>us-gaap:PaymentsOfDividends</x:v>
       </x:c>
-      <x:c r="J28" s="95" t="str">
+      <x:c r="J28" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K28" s="95" t="n">
+      <x:c r="K28" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L28" s="95" t="str">
+      <x:c r="L28" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M28" s="95" t="str">
+      <x:c r="M28" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N28" s="95" t="str">
+      <x:c r="N28" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O28" s="95" t="str">
+      <x:c r="O28" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P28" s="95" t="str">
+      <x:c r="P28" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q28" s="95" t="str"/>
-      <x:c r="R28" s="55" t="str">
+      <x:c r="Q28" s="100" t="str"/>
+      <x:c r="R28" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S28" s="134"/>
+      <x:c r="T28" s="135"/>
     </x:row>
     <x:row r="29" ht="85" customHeight="1">
-      <x:c r="A29" s="52" t="str">
+      <x:c r="A29" s="57" t="str">
         <x:v>short_debt</x:v>
       </x:c>
-      <x:c r="B29" s="94" t="n">
+      <x:c r="B29" s="99" t="n">
         <x:v>5284000000</x:v>
       </x:c>
-      <x:c r="C29" s="95" t="str">
+      <x:c r="C29" s="100" t="str">
         <x:v>Short-term borrowings, net</x:v>
       </x:c>
-      <x:c r="D29" s="54" t="d">
+      <x:c r="D29" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E29" s="54" t="d">
+      <x:c r="E29" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F29" s="95" t="str">
+      <x:c r="F29" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G29" s="54" t="d">
+      <x:c r="G29" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H29" s="95" t="str">
+      <x:c r="H29" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I29" s="95" t="str">
+      <x:c r="I29" s="100" t="str">
         <x:v>us-gaap:ProceedsFromRepaymentsOfShortTermDebt</x:v>
       </x:c>
-      <x:c r="J29" s="95" t="str">
+      <x:c r="J29" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K29" s="95" t="n">
+      <x:c r="K29" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L29" s="95" t="str">
+      <x:c r="L29" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M29" s="95" t="str">
+      <x:c r="M29" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N29" s="95" t="str">
+      <x:c r="N29" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O29" s="95" t="str">
+      <x:c r="O29" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P29" s="95" t="str">
+      <x:c r="P29" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q29" s="95" t="str"/>
-      <x:c r="R29" s="55" t="str">
+      <x:c r="Q29" s="100" t="str"/>
+      <x:c r="R29" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S29" s="134"/>
+      <x:c r="T29" s="135"/>
     </x:row>
     <x:row r="30" ht="85" customHeight="1">
-      <x:c r="A30" s="52" t="str">
+      <x:c r="A30" s="57" t="str">
         <x:v>long_proceeds</x:v>
       </x:c>
-      <x:c r="B30" s="94" t="n">
+      <x:c r="B30" s="99" t="n">
         <x:v>8941000000</x:v>
       </x:c>
-      <x:c r="C30" s="95" t="str">
+      <x:c r="C30" s="100" t="str">
         <x:v>Long-term borrowing proceeds, net</x:v>
       </x:c>
-      <x:c r="D30" s="54" t="d">
+      <x:c r="D30" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E30" s="54" t="d">
+      <x:c r="E30" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F30" s="95" t="str">
+      <x:c r="F30" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G30" s="54" t="d">
+      <x:c r="G30" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H30" s="95" t="str">
+      <x:c r="H30" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I30" s="95" t="str">
+      <x:c r="I30" s="100" t="str">
         <x:v>us-gaap:ProceedsFromIssuanceOfLongTermDebt</x:v>
       </x:c>
-      <x:c r="J30" s="95" t="str">
+      <x:c r="J30" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K30" s="95" t="n">
+      <x:c r="K30" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L30" s="95" t="str">
+      <x:c r="L30" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M30" s="95" t="str">
+      <x:c r="M30" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N30" s="95" t="str">
+      <x:c r="N30" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O30" s="95" t="str">
+      <x:c r="O30" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P30" s="95" t="str">
+      <x:c r="P30" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q30" s="95" t="str"/>
-      <x:c r="R30" s="55" t="str">
+      <x:c r="Q30" s="100" t="str"/>
+      <x:c r="R30" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S30" s="134"/>
+      <x:c r="T30" s="135"/>
     </x:row>
     <x:row r="31" ht="85" customHeight="1">
-      <x:c r="A31" s="52" t="str">
+      <x:c r="A31" s="57" t="str">
         <x:v>long_repayments</x:v>
       </x:c>
-      <x:c r="B31" s="94" t="n">
+      <x:c r="B31" s="99" t="n">
         <x:v>1623000000</x:v>
       </x:c>
-      <x:c r="C31" s="95" t="str">
+      <x:c r="C31" s="100" t="str">
         <x:v>Long-term debt repaid</x:v>
       </x:c>
-      <x:c r="D31" s="54" t="d">
+      <x:c r="D31" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E31" s="54" t="d">
+      <x:c r="E31" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F31" s="95" t="str">
+      <x:c r="F31" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G31" s="54" t="d">
+      <x:c r="G31" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H31" s="95" t="str">
+      <x:c r="H31" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I31" s="95" t="str">
+      <x:c r="I31" s="100" t="str">
         <x:v>us-gaap:RepaymentsOfLongTermDebt</x:v>
       </x:c>
-      <x:c r="J31" s="95" t="str">
+      <x:c r="J31" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K31" s="95" t="n">
+      <x:c r="K31" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L31" s="95" t="str">
+      <x:c r="L31" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M31" s="95" t="str">
+      <x:c r="M31" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N31" s="95" t="str">
+      <x:c r="N31" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O31" s="95" t="str">
+      <x:c r="O31" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P31" s="95" t="str">
+      <x:c r="P31" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q31" s="95" t="str"/>
-      <x:c r="R31" s="55" t="str">
+      <x:c r="Q31" s="100" t="str"/>
+      <x:c r="R31" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S31" s="134"/>
+      <x:c r="T31" s="135"/>
     </x:row>
     <x:row r="32" ht="85" customHeight="1">
-      <x:c r="A32" s="52" t="str">
+      <x:c r="A32" s="57" t="str">
         <x:v>buybacks</x:v>
       </x:c>
-      <x:c r="B32" s="94" t="n">
+      <x:c r="B32" s="99" t="n">
         <x:v>3957000000</x:v>
       </x:c>
-      <x:c r="C32" s="95" t="str">
+      <x:c r="C32" s="100" t="str">
         <x:v>Share repurchases</x:v>
       </x:c>
-      <x:c r="D32" s="54" t="d">
+      <x:c r="D32" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E32" s="54" t="d">
+      <x:c r="E32" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F32" s="95" t="str">
+      <x:c r="F32" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G32" s="54" t="d">
+      <x:c r="G32" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H32" s="95" t="str">
+      <x:c r="H32" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I32" s="95" t="str">
+      <x:c r="I32" s="100" t="str">
         <x:v>us-gaap:PaymentsForRepurchaseOfCommonStock</x:v>
       </x:c>
-      <x:c r="J32" s="95" t="str">
+      <x:c r="J32" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K32" s="95" t="n">
+      <x:c r="K32" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L32" s="95" t="str">
+      <x:c r="L32" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M32" s="95" t="str">
+      <x:c r="M32" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N32" s="95" t="str">
+      <x:c r="N32" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O32" s="95" t="str">
+      <x:c r="O32" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P32" s="95" t="str">
+      <x:c r="P32" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q32" s="95" t="str"/>
-      <x:c r="R32" s="55" t="str">
+      <x:c r="Q32" s="100" t="str"/>
+      <x:c r="R32" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S32" s="134"/>
+      <x:c r="T32" s="135"/>
     </x:row>
     <x:row r="33" ht="85" customHeight="1">
-      <x:c r="A33" s="52" t="str">
+      <x:c r="A33" s="57" t="str">
         <x:v>other_financing</x:v>
       </x:c>
-      <x:c r="B33" s="94" t="n">
+      <x:c r="B33" s="99" t="n">
         <x:v>-595000000</x:v>
       </x:c>
-      <x:c r="C33" s="95" t="str">
+      <x:c r="C33" s="100" t="str">
         <x:v>Other financing cash flow</x:v>
       </x:c>
-      <x:c r="D33" s="54" t="d">
+      <x:c r="D33" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E33" s="54" t="d">
+      <x:c r="E33" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F33" s="95" t="str">
+      <x:c r="F33" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G33" s="54" t="d">
+      <x:c r="G33" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H33" s="95" t="str">
+      <x:c r="H33" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I33" s="95" t="str">
+      <x:c r="I33" s="100" t="str">
         <x:v>us-gaap:ProceedsFromPaymentsForOtherFinancingActivities</x:v>
       </x:c>
-      <x:c r="J33" s="95" t="str">
+      <x:c r="J33" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K33" s="95" t="n">
+      <x:c r="K33" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L33" s="95" t="str">
+      <x:c r="L33" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M33" s="95" t="str">
+      <x:c r="M33" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N33" s="95" t="str">
+      <x:c r="N33" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O33" s="95" t="str">
+      <x:c r="O33" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P33" s="95" t="str">
+      <x:c r="P33" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q33" s="95" t="str"/>
-      <x:c r="R33" s="55" t="str">
+      <x:c r="Q33" s="100" t="str"/>
+      <x:c r="R33" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S33" s="134"/>
+      <x:c r="T33" s="135"/>
     </x:row>
     <x:row r="34" ht="85" customHeight="1">
-      <x:c r="A34" s="52" t="str">
+      <x:c r="A34" s="57" t="str">
         <x:v>financing_total</x:v>
       </x:c>
-      <x:c r="B34" s="94" t="n">
+      <x:c r="B34" s="99" t="n">
         <x:v>4956000000</x:v>
       </x:c>
-      <x:c r="C34" s="95" t="str">
+      <x:c r="C34" s="100" t="str">
         <x:v>Reported net financing cash flow</x:v>
       </x:c>
-      <x:c r="D34" s="54" t="d">
+      <x:c r="D34" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E34" s="54" t="d">
+      <x:c r="E34" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F34" s="95" t="str">
+      <x:c r="F34" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G34" s="54" t="d">
+      <x:c r="G34" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H34" s="95" t="str">
+      <x:c r="H34" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I34" s="95" t="str">
+      <x:c r="I34" s="100" t="str">
         <x:v>us-gaap:NetCashProvidedByUsedInFinancingActivities</x:v>
       </x:c>
-      <x:c r="J34" s="95" t="str">
+      <x:c r="J34" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K34" s="95" t="n">
+      <x:c r="K34" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L34" s="95" t="str">
+      <x:c r="L34" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M34" s="95" t="str">
+      <x:c r="M34" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N34" s="95" t="str">
+      <x:c r="N34" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O34" s="95" t="str">
+      <x:c r="O34" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P34" s="95" t="str">
+      <x:c r="P34" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q34" s="95" t="str"/>
-      <x:c r="R34" s="55" t="str">
+      <x:c r="Q34" s="100" t="str"/>
+      <x:c r="R34" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S34" s="134"/>
+      <x:c r="T34" s="135"/>
     </x:row>
     <x:row r="35" ht="85" customHeight="1">
-      <x:c r="A35" s="52" t="str">
+      <x:c r="A35" s="57" t="str">
         <x:v>fx</x:v>
       </x:c>
-      <x:c r="B35" s="94" t="n">
+      <x:c r="B35" s="99" t="n">
         <x:v>15000000</x:v>
       </x:c>
-      <x:c r="C35" s="95" t="str">
+      <x:c r="C35" s="100" t="str">
         <x:v>Exchange-rate effect on cash</x:v>
       </x:c>
-      <x:c r="D35" s="54" t="d">
+      <x:c r="D35" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E35" s="54" t="d">
+      <x:c r="E35" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F35" s="95" t="str">
+      <x:c r="F35" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G35" s="54" t="d">
+      <x:c r="G35" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H35" s="95" t="str">
+      <x:c r="H35" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I35" s="95" t="str">
+      <x:c r="I35" s="100" t="str">
         <x:v>us-gaap:EffectOfExchangeRateOnCashCashEquivalentsRestrictedCashAndRestrictedCashEquivalents</x:v>
       </x:c>
-      <x:c r="J35" s="95" t="str">
+      <x:c r="J35" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K35" s="95" t="n">
+      <x:c r="K35" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L35" s="95" t="str">
+      <x:c r="L35" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M35" s="95" t="str">
+      <x:c r="M35" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N35" s="95" t="str">
+      <x:c r="N35" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O35" s="95" t="str">
+      <x:c r="O35" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P35" s="95" t="str">
+      <x:c r="P35" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q35" s="95" t="str"/>
-      <x:c r="R35" s="55" t="str">
+      <x:c r="Q35" s="100" t="str"/>
+      <x:c r="R35" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S35" s="134"/>
+      <x:c r="T35" s="135"/>
     </x:row>
     <x:row r="36" ht="85" customHeight="1">
-      <x:c r="A36" s="52" t="str">
+      <x:c r="A36" s="57" t="str">
         <x:v>change</x:v>
       </x:c>
-      <x:c r="B36" s="94" t="n">
+      <x:c r="B36" s="99" t="n">
         <x:v>1682000000</x:v>
       </x:c>
-      <x:c r="C36" s="95" t="str">
+      <x:c r="C36" s="100" t="str">
         <x:v>Reported cash increase</x:v>
       </x:c>
-      <x:c r="D36" s="54" t="d">
+      <x:c r="D36" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="E36" s="54" t="d">
+      <x:c r="E36" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F36" s="95" t="str">
+      <x:c r="F36" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G36" s="54" t="d">
+      <x:c r="G36" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H36" s="95" t="str">
+      <x:c r="H36" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I36" s="95" t="str">
+      <x:c r="I36" s="100" t="str">
         <x:v>us-gaap:CashCashEquivalentsRestrictedCashAndRestrictedCashEquivalentsPeriodIncreaseDecreaseIncludingExchangeRateEffect</x:v>
       </x:c>
-      <x:c r="J36" s="95" t="str">
+      <x:c r="J36" s="100" t="str">
         <x:v>c-1</x:v>
       </x:c>
-      <x:c r="K36" s="95" t="n">
+      <x:c r="K36" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L36" s="95" t="str">
+      <x:c r="L36" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M36" s="95" t="str">
+      <x:c r="M36" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N36" s="95" t="str">
+      <x:c r="N36" s="100" t="str">
         <x:v>Cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O36" s="95" t="str">
+      <x:c r="O36" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P36" s="95" t="str">
+      <x:c r="P36" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q36" s="95" t="str"/>
-      <x:c r="R36" s="55" t="str">
+      <x:c r="Q36" s="100" t="str"/>
+      <x:c r="R36" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S36" s="134"/>
+      <x:c r="T36" s="135"/>
     </x:row>
     <x:row r="37" ht="85" customHeight="1">
-      <x:c r="A37" s="52" t="str">
+      <x:c r="A37" s="57" t="str">
         <x:v>opening</x:v>
       </x:c>
-      <x:c r="B37" s="94" t="n">
+      <x:c r="B37" s="99" t="n">
         <x:v>7268000000</x:v>
       </x:c>
-      <x:c r="C37" s="95" t="str">
+      <x:c r="C37" s="100" t="str">
         <x:v>Opening cash and equivalents</x:v>
       </x:c>
-      <x:c r="D37" s="54"/>
-      <x:c r="E37" s="54" t="d">
+      <x:c r="D37" s="59"/>
+      <x:c r="E37" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F37" s="95" t="str">
+      <x:c r="F37" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G37" s="54" t="d">
+      <x:c r="G37" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H37" s="95" t="str">
+      <x:c r="H37" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I37" s="95" t="str">
+      <x:c r="I37" s="100" t="str">
         <x:v>us-gaap:CashAndCashEquivalentsAtCarryingValue</x:v>
       </x:c>
-      <x:c r="J37" s="95" t="str">
+      <x:c r="J37" s="100" t="str">
         <x:v>c-16</x:v>
       </x:c>
-      <x:c r="K37" s="95" t="n">
+      <x:c r="K37" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L37" s="95" t="str">
+      <x:c r="L37" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M37" s="95" t="str">
+      <x:c r="M37" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N37" s="95" t="str">
+      <x:c r="N37" s="100" t="str">
         <x:v>Balance sheet p. 7; cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O37" s="95" t="str">
+      <x:c r="O37" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P37" s="95" t="str">
+      <x:c r="P37" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q37" s="95" t="str"/>
-      <x:c r="R37" s="55" t="str">
+      <x:c r="Q37" s="100" t="str"/>
+      <x:c r="R37" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S37" s="134"/>
+      <x:c r="T37" s="135"/>
     </x:row>
     <x:row r="38" ht="85" customHeight="1">
-      <x:c r="A38" s="52" t="str">
+      <x:c r="A38" s="57" t="str">
         <x:v>closing</x:v>
       </x:c>
-      <x:c r="B38" s="94" t="n">
+      <x:c r="B38" s="99" t="n">
         <x:v>8950000000</x:v>
       </x:c>
-      <x:c r="C38" s="95" t="str">
+      <x:c r="C38" s="100" t="str">
         <x:v>Closing cash and equivalents</x:v>
       </x:c>
-      <x:c r="D38" s="54"/>
-      <x:c r="E38" s="54" t="d">
+      <x:c r="D38" s="59"/>
+      <x:c r="E38" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F38" s="95" t="str">
+      <x:c r="F38" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G38" s="54" t="d">
+      <x:c r="G38" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H38" s="95" t="str">
+      <x:c r="H38" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I38" s="95" t="str">
+      <x:c r="I38" s="100" t="str">
         <x:v>us-gaap:CashAndCashEquivalentsAtCarryingValue</x:v>
       </x:c>
-      <x:c r="J38" s="95" t="str">
+      <x:c r="J38" s="100" t="str">
         <x:v>c-15</x:v>
       </x:c>
-      <x:c r="K38" s="95" t="n">
+      <x:c r="K38" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L38" s="95" t="str">
+      <x:c r="L38" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M38" s="95" t="str">
+      <x:c r="M38" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N38" s="95" t="str">
+      <x:c r="N38" s="100" t="str">
         <x:v>Balance sheet p. 7; cash flows p. 8</x:v>
       </x:c>
-      <x:c r="O38" s="95" t="str">
+      <x:c r="O38" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P38" s="95" t="str">
+      <x:c r="P38" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q38" s="95" t="str"/>
-      <x:c r="R38" s="55" t="str">
+      <x:c r="Q38" s="100" t="str"/>
+      <x:c r="R38" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S38" s="134"/>
+      <x:c r="T38" s="135"/>
     </x:row>
     <x:row r="39" ht="85" customHeight="1">
-      <x:c r="A39" s="52" t="str">
+      <x:c r="A39" s="57" t="str">
         <x:v>current_debt</x:v>
       </x:c>
-      <x:c r="B39" s="94" t="n">
+      <x:c r="B39" s="99" t="n">
         <x:v>7050000000</x:v>
       </x:c>
-      <x:c r="C39" s="95" t="str">
+      <x:c r="C39" s="100" t="str">
         <x:v>Current borrowing</x:v>
       </x:c>
-      <x:c r="D39" s="54"/>
-      <x:c r="E39" s="54" t="d">
+      <x:c r="D39" s="59"/>
+      <x:c r="E39" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F39" s="95" t="str">
+      <x:c r="F39" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G39" s="54" t="d">
+      <x:c r="G39" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H39" s="95" t="str">
+      <x:c r="H39" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I39" s="95" t="str">
+      <x:c r="I39" s="100" t="str">
         <x:v>us-gaap:DebtCurrent</x:v>
       </x:c>
-      <x:c r="J39" s="95" t="str">
+      <x:c r="J39" s="100" t="str">
         <x:v>c-15</x:v>
       </x:c>
-      <x:c r="K39" s="95" t="n">
+      <x:c r="K39" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L39" s="95" t="str">
+      <x:c r="L39" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M39" s="95" t="str">
+      <x:c r="M39" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N39" s="95" t="str">
+      <x:c r="N39" s="100" t="str">
         <x:v>Balance sheet p. 7</x:v>
       </x:c>
-      <x:c r="O39" s="95" t="str">
+      <x:c r="O39" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P39" s="95" t="str">
+      <x:c r="P39" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q39" s="95" t="str"/>
-      <x:c r="R39" s="55" t="str">
+      <x:c r="Q39" s="100" t="str"/>
+      <x:c r="R39" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S39" s="134"/>
+      <x:c r="T39" s="135"/>
     </x:row>
     <x:row r="40" ht="85" customHeight="1">
-      <x:c r="A40" s="52" t="str">
+      <x:c r="A40" s="57" t="str">
         <x:v>noncurrent_debt</x:v>
       </x:c>
-      <x:c r="B40" s="94" t="n">
+      <x:c r="B40" s="99" t="n">
         <x:v>47858000000</x:v>
       </x:c>
-      <x:c r="C40" s="95" t="str">
+      <x:c r="C40" s="100" t="str">
         <x:v>Noncurrent borrowing</x:v>
       </x:c>
-      <x:c r="D40" s="54"/>
-      <x:c r="E40" s="54" t="d">
+      <x:c r="D40" s="59"/>
+      <x:c r="E40" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F40" s="95" t="str">
+      <x:c r="F40" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G40" s="54" t="d">
+      <x:c r="G40" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H40" s="95" t="str">
+      <x:c r="H40" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I40" s="95" t="str">
+      <x:c r="I40" s="100" t="str">
         <x:v>us-gaap:LongTermDebtNoncurrent</x:v>
       </x:c>
-      <x:c r="J40" s="95" t="str">
+      <x:c r="J40" s="100" t="str">
         <x:v>c-15</x:v>
       </x:c>
-      <x:c r="K40" s="95" t="n">
+      <x:c r="K40" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L40" s="95" t="str">
+      <x:c r="L40" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M40" s="95" t="str">
+      <x:c r="M40" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N40" s="95" t="str">
+      <x:c r="N40" s="100" t="str">
         <x:v>Balance sheet p. 7</x:v>
       </x:c>
-      <x:c r="O40" s="95" t="str">
+      <x:c r="O40" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P40" s="95" t="str">
+      <x:c r="P40" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q40" s="95" t="str"/>
-      <x:c r="R40" s="55" t="str">
+      <x:c r="Q40" s="100" t="str"/>
+      <x:c r="R40" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S40" s="134"/>
+      <x:c r="T40" s="135"/>
     </x:row>
     <x:row r="41" ht="85" customHeight="1">
-      <x:c r="A41" s="52" t="str">
+      <x:c r="A41" s="57" t="str">
         <x:v>contingent_current</x:v>
       </x:c>
-      <x:c r="B41" s="94" t="n">
+      <x:c r="B41" s="99" t="n">
         <x:v>814000000</x:v>
       </x:c>
-      <x:c r="C41" s="95" t="str">
+      <x:c r="C41" s="100" t="str">
         <x:v>Contingent consideration fair value: current</x:v>
       </x:c>
-      <x:c r="D41" s="54"/>
-      <x:c r="E41" s="54" t="d">
+      <x:c r="D41" s="59"/>
+      <x:c r="E41" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F41" s="95" t="str">
+      <x:c r="F41" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G41" s="54" t="d">
+      <x:c r="G41" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H41" s="95" t="str">
+      <x:c r="H41" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I41" s="95" t="str">
+      <x:c r="I41" s="100" t="str">
         <x:v>us-gaap:BusinessCombinationContingentConsiderationLiabilityCurrent</x:v>
       </x:c>
-      <x:c r="J41" s="95" t="str">
+      <x:c r="J41" s="100" t="str">
         <x:v>c-301</x:v>
       </x:c>
-      <x:c r="K41" s="95" t="n">
+      <x:c r="K41" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L41" s="95" t="str">
+      <x:c r="L41" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M41" s="95" t="str">
+      <x:c r="M41" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N41" s="95" t="str">
+      <x:c r="N41" s="100" t="str">
         <x:v>Note 8 p. 17</x:v>
       </x:c>
-      <x:c r="O41" s="95" t="str">
+      <x:c r="O41" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P41" s="95" t="str">
+      <x:c r="P41" s="100" t="str">
         <x:v>[["us-gaap:FairValueByFairValueHierarchyLevelAxis","us-gaap:FairValueInputsLevel3Member"]]</x:v>
       </x:c>
-      <x:c r="Q41" s="95" t="str"/>
-      <x:c r="R41" s="55" t="str">
+      <x:c r="Q41" s="100" t="str"/>
+      <x:c r="R41" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S41" s="134"/>
+      <x:c r="T41" s="135"/>
     </x:row>
     <x:row r="42" ht="85" customHeight="1">
-      <x:c r="A42" s="52" t="str">
+      <x:c r="A42" s="57" t="str">
         <x:v>contingent_noncurrent</x:v>
       </x:c>
-      <x:c r="B42" s="94" t="n">
+      <x:c r="B42" s="99" t="n">
         <x:v>1704000000</x:v>
       </x:c>
-      <x:c r="C42" s="95" t="str">
+      <x:c r="C42" s="100" t="str">
         <x:v>Contingent consideration fair value: noncurrent</x:v>
       </x:c>
-      <x:c r="D42" s="54"/>
-      <x:c r="E42" s="54" t="d">
+      <x:c r="D42" s="59"/>
+      <x:c r="E42" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F42" s="95" t="str">
+      <x:c r="F42" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G42" s="54" t="d">
+      <x:c r="G42" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H42" s="95" t="str">
+      <x:c r="H42" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I42" s="95" t="str">
+      <x:c r="I42" s="100" t="str">
         <x:v>us-gaap:BusinessCombinationContingentConsiderationLiabilityNoncurrent</x:v>
       </x:c>
-      <x:c r="J42" s="95" t="str">
+      <x:c r="J42" s="100" t="str">
         <x:v>c-301</x:v>
       </x:c>
-      <x:c r="K42" s="95" t="n">
+      <x:c r="K42" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L42" s="95" t="str">
+      <x:c r="L42" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M42" s="95" t="str">
+      <x:c r="M42" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N42" s="95" t="str">
+      <x:c r="N42" s="100" t="str">
         <x:v>Note 8 p. 17</x:v>
       </x:c>
-      <x:c r="O42" s="95" t="str">
+      <x:c r="O42" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P42" s="95" t="str">
+      <x:c r="P42" s="100" t="str">
         <x:v>[["us-gaap:FairValueByFairValueHierarchyLevelAxis","us-gaap:FairValueInputsLevel3Member"]]</x:v>
       </x:c>
-      <x:c r="Q42" s="95" t="str"/>
-      <x:c r="R42" s="55" t="str">
+      <x:c r="Q42" s="100" t="str"/>
+      <x:c r="R42" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S42" s="134"/>
+      <x:c r="T42" s="135"/>
     </x:row>
     <x:row r="43" ht="85" customHeight="1">
-      <x:c r="A43" s="52" t="str">
+      <x:c r="A43" s="57" t="str">
         <x:v>notes_2026</x:v>
       </x:c>
-      <x:c r="B43" s="94" t="n">
+      <x:c r="B43" s="99" t="n">
         <x:v>1632000000</x:v>
       </x:c>
-      <x:c r="C43" s="95" t="str">
+      <x:c r="C43" s="100" t="str">
         <x:v>Notes due 2026</x:v>
       </x:c>
-      <x:c r="D43" s="54"/>
-      <x:c r="E43" s="54" t="d">
+      <x:c r="D43" s="59"/>
+      <x:c r="E43" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F43" s="95" t="str">
+      <x:c r="F43" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G43" s="54" t="d">
+      <x:c r="G43" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H43" s="95" t="str">
+      <x:c r="H43" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I43" s="95" t="str">
+      <x:c r="I43" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J43" s="95" t="str">
+      <x:c r="J43" s="100" t="str">
         <x:v>c-297</x:v>
       </x:c>
-      <x:c r="K43" s="95" t="n">
+      <x:c r="K43" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L43" s="95" t="str">
+      <x:c r="L43" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M43" s="95" t="str">
+      <x:c r="M43" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N43" s="95" t="str">
+      <x:c r="N43" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O43" s="95" t="str">
+      <x:c r="O43" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P43" s="95" t="str">
+      <x:c r="P43" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2026Member"]]</x:v>
       </x:c>
-      <x:c r="Q43" s="95" t="str"/>
-      <x:c r="R43" s="55" t="str">
+      <x:c r="Q43" s="100" t="str"/>
+      <x:c r="R43" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S43" s="134"/>
+      <x:c r="T43" s="135"/>
     </x:row>
     <x:row r="44" ht="85" customHeight="1">
-      <x:c r="A44" s="52" t="str">
+      <x:c r="A44" s="57" t="str">
         <x:v>notes_2027</x:v>
       </x:c>
-      <x:c r="B44" s="94" t="n">
+      <x:c r="B44" s="99" t="n">
         <x:v>2516000000</x:v>
       </x:c>
-      <x:c r="C44" s="95" t="str">
+      <x:c r="C44" s="100" t="str">
         <x:v>Notes due 2027</x:v>
       </x:c>
-      <x:c r="D44" s="54"/>
-      <x:c r="E44" s="54" t="d">
+      <x:c r="D44" s="59"/>
+      <x:c r="E44" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F44" s="95" t="str">
+      <x:c r="F44" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G44" s="54" t="d">
+      <x:c r="G44" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H44" s="95" t="str">
+      <x:c r="H44" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I44" s="95" t="str">
+      <x:c r="I44" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J44" s="95" t="str">
+      <x:c r="J44" s="100" t="str">
         <x:v>c-301</x:v>
       </x:c>
-      <x:c r="K44" s="95" t="n">
+      <x:c r="K44" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L44" s="95" t="str">
+      <x:c r="L44" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M44" s="95" t="str">
+      <x:c r="M44" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N44" s="95" t="str">
+      <x:c r="N44" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O44" s="95" t="str">
+      <x:c r="O44" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P44" s="95" t="str">
+      <x:c r="P44" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2027Member"]]</x:v>
       </x:c>
-      <x:c r="Q44" s="95" t="str"/>
-      <x:c r="R44" s="55" t="str">
+      <x:c r="Q44" s="100" t="str"/>
+      <x:c r="R44" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S44" s="134"/>
+      <x:c r="T44" s="135"/>
     </x:row>
     <x:row r="45" ht="85" customHeight="1">
-      <x:c r="A45" s="52" t="str">
+      <x:c r="A45" s="57" t="str">
         <x:v>notes_2028</x:v>
       </x:c>
-      <x:c r="B45" s="94" t="n">
+      <x:c r="B45" s="99" t="n">
         <x:v>3256000000</x:v>
       </x:c>
-      <x:c r="C45" s="95" t="str">
+      <x:c r="C45" s="100" t="str">
         <x:v>Notes due 2028</x:v>
       </x:c>
-      <x:c r="D45" s="54"/>
-      <x:c r="E45" s="54" t="d">
+      <x:c r="D45" s="59"/>
+      <x:c r="E45" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F45" s="95" t="str">
+      <x:c r="F45" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G45" s="54" t="d">
+      <x:c r="G45" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H45" s="95" t="str">
+      <x:c r="H45" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I45" s="95" t="str">
+      <x:c r="I45" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J45" s="95" t="str">
+      <x:c r="J45" s="100" t="str">
         <x:v>c-305</x:v>
       </x:c>
-      <x:c r="K45" s="95" t="n">
+      <x:c r="K45" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L45" s="95" t="str">
+      <x:c r="L45" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M45" s="95" t="str">
+      <x:c r="M45" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N45" s="95" t="str">
+      <x:c r="N45" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O45" s="95" t="str">
+      <x:c r="O45" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P45" s="95" t="str">
+      <x:c r="P45" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2028Member"]]</x:v>
       </x:c>
-      <x:c r="Q45" s="95" t="str"/>
-      <x:c r="R45" s="55" t="str">
+      <x:c r="Q45" s="100" t="str"/>
+      <x:c r="R45" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S45" s="134"/>
+      <x:c r="T45" s="135"/>
     </x:row>
     <x:row r="46" ht="85" customHeight="1">
-      <x:c r="A46" s="52" t="str">
+      <x:c r="A46" s="57" t="str">
         <x:v>notes_2029</x:v>
       </x:c>
-      <x:c r="B46" s="94" t="n">
+      <x:c r="B46" s="99" t="n">
         <x:v>3077000000</x:v>
       </x:c>
-      <x:c r="C46" s="95" t="str">
+      <x:c r="C46" s="100" t="str">
         <x:v>Notes due 2029</x:v>
       </x:c>
-      <x:c r="D46" s="54"/>
-      <x:c r="E46" s="54" t="d">
+      <x:c r="D46" s="59"/>
+      <x:c r="E46" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F46" s="95" t="str">
+      <x:c r="F46" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G46" s="54" t="d">
+      <x:c r="G46" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H46" s="95" t="str">
+      <x:c r="H46" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I46" s="95" t="str">
+      <x:c r="I46" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J46" s="95" t="str">
+      <x:c r="J46" s="100" t="str">
         <x:v>c-309</x:v>
       </x:c>
-      <x:c r="K46" s="95" t="n">
+      <x:c r="K46" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L46" s="95" t="str">
+      <x:c r="L46" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M46" s="95" t="str">
+      <x:c r="M46" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N46" s="95" t="str">
+      <x:c r="N46" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O46" s="95" t="str">
+      <x:c r="O46" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P46" s="95" t="str">
+      <x:c r="P46" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2029Member"]]</x:v>
       </x:c>
-      <x:c r="Q46" s="95" t="str"/>
-      <x:c r="R46" s="55" t="str">
+      <x:c r="Q46" s="100" t="str"/>
+      <x:c r="R46" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S46" s="134"/>
+      <x:c r="T46" s="135"/>
     </x:row>
     <x:row r="47" ht="85" customHeight="1">
-      <x:c r="A47" s="52" t="str">
+      <x:c r="A47" s="57" t="str">
         <x:v>notes_2030</x:v>
       </x:c>
-      <x:c r="B47" s="94" t="n">
+      <x:c r="B47" s="99" t="n">
         <x:v>2132000000</x:v>
       </x:c>
-      <x:c r="C47" s="95" t="str">
+      <x:c r="C47" s="100" t="str">
         <x:v>Notes due 2030</x:v>
       </x:c>
-      <x:c r="D47" s="54"/>
-      <x:c r="E47" s="54" t="d">
+      <x:c r="D47" s="59"/>
+      <x:c r="E47" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F47" s="95" t="str">
+      <x:c r="F47" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G47" s="54" t="d">
+      <x:c r="G47" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H47" s="95" t="str">
+      <x:c r="H47" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I47" s="95" t="str">
+      <x:c r="I47" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J47" s="95" t="str">
+      <x:c r="J47" s="100" t="str">
         <x:v>c-313</x:v>
       </x:c>
-      <x:c r="K47" s="95" t="n">
+      <x:c r="K47" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L47" s="95" t="str">
+      <x:c r="L47" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M47" s="95" t="str">
+      <x:c r="M47" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N47" s="95" t="str">
+      <x:c r="N47" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O47" s="95" t="str">
+      <x:c r="O47" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P47" s="95" t="str">
+      <x:c r="P47" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue2030Member"]]</x:v>
       </x:c>
-      <x:c r="Q47" s="95" t="str"/>
-      <x:c r="R47" s="55" t="str">
+      <x:c r="Q47" s="100" t="str"/>
+      <x:c r="R47" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S47" s="134"/>
+      <x:c r="T47" s="135"/>
     </x:row>
     <x:row r="48" ht="85" customHeight="1">
-      <x:c r="A48" s="52" t="str">
+      <x:c r="A48" s="57" t="str">
         <x:v>notes_20312040</x:v>
       </x:c>
-      <x:c r="B48" s="94" t="n">
+      <x:c r="B48" s="99" t="n">
         <x:v>11582000000</x:v>
       </x:c>
-      <x:c r="C48" s="95" t="str">
+      <x:c r="C48" s="100" t="str">
         <x:v>Notes due 2031–2040</x:v>
       </x:c>
-      <x:c r="D48" s="54"/>
-      <x:c r="E48" s="54" t="d">
+      <x:c r="D48" s="59"/>
+      <x:c r="E48" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F48" s="95" t="str">
+      <x:c r="F48" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G48" s="54" t="d">
+      <x:c r="G48" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H48" s="95" t="str">
+      <x:c r="H48" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I48" s="95" t="str">
+      <x:c r="I48" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J48" s="95" t="str">
+      <x:c r="J48" s="100" t="str">
         <x:v>c-317</x:v>
       </x:c>
-      <x:c r="K48" s="95" t="n">
+      <x:c r="K48" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L48" s="95" t="str">
+      <x:c r="L48" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M48" s="95" t="str">
+      <x:c r="M48" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N48" s="95" t="str">
+      <x:c r="N48" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O48" s="95" t="str">
+      <x:c r="O48" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P48" s="95" t="str">
+      <x:c r="P48" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue20312040Member"]]</x:v>
       </x:c>
-      <x:c r="Q48" s="95" t="str"/>
-      <x:c r="R48" s="55" t="str">
+      <x:c r="Q48" s="100" t="str"/>
+      <x:c r="R48" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S48" s="134"/>
+      <x:c r="T48" s="135"/>
     </x:row>
     <x:row r="49" ht="85" customHeight="1">
-      <x:c r="A49" s="52" t="str">
+      <x:c r="A49" s="57" t="str">
         <x:v>notes_20412050</x:v>
       </x:c>
-      <x:c r="B49" s="94" t="n">
+      <x:c r="B49" s="99" t="n">
         <x:v>4543000000</x:v>
       </x:c>
-      <x:c r="C49" s="95" t="str">
+      <x:c r="C49" s="100" t="str">
         <x:v>Notes due 2041–2050</x:v>
       </x:c>
-      <x:c r="D49" s="54"/>
-      <x:c r="E49" s="54" t="d">
+      <x:c r="D49" s="59"/>
+      <x:c r="E49" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F49" s="95" t="str">
+      <x:c r="F49" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G49" s="54" t="d">
+      <x:c r="G49" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H49" s="95" t="str">
+      <x:c r="H49" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I49" s="95" t="str">
+      <x:c r="I49" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J49" s="95" t="str">
+      <x:c r="J49" s="100" t="str">
         <x:v>c-321</x:v>
       </x:c>
-      <x:c r="K49" s="95" t="n">
+      <x:c r="K49" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L49" s="95" t="str">
+      <x:c r="L49" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M49" s="95" t="str">
+      <x:c r="M49" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N49" s="95" t="str">
+      <x:c r="N49" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O49" s="95" t="str">
+      <x:c r="O49" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P49" s="95" t="str">
+      <x:c r="P49" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue20412050Member"]]</x:v>
       </x:c>
-      <x:c r="Q49" s="95" t="str"/>
-      <x:c r="R49" s="55" t="str">
+      <x:c r="Q49" s="100" t="str"/>
+      <x:c r="R49" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S49" s="134"/>
+      <x:c r="T49" s="135"/>
     </x:row>
     <x:row r="50" ht="85" customHeight="1">
-      <x:c r="A50" s="52" t="str">
+      <x:c r="A50" s="57" t="str">
         <x:v>notes_20512060</x:v>
       </x:c>
-      <x:c r="B50" s="94" t="n">
+      <x:c r="B50" s="99" t="n">
         <x:v>8280000000</x:v>
       </x:c>
-      <x:c r="C50" s="95" t="str">
+      <x:c r="C50" s="100" t="str">
         <x:v>Notes due 2051–2060</x:v>
       </x:c>
-      <x:c r="D50" s="54"/>
-      <x:c r="E50" s="54" t="d">
+      <x:c r="D50" s="59"/>
+      <x:c r="E50" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F50" s="95" t="str">
+      <x:c r="F50" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G50" s="54" t="d">
+      <x:c r="G50" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H50" s="95" t="str">
+      <x:c r="H50" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I50" s="95" t="str">
+      <x:c r="I50" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J50" s="95" t="str">
+      <x:c r="J50" s="100" t="str">
         <x:v>c-325</x:v>
       </x:c>
-      <x:c r="K50" s="95" t="n">
+      <x:c r="K50" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L50" s="95" t="str">
+      <x:c r="L50" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M50" s="95" t="str">
+      <x:c r="M50" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N50" s="95" t="str">
+      <x:c r="N50" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O50" s="95" t="str">
+      <x:c r="O50" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P50" s="95" t="str">
+      <x:c r="P50" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue20512060Member"]]</x:v>
       </x:c>
-      <x:c r="Q50" s="95" t="str"/>
-      <x:c r="R50" s="55" t="str">
+      <x:c r="Q50" s="100" t="str"/>
+      <x:c r="R50" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S50" s="134"/>
+      <x:c r="T50" s="135"/>
     </x:row>
     <x:row r="51" ht="85" customHeight="1">
-      <x:c r="A51" s="52" t="str">
+      <x:c r="A51" s="57" t="str">
         <x:v>notes_20612070</x:v>
       </x:c>
-      <x:c r="B51" s="94" t="n">
+      <x:c r="B51" s="99" t="n">
         <x:v>5824000000</x:v>
       </x:c>
-      <x:c r="C51" s="95" t="str">
+      <x:c r="C51" s="100" t="str">
         <x:v>Notes due 2061–2070</x:v>
       </x:c>
-      <x:c r="D51" s="54"/>
-      <x:c r="E51" s="54" t="d">
+      <x:c r="D51" s="59"/>
+      <x:c r="E51" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F51" s="95" t="str">
+      <x:c r="F51" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G51" s="54" t="d">
+      <x:c r="G51" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H51" s="95" t="str">
+      <x:c r="H51" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I51" s="95" t="str">
+      <x:c r="I51" s="100" t="str">
         <x:v>us-gaap:DebtInstrumentCarryingAmount</x:v>
       </x:c>
-      <x:c r="J51" s="95" t="str">
+      <x:c r="J51" s="100" t="str">
         <x:v>c-329</x:v>
       </x:c>
-      <x:c r="K51" s="95" t="n">
+      <x:c r="K51" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L51" s="95" t="str">
+      <x:c r="L51" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M51" s="95" t="str">
+      <x:c r="M51" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N51" s="95" t="str">
+      <x:c r="N51" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O51" s="95" t="str">
+      <x:c r="O51" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P51" s="95" t="str">
+      <x:c r="P51" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentAxis","lly:NotesDue20612070Member"]]</x:v>
       </x:c>
-      <x:c r="Q51" s="95" t="str"/>
-      <x:c r="R51" s="55" t="str">
+      <x:c r="Q51" s="100" t="str"/>
+      <x:c r="R51" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S51" s="134"/>
+      <x:c r="T51" s="135"/>
     </x:row>
     <x:row r="52" ht="85" customHeight="1">
-      <x:c r="A52" s="52" t="str">
+      <x:c r="A52" s="57" t="str">
         <x:v>adjustment</x:v>
       </x:c>
-      <x:c r="B52" s="94" t="n">
+      <x:c r="B52" s="99" t="n">
         <x:v>339000000</x:v>
       </x:c>
-      <x:c r="C52" s="95" t="str">
+      <x:c r="C52" s="100" t="str">
         <x:v>Other long-term debt and adjustments (source magnitude)</x:v>
       </x:c>
-      <x:c r="D52" s="54"/>
-      <x:c r="E52" s="54" t="d">
+      <x:c r="D52" s="59"/>
+      <x:c r="E52" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F52" s="95" t="str">
+      <x:c r="F52" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G52" s="54" t="d">
+      <x:c r="G52" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H52" s="95" t="str">
+      <x:c r="H52" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I52" s="95" t="str">
+      <x:c r="I52" s="100" t="str">
         <x:v>us-gaap:OtherLongTermDebt</x:v>
       </x:c>
-      <x:c r="J52" s="95" t="str">
+      <x:c r="J52" s="100" t="str">
         <x:v>c-16</x:v>
       </x:c>
-      <x:c r="K52" s="95" t="n">
+      <x:c r="K52" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L52" s="95" t="str">
+      <x:c r="L52" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M52" s="95" t="str">
+      <x:c r="M52" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N52" s="95" t="str">
+      <x:c r="N52" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O52" s="95" t="str">
+      <x:c r="O52" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P52" s="95" t="str">
+      <x:c r="P52" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q52" s="95" t="str"/>
-      <x:c r="R52" s="55" t="str">
+      <x:c r="Q52" s="100" t="str"/>
+      <x:c r="R52" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S52" s="134"/>
+      <x:c r="T52" s="135"/>
     </x:row>
     <x:row r="53" ht="85" customHeight="1">
-      <x:c r="A53" s="52" t="str">
+      <x:c r="A53" s="57" t="str">
         <x:v>annual_cp</x:v>
       </x:c>
-      <x:c r="B53" s="94" t="n">
+      <x:c r="B53" s="99" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C53" s="95" t="str">
+      <x:c r="C53" s="100" t="str">
         <x:v>Commercial paper</x:v>
       </x:c>
-      <x:c r="D53" s="54"/>
-      <x:c r="E53" s="54" t="d">
+      <x:c r="D53" s="59"/>
+      <x:c r="E53" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F53" s="95" t="str">
+      <x:c r="F53" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G53" s="54" t="d">
+      <x:c r="G53" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H53" s="95" t="str">
+      <x:c r="H53" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I53" s="95" t="str">
+      <x:c r="I53" s="100" t="str">
         <x:v>us-gaap:CommercialPaper</x:v>
       </x:c>
-      <x:c r="J53" s="95" t="str">
+      <x:c r="J53" s="100" t="str">
         <x:v>c-16</x:v>
       </x:c>
-      <x:c r="K53" s="95" t="n">
+      <x:c r="K53" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L53" s="95" t="str">
+      <x:c r="L53" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M53" s="95" t="str">
+      <x:c r="M53" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N53" s="95" t="str">
+      <x:c r="N53" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O53" s="95" t="str">
+      <x:c r="O53" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P53" s="95" t="str">
+      <x:c r="P53" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q53" s="95" t="str"/>
-      <x:c r="R53" s="55" t="str">
+      <x:c r="Q53" s="100" t="str"/>
+      <x:c r="R53" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S53" s="134"/>
+      <x:c r="T53" s="135"/>
     </x:row>
     <x:row r="54" ht="85" customHeight="1">
-      <x:c r="A54" s="52" t="str">
+      <x:c r="A54" s="57" t="str">
         <x:v>annual_total</x:v>
       </x:c>
-      <x:c r="B54" s="94" t="n">
+      <x:c r="B54" s="99" t="n">
         <x:v>42503000000</x:v>
       </x:c>
-      <x:c r="C54" s="95" t="str">
+      <x:c r="C54" s="100" t="str">
         <x:v>Reported total debt</x:v>
       </x:c>
-      <x:c r="D54" s="54"/>
-      <x:c r="E54" s="54" t="d">
+      <x:c r="D54" s="59"/>
+      <x:c r="E54" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F54" s="95" t="str">
+      <x:c r="F54" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G54" s="54" t="d">
+      <x:c r="G54" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H54" s="95" t="str">
+      <x:c r="H54" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I54" s="95" t="str">
+      <x:c r="I54" s="100" t="str">
         <x:v>us-gaap:DebtLongtermAndShorttermCombinedAmount</x:v>
       </x:c>
-      <x:c r="J54" s="95" t="str">
+      <x:c r="J54" s="100" t="str">
         <x:v>c-16</x:v>
       </x:c>
-      <x:c r="K54" s="95" t="n">
+      <x:c r="K54" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L54" s="95" t="str">
+      <x:c r="L54" s="100" t="str">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="M54" s="95" t="str">
+      <x:c r="M54" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N54" s="95" t="str">
+      <x:c r="N54" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O54" s="95" t="str">
+      <x:c r="O54" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P54" s="95" t="str">
+      <x:c r="P54" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q54" s="95" t="str"/>
-      <x:c r="R54" s="55" t="str">
+      <x:c r="Q54" s="100" t="str"/>
+      <x:c r="R54" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S54" s="134"/>
+      <x:c r="T54" s="135"/>
     </x:row>
     <x:row r="55" ht="85" customHeight="1">
-      <x:c r="A55" s="52" t="str">
+      <x:c r="A55" s="57" t="str">
         <x:v>annual_unused</x:v>
       </x:c>
-      <x:c r="B55" s="94" t="n">
+      <x:c r="B55" s="99" t="n">
         <x:v>10100000000</x:v>
       </x:c>
-      <x:c r="C55" s="95" t="str">
+      <x:c r="C55" s="100" t="str">
         <x:v>Unused facilities at December 31</x:v>
       </x:c>
-      <x:c r="D55" s="54"/>
-      <x:c r="E55" s="54" t="d">
+      <x:c r="D55" s="59"/>
+      <x:c r="E55" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F55" s="95" t="str">
+      <x:c r="F55" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G55" s="54" t="d">
+      <x:c r="G55" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H55" s="95" t="str">
+      <x:c r="H55" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I55" s="95" t="str">
+      <x:c r="I55" s="100" t="str">
         <x:v>us-gaap:LineOfCreditFacilityRemainingBorrowingCapacity</x:v>
       </x:c>
-      <x:c r="J55" s="95" t="str">
+      <x:c r="J55" s="100" t="str">
         <x:v>c-16</x:v>
       </x:c>
-      <x:c r="K55" s="95" t="n">
+      <x:c r="K55" s="100" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L55" s="95" t="str">
+      <x:c r="L55" s="100" t="str">
         <x:v>-8</x:v>
       </x:c>
-      <x:c r="M55" s="95" t="str">
+      <x:c r="M55" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N55" s="95" t="str">
+      <x:c r="N55" s="100" t="str">
         <x:v>Note 11 p. 76</x:v>
       </x:c>
-      <x:c r="O55" s="95" t="str">
+      <x:c r="O55" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P55" s="95" t="str">
+      <x:c r="P55" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q55" s="95" t="str"/>
-      <x:c r="R55" s="55" t="str">
+      <x:c r="Q55" s="100" t="str"/>
+      <x:c r="R55" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S55" s="134"/>
+      <x:c r="T55" s="135"/>
     </x:row>
     <x:row r="56" ht="85" customHeight="1">
-      <x:c r="A56" s="52" t="str">
+      <x:c r="A56" s="57" t="str">
         <x:v>facility_2026</x:v>
       </x:c>
-      <x:c r="B56" s="94" t="n">
+      <x:c r="B56" s="99" t="n">
         <x:v>6000000000</x:v>
       </x:c>
-      <x:c r="C56" s="95" t="str">
+      <x:c r="C56" s="100" t="str">
         <x:v>364-day facility expires August 2026</x:v>
       </x:c>
-      <x:c r="D56" s="54"/>
-      <x:c r="E56" s="54" t="d">
+      <x:c r="D56" s="59"/>
+      <x:c r="E56" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F56" s="95" t="str">
+      <x:c r="F56" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G56" s="54" t="d">
+      <x:c r="G56" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H56" s="95" t="str">
+      <x:c r="H56" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I56" s="95" t="str">
+      <x:c r="I56" s="100" t="str">
         <x:v>us-gaap:LineOfCreditFacilityMaximumBorrowingCapacity</x:v>
       </x:c>
-      <x:c r="J56" s="95" t="str">
+      <x:c r="J56" s="100" t="str">
         <x:v>c-334</x:v>
       </x:c>
-      <x:c r="K56" s="95" t="n">
+      <x:c r="K56" s="100" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L56" s="95" t="str">
+      <x:c r="L56" s="100" t="str">
         <x:v>INF</x:v>
       </x:c>
-      <x:c r="M56" s="95" t="str">
+      <x:c r="M56" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N56" s="95" t="str">
+      <x:c r="N56" s="100" t="str">
         <x:v>Note 11 p. 76; MD&amp;A p. 51</x:v>
       </x:c>
-      <x:c r="O56" s="95" t="str">
+      <x:c r="O56" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P56" s="95" t="str">
+      <x:c r="P56" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentRedemptionPeriodAxis","lly:MaturityDate2026Member"]]</x:v>
       </x:c>
-      <x:c r="Q56" s="95" t="str"/>
-      <x:c r="R56" s="55" t="str">
+      <x:c r="Q56" s="100" t="str"/>
+      <x:c r="R56" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S56" s="134"/>
+      <x:c r="T56" s="135"/>
     </x:row>
     <x:row r="57" ht="85" customHeight="1">
-      <x:c r="A57" s="52" t="str">
+      <x:c r="A57" s="57" t="str">
         <x:v>facility_2029</x:v>
       </x:c>
-      <x:c r="B57" s="94" t="n">
+      <x:c r="B57" s="99" t="n">
         <x:v>4000000000</x:v>
       </x:c>
-      <x:c r="C57" s="95" t="str">
+      <x:c r="C57" s="100" t="str">
         <x:v>Facility expires December 2029</x:v>
       </x:c>
-      <x:c r="D57" s="54"/>
-      <x:c r="E57" s="54" t="d">
+      <x:c r="D57" s="59"/>
+      <x:c r="E57" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F57" s="95" t="str">
+      <x:c r="F57" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G57" s="54" t="d">
+      <x:c r="G57" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H57" s="95" t="str">
+      <x:c r="H57" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I57" s="95" t="str">
+      <x:c r="I57" s="100" t="str">
         <x:v>us-gaap:LineOfCreditFacilityMaximumBorrowingCapacity</x:v>
       </x:c>
-      <x:c r="J57" s="95" t="str">
+      <x:c r="J57" s="100" t="str">
         <x:v>c-333</x:v>
       </x:c>
-      <x:c r="K57" s="95" t="n">
+      <x:c r="K57" s="100" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L57" s="95" t="str">
+      <x:c r="L57" s="100" t="str">
         <x:v>INF</x:v>
       </x:c>
-      <x:c r="M57" s="95" t="str">
+      <x:c r="M57" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N57" s="95" t="str">
+      <x:c r="N57" s="100" t="str">
         <x:v>Note 11 p. 76; MD&amp;A p. 51</x:v>
       </x:c>
-      <x:c r="O57" s="95" t="str">
+      <x:c r="O57" s="100" t="str">
         <x:v>Inline XBRL</x:v>
       </x:c>
-      <x:c r="P57" s="95" t="str">
+      <x:c r="P57" s="100" t="str">
         <x:v>[["us-gaap:DebtInstrumentRedemptionPeriodAxis","lly:MaturityDateDecember2029Member"]]</x:v>
       </x:c>
-      <x:c r="Q57" s="95" t="str"/>
-      <x:c r="R57" s="55" t="str">
+      <x:c r="Q57" s="100" t="str"/>
+      <x:c r="R57" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S57" s="134"/>
+      <x:c r="T57" s="135"/>
     </x:row>
     <x:row r="58" ht="85" customHeight="1">
-      <x:c r="A58" s="52" t="str">
+      <x:c r="A58" s="57" t="str">
         <x:v>unused_june</x:v>
       </x:c>
-      <x:c r="B58" s="94" t="n">
+      <x:c r="B58" s="99" t="n">
         <x:v>10100000000</x:v>
       </x:c>
-      <x:c r="C58" s="95" t="str">
+      <x:c r="C58" s="100" t="str">
         <x:v>Unused committed facilities</x:v>
       </x:c>
-      <x:c r="D58" s="54"/>
-      <x:c r="E58" s="54" t="d">
+      <x:c r="D58" s="59"/>
+      <x:c r="E58" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F58" s="95" t="str">
+      <x:c r="F58" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G58" s="54" t="d">
+      <x:c r="G58" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H58" s="95" t="str">
+      <x:c r="H58" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I58" s="95"/>
-      <x:c r="J58" s="95"/>
-      <x:c r="K58" s="95"/>
-      <x:c r="L58" s="95"/>
-      <x:c r="M58" s="95" t="str">
+      <x:c r="I58" s="100"/>
+      <x:c r="J58" s="100"/>
+      <x:c r="K58" s="100"/>
+      <x:c r="L58" s="100"/>
+      <x:c r="M58" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N58" s="95" t="str">
+      <x:c r="N58" s="100" t="str">
         <x:v>MD&amp;A p. 31</x:v>
       </x:c>
-      <x:c r="O58" s="95" t="str">
+      <x:c r="O58" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P58" s="95" t="str">
+      <x:c r="P58" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q58" s="95" t="str">
+      <x:c r="Q58" s="100" t="str">
         <x:v>Of this, $10B supports commercial paper. Not cash or verified drawable credit; do not add CP capacity again. Agreement conditions and facility-by-facility June composition are Unavailable.</x:v>
       </x:c>
-      <x:c r="R58" s="55" t="str">
+      <x:c r="R58" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S58" s="134"/>
+      <x:c r="T58" s="135"/>
     </x:row>
     <x:row r="59" ht="85" customHeight="1">
-      <x:c r="A59" s="52" t="str">
+      <x:c r="A59" s="57" t="str">
         <x:v>cp_support</x:v>
       </x:c>
-      <x:c r="B59" s="94" t="n">
+      <x:c r="B59" s="99" t="n">
         <x:v>10000000000</x:v>
       </x:c>
-      <x:c r="C59" s="95" t="str">
+      <x:c r="C59" s="100" t="str">
         <x:v>Facilities supporting commercial paper</x:v>
       </x:c>
-      <x:c r="D59" s="54"/>
-      <x:c r="E59" s="54" t="d">
+      <x:c r="D59" s="59"/>
+      <x:c r="E59" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F59" s="95" t="str">
+      <x:c r="F59" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G59" s="54" t="d">
+      <x:c r="G59" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H59" s="95" t="str">
+      <x:c r="H59" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I59" s="95"/>
-      <x:c r="J59" s="95"/>
-      <x:c r="K59" s="95"/>
-      <x:c r="L59" s="95"/>
-      <x:c r="M59" s="95" t="str">
+      <x:c r="I59" s="100"/>
+      <x:c r="J59" s="100"/>
+      <x:c r="K59" s="100"/>
+      <x:c r="L59" s="100"/>
+      <x:c r="M59" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N59" s="95" t="str">
+      <x:c r="N59" s="100" t="str">
         <x:v>MD&amp;A p. 31</x:v>
       </x:c>
-      <x:c r="O59" s="95" t="str">
+      <x:c r="O59" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P59" s="95" t="str">
+      <x:c r="P59" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q59" s="95" t="str">
+      <x:c r="Q59" s="100" t="str">
         <x:v>Included in the $10.1B; not another source of funds.</x:v>
       </x:c>
-      <x:c r="R59" s="55" t="str">
+      <x:c r="R59" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S59" s="134"/>
+      <x:c r="T59" s="135"/>
     </x:row>
     <x:row r="60" ht="85" customHeight="1">
-      <x:c r="A60" s="52" t="str">
+      <x:c r="A60" s="57" t="str">
         <x:v>atai</x:v>
       </x:c>
-      <x:c r="B60" s="94" t="n">
+      <x:c r="B60" s="99" t="n">
         <x:v>2800000000</x:v>
       </x:c>
-      <x:c r="C60" s="95" t="str">
+      <x:c r="C60" s="100" t="str">
         <x:v>Pending AtaiBeckley acquisition</x:v>
       </x:c>
-      <x:c r="D60" s="54"/>
-      <x:c r="E60" s="54" t="str">
+      <x:c r="D60" s="59"/>
+      <x:c r="E60" s="59" t="str">
         <x:v>Disclosed August 5, 2026</x:v>
       </x:c>
-      <x:c r="F60" s="95" t="str">
+      <x:c r="F60" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G60" s="54" t="d">
+      <x:c r="G60" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H60" s="95" t="str">
+      <x:c r="H60" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I60" s="95"/>
-      <x:c r="J60" s="95"/>
-      <x:c r="K60" s="95"/>
-      <x:c r="L60" s="95"/>
-      <x:c r="M60" s="95" t="str">
+      <x:c r="I60" s="100"/>
+      <x:c r="J60" s="100"/>
+      <x:c r="K60" s="100"/>
+      <x:c r="L60" s="100"/>
+      <x:c r="M60" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N60" s="95" t="str">
+      <x:c r="N60" s="100" t="str">
         <x:v>MD&amp;A p. 31</x:v>
       </x:c>
-      <x:c r="O60" s="95" t="str">
+      <x:c r="O60" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P60" s="95" t="str">
+      <x:c r="P60" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q60" s="95" t="str">
+      <x:c r="Q60" s="100" t="str">
         <x:v>Payable at closing, subject to conditions. Disclosed after quarter end; closing date, completion and funding allocation are not established here.</x:v>
       </x:c>
-      <x:c r="R60" s="55" t="str">
+      <x:c r="R60" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S60" s="134"/>
+      <x:c r="T60" s="135"/>
     </x:row>
     <x:row r="61" ht="85" customHeight="1">
-      <x:c r="A61" s="52" t="str">
+      <x:c r="A61" s="57" t="str">
         <x:v>unpaid_kelonia</x:v>
       </x:c>
-      <x:c r="B61" s="94" t="n">
+      <x:c r="B61" s="99" t="n">
         <x:v>208000000</x:v>
       </x:c>
-      <x:c r="C61" s="95" t="str">
+      <x:c r="C61" s="100" t="str">
         <x:v>Unpaid Kelonia cash consideration</x:v>
       </x:c>
-      <x:c r="D61" s="54"/>
-      <x:c r="E61" s="54" t="d">
+      <x:c r="D61" s="59"/>
+      <x:c r="E61" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F61" s="95" t="str">
+      <x:c r="F61" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G61" s="54" t="d">
+      <x:c r="G61" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H61" s="95" t="str">
+      <x:c r="H61" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I61" s="95"/>
-      <x:c r="J61" s="95"/>
-      <x:c r="K61" s="95"/>
-      <x:c r="L61" s="95"/>
-      <x:c r="M61" s="95" t="str">
+      <x:c r="I61" s="100"/>
+      <x:c r="J61" s="100"/>
+      <x:c r="K61" s="100"/>
+      <x:c r="L61" s="100"/>
+      <x:c r="M61" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N61" s="95" t="str">
+      <x:c r="N61" s="100" t="str">
         <x:v>Note 4 p. 13</x:v>
       </x:c>
-      <x:c r="O61" s="95" t="str">
+      <x:c r="O61" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P61" s="95" t="str">
+      <x:c r="P61" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q61" s="95" t="str">
+      <x:c r="Q61" s="100" t="str">
         <x:v>Payment date Unavailable. Separate from cash already paid and from contingent-consideration fair value.</x:v>
       </x:c>
-      <x:c r="R61" s="55" t="str">
+      <x:c r="R61" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S61" s="134"/>
+      <x:c r="T61" s="135"/>
     </x:row>
     <x:row r="62" ht="85" customHeight="1">
-      <x:c r="A62" s="52" t="str">
+      <x:c r="A62" s="57" t="str">
         <x:v>unpaid_centessa</x:v>
       </x:c>
-      <x:c r="B62" s="94" t="n">
+      <x:c r="B62" s="99" t="n">
         <x:v>88000000</x:v>
       </x:c>
-      <x:c r="C62" s="95" t="str">
+      <x:c r="C62" s="100" t="str">
         <x:v>Unpaid Centessa cash consideration</x:v>
       </x:c>
-      <x:c r="D62" s="54"/>
-      <x:c r="E62" s="54" t="d">
+      <x:c r="D62" s="59"/>
+      <x:c r="E62" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F62" s="95" t="str">
+      <x:c r="F62" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G62" s="54" t="d">
+      <x:c r="G62" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H62" s="95" t="str">
+      <x:c r="H62" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I62" s="95"/>
-      <x:c r="J62" s="95"/>
-      <x:c r="K62" s="95"/>
-      <x:c r="L62" s="95"/>
-      <x:c r="M62" s="95" t="str">
+      <x:c r="I62" s="100"/>
+      <x:c r="J62" s="100"/>
+      <x:c r="K62" s="100"/>
+      <x:c r="L62" s="100"/>
+      <x:c r="M62" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N62" s="95" t="str">
+      <x:c r="N62" s="100" t="str">
         <x:v>Note 4 p. 13</x:v>
       </x:c>
-      <x:c r="O62" s="95" t="str">
+      <x:c r="O62" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P62" s="95" t="str">
+      <x:c r="P62" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q62" s="95" t="str">
+      <x:c r="Q62" s="100" t="str">
         <x:v>Payment date Unavailable. Do not add to paid acquisition cash or contingent-consideration fair value.</x:v>
       </x:c>
-      <x:c r="R62" s="55" t="str">
+      <x:c r="R62" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S62" s="134"/>
+      <x:c r="T62" s="135"/>
     </x:row>
     <x:row r="63" ht="85" customHeight="1">
-      <x:c r="A63" s="52" t="str">
+      <x:c r="A63" s="57" t="str">
         <x:v>july_paid</x:v>
       </x:c>
-      <x:c r="B63" s="94" t="n">
+      <x:c r="B63" s="99" t="n">
         <x:v>2000000000</x:v>
       </x:c>
-      <x:c r="C63" s="95" t="str">
+      <x:c r="C63" s="100" t="str">
         <x:v>July infectious-disease acquisitions: cash paid</x:v>
       </x:c>
-      <x:c r="D63" s="54"/>
-      <x:c r="E63" s="54" t="str">
+      <x:c r="D63" s="59"/>
+      <x:c r="E63" s="59" t="str">
         <x:v>July 2026</x:v>
       </x:c>
-      <x:c r="F63" s="95" t="str">
+      <x:c r="F63" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G63" s="54" t="d">
+      <x:c r="G63" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H63" s="95" t="str">
+      <x:c r="H63" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I63" s="95"/>
-      <x:c r="J63" s="95"/>
-      <x:c r="K63" s="95"/>
-      <x:c r="L63" s="95"/>
-      <x:c r="M63" s="95" t="str">
+      <x:c r="I63" s="100"/>
+      <x:c r="J63" s="100"/>
+      <x:c r="K63" s="100"/>
+      <x:c r="L63" s="100"/>
+      <x:c r="M63" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N63" s="95" t="str">
+      <x:c r="N63" s="100" t="str">
         <x:v>MD&amp;A p. 31; Note 4 pp. 13–14</x:v>
       </x:c>
-      <x:c r="O63" s="95" t="str">
+      <x:c r="O63" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P63" s="95" t="str">
+      <x:c r="P63" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q63" s="95" t="str">
+      <x:c r="Q63" s="100" t="str">
         <x:v>Already paid after June. Other July cash flows are unknown; June cash less this payment is not a current cash balance.</x:v>
       </x:c>
-      <x:c r="R63" s="55" t="str">
+      <x:c r="R63" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S63" s="134"/>
+      <x:c r="T63" s="135"/>
     </x:row>
     <x:row r="64" ht="85" customHeight="1">
-      <x:c r="A64" s="52" t="str">
+      <x:c r="A64" s="57" t="str">
         <x:v>july_ceiling</x:v>
       </x:c>
-      <x:c r="B64" s="94" t="n">
+      <x:c r="B64" s="99" t="n">
         <x:v>3900000000</x:v>
       </x:c>
-      <x:c r="C64" s="95" t="str">
+      <x:c r="C64" s="100" t="str">
         <x:v>July acquisitions: aggregate consideration up to</x:v>
       </x:c>
-      <x:c r="D64" s="54"/>
-      <x:c r="E64" s="54" t="str">
+      <x:c r="D64" s="59"/>
+      <x:c r="E64" s="59" t="str">
         <x:v>July 2026</x:v>
       </x:c>
-      <x:c r="F64" s="95" t="str">
+      <x:c r="F64" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G64" s="54" t="d">
+      <x:c r="G64" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H64" s="95" t="str">
+      <x:c r="H64" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I64" s="95"/>
-      <x:c r="J64" s="95"/>
-      <x:c r="K64" s="95"/>
-      <x:c r="L64" s="95"/>
-      <x:c r="M64" s="95" t="str">
+      <x:c r="I64" s="100"/>
+      <x:c r="J64" s="100"/>
+      <x:c r="K64" s="100"/>
+      <x:c r="L64" s="100"/>
+      <x:c r="M64" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N64" s="95" t="str">
+      <x:c r="N64" s="100" t="str">
         <x:v>Note 4 pp. 13–14</x:v>
       </x:c>
-      <x:c r="O64" s="95" t="str">
+      <x:c r="O64" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P64" s="95" t="str">
+      <x:c r="P64" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q64" s="95" t="str">
+      <x:c r="Q64" s="100" t="str">
         <x:v>Includes upfront cash and potential clinical, regulatory and commercial milestones. Includes the approximately $2B paid; do not add the two amounts or infer a precise remaining cash bill.</x:v>
       </x:c>
-      <x:c r="R64" s="55" t="str">
+      <x:c r="R64" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S64" s="134"/>
+      <x:c r="T64" s="135"/>
     </x:row>
     <x:row r="65" ht="85" customHeight="1">
-      <x:c r="A65" s="52" t="str">
+      <x:c r="A65" s="57" t="str">
         <x:v>vc</x:v>
       </x:c>
-      <x:c r="B65" s="94" t="n">
+      <x:c r="B65" s="99" t="n">
         <x:v>806000000</x:v>
       </x:c>
-      <x:c r="C65" s="95" t="str">
+      <x:c r="C65" s="100" t="str">
         <x:v>Unfunded venture fund commitments</x:v>
       </x:c>
-      <x:c r="D65" s="54"/>
-      <x:c r="E65" s="54" t="d">
+      <x:c r="D65" s="59"/>
+      <x:c r="E65" s="59" t="d">
         <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F65" s="95" t="str">
+      <x:c r="F65" s="100" t="str">
         <x:v>10-Q</x:v>
       </x:c>
-      <x:c r="G65" s="54" t="d">
+      <x:c r="G65" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H65" s="95" t="str">
+      <x:c r="H65" s="100" t="str">
         <x:v>0000059478-26-000081</x:v>
       </x:c>
-      <x:c r="I65" s="95"/>
-      <x:c r="J65" s="95"/>
-      <x:c r="K65" s="95"/>
-      <x:c r="L65" s="95"/>
-      <x:c r="M65" s="95" t="str">
+      <x:c r="I65" s="100"/>
+      <x:c r="J65" s="100"/>
+      <x:c r="K65" s="100"/>
+      <x:c r="L65" s="100"/>
+      <x:c r="M65" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
-      <x:c r="N65" s="95" t="str">
+      <x:c r="N65" s="100" t="str">
         <x:v>MD&amp;A p. 31</x:v>
       </x:c>
-      <x:c r="O65" s="95" t="str">
+      <x:c r="O65" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P65" s="95" t="str">
+      <x:c r="P65" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q65" s="95" t="str">
+      <x:c r="Q65" s="100" t="str">
         <x:v>Expected to be paid over up to ten years. Individual capital-call dates are Unavailable.</x:v>
       </x:c>
-      <x:c r="R65" s="55" t="str">
+      <x:c r="R65" s="60" t="str">
         <x:v>8e8f10cf3af98bc12a41985a98cfde9c2b9da8a812af18515d34ce3d8e1c1b3d</x:v>
       </x:c>
+      <x:c r="S65" s="134"/>
+      <x:c r="T65" s="135"/>
     </x:row>
     <x:row r="66" ht="85" customHeight="1">
-      <x:c r="A66" s="52" t="str">
+      <x:c r="A66" s="57" t="str">
         <x:v>manufacturing</x:v>
       </x:c>
-      <x:c r="B66" s="94" t="n">
+      <x:c r="B66" s="99" t="n">
         <x:v>10000000000</x:v>
       </x:c>
-      <x:c r="C66" s="95" t="str">
+      <x:c r="C66" s="100" t="str">
         <x:v>Development-medicine supply arrangements: up to</x:v>
       </x:c>
-      <x:c r="D66" s="54"/>
-      <x:c r="E66" s="54" t="d">
+      <x:c r="D66" s="59"/>
+      <x:c r="E66" s="59" t="d">
         <x:v>2025-12-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F66" s="95" t="str">
+      <x:c r="F66" s="100" t="str">
         <x:v>10-K</x:v>
       </x:c>
-      <x:c r="G66" s="54" t="d">
+      <x:c r="G66" s="59" t="d">
         <x:v>2026-02-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H66" s="95" t="str">
+      <x:c r="H66" s="100" t="str">
         <x:v>0000059478-26-000013</x:v>
       </x:c>
-      <x:c r="I66" s="95"/>
-      <x:c r="J66" s="95"/>
-      <x:c r="K66" s="95"/>
-      <x:c r="L66" s="95"/>
-      <x:c r="M66" s="95" t="str">
+      <x:c r="I66" s="100"/>
+      <x:c r="J66" s="100"/>
+      <x:c r="K66" s="100"/>
+      <x:c r="L66" s="100"/>
+      <x:c r="M66" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
-      <x:c r="N66" s="95" t="str">
+      <x:c r="N66" s="100" t="str">
         <x:v>MD&amp;A p. 51</x:v>
       </x:c>
-      <x:c r="O66" s="95" t="str">
+      <x:c r="O66" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P66" s="95" t="str">
+      <x:c r="P66" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q66" s="95" t="str">
+      <x:c r="Q66" s="100" t="str">
         <x:v>Payments if specified purchases are not met under executed manufacturing and supply agreements; durations generally up to eight years. Not an unconditional $10B bill. Updated June ceiling, annual payments and overlap with other spending are Unavailable.</x:v>
       </x:c>
-      <x:c r="R66" s="55" t="str">
+      <x:c r="R66" s="60" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
+      <x:c r="S66" s="134"/>
+      <x:c r="T66" s="135"/>
     </x:row>
     <x:row r="67" ht="85" customHeight="1">
-      <x:c r="A67" s="59" t="str">
+      <x:c r="A67" s="57" t="str">
         <x:v>indiana</x:v>
       </x:c>
-      <x:c r="B67" s="96" t="n">
+      <x:c r="B67" s="99" t="n">
         <x:v>4500000000</x:v>
       </x:c>
-      <x:c r="C67" s="97" t="str">
+      <x:c r="C67" s="100" t="str">
         <x:v>Additional Indiana manufacturing investment</x:v>
       </x:c>
-      <x:c r="D67" s="61"/>
-      <x:c r="E67" s="61" t="str">
+      <x:c r="D67" s="59"/>
+      <x:c r="E67" s="59" t="str">
         <x:v>Announced August 5, 2026</x:v>
       </x:c>
-      <x:c r="F67" s="97" t="str">
+      <x:c r="F67" s="100" t="str">
         <x:v>8-K Ex. 99.1</x:v>
       </x:c>
-      <x:c r="G67" s="61" t="d">
+      <x:c r="G67" s="59" t="d">
         <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H67" s="97" t="str">
+      <x:c r="H67" s="100" t="str">
         <x:v>0000059478-26-000077</x:v>
       </x:c>
-      <x:c r="I67" s="97"/>
-      <x:c r="J67" s="97"/>
-      <x:c r="K67" s="97"/>
-      <x:c r="L67" s="97"/>
-      <x:c r="M67" s="97" t="str">
+      <x:c r="I67" s="100"/>
+      <x:c r="J67" s="100"/>
+      <x:c r="K67" s="100"/>
+      <x:c r="L67" s="100"/>
+      <x:c r="M67" s="100" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000077/q226lillysalesandearningsp.htm</x:v>
       </x:c>
-      <x:c r="N67" s="97" t="str">
+      <x:c r="N67" s="100" t="str">
         <x:v>Highlights; Other announcements</x:v>
       </x:c>
-      <x:c r="O67" s="97" t="str">
+      <x:c r="O67" s="100" t="str">
         <x:v>Reviewed filing text</x:v>
       </x:c>
-      <x:c r="P67" s="97" t="str">
+      <x:c r="P67" s="100" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="Q67" s="97" t="str">
+      <x:c r="Q67" s="100" t="str">
         <x:v>Release says committed an additional $4.5B. Contractual payment schedule, spending to date and overlap with capex or supply commitments are not established by this release. Not added to debt or the $10B ceiling.</x:v>
       </x:c>
-      <x:c r="R67" s="62" t="str">
+      <x:c r="R67" s="60" t="str">
         <x:v>5397056cb6aebc1496e22de6f9c8b062b11ff0c7f5ee30428e3f68fc8aea748a</x:v>
       </x:c>
+      <x:c r="S67" s="134"/>
+      <x:c r="T67" s="135"/>
+    </x:row>
+    <x:row r="68" ht="85" customHeight="1">
+      <x:c r="A68" s="57" t="str">
+        <x:v>may_notes_0</x:v>
+      </x:c>
+      <x:c r="B68" s="99" t="n">
+        <x:v>750000000</x:v>
+      </x:c>
+      <x:c r="C68" s="100" t="str">
+        <x:v>Floating 2028 — May 20 initial issue</x:v>
+      </x:c>
+      <x:c r="D68" s="59"/>
+      <x:c r="E68" s="59" t="d">
+        <x:v>2028-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F68" s="100" t="str">
+        <x:v>8-K Ex. 4.4</x:v>
+      </x:c>
+      <x:c r="G68" s="59" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H68" s="100" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I68" s="100"/>
+      <x:c r="J68" s="100"/>
+      <x:c r="K68" s="100"/>
+      <x:c r="L68" s="100"/>
+      <x:c r="M68" s="100" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580dex44.htm</x:v>
+      </x:c>
+      <x:c r="N68" s="100" t="str">
+        <x:v>Certificate clauses (iii)–(v); note forms</x:v>
+      </x:c>
+      <x:c r="O68" s="100" t="str">
+        <x:v>Reviewed contract text</x:v>
+      </x:c>
+      <x:c r="P68" s="100" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q68" s="100" t="str">
+        <x:v>Initial issue principal, not June outstanding balance. Issued 2026-05-20. Stated maturity subject to applicable business-day, redemption and default provisions. Not added to June debt or the December carrying-amount table.</x:v>
+      </x:c>
+      <x:c r="R68" s="60" t="str">
+        <x:v>abe96195bc60dfbb1bbdb90af64d2e548b2b743cfe34901cdf512542c9c576b9</x:v>
+      </x:c>
+      <x:c r="S68" s="134"/>
+      <x:c r="T68" s="135" t="n">
+        <x:v>0.0035</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="85" customHeight="1">
+      <x:c r="A69" s="57" t="str">
+        <x:v>may_notes_1</x:v>
+      </x:c>
+      <x:c r="B69" s="99" t="n">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="C69" s="100" t="str">
+        <x:v>Floating 2029 — May 20 initial issue</x:v>
+      </x:c>
+      <x:c r="D69" s="59"/>
+      <x:c r="E69" s="59" t="d">
+        <x:v>2029-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F69" s="100" t="str">
+        <x:v>8-K Ex. 4.4</x:v>
+      </x:c>
+      <x:c r="G69" s="59" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H69" s="100" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I69" s="100"/>
+      <x:c r="J69" s="100"/>
+      <x:c r="K69" s="100"/>
+      <x:c r="L69" s="100"/>
+      <x:c r="M69" s="100" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580dex44.htm</x:v>
+      </x:c>
+      <x:c r="N69" s="100" t="str">
+        <x:v>Certificate clauses (iii)–(v); note forms</x:v>
+      </x:c>
+      <x:c r="O69" s="100" t="str">
+        <x:v>Reviewed contract text</x:v>
+      </x:c>
+      <x:c r="P69" s="100" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q69" s="100" t="str">
+        <x:v>Initial issue principal, not June outstanding balance. Issued 2026-05-20. Stated maturity subject to applicable business-day, redemption and default provisions. Not added to June debt or the December carrying-amount table.</x:v>
+      </x:c>
+      <x:c r="R69" s="60" t="str">
+        <x:v>abe96195bc60dfbb1bbdb90af64d2e548b2b743cfe34901cdf512542c9c576b9</x:v>
+      </x:c>
+      <x:c r="S69" s="134"/>
+      <x:c r="T69" s="135" t="n">
+        <x:v>0.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="85" customHeight="1">
+      <x:c r="A70" s="57" t="str">
+        <x:v>may_notes_2</x:v>
+      </x:c>
+      <x:c r="B70" s="99" t="n">
+        <x:v>750000000</x:v>
+      </x:c>
+      <x:c r="C70" s="100" t="str">
+        <x:v>Fixed 2029 — May 20 initial issue</x:v>
+      </x:c>
+      <x:c r="D70" s="59"/>
+      <x:c r="E70" s="59" t="d">
+        <x:v>2029-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F70" s="100" t="str">
+        <x:v>8-K Ex. 4.3</x:v>
+      </x:c>
+      <x:c r="G70" s="59" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H70" s="100" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I70" s="100"/>
+      <x:c r="J70" s="100"/>
+      <x:c r="K70" s="100"/>
+      <x:c r="L70" s="100"/>
+      <x:c r="M70" s="100" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580dex43.htm</x:v>
+      </x:c>
+      <x:c r="N70" s="100" t="str">
+        <x:v>Certificate clauses (iii)–(v); note forms</x:v>
+      </x:c>
+      <x:c r="O70" s="100" t="str">
+        <x:v>Reviewed contract text</x:v>
+      </x:c>
+      <x:c r="P70" s="100" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q70" s="100" t="str">
+        <x:v>Initial issue principal, not June outstanding balance. Issued 2026-05-20. Stated maturity subject to applicable business-day, redemption and default provisions. Not added to June debt or the December carrying-amount table.</x:v>
+      </x:c>
+      <x:c r="R70" s="60" t="str">
+        <x:v>23483435eff9194a1858f9a71159cb4d3d661db65eff0ff4d950bb7f4e783b97</x:v>
+      </x:c>
+      <x:c r="S70" s="134" t="n">
+        <x:v>0.0415</x:v>
+      </x:c>
+      <x:c r="T70" s="135"/>
+    </x:row>
+    <x:row r="71" ht="85" customHeight="1">
+      <x:c r="A71" s="57" t="str">
+        <x:v>may_notes_3</x:v>
+      </x:c>
+      <x:c r="B71" s="99" t="n">
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="C71" s="100" t="str">
+        <x:v>Fixed 2031 — May 20 initial issue</x:v>
+      </x:c>
+      <x:c r="D71" s="59"/>
+      <x:c r="E71" s="59" t="d">
+        <x:v>2031-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F71" s="100" t="str">
+        <x:v>8-K Ex. 4.3</x:v>
+      </x:c>
+      <x:c r="G71" s="59" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H71" s="100" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I71" s="100"/>
+      <x:c r="J71" s="100"/>
+      <x:c r="K71" s="100"/>
+      <x:c r="L71" s="100"/>
+      <x:c r="M71" s="100" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580dex43.htm</x:v>
+      </x:c>
+      <x:c r="N71" s="100" t="str">
+        <x:v>Certificate clauses (iii)–(v); note forms</x:v>
+      </x:c>
+      <x:c r="O71" s="100" t="str">
+        <x:v>Reviewed contract text</x:v>
+      </x:c>
+      <x:c r="P71" s="100" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q71" s="100" t="str">
+        <x:v>Initial issue principal, not June outstanding balance. Issued 2026-05-20. Stated maturity subject to applicable business-day, redemption and default provisions. Not added to June debt or the December carrying-amount table.</x:v>
+      </x:c>
+      <x:c r="R71" s="60" t="str">
+        <x:v>23483435eff9194a1858f9a71159cb4d3d661db65eff0ff4d950bb7f4e783b97</x:v>
+      </x:c>
+      <x:c r="S71" s="134" t="n">
+        <x:v>0.04375</x:v>
+      </x:c>
+      <x:c r="T71" s="135"/>
+    </x:row>
+    <x:row r="72" ht="85" customHeight="1">
+      <x:c r="A72" s="57" t="str">
+        <x:v>may_notes_4</x:v>
+      </x:c>
+      <x:c r="B72" s="99" t="n">
+        <x:v>1250000000</x:v>
+      </x:c>
+      <x:c r="C72" s="100" t="str">
+        <x:v>Fixed 2033 — May 20 initial issue</x:v>
+      </x:c>
+      <x:c r="D72" s="59"/>
+      <x:c r="E72" s="59" t="d">
+        <x:v>2033-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F72" s="100" t="str">
+        <x:v>8-K Ex. 4.3</x:v>
+      </x:c>
+      <x:c r="G72" s="59" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H72" s="100" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I72" s="100"/>
+      <x:c r="J72" s="100"/>
+      <x:c r="K72" s="100"/>
+      <x:c r="L72" s="100"/>
+      <x:c r="M72" s="100" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580dex43.htm</x:v>
+      </x:c>
+      <x:c r="N72" s="100" t="str">
+        <x:v>Certificate clauses (iii)–(v); note forms</x:v>
+      </x:c>
+      <x:c r="O72" s="100" t="str">
+        <x:v>Reviewed contract text</x:v>
+      </x:c>
+      <x:c r="P72" s="100" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q72" s="100" t="str">
+        <x:v>Initial issue principal, not June outstanding balance. Issued 2026-05-20. Stated maturity subject to applicable business-day, redemption and default provisions. Not added to June debt or the December carrying-amount table.</x:v>
+      </x:c>
+      <x:c r="R72" s="60" t="str">
+        <x:v>23483435eff9194a1858f9a71159cb4d3d661db65eff0ff4d950bb7f4e783b97</x:v>
+      </x:c>
+      <x:c r="S72" s="134" t="n">
+        <x:v>0.0465</x:v>
+      </x:c>
+      <x:c r="T72" s="135"/>
+    </x:row>
+    <x:row r="73" ht="85" customHeight="1">
+      <x:c r="A73" s="57" t="str">
+        <x:v>may_notes_5</x:v>
+      </x:c>
+      <x:c r="B73" s="99" t="n">
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="C73" s="100" t="str">
+        <x:v>Fixed 2036 — May 20 initial issue</x:v>
+      </x:c>
+      <x:c r="D73" s="59"/>
+      <x:c r="E73" s="59" t="d">
+        <x:v>2036-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F73" s="100" t="str">
+        <x:v>8-K Ex. 4.3</x:v>
+      </x:c>
+      <x:c r="G73" s="59" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H73" s="100" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I73" s="100"/>
+      <x:c r="J73" s="100"/>
+      <x:c r="K73" s="100"/>
+      <x:c r="L73" s="100"/>
+      <x:c r="M73" s="100" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580dex43.htm</x:v>
+      </x:c>
+      <x:c r="N73" s="100" t="str">
+        <x:v>Certificate clauses (iii)–(v); note forms</x:v>
+      </x:c>
+      <x:c r="O73" s="100" t="str">
+        <x:v>Reviewed contract text</x:v>
+      </x:c>
+      <x:c r="P73" s="100" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q73" s="100" t="str">
+        <x:v>Initial issue principal, not June outstanding balance. Issued 2026-05-20. Stated maturity subject to applicable business-day, redemption and default provisions. Not added to June debt or the December carrying-amount table.</x:v>
+      </x:c>
+      <x:c r="R73" s="60" t="str">
+        <x:v>23483435eff9194a1858f9a71159cb4d3d661db65eff0ff4d950bb7f4e783b97</x:v>
+      </x:c>
+      <x:c r="S73" s="134" t="n">
+        <x:v>0.0485</x:v>
+      </x:c>
+      <x:c r="T73" s="135"/>
+    </x:row>
+    <x:row r="74" ht="85" customHeight="1">
+      <x:c r="A74" s="57" t="str">
+        <x:v>may_notes_6</x:v>
+      </x:c>
+      <x:c r="B74" s="99" t="n">
+        <x:v>1750000000</x:v>
+      </x:c>
+      <x:c r="C74" s="100" t="str">
+        <x:v>Fixed 2056 — May 20 initial issue</x:v>
+      </x:c>
+      <x:c r="D74" s="59"/>
+      <x:c r="E74" s="59" t="d">
+        <x:v>2056-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F74" s="100" t="str">
+        <x:v>8-K Ex. 4.3</x:v>
+      </x:c>
+      <x:c r="G74" s="59" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H74" s="100" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I74" s="100"/>
+      <x:c r="J74" s="100"/>
+      <x:c r="K74" s="100"/>
+      <x:c r="L74" s="100"/>
+      <x:c r="M74" s="100" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580dex43.htm</x:v>
+      </x:c>
+      <x:c r="N74" s="100" t="str">
+        <x:v>Certificate clauses (iii)–(v); note forms</x:v>
+      </x:c>
+      <x:c r="O74" s="100" t="str">
+        <x:v>Reviewed contract text</x:v>
+      </x:c>
+      <x:c r="P74" s="100" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q74" s="100" t="str">
+        <x:v>Initial issue principal, not June outstanding balance. Issued 2026-05-20. Stated maturity subject to applicable business-day, redemption and default provisions. Not added to June debt or the December carrying-amount table.</x:v>
+      </x:c>
+      <x:c r="R74" s="60" t="str">
+        <x:v>23483435eff9194a1858f9a71159cb4d3d661db65eff0ff4d950bb7f4e783b97</x:v>
+      </x:c>
+      <x:c r="S74" s="134" t="n">
+        <x:v>0.056</x:v>
+      </x:c>
+      <x:c r="T74" s="135"/>
+    </x:row>
+    <x:row r="75" ht="85" customHeight="1">
+      <x:c r="A75" s="57" t="str">
+        <x:v>may_notes_7</x:v>
+      </x:c>
+      <x:c r="B75" s="99" t="n">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="C75" s="100" t="str">
+        <x:v>Fixed 2066 — May 20 initial issue</x:v>
+      </x:c>
+      <x:c r="D75" s="59"/>
+      <x:c r="E75" s="59" t="d">
+        <x:v>2066-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F75" s="100" t="str">
+        <x:v>8-K Ex. 4.3</x:v>
+      </x:c>
+      <x:c r="G75" s="59" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H75" s="100" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I75" s="100"/>
+      <x:c r="J75" s="100"/>
+      <x:c r="K75" s="100"/>
+      <x:c r="L75" s="100"/>
+      <x:c r="M75" s="100" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580dex43.htm</x:v>
+      </x:c>
+      <x:c r="N75" s="100" t="str">
+        <x:v>Certificate clauses (iii)–(v); note forms</x:v>
+      </x:c>
+      <x:c r="O75" s="100" t="str">
+        <x:v>Reviewed contract text</x:v>
+      </x:c>
+      <x:c r="P75" s="100" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q75" s="100" t="str">
+        <x:v>Initial issue principal, not June outstanding balance. Issued 2026-05-20. Stated maturity subject to applicable business-day, redemption and default provisions. Not added to June debt or the December carrying-amount table.</x:v>
+      </x:c>
+      <x:c r="R75" s="60" t="str">
+        <x:v>23483435eff9194a1858f9a71159cb4d3d661db65eff0ff4d950bb7f4e783b97</x:v>
+      </x:c>
+      <x:c r="S75" s="134" t="n">
+        <x:v>0.057</x:v>
+      </x:c>
+      <x:c r="T75" s="135"/>
+    </x:row>
+    <x:row r="76" ht="85" customHeight="1">
+      <x:c r="A76" s="64" t="str">
+        <x:v>may_issue_control</x:v>
+      </x:c>
+      <x:c r="B76" s="101" t="n">
+        <x:v>9000000000</x:v>
+      </x:c>
+      <x:c r="C76" s="102" t="str">
+        <x:v>Reported completed May issue, initial principal</x:v>
+      </x:c>
+      <x:c r="D76" s="66"/>
+      <x:c r="E76" s="66" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F76" s="102" t="str">
+        <x:v>8-K</x:v>
+      </x:c>
+      <x:c r="G76" s="66" t="d">
+        <x:v>2026-05-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H76" s="102" t="str">
+        <x:v>0001193125-26-232707</x:v>
+      </x:c>
+      <x:c r="I76" s="102"/>
+      <x:c r="J76" s="102"/>
+      <x:c r="K76" s="102"/>
+      <x:c r="L76" s="102"/>
+      <x:c r="M76" s="102" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000119312526232707/d148580d8k.htm</x:v>
+      </x:c>
+      <x:c r="N76" s="102" t="str">
+        <x:v>Item 8.01, completed offering</x:v>
+      </x:c>
+      <x:c r="O76" s="102" t="str">
+        <x:v>Reviewed filing text</x:v>
+      </x:c>
+      <x:c r="P76" s="102" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="Q76" s="102" t="str">
+        <x:v>Initial issue principal, not net cash proceeds, current outstanding debt or unused financing.</x:v>
+      </x:c>
+      <x:c r="R76" s="67" t="str">
+        <x:v>e88aeee8cddfc4b3459ec97cd166010b955ae2d8e5bcc2e59913f995c2e233f9</x:v>
+      </x:c>
+      <x:c r="S76" s="136"/>
+      <x:c r="T76" s="137"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5709,89 +6724,111 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="78" t="str">
+      <x:c r="A1" s="83" t="str">
         <x:v>Topic</x:v>
       </x:c>
-      <x:c r="B1" s="79" t="str">
+      <x:c r="B1" s="84" t="str">
         <x:v>Explanation</x:v>
       </x:c>
-      <x:c r="C1" s="80" t="str">
+      <x:c r="C1" s="85" t="str">
         <x:v>Source</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="70" customHeight="1">
-      <x:c r="A2" s="52" t="str">
+      <x:c r="A2" s="57" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="B2" s="95" t="str">
+      <x:c r="B2" s="100" t="str">
         <x:v>Lilly only. Checked snapshot October 14, 2026. Financial statements dated June 30, 2026. Not investment advice.</x:v>
       </x:c>
-      <x:c r="C2" s="55" t="str">
+      <x:c r="C2" s="60" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="70" customHeight="1">
-      <x:c r="A3" s="52" t="str">
+      <x:c r="A3" s="57" t="str">
         <x:v>Colors</x:v>
       </x:c>
-      <x:c r="B3" s="95" t="str">
+      <x:c r="B3" s="100" t="str">
         <x:v>Arial 10. Full USD displayed in millions. Blue reported inputs, green cross-sheet links, black same-sheet calculations. Zero is a dash. Missing inputs are not zero.</x:v>
       </x:c>
-      <x:c r="C3" s="55"/>
+      <x:c r="C3" s="60"/>
     </x:row>
     <x:row r="4" ht="70" customHeight="1">
-      <x:c r="A4" s="52" t="str">
+      <x:c r="A4" s="57" t="str">
         <x:v>Cash generation</x:v>
       </x:c>
-      <x:c r="B4" s="95" t="str">
+      <x:c r="B4" s="100" t="str">
         <x:v>Fiscal year + current YTD − prior YTD. Capital spending uses Lilly’s checked other-PP&amp;E tag. FCF excludes acquisitions, dividends and other cash uses.</x:v>
       </x:c>
-      <x:c r="C4" s="55" t="str">
+      <x:c r="C4" s="60" t="str">
         <x:v>docs/pilot_cashflow_reconciliation.md</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="70" customHeight="1">
-      <x:c r="A5" s="52" t="str">
+      <x:c r="A5" s="57" t="str">
         <x:v>Borrowing</x:v>
       </x:c>
-      <x:c r="B5" s="95" t="str">
+      <x:c r="B5" s="100" t="str">
         <x:v>Balance-sheet current and noncurrent borrowing are added once. Fair-value table carrying amounts are not added again.</x:v>
       </x:c>
-      <x:c r="C5" s="55" t="str">
+      <x:c r="C5" s="60" t="str">
         <x:v>docs/pilot_evidence_lly.md</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
-      <x:c r="A6" s="59" t="str">
+      <x:c r="A6" s="64" t="str">
         <x:v>Selected commitments</x:v>
       </x:c>
-      <x:c r="B6" s="97" t="str">
+      <x:c r="B6" s="102" t="str">
         <x:v>Descriptions retain their disclosure dates; AtaiBeckley was disclosed after quarter end. They are not added to debt or to each other.</x:v>
       </x:c>
-      <x:c r="C6" s="62" t="str">
+      <x:c r="C6" s="67" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="95" customHeight="1">
-      <x:c r="A7" s="52" t="str">
+      <x:c r="A7" s="57" t="str">
         <x:v>Dated review</x:v>
       </x:c>
-      <x:c r="B7" s="95" t="str">
+      <x:c r="B7" s="100" t="str">
         <x:v>Repayment review uses exact H1 cash flows and historical annual carrying-debt buckets. Future coverage remains Unavailable. Text disclosures are identified separately; source hashes and dimensions are in Data.</x:v>
       </x:c>
-      <x:c r="C7" s="55" t="str">
+      <x:c r="C7" s="60" t="str">
         <x:v>docs/lly_liquidity_review.md</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="95" customHeight="1">
-      <x:c r="A8" s="59" t="str">
+      <x:c r="A8" s="64" t="str">
         <x:v>Post-quarter events</x:v>
       </x:c>
-      <x:c r="B8" s="97" t="str">
+      <x:c r="B8" s="102" t="str">
         <x:v>July acquisition cash is separate from June cash. The July $3.9B ceiling includes upfront cash. August $4.5B manufacturing announcement has no dated cash schedule. No overlap total inferred.</x:v>
       </x:c>
-      <x:c r="C8" s="62" t="str">
+      <x:c r="C8" s="67" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000077/q226lillysalesandearningsp.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="85" customHeight="1">
+      <x:c r="A9" s="57" t="str">
+        <x:v>Financing inventory</x:v>
+      </x:c>
+      <x:c r="B9" s="100" t="str">
+        <x:v>SEC index screened through October 15, 2026. May offering terms added as initial principal; full June debt schedule and drawable capacity remain Unavailable.</x:v>
+      </x:c>
+      <x:c r="C9" s="60" t="str">
+        <x:v>https://data.sec.gov/submissions/CIK0000059478.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="85" customHeight="1">
+      <x:c r="A10" s="64" t="str">
+        <x:v>Contract evidence</x:v>
+      </x:c>
+      <x:c r="B10" s="102" t="str">
+        <x:v>Series rates and maturities come from the final prospectus and certificates, corroborated by the completed offering. An 8-K coupon conflict is flagged; the corroborated 2029 fixed rate is 4.150%.</x:v>
+      </x:c>
+      <x:c r="C10" s="67" t="str">
+        <x:v>docs/lly_financing_audit.md</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="Rf70c54d8804b432d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="2" r:id="R39aa0010726840c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="3" r:id="R9b0003417e5c473f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" r:id="R34b2559cf224497e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="5" r:id="Ra50cf1abecf44321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="Rc1d020c4a509471e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="2" r:id="R8a17fbeb69d54df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="3" r:id="R54d37a84a18f420a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" r:id="Rb86a2bfa21ba4fb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="5" r:id="Rf6d05661dade4526"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1038,7 +1038,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25e97008a7a949ab"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8704586239434e68"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2863,13 +2863,13 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B50" s="140" t="str">
-        <x:v>Saved filings only</x:v>
+        <x:v>Financing index through Oct 15, 2026</x:v>
       </x:c>
       <x:c r="C50" s="118" t="str">
-        <x:v>10-K; 10-Q; Aug 5 Ex. 99.1</x:v>
+        <x:v>10-K; 10-Q; earnings and financing documents</x:v>
       </x:c>
       <x:c r="D50" s="18" t="str">
-        <x:v>Not a complete SEC filing inventory. No combined total of commitments, milestones, capex plans or debt.</x:v>
+        <x:v>SEC financing candidates screened through October 15. Not a complete review of all liability notes. No combined obligations total.</x:v>
       </x:c>
       <x:c r="E50" s="4"/>
       <x:c r="F50" s="4"/>
@@ -3613,7 +3613,7 @@
     <x:mergeCell ref="A96:D96"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R648b8cfda5fc4258"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf433d9363a34e67"/>
 </x:worksheet>
 </file>
 
@@ -9141,7 +9141,7 @@
         <x:v>0000059478-26-000081</x:v>
       </x:c>
       <x:c r="D115" s="16" t="str">
-        <x:v>pp. 7–8, 12–14, 17, 23, 31</x:v>
+        <x:v>Operations p. 5; segment Note 11 p. 23</x:v>
       </x:c>
       <x:c r="L115" s="173" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
@@ -9158,7 +9158,7 @@
         <x:v>0000059478-26-000013</x:v>
       </x:c>
       <x:c r="D116" s="18" t="str">
-        <x:v>pp. 51, 57, 76–77</x:v>
+        <x:v>Operations p. 57; Borrowings Note 11 p. 77</x:v>
       </x:c>
       <x:c r="L116" s="174" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
@@ -9189,12 +9189,12 @@
         <x:v>Source</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="70" customHeight="1">
+    <x:row r="2" ht="100" customHeight="1">
       <x:c r="A2" s="25" t="str">
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B2" s="116" t="str">
-        <x:v>Lilly only. Checked snapshot October 14, 2026. Financial statements dated June 30, 2026. Not investment advice.</x:v>
+        <x:v>Lilly only. Balance-sheet facts checked October 14, 2026; financing and interest reviewed October 15; funding interpretation checked October 16. Financial statements dated June 30. Not investment advice.</x:v>
       </x:c>
       <x:c r="C2" s="16" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
@@ -9217,7 +9217,7 @@
         <x:v>Fiscal year + current YTD − prior YTD. Capital spending uses Lilly’s checked other-PP&amp;E tag. FCF excludes acquisitions, dividends and other cash uses.</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>docs/pilot_cashflow_reconciliation.md</x:v>
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/pilot_cashflow_reconciliation.md</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="70" customHeight="1">
@@ -9228,7 +9228,7 @@
         <x:v>Balance-sheet current and noncurrent borrowing are added once. Fair-value table carrying amounts are not added again.</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>docs/pilot_evidence_lly.md</x:v>
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/pilot_evidence_lly.md</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
@@ -9250,7 +9250,7 @@
         <x:v>Repayment review uses exact H1 cash flows and historical annual carrying-debt buckets. Future coverage remains Unavailable. Text disclosures are identified separately; source hashes and dimensions are in Data.</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str">
-        <x:v>docs/lly_liquidity_review.md</x:v>
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/lly_liquidity_review.md</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="95" customHeight="1">
@@ -9283,7 +9283,7 @@
         <x:v>Series rates and maturities come from the final prospectus and certificates, corroborated by the completed offering. An 8-K coupon conflict is flagged; the corroborated 2029 fixed rate is 4.150%.</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
-        <x:v>docs/lly_financing_audit.md</x:v>
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/lly_financing_audit.md</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="100" customHeight="1">
@@ -9294,7 +9294,7 @@
         <x:v>Derived TTM operating income / reported interest expense. FY + current H1 − prior H1; each operating-income period reconciles to pretax less tagged nonoperating income (expense).</x:v>
       </x:c>
       <x:c r="C11" s="16" t="str">
-        <x:v>docs/lly_interest_coverage.md</x:v>
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/lly_interest_coverage.md</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="100" customHeight="1">

--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2,11 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="Rc1d020c4a509471e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="2" r:id="R8a17fbeb69d54df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="3" r:id="R54d37a84a18f420a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" r:id="Rb86a2bfa21ba4fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="5" r:id="Rf6d05661dade4526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R0690a579cb1f471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="R68a141c45d2142da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="Re57f25ff60eb4c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="4" r:id="R53f5ac129a90469f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="5" r:id="R776c91b13bb947d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="6" r:id="R6f66b36fb08f4c06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -371,7 +372,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="179">
+  <x:cellXfs count="196">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -840,6 +841,57 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1038,7 +1090,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8704586239434e68"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R44aeeb1f676e41f0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1381,6 +1433,286 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="72" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="12" customHeight="1">
+      <x:c r="A1" s="4"/>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="7" t="str">
+        <x:v>Eli Lilly and Company borrowing and leases</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Amounts in USD millions. Each balance retains its own date. Baseline borrowing excludes leases.</x:v>
+      </x:c>
+      <x:c r="B3" s="4"/>
+      <x:c r="C3" s="4"/>
+      <x:c r="D3" s="4"/>
+      <x:c r="E3" s="4"/>
+    </x:row>
+    <x:row r="4" ht="12" customHeight="1">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="4"/>
+      <x:c r="C4" s="4"/>
+      <x:c r="D4" s="4"/>
+      <x:c r="E4" s="4"/>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="13" t="str">
+        <x:v>Borrowing component</x:v>
+      </x:c>
+      <x:c r="B5" s="103" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C5" s="103" t="str">
+        <x:v>As of</x:v>
+      </x:c>
+      <x:c r="D5" s="103" t="str">
+        <x:v>Source / filing</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>Basis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="25" t="str">
+        <x:v>Current borrowing</x:v>
+      </x:c>
+      <x:c r="B6" s="81" t="n">
+        <x:f>IF(ISNUMBER('Data'!B120),'Data'!B120,NA())</x:f>
+        <x:v>7050000000</x:v>
+      </x:c>
+      <x:c r="C6" s="82" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D6" s="116" t="str">
+        <x:v>10-Q balance sheet, p. 7; filed 2026-08-05</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
+        <x:v>Short-term borrowings and current maturities of long-term debt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="25" t="str">
+        <x:v>Noncurrent borrowing</x:v>
+      </x:c>
+      <x:c r="B7" s="81" t="n">
+        <x:f>IF(ISNUMBER('Data'!B121),'Data'!B121,NA())</x:f>
+        <x:v>47858000000</x:v>
+      </x:c>
+      <x:c r="C7" s="82" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D7" s="116" t="str">
+        <x:v>10-Q balance sheet, p. 7; filed 2026-08-05</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="str">
+        <x:v>Long-term debt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="130" t="str">
+        <x:v>Baseline gross debt</x:v>
+      </x:c>
+      <x:c r="B8" s="134" t="n">
+        <x:f>SUM(B6:B7)</x:f>
+        <x:v>54908000000</x:v>
+      </x:c>
+      <x:c r="C8" s="195" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D8" s="132" t="str">
+        <x:v>Derived from the components above</x:v>
+      </x:c>
+      <x:c r="E8" s="133" t="str">
+        <x:v>Carrying amount; excludes leases.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="12" customHeight="1">
+      <x:c r="A9" s="4"/>
+      <x:c r="B9" s="135"/>
+      <x:c r="C9" s="60"/>
+      <x:c r="D9" s="4"/>
+      <x:c r="E9" s="4"/>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="4" t="str">
+        <x:v>Borrowing scope</x:v>
+      </x:c>
+      <x:c r="B10" s="135"/>
+      <x:c r="C10" s="60"/>
+      <x:c r="D10" s="4"/>
+      <x:c r="E10" s="4" t="str">
+        <x:v>Current borrowing includes short-term borrowings and current maturities. The Note 8 fair-value carrying amounts describe the same debt and are not added.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="12" customHeight="1">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="135"/>
+      <x:c r="C11" s="60"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+    </x:row>
+    <x:row r="12" ht="12" customHeight="1">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="135"/>
+      <x:c r="C12" s="60"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="13" t="str">
+        <x:v>Lease liability / commitment</x:v>
+      </x:c>
+      <x:c r="B13" s="136" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C13" s="188" t="str">
+        <x:v>As of</x:v>
+      </x:c>
+      <x:c r="D13" s="103" t="str">
+        <x:v>Source / filing</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>Basis / Unavailable reason</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="25" t="str">
+        <x:v>Lease liabilities at latest balance sheet</x:v>
+      </x:c>
+      <x:c r="B14" s="137" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C14" s="82" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D14" s="116" t="str">
+        <x:v>Checked 10-Q review</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="str">
+        <x:v>No lease liability amounts established in this 10-Q. Older amounts below are not substituted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="25" t="str">
+        <x:v>Operating lease liabilities — current</x:v>
+      </x:c>
+      <x:c r="B15" s="81" t="n">
+        <x:f>IF(ISNUMBER('Data'!B123),'Data'!B123,NA())</x:f>
+        <x:v>222000000</x:v>
+      </x:c>
+      <x:c r="C15" s="82" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D15" s="116" t="str">
+        <x:v>10-K Note 10, p. 76; filed 2026-02-12</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>Recognized lease liability; excluded from baseline borrowing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="25" t="str">
+        <x:v>Operating lease liabilities — noncurrent</x:v>
+      </x:c>
+      <x:c r="B16" s="81" t="n">
+        <x:f>IF(ISNUMBER('Data'!B124),'Data'!B124,NA())</x:f>
+        <x:v>1140000000</x:v>
+      </x:c>
+      <x:c r="C16" s="82" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D16" s="116" t="str">
+        <x:v>10-K Note 10, p. 76; filed 2026-02-12</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="str">
+        <x:v>Recognized lease liability; excluded from baseline borrowing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="107" t="str">
+        <x:v>Operating lease liabilities — total</x:v>
+      </x:c>
+      <x:c r="B17" s="112" t="n">
+        <x:f>B15+B16</x:f>
+        <x:v>1362000000</x:v>
+      </x:c>
+      <x:c r="C17" s="109" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D17" s="126" t="str">
+        <x:v>10-K Note 10, p. 76</x:v>
+      </x:c>
+      <x:c r="E17" s="110" t="str">
+        <x:v>Derived current + noncurrent; no separately tagged total.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="26" t="str">
+        <x:v>Finance lease liabilities</x:v>
+      </x:c>
+      <x:c r="B18" s="140" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C18" s="87" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D18" s="118" t="str">
+        <x:v>10-Q review; June amount not established</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="str">
+        <x:v>No checked June amount. The 10-K describes operating leases only; finance leases are not reported, which is not zero.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="12" customHeight="1">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="135"/>
+      <x:c r="C19" s="60"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+    </x:row>
+    <x:row r="20" ht="54" customHeight="1">
+      <x:c r="A20" s="157" t="str">
+        <x:v>Leases not yet commenced</x:v>
+      </x:c>
+      <x:c r="B20" s="189" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C20" s="190" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D20" s="191" t="str">
+        <x:v>Saved pilot evidence; 10-Q review</x:v>
+      </x:c>
+      <x:c r="E20" s="192" t="str">
+        <x:v>No checked amount for leases not yet commenced is established in the saved pilot evidence. Unavailable does not mean zero.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="73" hidden="0" customWidth="1"/>
@@ -2027,7 +2359,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3613,11 +3945,11 @@
     <x:mergeCell ref="A96:D96"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf433d9363a34e67"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06119863eaed4991"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -9164,12 +9496,314 @@
         <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
       </x:c>
     </x:row>
+    <x:row r="119" ht="78" customHeight="1">
+      <x:c r="A119" s="13" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="B119" s="103" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C119" s="103" t="str">
+        <x:v>Period start</x:v>
+      </x:c>
+      <x:c r="D119" s="103" t="str">
+        <x:v>Period end</x:v>
+      </x:c>
+      <x:c r="E119" s="103" t="str">
+        <x:v>Form</x:v>
+      </x:c>
+      <x:c r="F119" s="103" t="str">
+        <x:v>Filed</x:v>
+      </x:c>
+      <x:c r="G119" s="103" t="str">
+        <x:v>Accession</x:v>
+      </x:c>
+      <x:c r="H119" s="103" t="str">
+        <x:v>Tag</x:v>
+      </x:c>
+      <x:c r="I119" s="103" t="str">
+        <x:v>Context</x:v>
+      </x:c>
+      <x:c r="J119" s="103" t="str">
+        <x:v>Scale</x:v>
+      </x:c>
+      <x:c r="K119" s="103" t="str">
+        <x:v>Decimals</x:v>
+      </x:c>
+      <x:c r="L119" s="103" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="M119" s="103" t="str">
+        <x:v>Filing location</x:v>
+      </x:c>
+      <x:c r="N119" s="103" t="str">
+        <x:v>Unavailable reason</x:v>
+      </x:c>
+      <x:c r="O119" s="14" t="str">
+        <x:v>Reviewed source SHA256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="78" customHeight="1">
+      <x:c r="A120" s="25" t="str">
+        <x:v>Current borrowing</x:v>
+      </x:c>
+      <x:c r="B120" s="115" t="n">
+        <x:v>7050000000</x:v>
+      </x:c>
+      <x:c r="C120" s="116"/>
+      <x:c r="D120" s="82" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E120" s="116" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="F120" s="82" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G120" s="116" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="H120" s="116" t="str">
+        <x:v>us-gaap:DebtCurrent</x:v>
+      </x:c>
+      <x:c r="I120" s="116"/>
+      <x:c r="J120" s="116"/>
+      <x:c r="K120" s="116"/>
+      <x:c r="L120" s="116" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="M120" s="116" t="str">
+        <x:v>10-Q balance sheet, p. 7</x:v>
+      </x:c>
+      <x:c r="N120" s="116" t="str"/>
+      <x:c r="O120" s="16" t="str"/>
+    </x:row>
+    <x:row r="121" ht="78" customHeight="1">
+      <x:c r="A121" s="25" t="str">
+        <x:v>Noncurrent borrowing</x:v>
+      </x:c>
+      <x:c r="B121" s="115" t="n">
+        <x:v>47858000000</x:v>
+      </x:c>
+      <x:c r="C121" s="116"/>
+      <x:c r="D121" s="82" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E121" s="116" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="F121" s="82" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G121" s="116" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="H121" s="116" t="str">
+        <x:v>us-gaap:LongTermDebtNoncurrent</x:v>
+      </x:c>
+      <x:c r="I121" s="116"/>
+      <x:c r="J121" s="116"/>
+      <x:c r="K121" s="116"/>
+      <x:c r="L121" s="116" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="M121" s="116" t="str">
+        <x:v>10-Q balance sheet, p. 7</x:v>
+      </x:c>
+      <x:c r="N121" s="116" t="str"/>
+      <x:c r="O121" s="16" t="str"/>
+    </x:row>
+    <x:row r="122" ht="78" customHeight="1">
+      <x:c r="A122" s="25" t="str">
+        <x:v>Latest-date lease liabilities — Unavailable</x:v>
+      </x:c>
+      <x:c r="B122" s="115"/>
+      <x:c r="C122" s="116"/>
+      <x:c r="D122" s="82" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E122" s="116" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="F122" s="82" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G122" s="116" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="H122" s="116"/>
+      <x:c r="I122" s="116"/>
+      <x:c r="J122" s="116"/>
+      <x:c r="K122" s="116"/>
+      <x:c r="L122" s="116" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="M122" s="116" t="str">
+        <x:v>10-Q balance sheet, p. 7</x:v>
+      </x:c>
+      <x:c r="N122" s="116" t="str">
+        <x:v>Latest-date lease liabilities Unavailable; no checked amount in the 10-Q.</x:v>
+      </x:c>
+      <x:c r="O122" s="16" t="str"/>
+    </x:row>
+    <x:row r="123" ht="78" customHeight="1">
+      <x:c r="A123" s="25" t="str">
+        <x:v>Operating lease liabilities — current</x:v>
+      </x:c>
+      <x:c r="B123" s="115" t="n">
+        <x:v>222000000</x:v>
+      </x:c>
+      <x:c r="C123" s="116"/>
+      <x:c r="D123" s="82" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E123" s="116" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F123" s="82" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G123" s="116" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H123" s="116" t="str">
+        <x:v>us-gaap:OperatingLeaseLiabilityCurrent</x:v>
+      </x:c>
+      <x:c r="I123" s="116" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="J123" s="116" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K123" s="116" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L123" s="116" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M123" s="116" t="str">
+        <x:v>10-K Note 10, p. 76</x:v>
+      </x:c>
+      <x:c r="N123" s="116" t="str"/>
+      <x:c r="O123" s="16" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="78" customHeight="1">
+      <x:c r="A124" s="25" t="str">
+        <x:v>Operating lease liabilities — noncurrent</x:v>
+      </x:c>
+      <x:c r="B124" s="115" t="n">
+        <x:v>1140000000</x:v>
+      </x:c>
+      <x:c r="C124" s="116"/>
+      <x:c r="D124" s="82" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E124" s="116" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F124" s="82" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G124" s="116" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H124" s="116" t="str">
+        <x:v>us-gaap:OperatingLeaseLiabilityNoncurrent</x:v>
+      </x:c>
+      <x:c r="I124" s="116" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="J124" s="116" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K124" s="116" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L124" s="116" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M124" s="116" t="str">
+        <x:v>10-K Note 10, p. 76</x:v>
+      </x:c>
+      <x:c r="N124" s="116" t="str"/>
+      <x:c r="O124" s="16" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="78" customHeight="1">
+      <x:c r="A125" s="25" t="str">
+        <x:v>Finance lease liabilities — requested date, Unavailable</x:v>
+      </x:c>
+      <x:c r="B125" s="115"/>
+      <x:c r="C125" s="116"/>
+      <x:c r="D125" s="82" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E125" s="116" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="F125" s="82" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G125" s="116" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="H125" s="116"/>
+      <x:c r="I125" s="116"/>
+      <x:c r="J125" s="116"/>
+      <x:c r="K125" s="116"/>
+      <x:c r="L125" s="116" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="M125" s="116" t="str">
+        <x:v>10-Q review; June amount not established</x:v>
+      </x:c>
+      <x:c r="N125" s="116" t="str">
+        <x:v>No checked June amount. The 10-K describes operating leases only; finance leases are not reported, which is not zero.</x:v>
+      </x:c>
+      <x:c r="O125" s="16" t="str"/>
+    </x:row>
+    <x:row r="126" ht="78" customHeight="1">
+      <x:c r="A126" s="26" t="str">
+        <x:v>Leases not yet commenced — Unavailable</x:v>
+      </x:c>
+      <x:c r="B126" s="117"/>
+      <x:c r="C126" s="118"/>
+      <x:c r="D126" s="87" t="d">
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E126" s="118" t="str">
+        <x:v>10-Q</x:v>
+      </x:c>
+      <x:c r="F126" s="87" t="d">
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G126" s="118" t="str">
+        <x:v>0000059478-26-000081</x:v>
+      </x:c>
+      <x:c r="H126" s="118"/>
+      <x:c r="I126" s="118"/>
+      <x:c r="J126" s="118"/>
+      <x:c r="K126" s="118"/>
+      <x:c r="L126" s="118" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000081/lly-20260630.htm</x:v>
+      </x:c>
+      <x:c r="M126" s="118" t="str">
+        <x:v>Saved pilot evidence; 10-Q review</x:v>
+      </x:c>
+      <x:c r="N126" s="118" t="str">
+        <x:v>No checked amount for leases not yet commenced is established in the saved pilot evidence. Unavailable does not mean zero.</x:v>
+      </x:c>
+      <x:c r="O126" s="18" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -9308,6 +9942,17 @@
         <x:v>FY2025 10-K Note 11 p. 77; June 10-Q Note 11 p. 23</x:v>
       </x:c>
     </x:row>
+    <x:row r="13" ht="78" customHeight="1">
+      <x:c r="A13" s="157" t="str">
+        <x:v>Borrowing and leases</x:v>
+      </x:c>
+      <x:c r="B13" s="191" t="str">
+        <x:v>The Borrowing and leases sheet reconciles baseline borrowing and shows lease balances on their own dates. Unavailable means the amount was not established in the checked evidence. Leases never enter baseline debt or its ratios.</x:v>
+      </x:c>
+      <x:c r="C13" s="192" t="str">
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/borrowing_lease_presentation.md</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R44ba2e92ab82474f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="R42fc5e91854f41a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="R559c9296e69743ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="4" r:id="R7c8a89892f0c44b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="5" r:id="R6ce6e94b33334fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="6" r:id="R8d2c326248f74d6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R47119031e9e14377"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="R1eadd7c12bda4566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="R00ee6960dee7402b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="Rec05d0b4eb2448e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="5" r:id="R08107539c00f443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="6" r:id="Re4870f8b713940cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="7" r:id="R1de904192b7a4b79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -372,7 +373,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="193">
+  <x:cellXfs count="221">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -889,6 +890,60 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1087,7 +1142,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf65719a8d4ee4135"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R81d2be1fe1e74c04"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2370,6 +2425,259 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="43" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="29" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="85" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="4"/>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>Eli Lilly and Company — dated history</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
+        <x:v>USD millions unless x or %. Fiscal year and later TTM both span twelve months and overlap.</x:v>
+      </x:c>
+      <x:c r="B3" s="4"/>
+      <x:c r="C3" s="4"/>
+      <x:c r="D3" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="4"/>
+      <x:c r="C4" s="4"/>
+      <x:c r="D4" s="4"/>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="13" t="str">
+        <x:v>Measure</x:v>
+      </x:c>
+      <x:c r="B5" s="96" t="str">
+        <x:v>As of / FY ended 2025-12-31</x:v>
+      </x:c>
+      <x:c r="C5" s="96" t="str">
+        <x:v>As of / TTM ended 2026-06-30</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>Basis / limits</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="45" customHeight="1">
+      <x:c r="A6" s="25" t="str">
+        <x:v>Cash and cash equivalents</x:v>
+      </x:c>
+      <x:c r="B6" s="125" t="n">
+        <x:f>IF(ISNUMBER('Data'!B130),'Data'!B130,NA())</x:f>
+        <x:v>7268000000</x:v>
+      </x:c>
+      <x:c r="C6" s="125" t="n">
+        <x:f>'Debt and liquidity'!B6</x:f>
+        <x:v>8950000000</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>Cash and cash equivalents excluding restricted cash. Investments are not substituted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="62" customHeight="1">
+      <x:c r="A7" s="25" t="str">
+        <x:v>Baseline gross debt</x:v>
+      </x:c>
+      <x:c r="B7" s="125" t="n">
+        <x:f>IF(ISNUMBER('Data'!B133),'Data'!B133,NA())+IF(ISNUMBER('Data'!B134),'Data'!B134,NA())</x:f>
+        <x:v>42503000000</x:v>
+      </x:c>
+      <x:c r="C7" s="125" t="n">
+        <x:f>'Debt and liquidity'!B7</x:f>
+        <x:v>54908000000</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="str">
+        <x:v>Carrying amount of borrowing. Operating/finance leases and commitments are excluded. In this 10-Q, the Note 8 fair-value table's carrying amounts (commercial paper 5,284M plus long-term debt including current portion 49,624M) present the same 54,908M; they are not added.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="45" customHeight="1">
+      <x:c r="A8" s="25" t="str">
+        <x:v>Net debt</x:v>
+      </x:c>
+      <x:c r="B8" s="186" t="n">
+        <x:f>B7-B6</x:f>
+        <x:v>35235000000</x:v>
+      </x:c>
+      <x:c r="C8" s="125" t="n">
+        <x:f>'Debt and liquidity'!B8</x:f>
+        <x:v>45958000000</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="str">
+        <x:v>Baseline borrowing less cash excluding restricted cash. Same date and filing. Negative net debt is retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="49" customHeight="1">
+      <x:c r="A9" s="25" t="str">
+        <x:v>Current ratio</x:v>
+      </x:c>
+      <x:c r="B9" s="162" t="n">
+        <x:f>IF(IF(ISNUMBER('Data'!B132),'Data'!B132,NA())&gt;0,IF(ISNUMBER('Data'!B131),'Data'!B131,NA())/IF(ISNUMBER('Data'!B132),'Data'!B132,NA()),NA())</x:f>
+        <x:v>1.5791132054047916</x:v>
+      </x:c>
+      <x:c r="C9" s="162" t="n">
+        <x:f>'Debt and liquidity'!B9</x:f>
+        <x:v>1.3546427598919168</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>Total current assets / total current liabilities from one balance sheet. Liabilities include more than borrowing; assets include more than cash.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="45" customHeight="1">
+      <x:c r="A10" s="25" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="B10" s="125" t="n">
+        <x:f>IF(ISNUMBER('Data'!B135),'Data'!B135,NA())</x:f>
+        <x:v>16813000000</x:v>
+      </x:c>
+      <x:c r="C10" s="125" t="n">
+        <x:f>'Debt and liquidity'!B10</x:f>
+        <x:v>28083000000</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="str">
+        <x:v>Reported historical OCF; recurrence is not established. Uses FY + current YTD - prior YTD.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="45" customHeight="1">
+      <x:c r="A11" s="25" t="str">
+        <x:v>Purchases of property and equipment</x:v>
+      </x:c>
+      <x:c r="B11" s="125" t="n">
+        <x:f>IF(ISNUMBER('Data'!B136),'Data'!B136,NA())</x:f>
+        <x:v>7841000000</x:v>
+      </x:c>
+      <x:c r="C11" s="125" t="n">
+        <x:f>'Debt and liquidity'!B11</x:f>
+        <x:v>9893000000</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>Reported purchases of property and equipment; excludes acquisitions and other investing cash flows.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="45" customHeight="1">
+      <x:c r="A12" s="25" t="str">
+        <x:v>Free cash flow</x:v>
+      </x:c>
+      <x:c r="B12" s="186" t="n">
+        <x:f>B10-B11</x:f>
+        <x:v>8972000000</x:v>
+      </x:c>
+      <x:c r="C12" s="125" t="n">
+        <x:f>'Debt and liquidity'!B12</x:f>
+        <x:v>18190000000</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="str">
+        <x:v>OCF less reported capital spending. Uses the spending basis above; excludes acquisitions, dividends and other cash uses.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="45" customHeight="1">
+      <x:c r="A13" s="25" t="str">
+        <x:v>Operating cash flow / debt</x:v>
+      </x:c>
+      <x:c r="B13" s="163" t="n">
+        <x:f>IF(B7&gt;0,B10/B7,NA())</x:f>
+        <x:v>0.3955720772651342</x:v>
+      </x:c>
+      <x:c r="C13" s="216" t="n">
+        <x:f>'Debt and liquidity'!B13</x:f>
+        <x:v>0.511455525606469</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="str">
+        <x:v>Twelve-month OCF / borrowing at each period end. Prior column uses the fiscal year; later column uses TTM. Not repayment coverage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="45" customHeight="1">
+      <x:c r="A14" s="25" t="str">
+        <x:v>Free cash flow / debt</x:v>
+      </x:c>
+      <x:c r="B14" s="163" t="n">
+        <x:f>IF(B7&gt;0,B12/B7,NA())</x:f>
+        <x:v>0.2110909818130485</x:v>
+      </x:c>
+      <x:c r="C14" s="216" t="n">
+        <x:f>'Debt and liquidity'!B14</x:f>
+        <x:v>0.33128141618707657</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="str">
+        <x:v>Twelve-month FCF / borrowing at each period end. Prior column uses the fiscal year; later column uses TTM. Not repayment coverage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="88" customHeight="1">
+      <x:c r="A15" s="26" t="str">
+        <x:v>Historical interest coverage</x:v>
+      </x:c>
+      <x:c r="B15" s="217" t="n">
+        <x:f>IF(AND('Debt and liquidity'!B46&gt;0,'Debt and liquidity'!B44=0),'Debt and liquidity'!B40/'Debt and liquidity'!B46,NA())</x:f>
+        <x:v>29.387709497206703</x:v>
+      </x:c>
+      <x:c r="C15" s="217" t="n">
+        <x:f>'Debt and liquidity'!B15</x:f>
+        <x:v>31.17052826691381</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="str">
+        <x:v>FY2025 Note 11 explicitly reports interest on borrowings net of capitalized interest. The interim segment table labels the line interest expense without explicitly stating its capitalization basis. All three amounts are used as reported, before any interest-income offset. Capitalized interest is not added or subtracted; its amount and total interest incurred are Unavailable.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+    </x:row>
+    <x:row r="17" ht="70" customHeight="1">
+      <x:c r="A17" s="4" t="str">
+        <x:v>Period definitions</x:v>
+      </x:c>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4" t="str">
+        <x:v>Balance-sheet figures compare the stated dates. Flows and interest coverage compare a fiscal year with a later TTM: both span twelve months and overlap. No interim annualization, independent-period growth rate or future repayment coverage is inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="4" t="str">
+        <x:v>Fiscal-year flows</x:v>
+      </x:c>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4" t="str">
+        <x:v>2025-01-01 to 2025-12-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="4" t="str">
+        <x:v>Later TTM flows</x:v>
+      </x:c>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4" t="str">
+        <x:v>2025-07-01 to 2026-06-30</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
@@ -3952,11 +4260,11 @@
     <x:mergeCell ref="A96:D96"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7fa7867d1754332"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1ec28f33921480d"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -9805,12 +10113,360 @@
       </x:c>
       <x:c r="O126" s="18" t="str"/>
     </x:row>
+    <x:row r="129" ht="70" customHeight="1">
+      <x:c r="A129" s="13" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="B129" s="96" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C129" s="96" t="str">
+        <x:v>Period start</x:v>
+      </x:c>
+      <x:c r="D129" s="96" t="str">
+        <x:v>Period end</x:v>
+      </x:c>
+      <x:c r="E129" s="96" t="str">
+        <x:v>Form</x:v>
+      </x:c>
+      <x:c r="F129" s="96" t="str">
+        <x:v>Filed</x:v>
+      </x:c>
+      <x:c r="G129" s="96" t="str">
+        <x:v>Accession</x:v>
+      </x:c>
+      <x:c r="H129" s="96" t="str">
+        <x:v>Tag</x:v>
+      </x:c>
+      <x:c r="I129" s="96" t="str">
+        <x:v>Context</x:v>
+      </x:c>
+      <x:c r="J129" s="96" t="str">
+        <x:v>Scale</x:v>
+      </x:c>
+      <x:c r="K129" s="96" t="str">
+        <x:v>Decimals</x:v>
+      </x:c>
+      <x:c r="L129" s="96" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="M129" s="96" t="str">
+        <x:v>Selection rule</x:v>
+      </x:c>
+      <x:c r="N129" s="96" t="str">
+        <x:v>Unavailable reason</x:v>
+      </x:c>
+      <x:c r="O129" s="14" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="70" customHeight="1">
+      <x:c r="A130" s="25" t="str">
+        <x:v>Cash and cash equivalents</x:v>
+      </x:c>
+      <x:c r="B130" s="106" t="n">
+        <x:v>7268000000</x:v>
+      </x:c>
+      <x:c r="C130" s="76"/>
+      <x:c r="D130" s="76" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E130" s="107" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F130" s="76" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G130" s="107" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H130" s="107" t="str">
+        <x:v>us-gaap:CashAndCashEquivalentsAtCarryingValue</x:v>
+      </x:c>
+      <x:c r="I130" s="107" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="J130" s="107" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K130" s="107" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L130" s="107" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M130" s="107" t="str">
+        <x:v>10-K balance sheet p. 56; cash flows p. 58</x:v>
+      </x:c>
+      <x:c r="N130" s="107" t="str"/>
+      <x:c r="O130" s="16" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="70" customHeight="1">
+      <x:c r="A131" s="25" t="str">
+        <x:v>Current assets</x:v>
+      </x:c>
+      <x:c r="B131" s="106" t="n">
+        <x:v>55629000000</x:v>
+      </x:c>
+      <x:c r="C131" s="76"/>
+      <x:c r="D131" s="76" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E131" s="107" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F131" s="76" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G131" s="107" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H131" s="107" t="str">
+        <x:v>us-gaap:AssetsCurrent</x:v>
+      </x:c>
+      <x:c r="I131" s="107" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="J131" s="107" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K131" s="107" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L131" s="107" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M131" s="107" t="str">
+        <x:v>10-K balance sheet p. 56; cash flows p. 58</x:v>
+      </x:c>
+      <x:c r="N131" s="107" t="str"/>
+      <x:c r="O131" s="16" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="70" customHeight="1">
+      <x:c r="A132" s="25" t="str">
+        <x:v>Current liabilities</x:v>
+      </x:c>
+      <x:c r="B132" s="106" t="n">
+        <x:v>35228000000</x:v>
+      </x:c>
+      <x:c r="C132" s="76"/>
+      <x:c r="D132" s="76" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E132" s="107" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F132" s="76" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G132" s="107" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H132" s="107" t="str">
+        <x:v>us-gaap:LiabilitiesCurrent</x:v>
+      </x:c>
+      <x:c r="I132" s="107" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="J132" s="107" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K132" s="107" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L132" s="107" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M132" s="107" t="str">
+        <x:v>10-K balance sheet p. 56; cash flows p. 58</x:v>
+      </x:c>
+      <x:c r="N132" s="107" t="str"/>
+      <x:c r="O132" s="16" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="70" customHeight="1">
+      <x:c r="A133" s="25" t="str">
+        <x:v>Short-term borrowings and current maturities of long-term debt</x:v>
+      </x:c>
+      <x:c r="B133" s="106" t="n">
+        <x:v>1635000000</x:v>
+      </x:c>
+      <x:c r="C133" s="76"/>
+      <x:c r="D133" s="76" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E133" s="107" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F133" s="76" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G133" s="107" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H133" s="107" t="str">
+        <x:v>us-gaap:DebtCurrent</x:v>
+      </x:c>
+      <x:c r="I133" s="107" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="J133" s="107" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K133" s="107" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L133" s="107" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M133" s="107" t="str">
+        <x:v>10-K balance sheet p. 56; cash flows p. 58</x:v>
+      </x:c>
+      <x:c r="N133" s="107" t="str"/>
+      <x:c r="O133" s="16" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="70" customHeight="1">
+      <x:c r="A134" s="25" t="str">
+        <x:v>Long-term debt</x:v>
+      </x:c>
+      <x:c r="B134" s="106" t="n">
+        <x:v>40868000000</x:v>
+      </x:c>
+      <x:c r="C134" s="76"/>
+      <x:c r="D134" s="76" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E134" s="107" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F134" s="76" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G134" s="107" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H134" s="107" t="str">
+        <x:v>us-gaap:LongTermDebtNoncurrent</x:v>
+      </x:c>
+      <x:c r="I134" s="107" t="str">
+        <x:v>c-16</x:v>
+      </x:c>
+      <x:c r="J134" s="107" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K134" s="107" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L134" s="107" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M134" s="107" t="str">
+        <x:v>10-K balance sheet p. 56; cash flows p. 58</x:v>
+      </x:c>
+      <x:c r="N134" s="107" t="str"/>
+      <x:c r="O134" s="16" t="str">
+        <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="70" customHeight="1">
+      <x:c r="A135" s="25" t="str">
+        <x:v>Operating cash flow · fiscal year</x:v>
+      </x:c>
+      <x:c r="B135" s="106" t="n">
+        <x:v>16813000000</x:v>
+      </x:c>
+      <x:c r="C135" s="76" t="d">
+        <x:v>2025-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D135" s="76" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E135" s="107" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F135" s="76" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G135" s="107" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H135" s="107" t="str">
+        <x:v>us-gaap:NetCashProvidedByUsedInOperatingActivities</x:v>
+      </x:c>
+      <x:c r="I135" s="107" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="J135" s="107" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K135" s="107" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L135" s="107" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M135" s="107" t="str">
+        <x:v>Annual cash-flow statement</x:v>
+      </x:c>
+      <x:c r="N135" s="107" t="str"/>
+      <x:c r="O135" s="16" t="str"/>
+    </x:row>
+    <x:row r="136" ht="70" customHeight="1">
+      <x:c r="A136" s="26" t="str">
+        <x:v>Purchases of property and equipment · fiscal year</x:v>
+      </x:c>
+      <x:c r="B136" s="108" t="n">
+        <x:v>7841000000</x:v>
+      </x:c>
+      <x:c r="C136" s="80" t="d">
+        <x:v>2025-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D136" s="80" t="d">
+        <x:v>2025-12-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E136" s="109" t="str">
+        <x:v>10-K</x:v>
+      </x:c>
+      <x:c r="F136" s="80" t="d">
+        <x:v>2026-02-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G136" s="109" t="str">
+        <x:v>0000059478-26-000013</x:v>
+      </x:c>
+      <x:c r="H136" s="109" t="str">
+        <x:v>us-gaap:PaymentsToAcquireOtherPropertyPlantAndEquipment</x:v>
+      </x:c>
+      <x:c r="I136" s="109" t="str">
+        <x:v>c-1</x:v>
+      </x:c>
+      <x:c r="J136" s="109" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K136" s="109" t="str">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="L136" s="109" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</x:v>
+      </x:c>
+      <x:c r="M136" s="109" t="str">
+        <x:v>Annual cash-flow statement</x:v>
+      </x:c>
+      <x:c r="N136" s="109" t="str"/>
+      <x:c r="O136" s="18" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -9971,6 +10627,17 @@
         <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/borrowing_lease_presentation.md</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="70" customHeight="1">
+      <x:c r="A15" s="218" t="str">
+        <x:v>History</x:v>
+      </x:c>
+      <x:c r="B15" s="219" t="str">
+        <x:v>Two dated observations per company. Fiscal-year and TTM flows are overlapping twelve-month windows. Unsupported older Vistra borrowing and dependent ratios remain Unavailable.</x:v>
+      </x:c>
+      <x:c r="C15" s="220" t="str">
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/company_history.md</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R47119031e9e14377"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="R1eadd7c12bda4566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="R00ee6960dee7402b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="Rec05d0b4eb2448e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="5" r:id="R08107539c00f443e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="6" r:id="Re4870f8b713940cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="7" r:id="R1de904192b7a4b79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R545cd74760084c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="R238cedd23ec247d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="Rd81cc1e44b5f4b44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="R36028c37b97841dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core charts" sheetId="5" r:id="Ra3a09e8001d84070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="6" r:id="Rf3d8710805a74af5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R1a331d15f7f4430c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="8" r:id="R32f8516f62b34357"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -373,7 +374,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="221">
+  <x:cellXfs count="222">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -945,6 +946,9 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -953,6 +957,418 @@
 </file>
 
 <file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>What remained after capital spending?</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>USD millions</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8D99A8"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Core charts'!$A$6:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Core charts'!$B$6:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,);"-"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="750">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:r>
+                  <a:t>USD millions</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0,,;(#,##0,,)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="750">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>How did borrowing and cash change?</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Cash and equivalents</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8D99A8"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Core charts'!$A$25:$A$26</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Core charts'!$B$25:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,);"-"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Baseline borrowing</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="47627F"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Core charts'!$A$25:$A$26</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Core charts'!$C$25:$C$26</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,);"-"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="750">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:r>
+                  <a:t>USD millions</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0,,;(#,##0,,)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="750">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1122,6 +1538,71 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8ebdb1b61a44431d"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5d1e072ed27a4814"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -1142,7 +1623,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R81d2be1fe1e74c04"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8fd9f5b2b7b470e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2678,6 +3159,817 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="3" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="10" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="35" customHeight="1">
+      <x:c r="A1" s="4"/>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="2"/>
+      <x:c r="K1" s="2"/>
+      <x:c r="L1" s="2"/>
+      <x:c r="M1" s="2"/>
+      <x:c r="N1" s="2"/>
+      <x:c r="O1" s="2"/>
+    </x:row>
+    <x:row r="2" ht="35" customHeight="1">
+      <x:c r="A2" s="7" t="str">
+        <x:v>LLY — two chart questions</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+      <x:c r="I2" s="2"/>
+      <x:c r="J2" s="2"/>
+      <x:c r="K2" s="2"/>
+      <x:c r="L2" s="2"/>
+      <x:c r="M2" s="2"/>
+      <x:c r="N2" s="2"/>
+      <x:c r="O2" s="2"/>
+    </x:row>
+    <x:row r="3" ht="35" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>TTM 2025-07-01 to 2026-06-30. Values stored in USD, displayed in millions.</x:v>
+      </x:c>
+      <x:c r="B3" s="4"/>
+      <x:c r="C3" s="4"/>
+      <x:c r="D3" s="4"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+      <x:c r="I3" s="2"/>
+      <x:c r="J3" s="2"/>
+      <x:c r="K3" s="2"/>
+      <x:c r="L3" s="2"/>
+      <x:c r="M3" s="2"/>
+      <x:c r="N3" s="2"/>
+      <x:c r="O3" s="2"/>
+    </x:row>
+    <x:row r="4" ht="35" customHeight="1">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="4"/>
+      <x:c r="C4" s="4"/>
+      <x:c r="D4" s="4"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+      <x:c r="I4" s="2"/>
+      <x:c r="J4" s="2"/>
+      <x:c r="K4" s="2"/>
+      <x:c r="L4" s="2"/>
+      <x:c r="M4" s="2"/>
+      <x:c r="N4" s="2"/>
+      <x:c r="O4" s="2"/>
+    </x:row>
+    <x:row r="5" ht="35" customHeight="1">
+      <x:c r="A5" s="13" t="str">
+        <x:v>TTM measure</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>USD millions</x:v>
+      </x:c>
+      <x:c r="C5" s="4"/>
+      <x:c r="D5" s="4"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+      <x:c r="I5" s="2"/>
+      <x:c r="J5" s="2"/>
+      <x:c r="K5" s="2"/>
+      <x:c r="L5" s="2"/>
+      <x:c r="M5" s="2"/>
+      <x:c r="N5" s="2"/>
+      <x:c r="O5" s="2"/>
+    </x:row>
+    <x:row r="6" ht="35" customHeight="1">
+      <x:c r="A6" s="25" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="B6" s="144" t="n">
+        <x:f>'Debt and liquidity'!B10</x:f>
+        <x:v>28083000000</x:v>
+      </x:c>
+      <x:c r="C6" s="4"/>
+      <x:c r="D6" s="4"/>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="2"/>
+      <x:c r="I6" s="2"/>
+      <x:c r="J6" s="2"/>
+      <x:c r="K6" s="2"/>
+      <x:c r="L6" s="2"/>
+      <x:c r="M6" s="2"/>
+      <x:c r="N6" s="2"/>
+      <x:c r="O6" s="2"/>
+    </x:row>
+    <x:row r="7" ht="35" customHeight="1">
+      <x:c r="A7" s="25" t="str">
+        <x:v>Capital spending</x:v>
+      </x:c>
+      <x:c r="B7" s="144" t="n">
+        <x:f>-'Debt and liquidity'!B11</x:f>
+        <x:v>-9893000000</x:v>
+      </x:c>
+      <x:c r="C7" s="4"/>
+      <x:c r="D7" s="4"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+      <x:c r="I7" s="2"/>
+      <x:c r="J7" s="2"/>
+      <x:c r="K7" s="2"/>
+      <x:c r="L7" s="2"/>
+      <x:c r="M7" s="2"/>
+      <x:c r="N7" s="2"/>
+      <x:c r="O7" s="2"/>
+    </x:row>
+    <x:row r="8" ht="35" customHeight="1">
+      <x:c r="A8" s="26" t="str">
+        <x:v>Free cash flow</x:v>
+      </x:c>
+      <x:c r="B8" s="221" t="n">
+        <x:f>'Debt and liquidity'!B12</x:f>
+        <x:v>18190000000</x:v>
+      </x:c>
+      <x:c r="C8" s="4"/>
+      <x:c r="D8" s="4"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+      <x:c r="I8" s="2"/>
+      <x:c r="J8" s="2"/>
+      <x:c r="K8" s="2"/>
+      <x:c r="L8" s="2"/>
+      <x:c r="M8" s="2"/>
+      <x:c r="N8" s="2"/>
+      <x:c r="O8" s="2"/>
+    </x:row>
+    <x:row r="9" ht="35" customHeight="1">
+      <x:c r="A9" s="4"/>
+      <x:c r="B9" s="4"/>
+      <x:c r="C9" s="4"/>
+      <x:c r="D9" s="4"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+      <x:c r="I9" s="2"/>
+      <x:c r="J9" s="2"/>
+      <x:c r="K9" s="2"/>
+      <x:c r="L9" s="2"/>
+      <x:c r="M9" s="2"/>
+      <x:c r="N9" s="2"/>
+      <x:c r="O9" s="2"/>
+    </x:row>
+    <x:row r="10" ht="80" customHeight="1">
+      <x:c r="A10" s="4" t="str">
+        <x:v>Calculation basis</x:v>
+      </x:c>
+      <x:c r="B10" s="4"/>
+      <x:c r="C10" s="4"/>
+      <x:c r="D10" s="4" t="str">
+        <x:v>FCF = OCF − capital spending. FCF is a result, not an additional cash flow. Capital spending is shown negative.</x:v>
+      </x:c>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+      <x:c r="I10" s="2"/>
+      <x:c r="J10" s="2"/>
+      <x:c r="K10" s="2"/>
+      <x:c r="L10" s="2"/>
+      <x:c r="M10" s="2"/>
+      <x:c r="N10" s="2"/>
+      <x:c r="O10" s="2"/>
+    </x:row>
+    <x:row r="11" ht="35" customHeight="1">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+      <x:c r="I11" s="2"/>
+      <x:c r="J11" s="2"/>
+      <x:c r="K11" s="2"/>
+      <x:c r="L11" s="2"/>
+      <x:c r="M11" s="2"/>
+      <x:c r="N11" s="2"/>
+      <x:c r="O11" s="2"/>
+    </x:row>
+    <x:row r="12" ht="35" customHeight="1">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+      <x:c r="I12" s="2"/>
+      <x:c r="J12" s="2"/>
+      <x:c r="K12" s="2"/>
+      <x:c r="L12" s="2"/>
+      <x:c r="M12" s="2"/>
+      <x:c r="N12" s="2"/>
+      <x:c r="O12" s="2"/>
+    </x:row>
+    <x:row r="13" ht="35" customHeight="1">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+      <x:c r="I13" s="2"/>
+      <x:c r="J13" s="2"/>
+      <x:c r="K13" s="2"/>
+      <x:c r="L13" s="2"/>
+      <x:c r="M13" s="2"/>
+      <x:c r="N13" s="2"/>
+      <x:c r="O13" s="2"/>
+    </x:row>
+    <x:row r="14" ht="35" customHeight="1">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+      <x:c r="I14" s="2"/>
+      <x:c r="J14" s="2"/>
+      <x:c r="K14" s="2"/>
+      <x:c r="L14" s="2"/>
+      <x:c r="M14" s="2"/>
+      <x:c r="N14" s="2"/>
+      <x:c r="O14" s="2"/>
+    </x:row>
+    <x:row r="15" ht="35" customHeight="1">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="4"/>
+      <x:c r="C15" s="4"/>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+      <x:c r="I15" s="2"/>
+      <x:c r="J15" s="2"/>
+      <x:c r="K15" s="2"/>
+      <x:c r="L15" s="2"/>
+      <x:c r="M15" s="2"/>
+      <x:c r="N15" s="2"/>
+      <x:c r="O15" s="2"/>
+    </x:row>
+    <x:row r="16" ht="35" customHeight="1">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+      <x:c r="I16" s="2"/>
+      <x:c r="J16" s="2"/>
+      <x:c r="K16" s="2"/>
+      <x:c r="L16" s="2"/>
+      <x:c r="M16" s="2"/>
+      <x:c r="N16" s="2"/>
+      <x:c r="O16" s="2"/>
+    </x:row>
+    <x:row r="17" ht="35" customHeight="1">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+      <x:c r="I17" s="2"/>
+      <x:c r="J17" s="2"/>
+      <x:c r="K17" s="2"/>
+      <x:c r="L17" s="2"/>
+      <x:c r="M17" s="2"/>
+      <x:c r="N17" s="2"/>
+      <x:c r="O17" s="2"/>
+    </x:row>
+    <x:row r="18" ht="35" customHeight="1">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="2"/>
+      <x:c r="I18" s="2"/>
+      <x:c r="J18" s="2"/>
+      <x:c r="K18" s="2"/>
+      <x:c r="L18" s="2"/>
+      <x:c r="M18" s="2"/>
+      <x:c r="N18" s="2"/>
+      <x:c r="O18" s="2"/>
+    </x:row>
+    <x:row r="19" ht="35" customHeight="1">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+      <x:c r="I19" s="2"/>
+      <x:c r="J19" s="2"/>
+      <x:c r="K19" s="2"/>
+      <x:c r="L19" s="2"/>
+      <x:c r="M19" s="2"/>
+      <x:c r="N19" s="2"/>
+      <x:c r="O19" s="2"/>
+    </x:row>
+    <x:row r="20" ht="35" customHeight="1">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+      <x:c r="I20" s="2"/>
+      <x:c r="J20" s="2"/>
+      <x:c r="K20" s="2"/>
+      <x:c r="L20" s="2"/>
+      <x:c r="M20" s="2"/>
+      <x:c r="N20" s="2"/>
+      <x:c r="O20" s="2"/>
+    </x:row>
+    <x:row r="21" ht="35" customHeight="1">
+      <x:c r="A21" s="4"/>
+      <x:c r="B21" s="4"/>
+      <x:c r="C21" s="4"/>
+      <x:c r="D21" s="4"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+      <x:c r="I21" s="2"/>
+      <x:c r="J21" s="2"/>
+      <x:c r="K21" s="2"/>
+      <x:c r="L21" s="2"/>
+      <x:c r="M21" s="2"/>
+      <x:c r="N21" s="2"/>
+      <x:c r="O21" s="2"/>
+    </x:row>
+    <x:row r="22" ht="35" customHeight="1">
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+      <x:c r="I22" s="2"/>
+      <x:c r="J22" s="2"/>
+      <x:c r="K22" s="2"/>
+      <x:c r="L22" s="2"/>
+      <x:c r="M22" s="2"/>
+      <x:c r="N22" s="2"/>
+      <x:c r="O22" s="2"/>
+    </x:row>
+    <x:row r="23" ht="35" customHeight="1">
+      <x:c r="A23" s="4"/>
+      <x:c r="B23" s="4"/>
+      <x:c r="C23" s="4"/>
+      <x:c r="D23" s="4"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+      <x:c r="I23" s="2"/>
+      <x:c r="J23" s="2"/>
+      <x:c r="K23" s="2"/>
+      <x:c r="L23" s="2"/>
+      <x:c r="M23" s="2"/>
+      <x:c r="N23" s="2"/>
+      <x:c r="O23" s="2"/>
+    </x:row>
+    <x:row r="24" ht="35" customHeight="1">
+      <x:c r="A24" s="13" t="str">
+        <x:v>Balance-sheet date</x:v>
+      </x:c>
+      <x:c r="B24" s="96" t="str">
+        <x:v>Cash and equivalents</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>Baseline borrowing</x:v>
+      </x:c>
+      <x:c r="D24" s="4"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+      <x:c r="I24" s="2"/>
+      <x:c r="J24" s="2"/>
+      <x:c r="K24" s="2"/>
+      <x:c r="L24" s="2"/>
+      <x:c r="M24" s="2"/>
+      <x:c r="N24" s="2"/>
+      <x:c r="O24" s="2"/>
+    </x:row>
+    <x:row r="25" ht="35" customHeight="1">
+      <x:c r="A25" s="25" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="B25" s="125" t="n">
+        <x:f>'History'!B6</x:f>
+        <x:v>7268000000</x:v>
+      </x:c>
+      <x:c r="C25" s="144" t="n">
+        <x:f>'History'!B7</x:f>
+        <x:v>42503000000</x:v>
+      </x:c>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+      <x:c r="I25" s="2"/>
+      <x:c r="J25" s="2"/>
+      <x:c r="K25" s="2"/>
+      <x:c r="L25" s="2"/>
+      <x:c r="M25" s="2"/>
+      <x:c r="N25" s="2"/>
+      <x:c r="O25" s="2"/>
+    </x:row>
+    <x:row r="26" ht="35" customHeight="1">
+      <x:c r="A26" s="26" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="B26" s="129" t="n">
+        <x:f>'History'!C6</x:f>
+        <x:v>8950000000</x:v>
+      </x:c>
+      <x:c r="C26" s="221" t="n">
+        <x:f>'History'!C7</x:f>
+        <x:v>54908000000</x:v>
+      </x:c>
+      <x:c r="D26" s="4"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+      <x:c r="I26" s="2"/>
+      <x:c r="J26" s="2"/>
+      <x:c r="K26" s="2"/>
+      <x:c r="L26" s="2"/>
+      <x:c r="M26" s="2"/>
+      <x:c r="N26" s="2"/>
+      <x:c r="O26" s="2"/>
+    </x:row>
+    <x:row r="27" ht="35" customHeight="1">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="4"/>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="2"/>
+      <x:c r="H27" s="2"/>
+      <x:c r="I27" s="2"/>
+      <x:c r="J27" s="2"/>
+      <x:c r="K27" s="2"/>
+      <x:c r="L27" s="2"/>
+      <x:c r="M27" s="2"/>
+      <x:c r="N27" s="2"/>
+      <x:c r="O27" s="2"/>
+    </x:row>
+    <x:row r="28" ht="35" customHeight="1">
+      <x:c r="A28" s="4"/>
+      <x:c r="B28" s="4"/>
+      <x:c r="C28" s="4"/>
+      <x:c r="D28" s="4"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="2"/>
+      <x:c r="I28" s="2"/>
+      <x:c r="J28" s="2"/>
+      <x:c r="K28" s="2"/>
+      <x:c r="L28" s="2"/>
+      <x:c r="M28" s="2"/>
+      <x:c r="N28" s="2"/>
+      <x:c r="O28" s="2"/>
+    </x:row>
+    <x:row r="29" ht="95" customHeight="1">
+      <x:c r="A29" s="4" t="str">
+        <x:v>Scope / missing history</x:v>
+      </x:c>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="4" t="str">
+        <x:v>Baseline borrowing excludes leases; cash excludes restricted cash and investments. These balances do not establish repayment coverage.</x:v>
+      </x:c>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+      <x:c r="I29" s="2"/>
+      <x:c r="J29" s="2"/>
+      <x:c r="K29" s="2"/>
+      <x:c r="L29" s="2"/>
+      <x:c r="M29" s="2"/>
+      <x:c r="N29" s="2"/>
+      <x:c r="O29" s="2"/>
+    </x:row>
+    <x:row r="30" ht="35" customHeight="1">
+      <x:c r="A30" s="4"/>
+      <x:c r="B30" s="4"/>
+      <x:c r="C30" s="4"/>
+      <x:c r="D30" s="4"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+      <x:c r="I30" s="2"/>
+      <x:c r="J30" s="2"/>
+      <x:c r="K30" s="2"/>
+      <x:c r="L30" s="2"/>
+      <x:c r="M30" s="2"/>
+      <x:c r="N30" s="2"/>
+      <x:c r="O30" s="2"/>
+    </x:row>
+    <x:row r="31" ht="35" customHeight="1">
+      <x:c r="A31" s="4"/>
+      <x:c r="B31" s="4"/>
+      <x:c r="C31" s="4"/>
+      <x:c r="D31" s="4"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+      <x:c r="I31" s="2"/>
+      <x:c r="J31" s="2"/>
+      <x:c r="K31" s="2"/>
+      <x:c r="L31" s="2"/>
+      <x:c r="M31" s="2"/>
+      <x:c r="N31" s="2"/>
+      <x:c r="O31" s="2"/>
+    </x:row>
+    <x:row r="32" ht="35" customHeight="1">
+      <x:c r="A32" s="4"/>
+      <x:c r="B32" s="4"/>
+      <x:c r="C32" s="4"/>
+      <x:c r="D32" s="4"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+      <x:c r="I32" s="2"/>
+      <x:c r="J32" s="2"/>
+      <x:c r="K32" s="2"/>
+      <x:c r="L32" s="2"/>
+      <x:c r="M32" s="2"/>
+      <x:c r="N32" s="2"/>
+      <x:c r="O32" s="2"/>
+    </x:row>
+    <x:row r="33" ht="35" customHeight="1">
+      <x:c r="A33" s="4"/>
+      <x:c r="B33" s="4"/>
+      <x:c r="C33" s="4"/>
+      <x:c r="D33" s="4"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+      <x:c r="I33" s="2"/>
+      <x:c r="J33" s="2"/>
+      <x:c r="K33" s="2"/>
+      <x:c r="L33" s="2"/>
+      <x:c r="M33" s="2"/>
+      <x:c r="N33" s="2"/>
+      <x:c r="O33" s="2"/>
+    </x:row>
+    <x:row r="34" ht="35" customHeight="1">
+      <x:c r="A34" s="4"/>
+      <x:c r="B34" s="4"/>
+      <x:c r="C34" s="4"/>
+      <x:c r="D34" s="4"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+      <x:c r="I34" s="2"/>
+      <x:c r="J34" s="2"/>
+      <x:c r="K34" s="2"/>
+      <x:c r="L34" s="2"/>
+      <x:c r="M34" s="2"/>
+      <x:c r="N34" s="2"/>
+      <x:c r="O34" s="2"/>
+    </x:row>
+    <x:row r="35" ht="35" customHeight="1">
+      <x:c r="A35" s="4"/>
+      <x:c r="B35" s="4"/>
+      <x:c r="C35" s="4"/>
+      <x:c r="D35" s="4"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+      <x:c r="I35" s="2"/>
+      <x:c r="J35" s="2"/>
+      <x:c r="K35" s="2"/>
+      <x:c r="L35" s="2"/>
+      <x:c r="M35" s="2"/>
+      <x:c r="N35" s="2"/>
+      <x:c r="O35" s="2"/>
+    </x:row>
+    <x:row r="36" ht="35" customHeight="1">
+      <x:c r="A36" s="4"/>
+      <x:c r="B36" s="4"/>
+      <x:c r="C36" s="4"/>
+      <x:c r="D36" s="4"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
+      <x:c r="H36" s="2"/>
+      <x:c r="I36" s="2"/>
+      <x:c r="J36" s="2"/>
+      <x:c r="K36" s="2"/>
+      <x:c r="L36" s="2"/>
+      <x:c r="M36" s="2"/>
+      <x:c r="N36" s="2"/>
+      <x:c r="O36" s="2"/>
+    </x:row>
+    <x:row r="37" ht="35" customHeight="1">
+      <x:c r="A37" s="4"/>
+      <x:c r="B37" s="4"/>
+      <x:c r="C37" s="4"/>
+      <x:c r="D37" s="4"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
+      <x:c r="H37" s="2"/>
+      <x:c r="I37" s="2"/>
+      <x:c r="J37" s="2"/>
+      <x:c r="K37" s="2"/>
+      <x:c r="L37" s="2"/>
+      <x:c r="M37" s="2"/>
+      <x:c r="N37" s="2"/>
+      <x:c r="O37" s="2"/>
+    </x:row>
+    <x:row r="38" ht="35" customHeight="1">
+      <x:c r="A38" s="4"/>
+      <x:c r="B38" s="4"/>
+      <x:c r="C38" s="4"/>
+      <x:c r="D38" s="4"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="2"/>
+      <x:c r="I38" s="2"/>
+      <x:c r="J38" s="2"/>
+      <x:c r="K38" s="2"/>
+      <x:c r="L38" s="2"/>
+      <x:c r="M38" s="2"/>
+      <x:c r="N38" s="2"/>
+      <x:c r="O38" s="2"/>
+    </x:row>
+    <x:row r="39" ht="35" customHeight="1">
+      <x:c r="A39" s="4"/>
+      <x:c r="B39" s="4"/>
+      <x:c r="C39" s="4"/>
+      <x:c r="D39" s="4"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+      <x:c r="H39" s="2"/>
+      <x:c r="I39" s="2"/>
+      <x:c r="J39" s="2"/>
+      <x:c r="K39" s="2"/>
+      <x:c r="L39" s="2"/>
+      <x:c r="M39" s="2"/>
+      <x:c r="N39" s="2"/>
+      <x:c r="O39" s="2"/>
+    </x:row>
+    <x:row r="40" ht="35" customHeight="1">
+      <x:c r="A40" s="4"/>
+      <x:c r="B40" s="4"/>
+      <x:c r="C40" s="4"/>
+      <x:c r="D40" s="4"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="2"/>
+      <x:c r="I40" s="2"/>
+      <x:c r="J40" s="2"/>
+      <x:c r="K40" s="2"/>
+      <x:c r="L40" s="2"/>
+      <x:c r="M40" s="2"/>
+      <x:c r="N40" s="2"/>
+      <x:c r="O40" s="2"/>
+    </x:row>
+    <x:row r="41" ht="35" customHeight="1">
+      <x:c r="A41" s="4"/>
+      <x:c r="B41" s="4"/>
+      <x:c r="C41" s="4"/>
+      <x:c r="D41" s="4"/>
+      <x:c r="E41" s="2"/>
+      <x:c r="F41" s="2"/>
+      <x:c r="G41" s="2"/>
+      <x:c r="H41" s="2"/>
+      <x:c r="I41" s="2"/>
+      <x:c r="J41" s="2"/>
+      <x:c r="K41" s="2"/>
+      <x:c r="L41" s="2"/>
+      <x:c r="M41" s="2"/>
+      <x:c r="N41" s="2"/>
+      <x:c r="O41" s="2"/>
+    </x:row>
+    <x:row r="42" ht="35" customHeight="1">
+      <x:c r="A42" s="4"/>
+      <x:c r="B42" s="4"/>
+      <x:c r="C42" s="4"/>
+      <x:c r="D42" s="4"/>
+      <x:c r="E42" s="2"/>
+      <x:c r="F42" s="2"/>
+      <x:c r="G42" s="2"/>
+      <x:c r="H42" s="2"/>
+      <x:c r="I42" s="2"/>
+      <x:c r="J42" s="2"/>
+      <x:c r="K42" s="2"/>
+      <x:c r="L42" s="2"/>
+      <x:c r="M42" s="2"/>
+      <x:c r="N42" s="2"/>
+      <x:c r="O42" s="2"/>
+    </x:row>
+    <x:row r="43" ht="35" customHeight="1">
+      <x:c r="A43" s="4"/>
+      <x:c r="B43" s="4"/>
+      <x:c r="C43" s="4"/>
+      <x:c r="D43" s="4"/>
+      <x:c r="E43" s="2"/>
+      <x:c r="F43" s="2"/>
+      <x:c r="G43" s="2"/>
+      <x:c r="H43" s="2"/>
+      <x:c r="I43" s="2"/>
+      <x:c r="J43" s="2"/>
+      <x:c r="K43" s="2"/>
+      <x:c r="L43" s="2"/>
+      <x:c r="M43" s="2"/>
+      <x:c r="N43" s="2"/>
+      <x:c r="O43" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89ff47f5e478437c"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
@@ -4260,11 +5552,11 @@
     <x:mergeCell ref="A96:D96"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1ec28f33921480d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79db98eea22941d4"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -10466,7 +11758,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -10638,6 +11930,17 @@
         <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/company_history.md</x:v>
       </x:c>
     </x:row>
+    <x:row r="16" ht="70" customHeight="1">
+      <x:c r="A16" s="218" t="str">
+        <x:v>Core charts</x:v>
+      </x:c>
+      <x:c r="B16" s="219" t="str">
+        <x:v>Two native charts link to Debt and liquidity and History. Signed capital spending is a use; FCF is the result. Unsupported older Vistra borrowing is omitted, never plotted as zero.</x:v>
+      </x:c>
+      <x:c r="C16" s="220" t="str">
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/core_charts.md</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R545cd74760084c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="R238cedd23ec247d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="Rd81cc1e44b5f4b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="R36028c37b97841dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core charts" sheetId="5" r:id="Ra3a09e8001d84070"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="6" r:id="Rf3d8710805a74af5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R1a331d15f7f4430c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="8" r:id="R32f8516f62b34357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R1c6648e8b7ec4225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="Rf45888c3a1df4b17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="Rc135515193e649c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="R6ae98e4280914bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core charts" sheetId="5" r:id="R23a724ea0449445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="6" r:id="Ra29616e5a8fc4e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R7fe6dbf74c584970"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="8" r:id="Rb006a05c25e84490"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1558,7 +1558,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8ebdb1b61a44431d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9c8bf6543f4249c6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1588,7 +1588,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5d1e072ed27a4814"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0bd32b698ae448f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1623,7 +1623,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8fd9f5b2b7b470e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad4eba411b834422"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1956,6 +1956,110 @@
         <x:v>Narrative reflects the checked source snapshot. Editing workbook inputs updates calculations but requires a new review of the narrative.</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" ht="44" customHeight="1">
+      <x:c r="A20" s="13" t="str">
+        <x:v>Workbook contents — select the named tab</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>Question / evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="44" customHeight="1">
+      <x:c r="A21" s="15" t="str">
+        <x:v>Funding conclusion</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="str">
+        <x:v>Start here: obligations, accessible resources, competing uses and decisive unknowns.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="44" customHeight="1">
+      <x:c r="A22" s="15" t="str">
+        <x:v>Borrowing and leases</x:v>
+      </x:c>
+      <x:c r="B22" s="16" t="str">
+        <x:v>Borrowing components, dated lease liabilities and uncommenced commitments, separately.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="44" customHeight="1">
+      <x:c r="A23" s="15" t="str">
+        <x:v>Debt and liquidity</x:v>
+      </x:c>
+      <x:c r="B23" s="16" t="str">
+        <x:v>Latest checked ratios, formulas, periods and company-specific limits.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="44" customHeight="1">
+      <x:c r="A24" s="15" t="str">
+        <x:v>History</x:v>
+      </x:c>
+      <x:c r="B24" s="16" t="str">
+        <x:v>Annual versus latest dated balances; overlapping FY and TTM flows. Unavailable is not zero.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="44" customHeight="1">
+      <x:c r="A25" s="15" t="str">
+        <x:v>Core charts</x:v>
+      </x:c>
+      <x:c r="B25" s="16" t="str">
+        <x:v>What remained after capital spending, and how checked cash/borrowing balances changed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="44" customHeight="1">
+      <x:c r="A26" s="15" t="str">
+        <x:v>Repayment review</x:v>
+      </x:c>
+      <x:c r="B26" s="16" t="str">
+        <x:v>H1 cash uses, conditional commitments, credit evidence and selected May issuance maturities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="44" customHeight="1">
+      <x:c r="A27" s="15" t="str">
+        <x:v>Data</x:v>
+      </x:c>
+      <x:c r="B27" s="16" t="str">
+        <x:v>Reported inputs with filing dates, accessions, tags, contexts and source URLs; separate evidence blocks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="44" customHeight="1">
+      <x:c r="A28" s="17" t="str">
+        <x:v>About</x:v>
+      </x:c>
+      <x:c r="B28" s="18" t="str">
+        <x:v>Definitions, source scope, missing values, colors and methodology references.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="55" customHeight="1">
+      <x:c r="A30" s="72" t="str">
+        <x:v>Units and dates</x:v>
+      </x:c>
+      <x:c r="B30" s="74" t="str">
+        <x:v>Amounts are stored as whole USD and displayed in millions unless marked x or %. Balance sheets are instants; FY and later TTM are overlapping twelve-month windows.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="55" customHeight="1">
+      <x:c r="A31" s="25" t="str">
+        <x:v>Colors</x:v>
+      </x:c>
+      <x:c r="B31" s="16" t="str">
+        <x:v>Blue numeric cells are reported inputs; green formulas reference other sheets; black formulas calculate within a sheet. Green does not mean favorable or recurring cash.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="55" customHeight="1">
+      <x:c r="A32" s="25" t="str">
+        <x:v>Evidence and uncertainty</x:v>
+      </x:c>
+      <x:c r="B32" s="16" t="str">
+        <x:v>Data contains source URLs and filing metadata. Copy a full URL into a browser to open the source. Unavailable is never zero; capacity and later events do not update balance-sheet cash or borrowing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="55" customHeight="1">
+      <x:c r="A33" s="26" t="str">
+        <x:v>Reading the charts</x:v>
+      </x:c>
+      <x:c r="B33" s="18" t="str">
+        <x:v>FCF is OCF less capital spending, not another cash flow to add. Vistra has no supported older borrowing series. Other existing company-specific charts retain their own dated scope.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2983,7 +3087,7 @@
         <x:v>54908000000</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
-        <x:v>Carrying amount of borrowing. Operating/finance leases and commitments are excluded. In this 10-Q, the Note 8 fair-value table's carrying amounts (commercial paper 5,284M plus long-term debt including current portion 49,624M) present the same 54,908M; they are not added.</x:v>
+        <x:v>Carrying borrowing; leases and commitments excluded. Latest column only: In this 10-Q, the Note 8 fair-value table's carrying amounts (commercial paper 5,284M plus long-term debt including current portion 49,624M) present the same 54,908M; they are not added.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="45" customHeight="1">
@@ -3018,7 +3122,7 @@
         <x:v>Total current assets / total current liabilities from one balance sheet. Liabilities include more than borrowing; assets include more than cash.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="45" customHeight="1">
+    <x:row r="10" ht="49" customHeight="1">
       <x:c r="A10" s="25" t="str">
         <x:v>Operating cash flow</x:v>
       </x:c>
@@ -3031,7 +3135,7 @@
         <x:v>28083000000</x:v>
       </x:c>
       <x:c r="D10" s="16" t="str">
-        <x:v>Reported historical OCF; recurrence is not established. Uses FY + current YTD - prior YTD.</x:v>
+        <x:v>Annual column: reported fiscal-year OCF. Latest column only: Reported historical OCF; recurrence is not established. Uses FY + current YTD - prior YTD.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="45" customHeight="1">
@@ -3079,7 +3183,7 @@
         <x:v>0.511455525606469</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
-        <x:v>Twelve-month OCF / borrowing at each period end. Prior column uses the fiscal year; later column uses TTM. Not repayment coverage.</x:v>
+        <x:v>Twelve-month flow / borrowing at each period end. Annual column uses FY; latest column uses TTM. Not repayment coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="45" customHeight="1">
@@ -3095,10 +3199,10 @@
         <x:v>0.33128141618707657</x:v>
       </x:c>
       <x:c r="D14" s="16" t="str">
-        <x:v>Twelve-month FCF / borrowing at each period end. Prior column uses the fiscal year; later column uses TTM. Not repayment coverage.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="88" customHeight="1">
+        <x:v>Twelve-month flow / borrowing at each period end. Annual column uses FY; latest column uses TTM. Not repayment coverage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="49" customHeight="1">
       <x:c r="A15" s="26" t="str">
         <x:v>Historical interest coverage</x:v>
       </x:c>
@@ -3111,7 +3215,7 @@
         <x:v>31.17052826691381</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>FY2025 Note 11 explicitly reports interest on borrowings net of capitalized interest. The interim segment table labels the line interest expense without explicitly stating its capitalization basis. All three amounts are used as reported, before any interest-income offset. Capitalized interest is not added or subtracted; its amount and total interest incurred are Unavailable.</x:v>
+        <x:v>Annual interest is reported net of capitalized interest; the later TTM includes interim expense whose capitalization basis is unstated. Amounts remain as reported.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3909,11 +4013,15 @@
       <x:c r="N40" s="2"/>
       <x:c r="O40" s="2"/>
     </x:row>
-    <x:row r="41" ht="35" customHeight="1">
-      <x:c r="A41" s="4"/>
+    <x:row r="41" ht="65" customHeight="1">
+      <x:c r="A41" s="4" t="str">
+        <x:v>Evidence trail</x:v>
+      </x:c>
       <x:c r="B41" s="4"/>
       <x:c r="C41" s="4"/>
-      <x:c r="D41" s="4"/>
+      <x:c r="D41" s="4" t="str">
+        <x:v>Chart values link to Debt and liquidity and History. Data retains the exact input periods, tags, accessions and source URLs.</x:v>
+      </x:c>
       <x:c r="E41" s="2"/>
       <x:c r="F41" s="2"/>
       <x:c r="G41" s="2"/>
@@ -3962,7 +4070,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89ff47f5e478437c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dfab275f4374f09"/>
 </x:worksheet>
 </file>
 
@@ -5552,7 +5660,7 @@
     <x:mergeCell ref="A96:D96"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79db98eea22941d4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re356147f3866488b"/>
 </x:worksheet>
 </file>
 
@@ -11941,6 +12049,17 @@
         <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/core_charts.md</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="76" customHeight="1">
+      <x:c r="A17" s="218" t="str">
+        <x:v>Workbook guide</x:v>
+      </x:c>
+      <x:c r="B17" s="219" t="str">
+        <x:v>The first sheet lists all workbook tabs and their questions. Core metrics, dated history and common charts agree with the app. URLs remain full, copyable source text. Native hyperlink actions are not authored by this spreadsheet runtime.</x:v>
+      </x:c>
+      <x:c r="C17" s="220" t="str">
+        <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/excel_parity.md</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R1c6648e8b7ec4225"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="Rf45888c3a1df4b17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="Rc135515193e649c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="R6ae98e4280914bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core charts" sheetId="5" r:id="R23a724ea0449445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="6" r:id="Ra29616e5a8fc4e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R7fe6dbf74c584970"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="8" r:id="Rb006a05c25e84490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding conclusion" sheetId="1" r:id="R5d8071a01baa4740"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Borrowing and leases" sheetId="2" r:id="Rdb561f41d7664885"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and liquidity" sheetId="3" r:id="R678973a6daee4721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="R61b303ccd30848b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core charts" sheetId="5" r:id="R147af0f1d96f4e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repayment review" sheetId="6" r:id="R2d31b716f68d4673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="Re3efeb6e05ad497b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="8" r:id="Rc20a55f23ee44f8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1558,7 +1558,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9c8bf6543f4249c6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rccfae7a6dcce464b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1588,7 +1588,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0bd32b698ae448f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R530913a246744b55"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1623,7 +1623,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad4eba411b834422"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b2c78017318491a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4070,7 +4070,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dfab275f4374f09"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3cb24b69ae24fc0"/>
 </x:worksheet>
 </file>
 
@@ -5660,7 +5660,7 @@
     <x:mergeCell ref="A96:D96"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re356147f3866488b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf804cb9b07954525"/>
 </x:worksheet>
 </file>
 
@@ -11252,7 +11252,7 @@
         <x:v>Filing location</x:v>
       </x:c>
       <x:c r="N119" s="96" t="str">
-        <x:v>Unavailable reason</x:v>
+        <x:v>Selection / Unavailable reason</x:v>
       </x:c>
       <x:c r="O119" s="14" t="str">
         <x:v>Reviewed source SHA256</x:v>
@@ -11290,7 +11290,9 @@
       <x:c r="M120" s="107" t="str">
         <x:v>10-Q balance sheet, p. 7</x:v>
       </x:c>
-      <x:c r="N120" s="107" t="str"/>
+      <x:c r="N120" s="107" t="str">
+        <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
+      </x:c>
       <x:c r="O120" s="16" t="str"/>
     </x:row>
     <x:row r="121" ht="78" customHeight="1">
@@ -11325,7 +11327,9 @@
       <x:c r="M121" s="107" t="str">
         <x:v>10-Q balance sheet, p. 7</x:v>
       </x:c>
-      <x:c r="N121" s="107" t="str"/>
+      <x:c r="N121" s="107" t="str">
+        <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
+      </x:c>
       <x:c r="O121" s="16" t="str"/>
     </x:row>
     <x:row r="122" ht="78" customHeight="1">
@@ -11357,7 +11361,7 @@
         <x:v>10-Q balance sheet, p. 7</x:v>
       </x:c>
       <x:c r="N122" s="107" t="str">
-        <x:v>Latest-date lease liabilities Unavailable; no checked amount in the 10-Q.</x:v>
+        <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself Latest-date lease liabilities Unavailable; no checked amount in the 10-Q.</x:v>
       </x:c>
       <x:c r="O122" s="16" t="str"/>
     </x:row>
@@ -11399,7 +11403,9 @@
       <x:c r="M123" s="107" t="str">
         <x:v>10-K Note 10, p. 76</x:v>
       </x:c>
-      <x:c r="N123" s="107" t="str"/>
+      <x:c r="N123" s="107" t="str">
+        <x:v>Exact prefixed tag; exact stated instant; USD; no dimensions; agreeing duplicates.</x:v>
+      </x:c>
       <x:c r="O123" s="16" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
@@ -11442,7 +11448,9 @@
       <x:c r="M124" s="107" t="str">
         <x:v>10-K Note 10, p. 76</x:v>
       </x:c>
-      <x:c r="N124" s="107" t="str"/>
+      <x:c r="N124" s="107" t="str">
+        <x:v>Exact prefixed tag; exact stated instant; USD; no dimensions; agreeing duplicates.</x:v>
+      </x:c>
       <x:c r="O124" s="16" t="str">
         <x:v>d45f8d1e0945df0b7b30254e96ff8c5dbd1df7d15b17c8ef7399c8e0206b7d7f</x:v>
       </x:c>
@@ -11476,7 +11484,7 @@
         <x:v>10-Q review; June amount not established</x:v>
       </x:c>
       <x:c r="N125" s="107" t="str">
-        <x:v>No checked June amount. The 10-K describes operating leases only; finance leases are not reported, which is not zero.</x:v>
+        <x:v> No checked June amount. The 10-K describes operating leases only; finance leases are not reported, which is not zero.</x:v>
       </x:c>
       <x:c r="O125" s="16" t="str"/>
     </x:row>
@@ -11509,7 +11517,7 @@
         <x:v>Saved pilot evidence; 10-Q review</x:v>
       </x:c>
       <x:c r="N126" s="109" t="str">
-        <x:v>No checked amount for leases not yet commenced is established in the saved pilot evidence. Unavailable does not mean zero.</x:v>
+        <x:v> No checked amount for leases not yet commenced is established in the saved pilot evidence. Unavailable does not mean zero.</x:v>
       </x:c>
       <x:c r="O126" s="18" t="str"/>
     </x:row>

--- a/samples/lly_liquidity.xlsx
+++ b/samples/lly_liquidity.xlsx
@@ -2049,7 +2049,7 @@
         <x:v>Evidence and uncertainty</x:v>
       </x:c>
       <x:c r="B32" s="16" t="str">
-        <x:v>Data contains source URLs and filing metadata. Copy a full URL into a browser to open the source. Unavailable is never zero; capacity and later events do not update balance-sheet cash or borrowing.</x:v>
+        <x:v>Data contains source URLs and filing metadata. Select a source URL to open it in a browser. Unavailable is never zero; capacity and later events do not update balance-sheet cash or borrowing.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="55" customHeight="1">
@@ -11870,6 +11870,128 @@
       <x:c r="O136" s="18" t="str"/>
     </x:row>
   </x:sheetData>
+  <x:hyperlinks xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+    <x:hyperlink ref="L2" r:id="rIdSource1"/>
+    <x:hyperlink ref="L3" r:id="rIdSource2"/>
+    <x:hyperlink ref="L4" r:id="rIdSource3"/>
+    <x:hyperlink ref="L5" r:id="rIdSource4"/>
+    <x:hyperlink ref="L6" r:id="rIdSource5"/>
+    <x:hyperlink ref="L7" r:id="rIdSource6"/>
+    <x:hyperlink ref="L8" r:id="rIdSource7"/>
+    <x:hyperlink ref="L9" r:id="rIdSource8"/>
+    <x:hyperlink ref="L10" r:id="rIdSource9"/>
+    <x:hyperlink ref="L11" r:id="rIdSource10"/>
+    <x:hyperlink ref="L12" r:id="rIdSource11"/>
+    <x:hyperlink ref="G16" r:id="rIdSource12"/>
+    <x:hyperlink ref="G17" r:id="rIdSource13"/>
+    <x:hyperlink ref="M21" r:id="rIdSource14"/>
+    <x:hyperlink ref="M22" r:id="rIdSource15"/>
+    <x:hyperlink ref="M23" r:id="rIdSource16"/>
+    <x:hyperlink ref="M24" r:id="rIdSource17"/>
+    <x:hyperlink ref="M25" r:id="rIdSource18"/>
+    <x:hyperlink ref="M26" r:id="rIdSource19"/>
+    <x:hyperlink ref="M27" r:id="rIdSource20"/>
+    <x:hyperlink ref="M28" r:id="rIdSource21"/>
+    <x:hyperlink ref="M29" r:id="rIdSource22"/>
+    <x:hyperlink ref="M30" r:id="rIdSource23"/>
+    <x:hyperlink ref="M31" r:id="rIdSource24"/>
+    <x:hyperlink ref="M32" r:id="rIdSource25"/>
+    <x:hyperlink ref="M33" r:id="rIdSource26"/>
+    <x:hyperlink ref="M34" r:id="rIdSource27"/>
+    <x:hyperlink ref="M35" r:id="rIdSource28"/>
+    <x:hyperlink ref="M36" r:id="rIdSource29"/>
+    <x:hyperlink ref="M37" r:id="rIdSource30"/>
+    <x:hyperlink ref="M38" r:id="rIdSource31"/>
+    <x:hyperlink ref="M39" r:id="rIdSource32"/>
+    <x:hyperlink ref="M40" r:id="rIdSource33"/>
+    <x:hyperlink ref="M41" r:id="rIdSource34"/>
+    <x:hyperlink ref="M42" r:id="rIdSource35"/>
+    <x:hyperlink ref="M43" r:id="rIdSource36"/>
+    <x:hyperlink ref="M44" r:id="rIdSource37"/>
+    <x:hyperlink ref="M45" r:id="rIdSource38"/>
+    <x:hyperlink ref="M46" r:id="rIdSource39"/>
+    <x:hyperlink ref="M47" r:id="rIdSource40"/>
+    <x:hyperlink ref="M48" r:id="rIdSource41"/>
+    <x:hyperlink ref="M49" r:id="rIdSource42"/>
+    <x:hyperlink ref="M50" r:id="rIdSource43"/>
+    <x:hyperlink ref="M51" r:id="rIdSource44"/>
+    <x:hyperlink ref="M52" r:id="rIdSource45"/>
+    <x:hyperlink ref="M53" r:id="rIdSource46"/>
+    <x:hyperlink ref="M54" r:id="rIdSource47"/>
+    <x:hyperlink ref="M55" r:id="rIdSource48"/>
+    <x:hyperlink ref="M56" r:id="rIdSource49"/>
+    <x:hyperlink ref="M57" r:id="rIdSource50"/>
+    <x:hyperlink ref="M58" r:id="rIdSource51"/>
+    <x:hyperlink ref="M59" r:id="rIdSource52"/>
+    <x:hyperlink ref="M60" r:id="rIdSource53"/>
+    <x:hyperlink ref="M61" r:id="rIdSource54"/>
+    <x:hyperlink ref="M62" r:id="rIdSource55"/>
+    <x:hyperlink ref="M63" r:id="rIdSource56"/>
+    <x:hyperlink ref="M64" r:id="rIdSource57"/>
+    <x:hyperlink ref="M65" r:id="rIdSource58"/>
+    <x:hyperlink ref="M66" r:id="rIdSource59"/>
+    <x:hyperlink ref="M67" r:id="rIdSource60"/>
+    <x:hyperlink ref="M68" r:id="rIdSource61"/>
+    <x:hyperlink ref="M69" r:id="rIdSource62"/>
+    <x:hyperlink ref="M70" r:id="rIdSource63"/>
+    <x:hyperlink ref="M71" r:id="rIdSource64"/>
+    <x:hyperlink ref="M72" r:id="rIdSource65"/>
+    <x:hyperlink ref="M73" r:id="rIdSource66"/>
+    <x:hyperlink ref="M74" r:id="rIdSource67"/>
+    <x:hyperlink ref="M75" r:id="rIdSource68"/>
+    <x:hyperlink ref="M76" r:id="rIdSource69"/>
+    <x:hyperlink ref="M77" r:id="rIdSource70"/>
+    <x:hyperlink ref="M78" r:id="rIdSource71"/>
+    <x:hyperlink ref="M79" r:id="rIdSource72"/>
+    <x:hyperlink ref="M80" r:id="rIdSource73"/>
+    <x:hyperlink ref="M81" r:id="rIdSource74"/>
+    <x:hyperlink ref="M82" r:id="rIdSource75"/>
+    <x:hyperlink ref="M83" r:id="rIdSource76"/>
+    <x:hyperlink ref="M84" r:id="rIdSource77"/>
+    <x:hyperlink ref="M85" r:id="rIdSource78"/>
+    <x:hyperlink ref="M86" r:id="rIdSource79"/>
+    <x:hyperlink ref="M87" r:id="rIdSource80"/>
+    <x:hyperlink ref="M88" r:id="rIdSource81"/>
+    <x:hyperlink ref="M89" r:id="rIdSource82"/>
+    <x:hyperlink ref="M90" r:id="rIdSource83"/>
+    <x:hyperlink ref="M91" r:id="rIdSource84"/>
+    <x:hyperlink ref="M92" r:id="rIdSource85"/>
+    <x:hyperlink ref="M93" r:id="rIdSource86"/>
+    <x:hyperlink ref="M94" r:id="rIdSource87"/>
+    <x:hyperlink ref="M95" r:id="rIdSource88"/>
+    <x:hyperlink ref="M96" r:id="rIdSource89"/>
+    <x:hyperlink ref="M97" r:id="rIdSource90"/>
+    <x:hyperlink ref="M98" r:id="rIdSource91"/>
+    <x:hyperlink ref="M99" r:id="rIdSource92"/>
+    <x:hyperlink ref="M100" r:id="rIdSource93"/>
+    <x:hyperlink ref="M101" r:id="rIdSource94"/>
+    <x:hyperlink ref="M102" r:id="rIdSource95"/>
+    <x:hyperlink ref="M103" r:id="rIdSource96"/>
+    <x:hyperlink ref="L107" r:id="rIdSource97"/>
+    <x:hyperlink ref="L108" r:id="rIdSource98"/>
+    <x:hyperlink ref="L109" r:id="rIdSource99"/>
+    <x:hyperlink ref="L110" r:id="rIdSource100"/>
+    <x:hyperlink ref="L111" r:id="rIdSource101"/>
+    <x:hyperlink ref="L112" r:id="rIdSource102"/>
+    <x:hyperlink ref="L113" r:id="rIdSource103"/>
+    <x:hyperlink ref="L114" r:id="rIdSource104"/>
+    <x:hyperlink ref="L115" r:id="rIdSource105"/>
+    <x:hyperlink ref="L116" r:id="rIdSource106"/>
+    <x:hyperlink ref="L120" r:id="rIdSource107"/>
+    <x:hyperlink ref="L121" r:id="rIdSource108"/>
+    <x:hyperlink ref="L122" r:id="rIdSource109"/>
+    <x:hyperlink ref="L123" r:id="rIdSource110"/>
+    <x:hyperlink ref="L124" r:id="rIdSource111"/>
+    <x:hyperlink ref="L125" r:id="rIdSource112"/>
+    <x:hyperlink ref="L126" r:id="rIdSource113"/>
+    <x:hyperlink ref="L130" r:id="rIdSource114"/>
+    <x:hyperlink ref="L131" r:id="rIdSource115"/>
+    <x:hyperlink ref="L132" r:id="rIdSource116"/>
+    <x:hyperlink ref="L133" r:id="rIdSource117"/>
+    <x:hyperlink ref="L134" r:id="rIdSource118"/>
+    <x:hyperlink ref="L135" r:id="rIdSource119"/>
+    <x:hyperlink ref="L136" r:id="rIdSource120"/>
+  </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -12062,13 +12184,29 @@
         <x:v>Workbook guide</x:v>
       </x:c>
       <x:c r="B17" s="219" t="str">
-        <x:v>The first sheet lists all workbook tabs and their questions. Core metrics, dated history and common charts agree with the app. URLs remain full, copyable source text. Native hyperlink actions are not authored by this spreadsheet runtime.</x:v>
+        <x:v>The first sheet lists all workbook tabs and their questions. Core metrics, dated history and common charts agree with the app. Source URLs are full text and open as links when selected.</x:v>
       </x:c>
       <x:c r="C17" s="220" t="str">
         <x:v>https://github.com/jackconnolly1000-ux/sec-filing-research-terminal/blob/main/docs/excel_parity.md</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:hyperlinks xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+    <x:hyperlink ref="C2" r:id="rIdSource1"/>
+    <x:hyperlink ref="C4" r:id="rIdSource2"/>
+    <x:hyperlink ref="C5" r:id="rIdSource3"/>
+    <x:hyperlink ref="C6" r:id="rIdSource4"/>
+    <x:hyperlink ref="C7" r:id="rIdSource5"/>
+    <x:hyperlink ref="C8" r:id="rIdSource6"/>
+    <x:hyperlink ref="C9" r:id="rIdSource7"/>
+    <x:hyperlink ref="C10" r:id="rIdSource8"/>
+    <x:hyperlink ref="C11" r:id="rIdSource9"/>
+    <x:hyperlink ref="C13" r:id="rIdSource10"/>
+    <x:hyperlink ref="C14" r:id="rIdSource11"/>
+    <x:hyperlink ref="C15" r:id="rIdSource12"/>
+    <x:hyperlink ref="C16" r:id="rIdSource13"/>
+    <x:hyperlink ref="C17" r:id="rIdSource14"/>
+  </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>